--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Fiore and Sons\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Fiore and Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88E2F9B2-8061-4441-B344-AEB36D6FB0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C042EA0-95EF-4ABD-AA27-47FFD7882957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="23295" windowHeight="13380" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Fiore and Sons\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Fiore and Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C042EA0-95EF-4ABD-AA27-47FFD7882957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11783703-4CEA-4FEF-952E-6854E9E0C4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="84">
   <si>
     <t>Company Name</t>
   </si>
@@ -8112,7 +8112,7 @@
         <v>46083.755671296298</v>
       </c>
       <c r="J286">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K286" t="s">
         <v>11</v>
@@ -8141,7 +8141,7 @@
         <v>46083.756365740737</v>
       </c>
       <c r="J287">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K287" t="s">
         <v>11</v>
@@ -8170,7 +8170,7 @@
         <v>46083.756365740737</v>
       </c>
       <c r="J288">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K288" t="s">
         <v>11</v>
@@ -8199,7 +8199,7 @@
         <v>46083.757060185184</v>
       </c>
       <c r="J289">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K289" t="s">
         <v>11</v>
@@ -8257,7 +8257,7 @@
         <v>46083.757754629631</v>
       </c>
       <c r="J291">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K291" t="s">
         <v>11</v>
@@ -8364,16 +8364,16 @@
         <v>17</v>
       </c>
       <c r="G295" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H295" s="2">
-        <v>0</v>
+        <v>5.1273148148148146E-3</v>
       </c>
       <c r="I295" s="1">
         <v>46083.759837962964</v>
       </c>
       <c r="J295">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K295" t="s">
         <v>11</v>
@@ -8431,7 +8431,7 @@
         <v>46083.76053240741</v>
       </c>
       <c r="J297">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K297" t="s">
         <v>11</v>
@@ -8460,7 +8460,7 @@
         <v>46083.76122685185</v>
       </c>
       <c r="J298">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K298" t="s">
         <v>11</v>
@@ -8518,7 +8518,7 @@
         <v>46083.761921296296</v>
       </c>
       <c r="J300">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K300" t="s">
         <v>11</v>
@@ -8547,7 +8547,7 @@
         <v>46083.762615740743</v>
       </c>
       <c r="J301">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K301" t="s">
         <v>11</v>
@@ -8567,10 +8567,10 @@
         <v>17</v>
       </c>
       <c r="G302" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H302" s="2">
-        <v>2.3148148148148147E-5</v>
+        <v>4.6412037037037038E-3</v>
       </c>
       <c r="I302" s="1">
         <v>46083.762615740743</v>
@@ -8583,10 +8583,32 @@
       </c>
     </row>
     <row r="303" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H303" s="2"/>
-      <c r="I303" s="1"/>
+      <c r="B303" t="s">
+        <v>22</v>
+      </c>
+      <c r="C303">
+        <v>3499</v>
+      </c>
+      <c r="D303" t="s">
+        <v>46</v>
+      </c>
+      <c r="F303" t="s">
+        <v>17</v>
+      </c>
+      <c r="G303" t="s">
+        <v>13</v>
+      </c>
+      <c r="H303" s="2">
+        <v>0</v>
+      </c>
+      <c r="I303" s="1">
+        <v>46083.763310185182</v>
+      </c>
+      <c r="J303">
+        <v>3</v>
+      </c>
       <c r="K303" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="304" spans="2:11" x14ac:dyDescent="0.25">
@@ -8594,25 +8616,25 @@
         <v>22</v>
       </c>
       <c r="C304">
-        <v>3499</v>
+        <v>3699</v>
       </c>
       <c r="D304" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F304" t="s">
         <v>17</v>
       </c>
       <c r="G304" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H304" s="2">
-        <v>0</v>
+        <v>7.3958333333333333E-3</v>
       </c>
       <c r="I304" s="1">
         <v>46083.763310185182</v>
       </c>
       <c r="J304">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K304" t="s">
         <v>11</v>
@@ -8623,10 +8645,10 @@
         <v>22</v>
       </c>
       <c r="C305">
-        <v>3699</v>
+        <v>3491</v>
       </c>
       <c r="D305" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F305" t="s">
         <v>17</v>
@@ -8635,10 +8657,10 @@
         <v>10</v>
       </c>
       <c r="H305" s="2">
-        <v>7.3958333333333333E-3</v>
+        <v>5.5902777777777773E-3</v>
       </c>
       <c r="I305" s="1">
-        <v>46083.763310185182</v>
+        <v>46083.764004629629</v>
       </c>
       <c r="J305">
         <v>0</v>
@@ -8652,25 +8674,25 @@
         <v>22</v>
       </c>
       <c r="C306">
-        <v>3491</v>
+        <v>3487</v>
       </c>
       <c r="D306" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F306" t="s">
         <v>17</v>
       </c>
       <c r="G306" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H306" s="2">
-        <v>5.5902777777777773E-3</v>
+        <v>0</v>
       </c>
       <c r="I306" s="1">
-        <v>46083.764004629629</v>
+        <v>46083.764699074076</v>
       </c>
       <c r="J306">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K306" t="s">
         <v>11</v>
@@ -8681,10 +8703,10 @@
         <v>22</v>
       </c>
       <c r="C307">
-        <v>3487</v>
+        <v>3704</v>
       </c>
       <c r="D307" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F307" t="s">
         <v>17</v>
@@ -8699,7 +8721,7 @@
         <v>46083.764699074076</v>
       </c>
       <c r="J307">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K307" t="s">
         <v>11</v>
@@ -8710,25 +8732,25 @@
         <v>22</v>
       </c>
       <c r="C308">
-        <v>3704</v>
+        <v>3481</v>
       </c>
       <c r="D308" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F308" t="s">
         <v>17</v>
       </c>
       <c r="G308" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H308" s="2">
+        <v>7.8009259259259256E-3</v>
+      </c>
+      <c r="I308" s="1">
+        <v>46083.765393518515</v>
+      </c>
+      <c r="J308">
         <v>0</v>
-      </c>
-      <c r="I308" s="1">
-        <v>46083.764699074076</v>
-      </c>
-      <c r="J308">
-        <v>2</v>
       </c>
       <c r="K308" t="s">
         <v>11</v>
@@ -8739,10 +8761,10 @@
         <v>22</v>
       </c>
       <c r="C309">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="D309" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F309" t="s">
         <v>17</v>
@@ -8751,10 +8773,10 @@
         <v>10</v>
       </c>
       <c r="H309" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>6.2268518518518515E-3</v>
       </c>
       <c r="I309" s="1">
-        <v>46083.765393518515</v>
+        <v>46083.766087962962</v>
       </c>
       <c r="J309">
         <v>0</v>
@@ -8768,10 +8790,10 @@
         <v>22</v>
       </c>
       <c r="C310">
-        <v>3480</v>
+        <v>3511</v>
       </c>
       <c r="D310" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F310" t="s">
         <v>17</v>
@@ -8780,7 +8802,7 @@
         <v>10</v>
       </c>
       <c r="H310" s="2">
-        <v>6.2268518518518515E-3</v>
+        <v>5.5324074074074078E-3</v>
       </c>
       <c r="I310" s="1">
         <v>46083.766087962962</v>
@@ -8797,10 +8819,10 @@
         <v>22</v>
       </c>
       <c r="C311">
-        <v>3511</v>
+        <v>3484</v>
       </c>
       <c r="D311" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F311" t="s">
         <v>17</v>
@@ -8809,13 +8831,13 @@
         <v>10</v>
       </c>
       <c r="H311" s="2">
-        <v>5.5324074074074078E-3</v>
+        <v>4.9421296296296297E-3</v>
       </c>
       <c r="I311" s="1">
-        <v>46083.766087962962</v>
+        <v>46083.766782407409</v>
       </c>
       <c r="J311">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K311" t="s">
         <v>11</v>
@@ -8826,25 +8848,25 @@
         <v>22</v>
       </c>
       <c r="C312">
-        <v>3484</v>
+        <v>3514</v>
       </c>
       <c r="D312" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F312" t="s">
         <v>17</v>
       </c>
       <c r="G312" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H312" s="2">
-        <v>4.9421296296296297E-3</v>
+        <v>0</v>
       </c>
       <c r="I312" s="1">
-        <v>46083.766782407409</v>
+        <v>46083.767476851855</v>
       </c>
       <c r="J312">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K312" t="s">
         <v>11</v>
@@ -8855,10 +8877,10 @@
         <v>22</v>
       </c>
       <c r="C313">
-        <v>3514</v>
+        <v>3485</v>
       </c>
       <c r="D313" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F313" t="s">
         <v>17</v>
@@ -8873,7 +8895,7 @@
         <v>46083.767476851855</v>
       </c>
       <c r="J313">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K313" t="s">
         <v>11</v>
@@ -8884,64 +8906,64 @@
         <v>22</v>
       </c>
       <c r="C314">
-        <v>3485</v>
+        <v>3725</v>
       </c>
       <c r="D314" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F314" t="s">
         <v>17</v>
       </c>
       <c r="G314" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H314" s="2">
         <v>0</v>
       </c>
       <c r="I314" s="1">
-        <v>46083.767476851855</v>
+        <v>46083.768171296295</v>
       </c>
       <c r="J314">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K314" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="315" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B315" t="s">
+      <c r="H315" s="2"/>
+      <c r="I315" s="1"/>
+      <c r="K315" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="316" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B316" t="s">
         <v>22</v>
       </c>
-      <c r="C315">
-        <v>3725</v>
-      </c>
-      <c r="D315" t="s">
-        <v>58</v>
-      </c>
-      <c r="F315" t="s">
+      <c r="C316">
+        <v>3488</v>
+      </c>
+      <c r="D316" t="s">
+        <v>59</v>
+      </c>
+      <c r="F316" t="s">
         <v>17</v>
       </c>
-      <c r="G315" t="s">
-        <v>12</v>
-      </c>
-      <c r="H315" s="2">
-        <v>0</v>
-      </c>
-      <c r="I315" s="1">
+      <c r="G316" t="s">
+        <v>10</v>
+      </c>
+      <c r="H316" s="2">
+        <v>5.0115740740740737E-3</v>
+      </c>
+      <c r="I316" s="1">
         <v>46083.768171296295</v>
       </c>
-      <c r="J315">
-        <v>0</v>
-      </c>
-      <c r="K315" t="s">
+      <c r="J316">
+        <v>2</v>
+      </c>
+      <c r="K316" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="316" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H316" s="2"/>
-      <c r="I316" s="1"/>
-      <c r="K316" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="317" spans="2:11" x14ac:dyDescent="0.25">
@@ -8949,10 +8971,10 @@
         <v>22</v>
       </c>
       <c r="C317">
-        <v>3488</v>
+        <v>3478</v>
       </c>
       <c r="D317" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F317" t="s">
         <v>17</v>
@@ -8961,13 +8983,13 @@
         <v>10</v>
       </c>
       <c r="H317" s="2">
-        <v>5.0115740740740737E-3</v>
+        <v>2.7569444444444445E-2</v>
       </c>
       <c r="I317" s="1">
-        <v>46083.768171296295</v>
+        <v>46083.768865740742</v>
       </c>
       <c r="J317">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K317" t="s">
         <v>11</v>
@@ -8978,10 +9000,10 @@
         <v>22</v>
       </c>
       <c r="C318">
-        <v>3478</v>
+        <v>3494</v>
       </c>
       <c r="D318" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F318" t="s">
         <v>17</v>
@@ -8990,10 +9012,10 @@
         <v>10</v>
       </c>
       <c r="H318" s="2">
-        <v>2.7569444444444445E-2</v>
+        <v>4.4791666666666669E-3</v>
       </c>
       <c r="I318" s="1">
-        <v>46083.768865740742</v>
+        <v>46083.769560185188</v>
       </c>
       <c r="J318">
         <v>0</v>
@@ -9007,10 +9029,10 @@
         <v>22</v>
       </c>
       <c r="C319">
-        <v>3494</v>
+        <v>3523</v>
       </c>
       <c r="D319" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F319" t="s">
         <v>17</v>
@@ -9019,7 +9041,7 @@
         <v>10</v>
       </c>
       <c r="H319" s="2">
-        <v>4.4791666666666669E-3</v>
+        <v>5.9837962962962961E-3</v>
       </c>
       <c r="I319" s="1">
         <v>46083.769560185188</v>
@@ -9036,25 +9058,25 @@
         <v>22</v>
       </c>
       <c r="C320">
-        <v>3523</v>
+        <v>3504</v>
       </c>
       <c r="D320" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F320" t="s">
         <v>17</v>
       </c>
       <c r="G320" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H320" s="2">
-        <v>5.9837962962962961E-3</v>
+        <v>0</v>
       </c>
       <c r="I320" s="1">
-        <v>46083.769560185188</v>
+        <v>46083.770254629628</v>
       </c>
       <c r="J320">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K320" t="s">
         <v>11</v>
@@ -9065,25 +9087,25 @@
         <v>22</v>
       </c>
       <c r="C321">
-        <v>3504</v>
+        <v>3498</v>
       </c>
       <c r="D321" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F321" t="s">
         <v>17</v>
       </c>
       <c r="G321" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H321" s="2">
+        <v>6.099537037037037E-3</v>
+      </c>
+      <c r="I321" s="1">
+        <v>46083.770949074074</v>
+      </c>
+      <c r="J321">
         <v>0</v>
-      </c>
-      <c r="I321" s="1">
-        <v>46083.770254629628</v>
-      </c>
-      <c r="J321">
-        <v>2</v>
       </c>
       <c r="K321" t="s">
         <v>11</v>
@@ -9094,10 +9116,10 @@
         <v>22</v>
       </c>
       <c r="C322">
-        <v>3498</v>
+        <v>3344</v>
       </c>
       <c r="D322" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F322" t="s">
         <v>17</v>
@@ -9106,7 +9128,7 @@
         <v>10</v>
       </c>
       <c r="H322" s="2">
-        <v>6.099537037037037E-3</v>
+        <v>2.2476851851851852E-2</v>
       </c>
       <c r="I322" s="1">
         <v>46083.770949074074</v>
@@ -9123,25 +9145,25 @@
         <v>22</v>
       </c>
       <c r="C323">
-        <v>3344</v>
+        <v>3515</v>
       </c>
       <c r="D323" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F323" t="s">
         <v>17</v>
       </c>
       <c r="G323" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H323" s="2">
-        <v>2.2476851851851852E-2</v>
+        <v>0</v>
       </c>
       <c r="I323" s="1">
-        <v>46083.770949074074</v>
+        <v>46083.771643518521</v>
       </c>
       <c r="J323">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K323" t="s">
         <v>11</v>
@@ -9152,25 +9174,25 @@
         <v>22</v>
       </c>
       <c r="C324">
-        <v>3515</v>
+        <v>3522</v>
       </c>
       <c r="D324" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F324" t="s">
         <v>17</v>
       </c>
       <c r="G324" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H324" s="2">
-        <v>0</v>
+        <v>4.6064814814814814E-3</v>
       </c>
       <c r="I324" s="1">
         <v>46083.771643518521</v>
       </c>
       <c r="J324">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K324" t="s">
         <v>11</v>
@@ -9181,10 +9203,10 @@
         <v>22</v>
       </c>
       <c r="C325">
-        <v>3522</v>
+        <v>3751</v>
       </c>
       <c r="D325" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F325" t="s">
         <v>17</v>
@@ -9193,13 +9215,13 @@
         <v>10</v>
       </c>
       <c r="H325" s="2">
-        <v>4.6064814814814814E-3</v>
+        <v>4.7569444444444447E-3</v>
       </c>
       <c r="I325" s="1">
-        <v>46083.771643518521</v>
+        <v>46083.772337962961</v>
       </c>
       <c r="J325">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K325" t="s">
         <v>11</v>
@@ -9210,25 +9232,25 @@
         <v>22</v>
       </c>
       <c r="C326">
-        <v>3751</v>
+        <v>3662</v>
       </c>
       <c r="D326" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F326" t="s">
         <v>17</v>
       </c>
       <c r="G326" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H326" s="2">
-        <v>4.7569444444444447E-3</v>
+        <v>0</v>
       </c>
       <c r="I326" s="1">
-        <v>46083.772337962961</v>
+        <v>46083.773032407407</v>
       </c>
       <c r="J326">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K326" t="s">
         <v>11</v>
@@ -9239,25 +9261,25 @@
         <v>22</v>
       </c>
       <c r="C327">
-        <v>3662</v>
+        <v>3517</v>
       </c>
       <c r="D327" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F327" t="s">
         <v>17</v>
       </c>
       <c r="G327" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H327" s="2">
-        <v>0</v>
+        <v>5.2314814814814811E-3</v>
       </c>
       <c r="I327" s="1">
         <v>46083.773032407407</v>
       </c>
       <c r="J327">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K327" t="s">
         <v>11</v>
@@ -9268,25 +9290,25 @@
         <v>22</v>
       </c>
       <c r="C328">
-        <v>3517</v>
+        <v>3503</v>
       </c>
       <c r="D328" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F328" t="s">
         <v>17</v>
       </c>
       <c r="G328" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H328" s="2">
-        <v>5.2314814814814811E-3</v>
+        <v>0</v>
       </c>
       <c r="I328" s="1">
-        <v>46083.773032407407</v>
+        <v>46083.773726851854</v>
       </c>
       <c r="J328">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K328" t="s">
         <v>11</v>
@@ -9297,25 +9319,25 @@
         <v>22</v>
       </c>
       <c r="C329">
-        <v>3503</v>
+        <v>3652</v>
       </c>
       <c r="D329" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F329" t="s">
         <v>17</v>
       </c>
       <c r="G329" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H329" s="2">
+        <v>8.1365740740740738E-3</v>
+      </c>
+      <c r="I329" s="1">
+        <v>46083.774421296293</v>
+      </c>
+      <c r="J329">
         <v>0</v>
-      </c>
-      <c r="I329" s="1">
-        <v>46083.773726851854</v>
-      </c>
-      <c r="J329">
-        <v>2</v>
       </c>
       <c r="K329" t="s">
         <v>11</v>
@@ -9326,10 +9348,10 @@
         <v>22</v>
       </c>
       <c r="C330">
-        <v>3652</v>
+        <v>3509</v>
       </c>
       <c r="D330" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F330" t="s">
         <v>17</v>
@@ -9338,10 +9360,10 @@
         <v>10</v>
       </c>
       <c r="H330" s="2">
-        <v>8.1365740740740738E-3</v>
+        <v>8.1481481481481474E-3</v>
       </c>
       <c r="I330" s="1">
-        <v>46083.774421296293</v>
+        <v>46083.751620370371</v>
       </c>
       <c r="J330">
         <v>0</v>
@@ -9355,10 +9377,10 @@
         <v>22</v>
       </c>
       <c r="C331">
-        <v>3509</v>
+        <v>3512</v>
       </c>
       <c r="D331" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F331" t="s">
         <v>17</v>
@@ -9367,10 +9389,10 @@
         <v>10</v>
       </c>
       <c r="H331" s="2">
-        <v>8.1481481481481474E-3</v>
+        <v>4.8263888888888887E-3</v>
       </c>
       <c r="I331" s="1">
-        <v>46083.751620370371</v>
+        <v>46083.752314814818</v>
       </c>
       <c r="J331">
         <v>0</v>
@@ -9384,10 +9406,10 @@
         <v>22</v>
       </c>
       <c r="C332">
-        <v>3512</v>
+        <v>3489</v>
       </c>
       <c r="D332" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F332" t="s">
         <v>17</v>
@@ -9396,13 +9418,13 @@
         <v>10</v>
       </c>
       <c r="H332" s="2">
-        <v>4.8263888888888887E-3</v>
+        <v>5.3819444444444444E-3</v>
       </c>
       <c r="I332" s="1">
         <v>46083.752314814818</v>
       </c>
       <c r="J332">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K332" t="s">
         <v>11</v>
@@ -9413,25 +9435,25 @@
         <v>22</v>
       </c>
       <c r="C333">
-        <v>3489</v>
+        <v>3266</v>
       </c>
       <c r="D333" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F333" t="s">
         <v>17</v>
       </c>
       <c r="G333" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H333" s="2">
+        <v>4.5138888888888885E-3</v>
+      </c>
+      <c r="I333" s="1">
+        <v>46083.753009259257</v>
+      </c>
+      <c r="J333">
         <v>0</v>
-      </c>
-      <c r="I333" s="1">
-        <v>46083.752314814818</v>
-      </c>
-      <c r="J333">
-        <v>2</v>
       </c>
       <c r="K333" t="s">
         <v>11</v>
@@ -9442,10 +9464,10 @@
         <v>22</v>
       </c>
       <c r="C334">
-        <v>3266</v>
+        <v>3492</v>
       </c>
       <c r="D334" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F334" t="s">
         <v>17</v>
@@ -9454,7 +9476,7 @@
         <v>10</v>
       </c>
       <c r="H334" s="2">
-        <v>4.5138888888888885E-3</v>
+        <v>8.1018518518518514E-3</v>
       </c>
       <c r="I334" s="1">
         <v>46083.753009259257</v>
@@ -9471,25 +9493,25 @@
         <v>22</v>
       </c>
       <c r="C335">
-        <v>3492</v>
+        <v>3493</v>
       </c>
       <c r="D335" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F335" t="s">
         <v>17</v>
       </c>
       <c r="G335" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H335" s="2">
-        <v>8.1018518518518514E-3</v>
+        <v>0</v>
       </c>
       <c r="I335" s="1">
-        <v>46083.753009259257</v>
+        <v>46083.753703703704</v>
       </c>
       <c r="J335">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K335" t="s">
         <v>11</v>
@@ -9500,25 +9522,25 @@
         <v>22</v>
       </c>
       <c r="C336">
-        <v>3493</v>
+        <v>3505</v>
       </c>
       <c r="D336" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F336" t="s">
         <v>17</v>
       </c>
       <c r="G336" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H336" s="2">
+        <v>7.7083333333333335E-3</v>
+      </c>
+      <c r="I336" s="1">
+        <v>46083.75439814815</v>
+      </c>
+      <c r="J336">
         <v>0</v>
-      </c>
-      <c r="I336" s="1">
-        <v>46083.753703703704</v>
-      </c>
-      <c r="J336">
-        <v>2</v>
       </c>
       <c r="K336" t="s">
         <v>11</v>
@@ -9529,10 +9551,10 @@
         <v>22</v>
       </c>
       <c r="C337">
-        <v>3505</v>
+        <v>3861</v>
       </c>
       <c r="D337" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F337" t="s">
         <v>17</v>
@@ -9541,10 +9563,10 @@
         <v>10</v>
       </c>
       <c r="H337" s="2">
-        <v>7.7083333333333335E-3</v>
+        <v>7.2569444444444443E-3</v>
       </c>
       <c r="I337" s="1">
-        <v>46083.75439814815</v>
+        <v>46083.75509259259</v>
       </c>
       <c r="J337">
         <v>0</v>
@@ -9558,25 +9580,25 @@
         <v>22</v>
       </c>
       <c r="C338">
-        <v>3861</v>
+        <v>5205</v>
       </c>
       <c r="D338" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F338" t="s">
         <v>17</v>
       </c>
       <c r="G338" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H338" s="2">
-        <v>7.2569444444444443E-3</v>
+        <v>0</v>
       </c>
       <c r="I338" s="1">
         <v>46083.75509259259</v>
       </c>
       <c r="J338">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K338" t="s">
         <v>11</v>
@@ -9587,22 +9609,22 @@
         <v>22</v>
       </c>
       <c r="C339">
-        <v>5205</v>
+        <v>3538</v>
       </c>
       <c r="D339" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F339" t="s">
         <v>17</v>
       </c>
       <c r="G339" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H339" s="2">
-        <v>0</v>
+        <v>7.1643518518518514E-3</v>
       </c>
       <c r="I339" s="1">
-        <v>46083.75509259259</v>
+        <v>46083.755787037036</v>
       </c>
       <c r="J339">
         <v>2</v>
@@ -9612,40 +9634,12 @@
       </c>
     </row>
     <row r="340" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B340" t="s">
-        <v>22</v>
-      </c>
-      <c r="C340">
-        <v>3538</v>
-      </c>
-      <c r="D340" t="s">
-        <v>82</v>
-      </c>
-      <c r="F340" t="s">
-        <v>17</v>
-      </c>
-      <c r="G340" t="s">
-        <v>12</v>
-      </c>
-      <c r="H340" s="2">
-        <v>1.1574074074074075E-4</v>
-      </c>
-      <c r="I340" s="1">
-        <v>46083.755787037036</v>
-      </c>
-      <c r="J340">
-        <v>2</v>
-      </c>
-      <c r="K340" t="s">
-        <v>11</v>
-      </c>
+      <c r="H340" s="2"/>
+      <c r="I340" s="1"/>
     </row>
     <row r="341" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H341" s="2"/>
       <c r="I341" s="1"/>
-      <c r="K341" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="342" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H342" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Fiore and Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11783703-4CEA-4FEF-952E-6854E9E0C4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C0D644-DC08-41DE-93A2-8A2304C25647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -8112,7 +8112,7 @@
         <v>46083.755671296298</v>
       </c>
       <c r="J286">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K286" t="s">
         <v>11</v>
@@ -8141,7 +8141,7 @@
         <v>46083.756365740737</v>
       </c>
       <c r="J287">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K287" t="s">
         <v>11</v>
@@ -8170,7 +8170,7 @@
         <v>46083.756365740737</v>
       </c>
       <c r="J288">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K288" t="s">
         <v>11</v>
@@ -8199,7 +8199,7 @@
         <v>46083.757060185184</v>
       </c>
       <c r="J289">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K289" t="s">
         <v>11</v>
@@ -8257,7 +8257,7 @@
         <v>46083.757754629631</v>
       </c>
       <c r="J291">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K291" t="s">
         <v>11</v>
@@ -8431,7 +8431,7 @@
         <v>46083.76053240741</v>
       </c>
       <c r="J297">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K297" t="s">
         <v>11</v>
@@ -8460,7 +8460,7 @@
         <v>46083.76122685185</v>
       </c>
       <c r="J298">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K298" t="s">
         <v>11</v>
@@ -8518,7 +8518,7 @@
         <v>46083.761921296296</v>
       </c>
       <c r="J300">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K300" t="s">
         <v>11</v>
@@ -8547,7 +8547,7 @@
         <v>46083.762615740743</v>
       </c>
       <c r="J301">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K301" t="s">
         <v>11</v>
@@ -8605,7 +8605,7 @@
         <v>46083.763310185182</v>
       </c>
       <c r="J303">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K303" t="s">
         <v>11</v>
@@ -8683,10 +8683,10 @@
         <v>17</v>
       </c>
       <c r="G306" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H306" s="2">
-        <v>0</v>
+        <v>1.2048611111111111E-2</v>
       </c>
       <c r="I306" s="1">
         <v>46083.764699074076</v>
@@ -8721,7 +8721,7 @@
         <v>46083.764699074076</v>
       </c>
       <c r="J307">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K307" t="s">
         <v>11</v>
@@ -8866,7 +8866,7 @@
         <v>46083.767476851855</v>
       </c>
       <c r="J312">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K312" t="s">
         <v>11</v>
@@ -8895,7 +8895,7 @@
         <v>46083.767476851855</v>
       </c>
       <c r="J313">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K313" t="s">
         <v>11</v>
@@ -9076,7 +9076,7 @@
         <v>46083.770254629628</v>
       </c>
       <c r="J320">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K320" t="s">
         <v>11</v>
@@ -9154,16 +9154,16 @@
         <v>17</v>
       </c>
       <c r="G323" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H323" s="2">
-        <v>0</v>
+        <v>1.3958333333333333E-2</v>
       </c>
       <c r="I323" s="1">
         <v>46083.771643518521</v>
       </c>
       <c r="J323">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K323" t="s">
         <v>11</v>
@@ -9250,7 +9250,7 @@
         <v>46083.773032407407</v>
       </c>
       <c r="J326">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K326" t="s">
         <v>11</v>
@@ -9308,7 +9308,7 @@
         <v>46083.773726851854</v>
       </c>
       <c r="J328">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K328" t="s">
         <v>11</v>
@@ -9511,7 +9511,7 @@
         <v>46083.753703703704</v>
       </c>
       <c r="J335">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K335" t="s">
         <v>11</v>
@@ -9598,7 +9598,7 @@
         <v>46083.75509259259</v>
       </c>
       <c r="J338">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K338" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Fiore and Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C0D644-DC08-41DE-93A2-8A2304C25647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C2FB5E-08EB-4AD1-8D50-6DCA30C2C217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="85">
   <si>
     <t>Company Name</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>Truman Chambers</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
   </si>
 </sst>
 </file>
@@ -8857,10 +8860,10 @@
         <v>17</v>
       </c>
       <c r="G312" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H312" s="2">
-        <v>0</v>
+        <v>6.2731481481481484E-3</v>
       </c>
       <c r="I312" s="1">
         <v>46083.767476851855</v>
@@ -9634,246 +9637,1680 @@
       </c>
     </row>
     <row r="340" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H340" s="2"/>
-      <c r="I340" s="1"/>
+      <c r="B340" t="s">
+        <v>22</v>
+      </c>
+      <c r="C340">
+        <v>3200</v>
+      </c>
+      <c r="D340" t="s">
+        <v>23</v>
+      </c>
+      <c r="F340" t="s">
+        <v>84</v>
+      </c>
+      <c r="G340" t="s">
+        <v>13</v>
+      </c>
+      <c r="H340" s="2">
+        <v>0</v>
+      </c>
+      <c r="I340" s="1">
+        <v>46118.765625</v>
+      </c>
+      <c r="J340">
+        <v>1</v>
+      </c>
+      <c r="K340" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="341" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H341" s="2"/>
-      <c r="I341" s="1"/>
+      <c r="B341" t="s">
+        <v>22</v>
+      </c>
+      <c r="C341">
+        <v>3501</v>
+      </c>
+      <c r="D341" t="s">
+        <v>24</v>
+      </c>
+      <c r="F341" t="s">
+        <v>84</v>
+      </c>
+      <c r="G341" t="s">
+        <v>10</v>
+      </c>
+      <c r="H341" s="2">
+        <v>6.7824074074074071E-3</v>
+      </c>
+      <c r="I341" s="1">
+        <v>46118.766319444447</v>
+      </c>
+      <c r="J341">
+        <v>1</v>
+      </c>
+      <c r="K341" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="342" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H342" s="2"/>
-      <c r="I342" s="1"/>
+      <c r="B342" t="s">
+        <v>22</v>
+      </c>
+      <c r="C342">
+        <v>4915</v>
+      </c>
+      <c r="D342" t="s">
+        <v>25</v>
+      </c>
+      <c r="F342" t="s">
+        <v>84</v>
+      </c>
+      <c r="G342" t="s">
+        <v>13</v>
+      </c>
+      <c r="H342" s="2">
+        <v>0</v>
+      </c>
+      <c r="I342" s="1">
+        <v>46118.766319444447</v>
+      </c>
+      <c r="J342">
+        <v>1</v>
+      </c>
+      <c r="K342" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="343" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H343" s="2"/>
-      <c r="I343" s="1"/>
+      <c r="B343" t="s">
+        <v>22</v>
+      </c>
+      <c r="C343">
+        <v>3360</v>
+      </c>
+      <c r="D343" t="s">
+        <v>26</v>
+      </c>
+      <c r="F343" t="s">
+        <v>84</v>
+      </c>
+      <c r="G343" t="s">
+        <v>10</v>
+      </c>
+      <c r="H343" s="2">
+        <v>1.0405092592592593E-2</v>
+      </c>
+      <c r="I343" s="1">
+        <v>46118.767013888886</v>
+      </c>
+      <c r="J343">
+        <v>1</v>
+      </c>
+      <c r="K343" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="344" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H344" s="2"/>
-      <c r="I344" s="1"/>
+      <c r="B344" t="s">
+        <v>22</v>
+      </c>
+      <c r="C344">
+        <v>3521</v>
+      </c>
+      <c r="D344" t="s">
+        <v>27</v>
+      </c>
+      <c r="F344" t="s">
+        <v>84</v>
+      </c>
+      <c r="G344" t="s">
+        <v>13</v>
+      </c>
+      <c r="H344" s="2">
+        <v>0</v>
+      </c>
+      <c r="I344" s="1">
+        <v>46118.767708333333</v>
+      </c>
+      <c r="J344">
+        <v>1</v>
+      </c>
+      <c r="K344" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="345" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H345" s="2"/>
-      <c r="I345" s="1"/>
+      <c r="B345" t="s">
+        <v>22</v>
+      </c>
+      <c r="C345">
+        <v>3479</v>
+      </c>
+      <c r="D345" t="s">
+        <v>28</v>
+      </c>
+      <c r="F345" t="s">
+        <v>84</v>
+      </c>
+      <c r="G345" t="s">
+        <v>10</v>
+      </c>
+      <c r="H345" s="2">
+        <v>9.0856481481481483E-3</v>
+      </c>
+      <c r="I345" s="1">
+        <v>46118.767708333333</v>
+      </c>
+      <c r="J345">
+        <v>1</v>
+      </c>
+      <c r="K345" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="346" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H346" s="2"/>
-      <c r="I346" s="1"/>
+      <c r="B346" t="s">
+        <v>22</v>
+      </c>
+      <c r="C346">
+        <v>3526</v>
+      </c>
+      <c r="D346" t="s">
+        <v>29</v>
+      </c>
+      <c r="F346" t="s">
+        <v>84</v>
+      </c>
+      <c r="G346" t="s">
+        <v>13</v>
+      </c>
+      <c r="H346" s="2">
+        <v>0</v>
+      </c>
+      <c r="I346" s="1">
+        <v>46118.76840277778</v>
+      </c>
+      <c r="J346">
+        <v>1</v>
+      </c>
+      <c r="K346" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="347" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H347" s="2"/>
-      <c r="I347" s="1"/>
+      <c r="B347" t="s">
+        <v>22</v>
+      </c>
+      <c r="C347">
+        <v>4917</v>
+      </c>
+      <c r="D347" t="s">
+        <v>30</v>
+      </c>
+      <c r="F347" t="s">
+        <v>84</v>
+      </c>
+      <c r="G347" t="s">
+        <v>13</v>
+      </c>
+      <c r="H347" s="2">
+        <v>0</v>
+      </c>
+      <c r="I347" s="1">
+        <v>46118.76840277778</v>
+      </c>
+      <c r="J347">
+        <v>1</v>
+      </c>
+      <c r="K347" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="348" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H348" s="2"/>
-      <c r="I348" s="1"/>
+      <c r="B348" t="s">
+        <v>22</v>
+      </c>
+      <c r="C348">
+        <v>3524</v>
+      </c>
+      <c r="D348" t="s">
+        <v>31</v>
+      </c>
+      <c r="F348" t="s">
+        <v>84</v>
+      </c>
+      <c r="G348" t="s">
+        <v>13</v>
+      </c>
+      <c r="H348" s="2">
+        <v>0</v>
+      </c>
+      <c r="I348" s="1">
+        <v>46118.769097222219</v>
+      </c>
+      <c r="J348">
+        <v>1</v>
+      </c>
+      <c r="K348" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="349" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H349" s="2"/>
-      <c r="I349" s="1"/>
+      <c r="B349" t="s">
+        <v>22</v>
+      </c>
+      <c r="C349">
+        <v>3804</v>
+      </c>
+      <c r="D349" t="s">
+        <v>32</v>
+      </c>
+      <c r="F349" t="s">
+        <v>84</v>
+      </c>
+      <c r="G349" t="s">
+        <v>13</v>
+      </c>
+      <c r="H349" s="2">
+        <v>0</v>
+      </c>
+      <c r="I349" s="1">
+        <v>46118.769791666666</v>
+      </c>
+      <c r="J349">
+        <v>1</v>
+      </c>
+      <c r="K349" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="350" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H350" s="2"/>
-      <c r="I350" s="1"/>
+      <c r="B350" t="s">
+        <v>22</v>
+      </c>
+      <c r="C350">
+        <v>3495</v>
+      </c>
+      <c r="D350" t="s">
+        <v>33</v>
+      </c>
+      <c r="F350" t="s">
+        <v>84</v>
+      </c>
+      <c r="G350" t="s">
+        <v>10</v>
+      </c>
+      <c r="H350" s="2">
+        <v>6.9212962962962961E-3</v>
+      </c>
+      <c r="I350" s="1">
+        <v>46118.769791666666</v>
+      </c>
+      <c r="J350">
+        <v>0</v>
+      </c>
+      <c r="K350" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="351" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H351" s="2"/>
-      <c r="I351" s="1"/>
+      <c r="B351" t="s">
+        <v>22</v>
+      </c>
+      <c r="C351">
+        <v>3739</v>
+      </c>
+      <c r="D351" t="s">
+        <v>34</v>
+      </c>
+      <c r="F351" t="s">
+        <v>84</v>
+      </c>
+      <c r="G351" t="s">
+        <v>13</v>
+      </c>
+      <c r="H351" s="2">
+        <v>0</v>
+      </c>
+      <c r="I351" s="1">
+        <v>46118.770486111112</v>
+      </c>
+      <c r="J351">
+        <v>1</v>
+      </c>
+      <c r="K351" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="352" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H352" s="2"/>
-      <c r="I352" s="1"/>
-    </row>
-    <row r="353" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H353" s="2"/>
-      <c r="I353" s="1"/>
-    </row>
-    <row r="354" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H354" s="2"/>
-      <c r="I354" s="1"/>
-    </row>
-    <row r="355" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H355" s="2"/>
-      <c r="I355" s="1"/>
-    </row>
-    <row r="356" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H356" s="2"/>
-      <c r="I356" s="1"/>
-    </row>
-    <row r="357" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H357" s="2"/>
-      <c r="I357" s="1"/>
-    </row>
-    <row r="358" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H358" s="2"/>
-      <c r="I358" s="1"/>
-    </row>
-    <row r="359" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H359" s="2"/>
-      <c r="I359" s="1"/>
-    </row>
-    <row r="360" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H360" s="2"/>
-      <c r="I360" s="1"/>
-    </row>
-    <row r="361" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H361" s="2"/>
-      <c r="I361" s="1"/>
-    </row>
-    <row r="362" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H362" s="2"/>
-      <c r="I362" s="1"/>
-    </row>
-    <row r="363" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H363" s="2"/>
-      <c r="I363" s="1"/>
-    </row>
-    <row r="364" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H364" s="2"/>
-      <c r="I364" s="1"/>
-    </row>
-    <row r="365" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H365" s="2"/>
-      <c r="I365" s="1"/>
-    </row>
-    <row r="366" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H366" s="2"/>
-      <c r="I366" s="1"/>
-    </row>
-    <row r="367" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H367" s="2"/>
-      <c r="I367" s="1"/>
-    </row>
-    <row r="368" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H368" s="2"/>
-      <c r="I368" s="1"/>
-    </row>
-    <row r="369" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H369" s="2"/>
-      <c r="I369" s="1"/>
-    </row>
-    <row r="370" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H370" s="2"/>
-      <c r="I370" s="1"/>
-    </row>
-    <row r="371" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H371" s="2"/>
-      <c r="I371" s="1"/>
-    </row>
-    <row r="372" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H372" s="2"/>
-      <c r="I372" s="1"/>
-    </row>
-    <row r="373" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H373" s="2"/>
-      <c r="I373" s="1"/>
-    </row>
-    <row r="374" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H374" s="2"/>
-      <c r="I374" s="1"/>
-    </row>
-    <row r="375" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B352" t="s">
+        <v>22</v>
+      </c>
+      <c r="C352">
+        <v>3520</v>
+      </c>
+      <c r="D352" t="s">
+        <v>35</v>
+      </c>
+      <c r="F352" t="s">
+        <v>84</v>
+      </c>
+      <c r="G352" t="s">
+        <v>13</v>
+      </c>
+      <c r="H352" s="2">
+        <v>0</v>
+      </c>
+      <c r="I352" s="1">
+        <v>46118.770486111112</v>
+      </c>
+      <c r="J352">
+        <v>1</v>
+      </c>
+      <c r="K352" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="353" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B353" t="s">
+        <v>22</v>
+      </c>
+      <c r="C353">
+        <v>3486</v>
+      </c>
+      <c r="D353" t="s">
+        <v>36</v>
+      </c>
+      <c r="F353" t="s">
+        <v>84</v>
+      </c>
+      <c r="G353" t="s">
+        <v>10</v>
+      </c>
+      <c r="H353" s="2">
+        <v>7.0949074074074074E-3</v>
+      </c>
+      <c r="I353" s="1">
+        <v>46118.771180555559</v>
+      </c>
+      <c r="J353">
+        <v>1</v>
+      </c>
+      <c r="K353" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B354" t="s">
+        <v>22</v>
+      </c>
+      <c r="C354">
+        <v>3886</v>
+      </c>
+      <c r="D354" t="s">
+        <v>37</v>
+      </c>
+      <c r="F354" t="s">
+        <v>84</v>
+      </c>
+      <c r="G354" t="s">
+        <v>13</v>
+      </c>
+      <c r="H354" s="2">
+        <v>0</v>
+      </c>
+      <c r="I354" s="1">
+        <v>46118.771874999999</v>
+      </c>
+      <c r="J354">
+        <v>1</v>
+      </c>
+      <c r="K354" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="355" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B355" t="s">
+        <v>22</v>
+      </c>
+      <c r="C355">
+        <v>3397</v>
+      </c>
+      <c r="D355" t="s">
+        <v>38</v>
+      </c>
+      <c r="F355" t="s">
+        <v>84</v>
+      </c>
+      <c r="G355" t="s">
+        <v>10</v>
+      </c>
+      <c r="H355" s="2">
+        <v>1.699074074074074E-2</v>
+      </c>
+      <c r="I355" s="1">
+        <v>46118.771874999999</v>
+      </c>
+      <c r="J355">
+        <v>1</v>
+      </c>
+      <c r="K355" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B356" t="s">
+        <v>22</v>
+      </c>
+      <c r="C356">
+        <v>3765</v>
+      </c>
+      <c r="D356" t="s">
+        <v>39</v>
+      </c>
+      <c r="F356" t="s">
+        <v>84</v>
+      </c>
+      <c r="G356" t="s">
+        <v>10</v>
+      </c>
+      <c r="H356" s="2">
+        <v>6.6435185185185182E-3</v>
+      </c>
+      <c r="I356" s="1">
+        <v>46118.772569444445</v>
+      </c>
+      <c r="J356">
+        <v>0</v>
+      </c>
+      <c r="K356" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="357" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B357" t="s">
+        <v>22</v>
+      </c>
+      <c r="C357">
+        <v>3496</v>
+      </c>
+      <c r="D357" t="s">
+        <v>40</v>
+      </c>
+      <c r="F357" t="s">
+        <v>84</v>
+      </c>
+      <c r="G357" t="s">
+        <v>13</v>
+      </c>
+      <c r="H357" s="2">
+        <v>0</v>
+      </c>
+      <c r="I357" s="1">
+        <v>46118.773263888892</v>
+      </c>
+      <c r="J357">
+        <v>1</v>
+      </c>
+      <c r="K357" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="358" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B358" t="s">
+        <v>22</v>
+      </c>
+      <c r="C358">
+        <v>3525</v>
+      </c>
+      <c r="D358" t="s">
+        <v>42</v>
+      </c>
+      <c r="F358" t="s">
+        <v>84</v>
+      </c>
+      <c r="G358" t="s">
+        <v>10</v>
+      </c>
+      <c r="H358" s="2">
+        <v>7.2685185185185188E-3</v>
+      </c>
+      <c r="I358" s="1">
+        <v>46118.773263888892</v>
+      </c>
+      <c r="J358">
+        <v>0</v>
+      </c>
+      <c r="K358" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="359" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B359" t="s">
+        <v>22</v>
+      </c>
+      <c r="C359">
+        <v>3513</v>
+      </c>
+      <c r="D359" t="s">
+        <v>43</v>
+      </c>
+      <c r="F359" t="s">
+        <v>84</v>
+      </c>
+      <c r="G359" t="s">
+        <v>13</v>
+      </c>
+      <c r="H359" s="2">
+        <v>0</v>
+      </c>
+      <c r="I359" s="1">
+        <v>46118.752546296295</v>
+      </c>
+      <c r="J359">
+        <v>1</v>
+      </c>
+      <c r="K359" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="360" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B360" t="s">
+        <v>22</v>
+      </c>
+      <c r="C360">
+        <v>3508</v>
+      </c>
+      <c r="D360" t="s">
+        <v>44</v>
+      </c>
+      <c r="F360" t="s">
+        <v>84</v>
+      </c>
+      <c r="G360" t="s">
+        <v>13</v>
+      </c>
+      <c r="H360" s="2">
+        <v>0</v>
+      </c>
+      <c r="I360" s="1">
+        <v>46118.752546296295</v>
+      </c>
+      <c r="J360">
+        <v>1</v>
+      </c>
+      <c r="K360" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="361" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B361" t="s">
+        <v>22</v>
+      </c>
+      <c r="C361">
+        <v>3483</v>
+      </c>
+      <c r="D361" t="s">
+        <v>45</v>
+      </c>
+      <c r="F361" t="s">
+        <v>84</v>
+      </c>
+      <c r="G361" t="s">
+        <v>13</v>
+      </c>
+      <c r="H361" s="2">
+        <v>0</v>
+      </c>
+      <c r="I361" s="1">
+        <v>46118.753240740742</v>
+      </c>
+      <c r="J361">
+        <v>1</v>
+      </c>
+      <c r="K361" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="362" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B362" t="s">
+        <v>22</v>
+      </c>
+      <c r="C362">
+        <v>3499</v>
+      </c>
+      <c r="D362" t="s">
+        <v>46</v>
+      </c>
+      <c r="F362" t="s">
+        <v>84</v>
+      </c>
+      <c r="G362" t="s">
+        <v>13</v>
+      </c>
+      <c r="H362" s="2">
+        <v>0</v>
+      </c>
+      <c r="I362" s="1">
+        <v>46118.753240740742</v>
+      </c>
+      <c r="J362">
+        <v>1</v>
+      </c>
+      <c r="K362" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="363" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B363" t="s">
+        <v>22</v>
+      </c>
+      <c r="C363">
+        <v>3699</v>
+      </c>
+      <c r="D363" t="s">
+        <v>47</v>
+      </c>
+      <c r="F363" t="s">
+        <v>84</v>
+      </c>
+      <c r="G363" t="s">
+        <v>13</v>
+      </c>
+      <c r="H363" s="2">
+        <v>0</v>
+      </c>
+      <c r="I363" s="1">
+        <v>46118.753935185188</v>
+      </c>
+      <c r="J363">
+        <v>1</v>
+      </c>
+      <c r="K363" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="364" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B364" t="s">
+        <v>22</v>
+      </c>
+      <c r="C364">
+        <v>3491</v>
+      </c>
+      <c r="D364" t="s">
+        <v>48</v>
+      </c>
+      <c r="F364" t="s">
+        <v>84</v>
+      </c>
+      <c r="G364" t="s">
+        <v>10</v>
+      </c>
+      <c r="H364" s="2">
+        <v>8.2523148148148148E-3</v>
+      </c>
+      <c r="I364" s="1">
+        <v>46118.754629629628</v>
+      </c>
+      <c r="J364">
+        <v>1</v>
+      </c>
+      <c r="K364" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="365" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B365" t="s">
+        <v>22</v>
+      </c>
+      <c r="C365">
+        <v>3487</v>
+      </c>
+      <c r="D365" t="s">
+        <v>49</v>
+      </c>
+      <c r="F365" t="s">
+        <v>84</v>
+      </c>
+      <c r="G365" t="s">
+        <v>13</v>
+      </c>
+      <c r="H365" s="2">
+        <v>0</v>
+      </c>
+      <c r="I365" s="1">
+        <v>46118.754629629628</v>
+      </c>
+      <c r="J365">
+        <v>1</v>
+      </c>
+      <c r="K365" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="366" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B366" t="s">
+        <v>22</v>
+      </c>
+      <c r="C366">
+        <v>3704</v>
+      </c>
+      <c r="D366" t="s">
+        <v>50</v>
+      </c>
+      <c r="F366" t="s">
+        <v>84</v>
+      </c>
+      <c r="G366" t="s">
+        <v>13</v>
+      </c>
+      <c r="H366" s="2">
+        <v>0</v>
+      </c>
+      <c r="I366" s="1">
+        <v>46118.755324074074</v>
+      </c>
+      <c r="J366">
+        <v>1</v>
+      </c>
+      <c r="K366" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="367" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B367" t="s">
+        <v>22</v>
+      </c>
+      <c r="C367">
+        <v>3481</v>
+      </c>
+      <c r="D367" t="s">
+        <v>51</v>
+      </c>
+      <c r="F367" t="s">
+        <v>84</v>
+      </c>
+      <c r="G367" t="s">
+        <v>13</v>
+      </c>
+      <c r="H367" s="2">
+        <v>0</v>
+      </c>
+      <c r="I367" s="1">
+        <v>46118.756018518521</v>
+      </c>
+      <c r="J367">
+        <v>1</v>
+      </c>
+      <c r="K367" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="368" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B368" t="s">
+        <v>22</v>
+      </c>
+      <c r="C368">
+        <v>3480</v>
+      </c>
+      <c r="D368" t="s">
+        <v>52</v>
+      </c>
+      <c r="F368" t="s">
+        <v>84</v>
+      </c>
+      <c r="G368" t="s">
+        <v>10</v>
+      </c>
+      <c r="H368" s="2">
+        <v>1.1342592592592593E-2</v>
+      </c>
+      <c r="I368" s="1">
+        <v>46118.756018518521</v>
+      </c>
+      <c r="J368">
+        <v>1</v>
+      </c>
+      <c r="K368" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="369" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B369" t="s">
+        <v>22</v>
+      </c>
+      <c r="C369">
+        <v>3511</v>
+      </c>
+      <c r="D369" t="s">
+        <v>53</v>
+      </c>
+      <c r="F369" t="s">
+        <v>84</v>
+      </c>
+      <c r="G369" t="s">
+        <v>10</v>
+      </c>
+      <c r="H369" s="2">
+        <v>1.0393518518518519E-2</v>
+      </c>
+      <c r="I369" s="1">
+        <v>46118.756712962961</v>
+      </c>
+      <c r="J369">
+        <v>0</v>
+      </c>
+      <c r="K369" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="370" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B370" t="s">
+        <v>22</v>
+      </c>
+      <c r="C370">
+        <v>3484</v>
+      </c>
+      <c r="D370" t="s">
+        <v>55</v>
+      </c>
+      <c r="F370" t="s">
+        <v>84</v>
+      </c>
+      <c r="G370" t="s">
+        <v>10</v>
+      </c>
+      <c r="H370" s="2">
+        <v>1.1296296296296296E-2</v>
+      </c>
+      <c r="I370" s="1">
+        <v>46118.756712962961</v>
+      </c>
+      <c r="J370">
+        <v>1</v>
+      </c>
+      <c r="K370" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="371" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B371" t="s">
+        <v>22</v>
+      </c>
+      <c r="C371">
+        <v>3514</v>
+      </c>
+      <c r="D371" t="s">
+        <v>56</v>
+      </c>
+      <c r="F371" t="s">
+        <v>84</v>
+      </c>
+      <c r="G371" t="s">
+        <v>10</v>
+      </c>
+      <c r="H371" s="2">
+        <v>7.8009259259259256E-3</v>
+      </c>
+      <c r="I371" s="1">
+        <v>46118.757407407407</v>
+      </c>
+      <c r="J371">
+        <v>1</v>
+      </c>
+      <c r="K371" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B372" t="s">
+        <v>22</v>
+      </c>
+      <c r="C372">
+        <v>3725</v>
+      </c>
+      <c r="D372" t="s">
+        <v>58</v>
+      </c>
+      <c r="F372" t="s">
+        <v>84</v>
+      </c>
+      <c r="G372" t="s">
+        <v>13</v>
+      </c>
+      <c r="H372" s="2">
+        <v>0</v>
+      </c>
+      <c r="I372" s="1">
+        <v>46118.758101851854</v>
+      </c>
+      <c r="J372">
+        <v>1</v>
+      </c>
+      <c r="K372" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="373" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B373" t="s">
+        <v>22</v>
+      </c>
+      <c r="C373">
+        <v>3488</v>
+      </c>
+      <c r="D373" t="s">
+        <v>59</v>
+      </c>
+      <c r="F373" t="s">
+        <v>84</v>
+      </c>
+      <c r="G373" t="s">
+        <v>10</v>
+      </c>
+      <c r="H373" s="2">
+        <v>6.7824074074074071E-3</v>
+      </c>
+      <c r="I373" s="1">
+        <v>46118.758101851854</v>
+      </c>
+      <c r="J373">
+        <v>0</v>
+      </c>
+      <c r="K373" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="374" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B374" t="s">
+        <v>22</v>
+      </c>
+      <c r="C374">
+        <v>3478</v>
+      </c>
+      <c r="D374" t="s">
+        <v>60</v>
+      </c>
+      <c r="F374" t="s">
+        <v>84</v>
+      </c>
+      <c r="G374" t="s">
+        <v>12</v>
+      </c>
+      <c r="H374" s="2">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="I374" s="1">
+        <v>46118.758796296293</v>
+      </c>
+      <c r="J374">
+        <v>1</v>
+      </c>
+      <c r="K374" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="375" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H375" s="2"/>
       <c r="I375" s="1"/>
-    </row>
-    <row r="376" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H376" s="2"/>
-      <c r="I376" s="1"/>
-    </row>
-    <row r="377" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H377" s="2"/>
-      <c r="I377" s="1"/>
-    </row>
-    <row r="378" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H378" s="2"/>
-      <c r="I378" s="1"/>
-    </row>
-    <row r="379" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H379" s="2"/>
-      <c r="I379" s="1"/>
-    </row>
-    <row r="380" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H380" s="2"/>
-      <c r="I380" s="1"/>
-    </row>
-    <row r="381" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K375" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="376" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B376" t="s">
+        <v>22</v>
+      </c>
+      <c r="C376">
+        <v>3494</v>
+      </c>
+      <c r="D376" t="s">
+        <v>61</v>
+      </c>
+      <c r="F376" t="s">
+        <v>84</v>
+      </c>
+      <c r="G376" t="s">
+        <v>10</v>
+      </c>
+      <c r="H376" s="2">
+        <v>7.1064814814814819E-3</v>
+      </c>
+      <c r="I376" s="1">
+        <v>46118.758796296293</v>
+      </c>
+      <c r="J376">
+        <v>1</v>
+      </c>
+      <c r="K376" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="377" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B377" t="s">
+        <v>22</v>
+      </c>
+      <c r="C377">
+        <v>3523</v>
+      </c>
+      <c r="D377" t="s">
+        <v>62</v>
+      </c>
+      <c r="F377" t="s">
+        <v>84</v>
+      </c>
+      <c r="G377" t="s">
+        <v>13</v>
+      </c>
+      <c r="H377" s="2">
+        <v>0</v>
+      </c>
+      <c r="I377" s="1">
+        <v>46118.75949074074</v>
+      </c>
+      <c r="J377">
+        <v>1</v>
+      </c>
+      <c r="K377" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="378" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B378" t="s">
+        <v>22</v>
+      </c>
+      <c r="C378">
+        <v>3504</v>
+      </c>
+      <c r="D378" t="s">
+        <v>64</v>
+      </c>
+      <c r="F378" t="s">
+        <v>84</v>
+      </c>
+      <c r="G378" t="s">
+        <v>13</v>
+      </c>
+      <c r="H378" s="2">
+        <v>0</v>
+      </c>
+      <c r="I378" s="1">
+        <v>46118.760185185187</v>
+      </c>
+      <c r="J378">
+        <v>1</v>
+      </c>
+      <c r="K378" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="379" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B379" t="s">
+        <v>22</v>
+      </c>
+      <c r="C379">
+        <v>3498</v>
+      </c>
+      <c r="D379" t="s">
+        <v>65</v>
+      </c>
+      <c r="F379" t="s">
+        <v>84</v>
+      </c>
+      <c r="G379" t="s">
+        <v>10</v>
+      </c>
+      <c r="H379" s="2">
+        <v>8.1250000000000003E-3</v>
+      </c>
+      <c r="I379" s="1">
+        <v>46118.760185185187</v>
+      </c>
+      <c r="J379">
+        <v>1</v>
+      </c>
+      <c r="K379" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="380" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B380" t="s">
+        <v>22</v>
+      </c>
+      <c r="C380">
+        <v>3344</v>
+      </c>
+      <c r="D380" t="s">
+        <v>66</v>
+      </c>
+      <c r="F380" t="s">
+        <v>84</v>
+      </c>
+      <c r="G380" t="s">
+        <v>12</v>
+      </c>
+      <c r="H380" s="2">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="I380" s="1">
+        <v>46118.760879629626</v>
+      </c>
+      <c r="J380">
+        <v>1</v>
+      </c>
+      <c r="K380" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="381" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H381" s="2"/>
       <c r="I381" s="1"/>
-    </row>
-    <row r="382" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H382" s="2"/>
-      <c r="I382" s="1"/>
-    </row>
-    <row r="383" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H383" s="2"/>
-      <c r="I383" s="1"/>
-    </row>
-    <row r="384" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H384" s="2"/>
-      <c r="I384" s="1"/>
-    </row>
-    <row r="385" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H385" s="2"/>
-      <c r="I385" s="1"/>
-    </row>
-    <row r="386" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H386" s="2"/>
-      <c r="I386" s="1"/>
-    </row>
-    <row r="387" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H387" s="2"/>
-      <c r="I387" s="1"/>
-    </row>
-    <row r="388" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H388" s="2"/>
-      <c r="I388" s="1"/>
-    </row>
-    <row r="389" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H389" s="2"/>
-      <c r="I389" s="1"/>
-    </row>
-    <row r="390" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H390" s="2"/>
-      <c r="I390" s="1"/>
-    </row>
-    <row r="391" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H391" s="2"/>
-      <c r="I391" s="1"/>
-    </row>
-    <row r="392" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H392" s="2"/>
-      <c r="I392" s="1"/>
-    </row>
-    <row r="393" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H393" s="2"/>
-      <c r="I393" s="1"/>
-    </row>
-    <row r="394" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H394" s="2"/>
-      <c r="I394" s="1"/>
-    </row>
-    <row r="395" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H395" s="2"/>
-      <c r="I395" s="1"/>
-    </row>
-    <row r="396" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K381" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B382" t="s">
+        <v>22</v>
+      </c>
+      <c r="C382">
+        <v>3515</v>
+      </c>
+      <c r="D382" t="s">
+        <v>67</v>
+      </c>
+      <c r="F382" t="s">
+        <v>84</v>
+      </c>
+      <c r="G382" t="s">
+        <v>13</v>
+      </c>
+      <c r="H382" s="2">
+        <v>0</v>
+      </c>
+      <c r="I382" s="1">
+        <v>46118.760879629626</v>
+      </c>
+      <c r="J382">
+        <v>1</v>
+      </c>
+      <c r="K382" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="383" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B383" t="s">
+        <v>22</v>
+      </c>
+      <c r="C383">
+        <v>3522</v>
+      </c>
+      <c r="D383" t="s">
+        <v>68</v>
+      </c>
+      <c r="F383" t="s">
+        <v>84</v>
+      </c>
+      <c r="G383" t="s">
+        <v>13</v>
+      </c>
+      <c r="H383" s="2">
+        <v>0</v>
+      </c>
+      <c r="I383" s="1">
+        <v>46118.761574074073</v>
+      </c>
+      <c r="J383">
+        <v>1</v>
+      </c>
+      <c r="K383" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="384" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B384" t="s">
+        <v>22</v>
+      </c>
+      <c r="C384">
+        <v>3751</v>
+      </c>
+      <c r="D384" t="s">
+        <v>69</v>
+      </c>
+      <c r="F384" t="s">
+        <v>84</v>
+      </c>
+      <c r="G384" t="s">
+        <v>13</v>
+      </c>
+      <c r="H384" s="2">
+        <v>0</v>
+      </c>
+      <c r="I384" s="1">
+        <v>46118.76226851852</v>
+      </c>
+      <c r="J384">
+        <v>1</v>
+      </c>
+      <c r="K384" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="385" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B385" t="s">
+        <v>22</v>
+      </c>
+      <c r="C385">
+        <v>3662</v>
+      </c>
+      <c r="D385" t="s">
+        <v>70</v>
+      </c>
+      <c r="F385" t="s">
+        <v>84</v>
+      </c>
+      <c r="G385" t="s">
+        <v>13</v>
+      </c>
+      <c r="H385" s="2">
+        <v>0</v>
+      </c>
+      <c r="I385" s="1">
+        <v>46118.76226851852</v>
+      </c>
+      <c r="J385">
+        <v>1</v>
+      </c>
+      <c r="K385" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="386" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B386" t="s">
+        <v>22</v>
+      </c>
+      <c r="C386">
+        <v>3517</v>
+      </c>
+      <c r="D386" t="s">
+        <v>71</v>
+      </c>
+      <c r="F386" t="s">
+        <v>84</v>
+      </c>
+      <c r="G386" t="s">
+        <v>10</v>
+      </c>
+      <c r="H386" s="2">
+        <v>7.2800925925925923E-3</v>
+      </c>
+      <c r="I386" s="1">
+        <v>46118.762962962966</v>
+      </c>
+      <c r="J386">
+        <v>0</v>
+      </c>
+      <c r="K386" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="387" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B387" t="s">
+        <v>22</v>
+      </c>
+      <c r="C387">
+        <v>3503</v>
+      </c>
+      <c r="D387" t="s">
+        <v>72</v>
+      </c>
+      <c r="F387" t="s">
+        <v>84</v>
+      </c>
+      <c r="G387" t="s">
+        <v>13</v>
+      </c>
+      <c r="H387" s="2">
+        <v>0</v>
+      </c>
+      <c r="I387" s="1">
+        <v>46118.762962962966</v>
+      </c>
+      <c r="J387">
+        <v>1</v>
+      </c>
+      <c r="K387" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="388" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B388" t="s">
+        <v>22</v>
+      </c>
+      <c r="C388">
+        <v>3652</v>
+      </c>
+      <c r="D388" t="s">
+        <v>73</v>
+      </c>
+      <c r="F388" t="s">
+        <v>84</v>
+      </c>
+      <c r="G388" t="s">
+        <v>13</v>
+      </c>
+      <c r="H388" s="2">
+        <v>0</v>
+      </c>
+      <c r="I388" s="1">
+        <v>46118.763657407406</v>
+      </c>
+      <c r="J388">
+        <v>1</v>
+      </c>
+      <c r="K388" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="389" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B389" t="s">
+        <v>22</v>
+      </c>
+      <c r="C389">
+        <v>3509</v>
+      </c>
+      <c r="D389" t="s">
+        <v>74</v>
+      </c>
+      <c r="F389" t="s">
+        <v>84</v>
+      </c>
+      <c r="G389" t="s">
+        <v>13</v>
+      </c>
+      <c r="H389" s="2">
+        <v>0</v>
+      </c>
+      <c r="I389" s="1">
+        <v>46118.764351851853</v>
+      </c>
+      <c r="J389">
+        <v>1</v>
+      </c>
+      <c r="K389" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="390" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B390" t="s">
+        <v>22</v>
+      </c>
+      <c r="C390">
+        <v>3512</v>
+      </c>
+      <c r="D390" t="s">
+        <v>75</v>
+      </c>
+      <c r="F390" t="s">
+        <v>84</v>
+      </c>
+      <c r="G390" t="s">
+        <v>10</v>
+      </c>
+      <c r="H390" s="2">
+        <v>7.3726851851851852E-3</v>
+      </c>
+      <c r="I390" s="1">
+        <v>46118.765046296299</v>
+      </c>
+      <c r="J390">
+        <v>0</v>
+      </c>
+      <c r="K390" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="391" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B391" t="s">
+        <v>22</v>
+      </c>
+      <c r="C391">
+        <v>3489</v>
+      </c>
+      <c r="D391" t="s">
+        <v>76</v>
+      </c>
+      <c r="F391" t="s">
+        <v>84</v>
+      </c>
+      <c r="G391" t="s">
+        <v>10</v>
+      </c>
+      <c r="H391" s="2">
+        <v>7.5462962962962966E-3</v>
+      </c>
+      <c r="I391" s="1">
+        <v>46118.765046296299</v>
+      </c>
+      <c r="J391">
+        <v>1</v>
+      </c>
+      <c r="K391" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="392" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B392" t="s">
+        <v>22</v>
+      </c>
+      <c r="C392">
+        <v>3266</v>
+      </c>
+      <c r="D392" t="s">
+        <v>77</v>
+      </c>
+      <c r="F392" t="s">
+        <v>84</v>
+      </c>
+      <c r="G392" t="s">
+        <v>10</v>
+      </c>
+      <c r="H392" s="2">
+        <v>7.3842592592592597E-3</v>
+      </c>
+      <c r="I392" s="1">
+        <v>46118.765740740739</v>
+      </c>
+      <c r="J392">
+        <v>0</v>
+      </c>
+      <c r="K392" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="393" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B393" t="s">
+        <v>22</v>
+      </c>
+      <c r="C393">
+        <v>3492</v>
+      </c>
+      <c r="D393" t="s">
+        <v>78</v>
+      </c>
+      <c r="F393" t="s">
+        <v>84</v>
+      </c>
+      <c r="G393" t="s">
+        <v>10</v>
+      </c>
+      <c r="H393" s="2">
+        <v>9.8958333333333329E-3</v>
+      </c>
+      <c r="I393" s="1">
+        <v>46118.766435185185</v>
+      </c>
+      <c r="J393">
+        <v>1</v>
+      </c>
+      <c r="K393" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="394" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B394" t="s">
+        <v>22</v>
+      </c>
+      <c r="C394">
+        <v>3493</v>
+      </c>
+      <c r="D394" t="s">
+        <v>79</v>
+      </c>
+      <c r="F394" t="s">
+        <v>84</v>
+      </c>
+      <c r="G394" t="s">
+        <v>13</v>
+      </c>
+      <c r="H394" s="2">
+        <v>0</v>
+      </c>
+      <c r="I394" s="1">
+        <v>46118.766435185185</v>
+      </c>
+      <c r="J394">
+        <v>1</v>
+      </c>
+      <c r="K394" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="395" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B395" t="s">
+        <v>22</v>
+      </c>
+      <c r="C395">
+        <v>3505</v>
+      </c>
+      <c r="D395" t="s">
+        <v>80</v>
+      </c>
+      <c r="F395" t="s">
+        <v>84</v>
+      </c>
+      <c r="G395" t="s">
+        <v>12</v>
+      </c>
+      <c r="H395" s="2">
+        <v>6.145833333333333E-3</v>
+      </c>
+      <c r="I395" s="1">
+        <v>46118.767129629632</v>
+      </c>
+      <c r="J395">
+        <v>0</v>
+      </c>
+      <c r="K395" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="396" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H396" s="2"/>
       <c r="I396" s="1"/>
-    </row>
-    <row r="397" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H397" s="2"/>
-      <c r="I397" s="1"/>
-    </row>
-    <row r="398" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H398" s="2"/>
-      <c r="I398" s="1"/>
-    </row>
-    <row r="399" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H399" s="2"/>
-      <c r="I399" s="1"/>
-    </row>
-    <row r="400" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K396" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="397" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B397" t="s">
+        <v>22</v>
+      </c>
+      <c r="C397">
+        <v>3861</v>
+      </c>
+      <c r="D397" t="s">
+        <v>81</v>
+      </c>
+      <c r="F397" t="s">
+        <v>84</v>
+      </c>
+      <c r="G397" t="s">
+        <v>10</v>
+      </c>
+      <c r="H397" s="2">
+        <v>7.3611111111111108E-3</v>
+      </c>
+      <c r="I397" s="1">
+        <v>46118.767824074072</v>
+      </c>
+      <c r="J397">
+        <v>1</v>
+      </c>
+      <c r="K397" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="398" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B398" t="s">
+        <v>22</v>
+      </c>
+      <c r="C398">
+        <v>5205</v>
+      </c>
+      <c r="D398" t="s">
+        <v>83</v>
+      </c>
+      <c r="F398" t="s">
+        <v>84</v>
+      </c>
+      <c r="G398" t="s">
+        <v>13</v>
+      </c>
+      <c r="H398" s="2">
+        <v>0</v>
+      </c>
+      <c r="I398" s="1">
+        <v>46118.767824074072</v>
+      </c>
+      <c r="J398">
+        <v>1</v>
+      </c>
+      <c r="K398" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="399" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B399" t="s">
+        <v>22</v>
+      </c>
+      <c r="C399">
+        <v>3538</v>
+      </c>
+      <c r="D399" t="s">
+        <v>82</v>
+      </c>
+      <c r="F399" t="s">
+        <v>84</v>
+      </c>
+      <c r="G399" t="s">
+        <v>10</v>
+      </c>
+      <c r="H399" s="2">
+        <v>9.8032407407407408E-3</v>
+      </c>
+      <c r="I399" s="1">
+        <v>46118.768518518518</v>
+      </c>
+      <c r="J399">
+        <v>0</v>
+      </c>
+      <c r="K399" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="400" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H400" s="2"/>
       <c r="I400" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Fiore and Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C2FB5E-08EB-4AD1-8D50-6DCA30C2C217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FDACB3-C768-4742-B11D-9308C96FE3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="85">
   <si>
     <t>Company Name</t>
   </si>
@@ -9650,48 +9650,26 @@
         <v>84</v>
       </c>
       <c r="G340" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H340" s="2">
-        <v>0</v>
+        <v>6.9444444444444444E-5</v>
       </c>
       <c r="I340" s="1">
         <v>46118.765625</v>
       </c>
       <c r="J340">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K340" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="341" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B341" t="s">
-        <v>22</v>
-      </c>
-      <c r="C341">
-        <v>3501</v>
-      </c>
-      <c r="D341" t="s">
-        <v>24</v>
-      </c>
-      <c r="F341" t="s">
-        <v>84</v>
-      </c>
-      <c r="G341" t="s">
-        <v>10</v>
-      </c>
-      <c r="H341" s="2">
-        <v>6.7824074074074071E-3</v>
-      </c>
-      <c r="I341" s="1">
-        <v>46118.766319444447</v>
-      </c>
-      <c r="J341">
-        <v>1</v>
-      </c>
+      <c r="H341" s="2"/>
+      <c r="I341" s="1"/>
       <c r="K341" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="342" spans="2:11" x14ac:dyDescent="0.25">
@@ -9699,19 +9677,19 @@
         <v>22</v>
       </c>
       <c r="C342">
-        <v>4915</v>
+        <v>3501</v>
       </c>
       <c r="D342" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F342" t="s">
         <v>84</v>
       </c>
       <c r="G342" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H342" s="2">
-        <v>0</v>
+        <v>6.7824074074074071E-3</v>
       </c>
       <c r="I342" s="1">
         <v>46118.766319444447</v>
@@ -9728,10 +9706,10 @@
         <v>22</v>
       </c>
       <c r="C343">
-        <v>3360</v>
+        <v>4915</v>
       </c>
       <c r="D343" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F343" t="s">
         <v>84</v>
@@ -9740,13 +9718,13 @@
         <v>10</v>
       </c>
       <c r="H343" s="2">
-        <v>1.0405092592592593E-2</v>
+        <v>1.4120370370370369E-3</v>
       </c>
       <c r="I343" s="1">
-        <v>46118.767013888886</v>
+        <v>46118.766319444447</v>
       </c>
       <c r="J343">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K343" t="s">
         <v>11</v>
@@ -9757,22 +9735,22 @@
         <v>22</v>
       </c>
       <c r="C344">
-        <v>3521</v>
+        <v>3360</v>
       </c>
       <c r="D344" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F344" t="s">
         <v>84</v>
       </c>
       <c r="G344" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H344" s="2">
-        <v>0</v>
+        <v>1.0405092592592593E-2</v>
       </c>
       <c r="I344" s="1">
-        <v>46118.767708333333</v>
+        <v>46118.767013888886</v>
       </c>
       <c r="J344">
         <v>1</v>
@@ -9786,25 +9764,25 @@
         <v>22</v>
       </c>
       <c r="C345">
-        <v>3479</v>
+        <v>3521</v>
       </c>
       <c r="D345" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F345" t="s">
         <v>84</v>
       </c>
       <c r="G345" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H345" s="2">
-        <v>9.0856481481481483E-3</v>
+        <v>0</v>
       </c>
       <c r="I345" s="1">
         <v>46118.767708333333</v>
       </c>
       <c r="J345">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K345" t="s">
         <v>11</v>
@@ -9815,22 +9793,22 @@
         <v>22</v>
       </c>
       <c r="C346">
-        <v>3526</v>
+        <v>3479</v>
       </c>
       <c r="D346" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F346" t="s">
         <v>84</v>
       </c>
       <c r="G346" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H346" s="2">
-        <v>0</v>
+        <v>9.0856481481481483E-3</v>
       </c>
       <c r="I346" s="1">
-        <v>46118.76840277778</v>
+        <v>46118.767708333333</v>
       </c>
       <c r="J346">
         <v>1</v>
@@ -9844,10 +9822,10 @@
         <v>22</v>
       </c>
       <c r="C347">
-        <v>4917</v>
+        <v>3526</v>
       </c>
       <c r="D347" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F347" t="s">
         <v>84</v>
@@ -9862,7 +9840,7 @@
         <v>46118.76840277778</v>
       </c>
       <c r="J347">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K347" t="s">
         <v>11</v>
@@ -9873,10 +9851,10 @@
         <v>22</v>
       </c>
       <c r="C348">
-        <v>3524</v>
+        <v>4917</v>
       </c>
       <c r="D348" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F348" t="s">
         <v>84</v>
@@ -9888,10 +9866,10 @@
         <v>0</v>
       </c>
       <c r="I348" s="1">
-        <v>46118.769097222219</v>
+        <v>46118.76840277778</v>
       </c>
       <c r="J348">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K348" t="s">
         <v>11</v>
@@ -9902,10 +9880,10 @@
         <v>22</v>
       </c>
       <c r="C349">
-        <v>3804</v>
+        <v>3524</v>
       </c>
       <c r="D349" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F349" t="s">
         <v>84</v>
@@ -9917,10 +9895,10 @@
         <v>0</v>
       </c>
       <c r="I349" s="1">
-        <v>46118.769791666666</v>
+        <v>46118.769097222219</v>
       </c>
       <c r="J349">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K349" t="s">
         <v>11</v>
@@ -9931,25 +9909,25 @@
         <v>22</v>
       </c>
       <c r="C350">
-        <v>3495</v>
+        <v>3804</v>
       </c>
       <c r="D350" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F350" t="s">
         <v>84</v>
       </c>
       <c r="G350" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H350" s="2">
-        <v>6.9212962962962961E-3</v>
+        <v>0</v>
       </c>
       <c r="I350" s="1">
         <v>46118.769791666666</v>
       </c>
       <c r="J350">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K350" t="s">
         <v>11</v>
@@ -9960,25 +9938,25 @@
         <v>22</v>
       </c>
       <c r="C351">
-        <v>3739</v>
+        <v>3495</v>
       </c>
       <c r="D351" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F351" t="s">
         <v>84</v>
       </c>
       <c r="G351" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H351" s="2">
+        <v>6.9212962962962961E-3</v>
+      </c>
+      <c r="I351" s="1">
+        <v>46118.769791666666</v>
+      </c>
+      <c r="J351">
         <v>0</v>
-      </c>
-      <c r="I351" s="1">
-        <v>46118.770486111112</v>
-      </c>
-      <c r="J351">
-        <v>1</v>
       </c>
       <c r="K351" t="s">
         <v>11</v>
@@ -9989,10 +9967,10 @@
         <v>22</v>
       </c>
       <c r="C352">
-        <v>3520</v>
+        <v>3739</v>
       </c>
       <c r="D352" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F352" t="s">
         <v>84</v>
@@ -10007,7 +9985,7 @@
         <v>46118.770486111112</v>
       </c>
       <c r="J352">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K352" t="s">
         <v>11</v>
@@ -10018,25 +9996,25 @@
         <v>22</v>
       </c>
       <c r="C353">
-        <v>3486</v>
+        <v>3520</v>
       </c>
       <c r="D353" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F353" t="s">
         <v>84</v>
       </c>
       <c r="G353" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H353" s="2">
-        <v>7.0949074074074074E-3</v>
+        <v>0</v>
       </c>
       <c r="I353" s="1">
-        <v>46118.771180555559</v>
+        <v>46118.770486111112</v>
       </c>
       <c r="J353">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K353" t="s">
         <v>11</v>
@@ -10047,22 +10025,22 @@
         <v>22</v>
       </c>
       <c r="C354">
-        <v>3886</v>
+        <v>3486</v>
       </c>
       <c r="D354" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F354" t="s">
         <v>84</v>
       </c>
       <c r="G354" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H354" s="2">
-        <v>0</v>
+        <v>7.0949074074074074E-3</v>
       </c>
       <c r="I354" s="1">
-        <v>46118.771874999999</v>
+        <v>46118.771180555559</v>
       </c>
       <c r="J354">
         <v>1</v>
@@ -10076,25 +10054,25 @@
         <v>22</v>
       </c>
       <c r="C355">
-        <v>3397</v>
+        <v>3886</v>
       </c>
       <c r="D355" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F355" t="s">
         <v>84</v>
       </c>
       <c r="G355" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H355" s="2">
-        <v>1.699074074074074E-2</v>
+        <v>0</v>
       </c>
       <c r="I355" s="1">
         <v>46118.771874999999</v>
       </c>
       <c r="J355">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K355" t="s">
         <v>11</v>
@@ -10105,10 +10083,10 @@
         <v>22</v>
       </c>
       <c r="C356">
-        <v>3765</v>
+        <v>3397</v>
       </c>
       <c r="D356" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F356" t="s">
         <v>84</v>
@@ -10117,13 +10095,13 @@
         <v>10</v>
       </c>
       <c r="H356" s="2">
-        <v>6.6435185185185182E-3</v>
+        <v>1.699074074074074E-2</v>
       </c>
       <c r="I356" s="1">
-        <v>46118.772569444445</v>
+        <v>46118.771874999999</v>
       </c>
       <c r="J356">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K356" t="s">
         <v>11</v>
@@ -10134,25 +10112,25 @@
         <v>22</v>
       </c>
       <c r="C357">
-        <v>3496</v>
+        <v>3765</v>
       </c>
       <c r="D357" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F357" t="s">
         <v>84</v>
       </c>
       <c r="G357" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H357" s="2">
+        <v>6.6435185185185182E-3</v>
+      </c>
+      <c r="I357" s="1">
+        <v>46118.772569444445</v>
+      </c>
+      <c r="J357">
         <v>0</v>
-      </c>
-      <c r="I357" s="1">
-        <v>46118.773263888892</v>
-      </c>
-      <c r="J357">
-        <v>1</v>
       </c>
       <c r="K357" t="s">
         <v>11</v>
@@ -10163,25 +10141,25 @@
         <v>22</v>
       </c>
       <c r="C358">
-        <v>3525</v>
+        <v>3496</v>
       </c>
       <c r="D358" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F358" t="s">
         <v>84</v>
       </c>
       <c r="G358" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H358" s="2">
-        <v>7.2685185185185188E-3</v>
+        <v>0</v>
       </c>
       <c r="I358" s="1">
         <v>46118.773263888892</v>
       </c>
       <c r="J358">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K358" t="s">
         <v>11</v>
@@ -10192,25 +10170,25 @@
         <v>22</v>
       </c>
       <c r="C359">
-        <v>3513</v>
+        <v>3525</v>
       </c>
       <c r="D359" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F359" t="s">
         <v>84</v>
       </c>
       <c r="G359" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H359" s="2">
+        <v>7.2685185185185188E-3</v>
+      </c>
+      <c r="I359" s="1">
+        <v>46118.773263888892</v>
+      </c>
+      <c r="J359">
         <v>0</v>
-      </c>
-      <c r="I359" s="1">
-        <v>46118.752546296295</v>
-      </c>
-      <c r="J359">
-        <v>1</v>
       </c>
       <c r="K359" t="s">
         <v>11</v>
@@ -10221,10 +10199,10 @@
         <v>22</v>
       </c>
       <c r="C360">
-        <v>3508</v>
+        <v>3513</v>
       </c>
       <c r="D360" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F360" t="s">
         <v>84</v>
@@ -10239,7 +10217,7 @@
         <v>46118.752546296295</v>
       </c>
       <c r="J360">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K360" t="s">
         <v>11</v>
@@ -10250,10 +10228,10 @@
         <v>22</v>
       </c>
       <c r="C361">
-        <v>3483</v>
+        <v>3508</v>
       </c>
       <c r="D361" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F361" t="s">
         <v>84</v>
@@ -10265,10 +10243,10 @@
         <v>0</v>
       </c>
       <c r="I361" s="1">
-        <v>46118.753240740742</v>
+        <v>46118.752546296295</v>
       </c>
       <c r="J361">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K361" t="s">
         <v>11</v>
@@ -10279,10 +10257,10 @@
         <v>22</v>
       </c>
       <c r="C362">
-        <v>3499</v>
+        <v>3483</v>
       </c>
       <c r="D362" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F362" t="s">
         <v>84</v>
@@ -10297,7 +10275,7 @@
         <v>46118.753240740742</v>
       </c>
       <c r="J362">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K362" t="s">
         <v>11</v>
@@ -10308,10 +10286,10 @@
         <v>22</v>
       </c>
       <c r="C363">
-        <v>3699</v>
+        <v>3499</v>
       </c>
       <c r="D363" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F363" t="s">
         <v>84</v>
@@ -10323,10 +10301,10 @@
         <v>0</v>
       </c>
       <c r="I363" s="1">
-        <v>46118.753935185188</v>
+        <v>46118.753240740742</v>
       </c>
       <c r="J363">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K363" t="s">
         <v>11</v>
@@ -10337,25 +10315,25 @@
         <v>22</v>
       </c>
       <c r="C364">
-        <v>3491</v>
+        <v>3699</v>
       </c>
       <c r="D364" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F364" t="s">
         <v>84</v>
       </c>
       <c r="G364" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H364" s="2">
-        <v>8.2523148148148148E-3</v>
+        <v>0</v>
       </c>
       <c r="I364" s="1">
-        <v>46118.754629629628</v>
+        <v>46118.753935185188</v>
       </c>
       <c r="J364">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K364" t="s">
         <v>11</v>
@@ -10366,19 +10344,19 @@
         <v>22</v>
       </c>
       <c r="C365">
-        <v>3487</v>
+        <v>3491</v>
       </c>
       <c r="D365" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F365" t="s">
         <v>84</v>
       </c>
       <c r="G365" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H365" s="2">
-        <v>0</v>
+        <v>8.2523148148148148E-3</v>
       </c>
       <c r="I365" s="1">
         <v>46118.754629629628</v>
@@ -10395,10 +10373,10 @@
         <v>22</v>
       </c>
       <c r="C366">
-        <v>3704</v>
+        <v>3487</v>
       </c>
       <c r="D366" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F366" t="s">
         <v>84</v>
@@ -10410,10 +10388,10 @@
         <v>0</v>
       </c>
       <c r="I366" s="1">
-        <v>46118.755324074074</v>
+        <v>46118.754629629628</v>
       </c>
       <c r="J366">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K366" t="s">
         <v>11</v>
@@ -10424,10 +10402,10 @@
         <v>22</v>
       </c>
       <c r="C367">
-        <v>3481</v>
+        <v>3704</v>
       </c>
       <c r="D367" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F367" t="s">
         <v>84</v>
@@ -10439,10 +10417,10 @@
         <v>0</v>
       </c>
       <c r="I367" s="1">
-        <v>46118.756018518521</v>
+        <v>46118.755324074074</v>
       </c>
       <c r="J367">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K367" t="s">
         <v>11</v>
@@ -10453,25 +10431,25 @@
         <v>22</v>
       </c>
       <c r="C368">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="D368" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F368" t="s">
         <v>84</v>
       </c>
       <c r="G368" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H368" s="2">
-        <v>1.1342592592592593E-2</v>
+        <v>0</v>
       </c>
       <c r="I368" s="1">
         <v>46118.756018518521</v>
       </c>
       <c r="J368">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K368" t="s">
         <v>11</v>
@@ -10482,10 +10460,10 @@
         <v>22</v>
       </c>
       <c r="C369">
-        <v>3511</v>
+        <v>3480</v>
       </c>
       <c r="D369" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F369" t="s">
         <v>84</v>
@@ -10494,13 +10472,13 @@
         <v>10</v>
       </c>
       <c r="H369" s="2">
-        <v>1.0393518518518519E-2</v>
+        <v>1.1342592592592593E-2</v>
       </c>
       <c r="I369" s="1">
-        <v>46118.756712962961</v>
+        <v>46118.756018518521</v>
       </c>
       <c r="J369">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K369" t="s">
         <v>11</v>
@@ -10511,10 +10489,10 @@
         <v>22</v>
       </c>
       <c r="C370">
-        <v>3484</v>
+        <v>3511</v>
       </c>
       <c r="D370" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F370" t="s">
         <v>84</v>
@@ -10523,13 +10501,13 @@
         <v>10</v>
       </c>
       <c r="H370" s="2">
-        <v>1.1296296296296296E-2</v>
+        <v>1.0393518518518519E-2</v>
       </c>
       <c r="I370" s="1">
         <v>46118.756712962961</v>
       </c>
       <c r="J370">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K370" t="s">
         <v>11</v>
@@ -10540,10 +10518,10 @@
         <v>22</v>
       </c>
       <c r="C371">
-        <v>3514</v>
+        <v>3484</v>
       </c>
       <c r="D371" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F371" t="s">
         <v>84</v>
@@ -10552,10 +10530,10 @@
         <v>10</v>
       </c>
       <c r="H371" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>1.1296296296296296E-2</v>
       </c>
       <c r="I371" s="1">
-        <v>46118.757407407407</v>
+        <v>46118.756712962961</v>
       </c>
       <c r="J371">
         <v>1</v>
@@ -10569,22 +10547,22 @@
         <v>22</v>
       </c>
       <c r="C372">
-        <v>3725</v>
+        <v>3514</v>
       </c>
       <c r="D372" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F372" t="s">
         <v>84</v>
       </c>
       <c r="G372" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H372" s="2">
-        <v>0</v>
+        <v>7.8009259259259256E-3</v>
       </c>
       <c r="I372" s="1">
-        <v>46118.758101851854</v>
+        <v>46118.757407407407</v>
       </c>
       <c r="J372">
         <v>1</v>
@@ -10598,25 +10576,25 @@
         <v>22</v>
       </c>
       <c r="C373">
-        <v>3488</v>
+        <v>3725</v>
       </c>
       <c r="D373" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F373" t="s">
         <v>84</v>
       </c>
       <c r="G373" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H373" s="2">
-        <v>6.7824074074074071E-3</v>
+        <v>0</v>
       </c>
       <c r="I373" s="1">
         <v>46118.758101851854</v>
       </c>
       <c r="J373">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K373" t="s">
         <v>11</v>
@@ -10627,64 +10605,64 @@
         <v>22</v>
       </c>
       <c r="C374">
-        <v>3478</v>
+        <v>3488</v>
       </c>
       <c r="D374" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F374" t="s">
         <v>84</v>
       </c>
       <c r="G374" t="s">
+        <v>10</v>
+      </c>
+      <c r="H374" s="2">
+        <v>6.7824074074074071E-3</v>
+      </c>
+      <c r="I374" s="1">
+        <v>46118.758101851854</v>
+      </c>
+      <c r="J374">
+        <v>0</v>
+      </c>
+      <c r="K374" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="375" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B375" t="s">
+        <v>22</v>
+      </c>
+      <c r="C375">
+        <v>3478</v>
+      </c>
+      <c r="D375" t="s">
+        <v>60</v>
+      </c>
+      <c r="F375" t="s">
+        <v>84</v>
+      </c>
+      <c r="G375" t="s">
         <v>12</v>
       </c>
-      <c r="H374" s="2">
+      <c r="H375" s="2">
         <v>5.7870370370370373E-5</v>
       </c>
-      <c r="I374" s="1">
+      <c r="I375" s="1">
         <v>46118.758796296293</v>
       </c>
-      <c r="J374">
+      <c r="J375">
         <v>1</v>
       </c>
-      <c r="K374" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="375" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H375" s="2"/>
-      <c r="I375" s="1"/>
       <c r="K375" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="376" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H376" s="2"/>
+      <c r="I376" s="1"/>
+      <c r="K376" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="376" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B376" t="s">
-        <v>22</v>
-      </c>
-      <c r="C376">
-        <v>3494</v>
-      </c>
-      <c r="D376" t="s">
-        <v>61</v>
-      </c>
-      <c r="F376" t="s">
-        <v>84</v>
-      </c>
-      <c r="G376" t="s">
-        <v>10</v>
-      </c>
-      <c r="H376" s="2">
-        <v>7.1064814814814819E-3</v>
-      </c>
-      <c r="I376" s="1">
-        <v>46118.758796296293</v>
-      </c>
-      <c r="J376">
-        <v>1</v>
-      </c>
-      <c r="K376" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="377" spans="2:11" x14ac:dyDescent="0.25">
@@ -10692,22 +10670,22 @@
         <v>22</v>
       </c>
       <c r="C377">
-        <v>3523</v>
+        <v>3494</v>
       </c>
       <c r="D377" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F377" t="s">
         <v>84</v>
       </c>
       <c r="G377" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H377" s="2">
-        <v>0</v>
+        <v>7.1064814814814819E-3</v>
       </c>
       <c r="I377" s="1">
-        <v>46118.75949074074</v>
+        <v>46118.758796296293</v>
       </c>
       <c r="J377">
         <v>1</v>
@@ -10721,25 +10699,25 @@
         <v>22</v>
       </c>
       <c r="C378">
-        <v>3504</v>
+        <v>3523</v>
       </c>
       <c r="D378" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F378" t="s">
         <v>84</v>
       </c>
       <c r="G378" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H378" s="2">
-        <v>0</v>
+        <v>7.5925925925925926E-3</v>
       </c>
       <c r="I378" s="1">
-        <v>46118.760185185187</v>
+        <v>46118.75949074074</v>
       </c>
       <c r="J378">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K378" t="s">
         <v>11</v>
@@ -10750,10 +10728,10 @@
         <v>22</v>
       </c>
       <c r="C379">
-        <v>3498</v>
+        <v>3504</v>
       </c>
       <c r="D379" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F379" t="s">
         <v>84</v>
@@ -10762,13 +10740,13 @@
         <v>10</v>
       </c>
       <c r="H379" s="2">
-        <v>8.1250000000000003E-3</v>
+        <v>1.0763888888888889E-2</v>
       </c>
       <c r="I379" s="1">
         <v>46118.760185185187</v>
       </c>
       <c r="J379">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K379" t="s">
         <v>11</v>
@@ -10779,22 +10757,22 @@
         <v>22</v>
       </c>
       <c r="C380">
-        <v>3344</v>
+        <v>3498</v>
       </c>
       <c r="D380" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F380" t="s">
         <v>84</v>
       </c>
       <c r="G380" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H380" s="2">
-        <v>4.6296296296296294E-5</v>
+        <v>8.1250000000000003E-3</v>
       </c>
       <c r="I380" s="1">
-        <v>46118.760879629626</v>
+        <v>46118.760185185187</v>
       </c>
       <c r="J380">
         <v>1</v>
@@ -10804,39 +10782,39 @@
       </c>
     </row>
     <row r="381" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H381" s="2"/>
-      <c r="I381" s="1"/>
+      <c r="B381" t="s">
+        <v>22</v>
+      </c>
+      <c r="C381">
+        <v>3344</v>
+      </c>
+      <c r="D381" t="s">
+        <v>66</v>
+      </c>
+      <c r="F381" t="s">
+        <v>84</v>
+      </c>
+      <c r="G381" t="s">
+        <v>12</v>
+      </c>
+      <c r="H381" s="2">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="I381" s="1">
+        <v>46118.760879629626</v>
+      </c>
+      <c r="J381">
+        <v>1</v>
+      </c>
       <c r="K381" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H382" s="2"/>
+      <c r="I382" s="1"/>
+      <c r="K382" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B382" t="s">
-        <v>22</v>
-      </c>
-      <c r="C382">
-        <v>3515</v>
-      </c>
-      <c r="D382" t="s">
-        <v>67</v>
-      </c>
-      <c r="F382" t="s">
-        <v>84</v>
-      </c>
-      <c r="G382" t="s">
-        <v>13</v>
-      </c>
-      <c r="H382" s="2">
-        <v>0</v>
-      </c>
-      <c r="I382" s="1">
-        <v>46118.760879629626</v>
-      </c>
-      <c r="J382">
-        <v>1</v>
-      </c>
-      <c r="K382" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="383" spans="2:11" x14ac:dyDescent="0.25">
@@ -10844,10 +10822,10 @@
         <v>22</v>
       </c>
       <c r="C383">
-        <v>3522</v>
+        <v>3515</v>
       </c>
       <c r="D383" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F383" t="s">
         <v>84</v>
@@ -10859,10 +10837,10 @@
         <v>0</v>
       </c>
       <c r="I383" s="1">
-        <v>46118.761574074073</v>
+        <v>46118.760879629626</v>
       </c>
       <c r="J383">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K383" t="s">
         <v>11</v>
@@ -10873,25 +10851,25 @@
         <v>22</v>
       </c>
       <c r="C384">
-        <v>3751</v>
+        <v>3522</v>
       </c>
       <c r="D384" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F384" t="s">
         <v>84</v>
       </c>
       <c r="G384" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H384" s="2">
-        <v>0</v>
+        <v>7.5925925925925926E-3</v>
       </c>
       <c r="I384" s="1">
-        <v>46118.76226851852</v>
+        <v>46118.761574074073</v>
       </c>
       <c r="J384">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K384" t="s">
         <v>11</v>
@@ -10902,10 +10880,10 @@
         <v>22</v>
       </c>
       <c r="C385">
-        <v>3662</v>
+        <v>3751</v>
       </c>
       <c r="D385" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F385" t="s">
         <v>84</v>
@@ -10920,7 +10898,7 @@
         <v>46118.76226851852</v>
       </c>
       <c r="J385">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K385" t="s">
         <v>11</v>
@@ -10931,25 +10909,25 @@
         <v>22</v>
       </c>
       <c r="C386">
-        <v>3517</v>
+        <v>3662</v>
       </c>
       <c r="D386" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F386" t="s">
         <v>84</v>
       </c>
       <c r="G386" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H386" s="2">
-        <v>7.2800925925925923E-3</v>
+        <v>0</v>
       </c>
       <c r="I386" s="1">
-        <v>46118.762962962966</v>
+        <v>46118.76226851852</v>
       </c>
       <c r="J386">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K386" t="s">
         <v>11</v>
@@ -10960,25 +10938,25 @@
         <v>22</v>
       </c>
       <c r="C387">
-        <v>3503</v>
+        <v>3517</v>
       </c>
       <c r="D387" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F387" t="s">
         <v>84</v>
       </c>
       <c r="G387" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H387" s="2">
-        <v>0</v>
+        <v>7.2800925925925923E-3</v>
       </c>
       <c r="I387" s="1">
         <v>46118.762962962966</v>
       </c>
       <c r="J387">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K387" t="s">
         <v>11</v>
@@ -10989,10 +10967,10 @@
         <v>22</v>
       </c>
       <c r="C388">
-        <v>3652</v>
+        <v>3503</v>
       </c>
       <c r="D388" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F388" t="s">
         <v>84</v>
@@ -11004,10 +10982,10 @@
         <v>0</v>
       </c>
       <c r="I388" s="1">
-        <v>46118.763657407406</v>
+        <v>46118.762962962966</v>
       </c>
       <c r="J388">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K388" t="s">
         <v>11</v>
@@ -11018,25 +10996,25 @@
         <v>22</v>
       </c>
       <c r="C389">
-        <v>3509</v>
+        <v>3652</v>
       </c>
       <c r="D389" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F389" t="s">
         <v>84</v>
       </c>
       <c r="G389" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H389" s="2">
-        <v>0</v>
+        <v>1.0462962962962962E-2</v>
       </c>
       <c r="I389" s="1">
-        <v>46118.764351851853</v>
+        <v>46118.763657407406</v>
       </c>
       <c r="J389">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K389" t="s">
         <v>11</v>
@@ -11047,25 +11025,25 @@
         <v>22</v>
       </c>
       <c r="C390">
-        <v>3512</v>
+        <v>3509</v>
       </c>
       <c r="D390" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F390" t="s">
         <v>84</v>
       </c>
       <c r="G390" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H390" s="2">
-        <v>7.3726851851851852E-3</v>
+        <v>0</v>
       </c>
       <c r="I390" s="1">
-        <v>46118.765046296299</v>
+        <v>46118.764351851853</v>
       </c>
       <c r="J390">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K390" t="s">
         <v>11</v>
@@ -11076,10 +11054,10 @@
         <v>22</v>
       </c>
       <c r="C391">
-        <v>3489</v>
+        <v>3512</v>
       </c>
       <c r="D391" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F391" t="s">
         <v>84</v>
@@ -11088,13 +11066,13 @@
         <v>10</v>
       </c>
       <c r="H391" s="2">
-        <v>7.5462962962962966E-3</v>
+        <v>7.3726851851851852E-3</v>
       </c>
       <c r="I391" s="1">
         <v>46118.765046296299</v>
       </c>
       <c r="J391">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K391" t="s">
         <v>11</v>
@@ -11105,10 +11083,10 @@
         <v>22</v>
       </c>
       <c r="C392">
-        <v>3266</v>
+        <v>3489</v>
       </c>
       <c r="D392" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F392" t="s">
         <v>84</v>
@@ -11117,13 +11095,13 @@
         <v>10</v>
       </c>
       <c r="H392" s="2">
-        <v>7.3842592592592597E-3</v>
+        <v>7.5462962962962966E-3</v>
       </c>
       <c r="I392" s="1">
-        <v>46118.765740740739</v>
+        <v>46118.765046296299</v>
       </c>
       <c r="J392">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K392" t="s">
         <v>11</v>
@@ -11134,10 +11112,10 @@
         <v>22</v>
       </c>
       <c r="C393">
-        <v>3492</v>
+        <v>3266</v>
       </c>
       <c r="D393" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F393" t="s">
         <v>84</v>
@@ -11146,13 +11124,13 @@
         <v>10</v>
       </c>
       <c r="H393" s="2">
-        <v>9.8958333333333329E-3</v>
+        <v>7.3842592592592597E-3</v>
       </c>
       <c r="I393" s="1">
-        <v>46118.766435185185</v>
+        <v>46118.765740740739</v>
       </c>
       <c r="J393">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K393" t="s">
         <v>11</v>
@@ -11163,19 +11141,19 @@
         <v>22</v>
       </c>
       <c r="C394">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="D394" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F394" t="s">
         <v>84</v>
       </c>
       <c r="G394" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H394" s="2">
-        <v>0</v>
+        <v>9.8958333333333329E-3</v>
       </c>
       <c r="I394" s="1">
         <v>46118.766435185185</v>
@@ -11192,64 +11170,64 @@
         <v>22</v>
       </c>
       <c r="C395">
-        <v>3505</v>
+        <v>3493</v>
       </c>
       <c r="D395" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F395" t="s">
         <v>84</v>
       </c>
       <c r="G395" t="s">
+        <v>13</v>
+      </c>
+      <c r="H395" s="2">
+        <v>0</v>
+      </c>
+      <c r="I395" s="1">
+        <v>46118.766435185185</v>
+      </c>
+      <c r="J395">
+        <v>2</v>
+      </c>
+      <c r="K395" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="396" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B396" t="s">
+        <v>22</v>
+      </c>
+      <c r="C396">
+        <v>3505</v>
+      </c>
+      <c r="D396" t="s">
+        <v>80</v>
+      </c>
+      <c r="F396" t="s">
+        <v>84</v>
+      </c>
+      <c r="G396" t="s">
         <v>12</v>
       </c>
-      <c r="H395" s="2">
+      <c r="H396" s="2">
         <v>6.145833333333333E-3</v>
       </c>
-      <c r="I395" s="1">
+      <c r="I396" s="1">
         <v>46118.767129629632</v>
       </c>
-      <c r="J395">
+      <c r="J396">
         <v>0</v>
       </c>
-      <c r="K395" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="396" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H396" s="2"/>
-      <c r="I396" s="1"/>
       <c r="K396" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="397" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H397" s="2"/>
+      <c r="I397" s="1"/>
+      <c r="K397" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="397" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B397" t="s">
-        <v>22</v>
-      </c>
-      <c r="C397">
-        <v>3861</v>
-      </c>
-      <c r="D397" t="s">
-        <v>81</v>
-      </c>
-      <c r="F397" t="s">
-        <v>84</v>
-      </c>
-      <c r="G397" t="s">
-        <v>10</v>
-      </c>
-      <c r="H397" s="2">
-        <v>7.3611111111111108E-3</v>
-      </c>
-      <c r="I397" s="1">
-        <v>46118.767824074072</v>
-      </c>
-      <c r="J397">
-        <v>1</v>
-      </c>
-      <c r="K397" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="398" spans="2:11" x14ac:dyDescent="0.25">
@@ -11257,19 +11235,19 @@
         <v>22</v>
       </c>
       <c r="C398">
-        <v>5205</v>
+        <v>3861</v>
       </c>
       <c r="D398" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F398" t="s">
         <v>84</v>
       </c>
       <c r="G398" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H398" s="2">
-        <v>0</v>
+        <v>7.3611111111111108E-3</v>
       </c>
       <c r="I398" s="1">
         <v>46118.767824074072</v>
@@ -11286,33 +11264,58 @@
         <v>22</v>
       </c>
       <c r="C399">
-        <v>3538</v>
+        <v>5205</v>
       </c>
       <c r="D399" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F399" t="s">
         <v>84</v>
       </c>
       <c r="G399" t="s">
+        <v>13</v>
+      </c>
+      <c r="H399" s="2">
+        <v>0</v>
+      </c>
+      <c r="I399" s="1">
+        <v>46118.767824074072</v>
+      </c>
+      <c r="J399">
+        <v>2</v>
+      </c>
+      <c r="K399" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="400" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B400" t="s">
+        <v>22</v>
+      </c>
+      <c r="C400">
+        <v>3538</v>
+      </c>
+      <c r="D400" t="s">
+        <v>82</v>
+      </c>
+      <c r="F400" t="s">
+        <v>84</v>
+      </c>
+      <c r="G400" t="s">
         <v>10</v>
       </c>
-      <c r="H399" s="2">
+      <c r="H400" s="2">
         <v>9.8032407407407408E-3</v>
       </c>
-      <c r="I399" s="1">
+      <c r="I400" s="1">
         <v>46118.768518518518</v>
       </c>
-      <c r="J399">
+      <c r="J400">
         <v>0</v>
       </c>
-      <c r="K399" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="400" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H400" s="2"/>
-      <c r="I400" s="1"/>
+      <c r="K400" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="401" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H401" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Fiore and Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FDACB3-C768-4742-B11D-9308C96FE3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F3B295-04D2-4410-BB73-177AB1597A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -9044,7 +9044,7 @@
         <v>10</v>
       </c>
       <c r="H319" s="2">
-        <v>5.9837962962962961E-3</v>
+        <v>6.1111111111111114E-3</v>
       </c>
       <c r="I319" s="1">
         <v>46083.769560185188</v>
@@ -9773,16 +9773,16 @@
         <v>84</v>
       </c>
       <c r="G345" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H345" s="2">
-        <v>0</v>
+        <v>2.7719907407407408E-2</v>
       </c>
       <c r="I345" s="1">
         <v>46118.767708333333</v>
       </c>
       <c r="J345">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K345" t="s">
         <v>11</v>
@@ -9840,7 +9840,7 @@
         <v>46118.76840277778</v>
       </c>
       <c r="J347">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K347" t="s">
         <v>11</v>
@@ -9869,7 +9869,7 @@
         <v>46118.76840277778</v>
       </c>
       <c r="J348">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K348" t="s">
         <v>11</v>
@@ -9898,7 +9898,7 @@
         <v>46118.769097222219</v>
       </c>
       <c r="J349">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K349" t="s">
         <v>11</v>
@@ -9927,7 +9927,7 @@
         <v>46118.769791666666</v>
       </c>
       <c r="J350">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K350" t="s">
         <v>11</v>
@@ -9985,7 +9985,7 @@
         <v>46118.770486111112</v>
       </c>
       <c r="J352">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K352" t="s">
         <v>11</v>
@@ -10005,16 +10005,16 @@
         <v>84</v>
       </c>
       <c r="G353" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H353" s="2">
-        <v>0</v>
+        <v>9.2013888888888892E-3</v>
       </c>
       <c r="I353" s="1">
         <v>46118.770486111112</v>
       </c>
       <c r="J353">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K353" t="s">
         <v>11</v>
@@ -10063,16 +10063,16 @@
         <v>84</v>
       </c>
       <c r="G355" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H355" s="2">
-        <v>0</v>
+        <v>4.1435185185185186E-3</v>
       </c>
       <c r="I355" s="1">
         <v>46118.771874999999</v>
       </c>
       <c r="J355">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K355" t="s">
         <v>11</v>
@@ -10159,7 +10159,7 @@
         <v>46118.773263888892</v>
       </c>
       <c r="J358">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K358" t="s">
         <v>11</v>
@@ -10217,7 +10217,7 @@
         <v>46118.752546296295</v>
       </c>
       <c r="J360">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K360" t="s">
         <v>11</v>
@@ -10246,7 +10246,7 @@
         <v>46118.752546296295</v>
       </c>
       <c r="J361">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K361" t="s">
         <v>11</v>
@@ -10266,16 +10266,16 @@
         <v>84</v>
       </c>
       <c r="G362" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H362" s="2">
-        <v>0</v>
+        <v>7.6967592592592591E-3</v>
       </c>
       <c r="I362" s="1">
         <v>46118.753240740742</v>
       </c>
       <c r="J362">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K362" t="s">
         <v>11</v>
@@ -10304,7 +10304,7 @@
         <v>46118.753240740742</v>
       </c>
       <c r="J363">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K363" t="s">
         <v>11</v>
@@ -10324,16 +10324,16 @@
         <v>84</v>
       </c>
       <c r="G364" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H364" s="2">
-        <v>0</v>
+        <v>9.7106481481481488E-3</v>
       </c>
       <c r="I364" s="1">
         <v>46118.753935185188</v>
       </c>
       <c r="J364">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K364" t="s">
         <v>11</v>
@@ -10391,7 +10391,7 @@
         <v>46118.754629629628</v>
       </c>
       <c r="J366">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K366" t="s">
         <v>11</v>
@@ -10420,7 +10420,7 @@
         <v>46118.755324074074</v>
       </c>
       <c r="J367">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K367" t="s">
         <v>11</v>
@@ -10440,16 +10440,16 @@
         <v>84</v>
       </c>
       <c r="G368" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H368" s="2">
-        <v>0</v>
+        <v>7.3379629629629628E-3</v>
       </c>
       <c r="I368" s="1">
         <v>46118.756018518521</v>
       </c>
       <c r="J368">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K368" t="s">
         <v>11</v>
@@ -10594,7 +10594,7 @@
         <v>46118.758101851854</v>
       </c>
       <c r="J373">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K373" t="s">
         <v>11</v>
@@ -10840,7 +10840,7 @@
         <v>46118.760879629626</v>
       </c>
       <c r="J383">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K383" t="s">
         <v>11</v>
@@ -10898,7 +10898,7 @@
         <v>46118.76226851852</v>
       </c>
       <c r="J385">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K385" t="s">
         <v>11</v>
@@ -10927,7 +10927,7 @@
         <v>46118.76226851852</v>
       </c>
       <c r="J386">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K386" t="s">
         <v>11</v>
@@ -10985,7 +10985,7 @@
         <v>46118.762962962966</v>
       </c>
       <c r="J388">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K388" t="s">
         <v>11</v>
@@ -11043,7 +11043,7 @@
         <v>46118.764351851853</v>
       </c>
       <c r="J390">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K390" t="s">
         <v>11</v>
@@ -11188,7 +11188,7 @@
         <v>46118.766435185185</v>
       </c>
       <c r="J395">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K395" t="s">
         <v>11</v>
@@ -11282,7 +11282,7 @@
         <v>46118.767824074072</v>
       </c>
       <c r="J399">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K399" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Fiore and Sons\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Fiore and Sons - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F3B295-04D2-4410-BB73-177AB1597A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D29EAF-1FDE-4337-B93F-B1FD540317DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3510" yWindow="1635" windowWidth="27840" windowHeight="14565" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -9840,7 +9840,7 @@
         <v>46118.76840277778</v>
       </c>
       <c r="J347">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K347" t="s">
         <v>11</v>
@@ -9869,7 +9869,7 @@
         <v>46118.76840277778</v>
       </c>
       <c r="J348">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K348" t="s">
         <v>11</v>
@@ -9898,7 +9898,7 @@
         <v>46118.769097222219</v>
       </c>
       <c r="J349">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K349" t="s">
         <v>11</v>
@@ -9927,7 +9927,7 @@
         <v>46118.769791666666</v>
       </c>
       <c r="J350">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K350" t="s">
         <v>11</v>
@@ -9985,7 +9985,7 @@
         <v>46118.770486111112</v>
       </c>
       <c r="J352">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K352" t="s">
         <v>11</v>
@@ -10159,7 +10159,7 @@
         <v>46118.773263888892</v>
       </c>
       <c r="J358">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K358" t="s">
         <v>11</v>
@@ -10217,7 +10217,7 @@
         <v>46118.752546296295</v>
       </c>
       <c r="J360">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K360" t="s">
         <v>11</v>
@@ -10246,7 +10246,7 @@
         <v>46118.752546296295</v>
       </c>
       <c r="J361">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K361" t="s">
         <v>11</v>
@@ -10295,16 +10295,16 @@
         <v>84</v>
       </c>
       <c r="G363" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H363" s="2">
-        <v>0</v>
+        <v>9.6296296296296303E-3</v>
       </c>
       <c r="I363" s="1">
         <v>46118.753240740742</v>
       </c>
       <c r="J363">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K363" t="s">
         <v>11</v>
@@ -10391,7 +10391,7 @@
         <v>46118.754629629628</v>
       </c>
       <c r="J366">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K366" t="s">
         <v>11</v>
@@ -10420,7 +10420,7 @@
         <v>46118.755324074074</v>
       </c>
       <c r="J367">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K367" t="s">
         <v>11</v>
@@ -10594,7 +10594,7 @@
         <v>46118.758101851854</v>
       </c>
       <c r="J373">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K373" t="s">
         <v>11</v>
@@ -10840,7 +10840,7 @@
         <v>46118.760879629626</v>
       </c>
       <c r="J383">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K383" t="s">
         <v>11</v>
@@ -10898,7 +10898,7 @@
         <v>46118.76226851852</v>
       </c>
       <c r="J385">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K385" t="s">
         <v>11</v>
@@ -10927,7 +10927,7 @@
         <v>46118.76226851852</v>
       </c>
       <c r="J386">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K386" t="s">
         <v>11</v>
@@ -10985,7 +10985,7 @@
         <v>46118.762962962966</v>
       </c>
       <c r="J388">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K388" t="s">
         <v>11</v>
@@ -11043,7 +11043,7 @@
         <v>46118.764351851853</v>
       </c>
       <c r="J390">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K390" t="s">
         <v>11</v>
@@ -11188,7 +11188,7 @@
         <v>46118.766435185185</v>
       </c>
       <c r="J395">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K395" t="s">
         <v>11</v>
@@ -11273,16 +11273,16 @@
         <v>84</v>
       </c>
       <c r="G399" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H399" s="2">
-        <v>0</v>
+        <v>7.6273148148148151E-3</v>
       </c>
       <c r="I399" s="1">
         <v>46118.767824074072</v>
       </c>
       <c r="J399">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K399" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Fiore and Sons - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D29EAF-1FDE-4337-B93F-B1FD540317DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47721AC2-44E0-4F76-8F1E-51F99CA91770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1635" windowWidth="27840" windowHeight="14565" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="88">
   <si>
     <t>Company Name</t>
   </si>
@@ -294,6 +294,15 @@
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>Rules for Safe Driving</t>
+  </si>
+  <si>
+    <t>Aldo Salinas</t>
+  </si>
+  <si>
+    <t>Richard Fleckenstein</t>
   </si>
 </sst>
 </file>
@@ -11317,323 +11326,1794 @@
         <v>11</v>
       </c>
     </row>
-    <row r="401" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H401" s="2"/>
-      <c r="I401" s="1"/>
-    </row>
-    <row r="402" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H402" s="2"/>
-      <c r="I402" s="1"/>
-    </row>
-    <row r="403" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H403" s="2"/>
-      <c r="I403" s="1"/>
-    </row>
-    <row r="404" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H404" s="2"/>
-      <c r="I404" s="1"/>
-    </row>
-    <row r="405" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B401" t="s">
+        <v>22</v>
+      </c>
+      <c r="C401">
+        <v>3200</v>
+      </c>
+      <c r="D401" t="s">
+        <v>23</v>
+      </c>
+      <c r="F401" t="s">
+        <v>85</v>
+      </c>
+      <c r="G401" t="s">
+        <v>13</v>
+      </c>
+      <c r="H401" s="2">
+        <v>0</v>
+      </c>
+      <c r="I401" s="1">
+        <v>46146.67083333333</v>
+      </c>
+      <c r="J401">
+        <v>0</v>
+      </c>
+      <c r="K401" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="402" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B402" t="s">
+        <v>22</v>
+      </c>
+      <c r="C402">
+        <v>3501</v>
+      </c>
+      <c r="D402" t="s">
+        <v>24</v>
+      </c>
+      <c r="F402" t="s">
+        <v>85</v>
+      </c>
+      <c r="G402" t="s">
+        <v>10</v>
+      </c>
+      <c r="H402" s="2">
+        <v>4.31712962962963E-3</v>
+      </c>
+      <c r="I402" s="1">
+        <v>46146.671527777777</v>
+      </c>
+      <c r="J402">
+        <v>0</v>
+      </c>
+      <c r="K402" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="403" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B403" t="s">
+        <v>22</v>
+      </c>
+      <c r="C403">
+        <v>4915</v>
+      </c>
+      <c r="D403" t="s">
+        <v>25</v>
+      </c>
+      <c r="F403" t="s">
+        <v>85</v>
+      </c>
+      <c r="G403" t="s">
+        <v>13</v>
+      </c>
+      <c r="H403" s="2">
+        <v>0</v>
+      </c>
+      <c r="I403" s="1">
+        <v>46146.672222222223</v>
+      </c>
+      <c r="J403">
+        <v>0</v>
+      </c>
+      <c r="K403" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="404" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B404" t="s">
+        <v>22</v>
+      </c>
+      <c r="C404">
+        <v>5524</v>
+      </c>
+      <c r="D404" t="s">
+        <v>86</v>
+      </c>
+      <c r="F404" t="s">
+        <v>85</v>
+      </c>
+      <c r="G404" t="s">
+        <v>12</v>
+      </c>
+      <c r="H404" s="2">
+        <v>0</v>
+      </c>
+      <c r="I404" s="1">
+        <v>46146.672222222223</v>
+      </c>
+      <c r="J404">
+        <v>0</v>
+      </c>
+      <c r="K404" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="405" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H405" s="2"/>
       <c r="I405" s="1"/>
-    </row>
-    <row r="406" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H406" s="2"/>
-      <c r="I406" s="1"/>
-    </row>
-    <row r="407" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H407" s="2"/>
-      <c r="I407" s="1"/>
-    </row>
-    <row r="408" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H408" s="2"/>
-      <c r="I408" s="1"/>
-    </row>
-    <row r="409" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H409" s="2"/>
-      <c r="I409" s="1"/>
-    </row>
-    <row r="410" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H410" s="2"/>
-      <c r="I410" s="1"/>
-    </row>
-    <row r="411" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H411" s="2"/>
-      <c r="I411" s="1"/>
-    </row>
-    <row r="412" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H412" s="2"/>
-      <c r="I412" s="1"/>
-    </row>
-    <row r="413" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H413" s="2"/>
-      <c r="I413" s="1"/>
-    </row>
-    <row r="414" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H414" s="2"/>
-      <c r="I414" s="1"/>
-    </row>
-    <row r="415" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K405" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="406" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B406" t="s">
+        <v>22</v>
+      </c>
+      <c r="C406">
+        <v>3360</v>
+      </c>
+      <c r="D406" t="s">
+        <v>26</v>
+      </c>
+      <c r="F406" t="s">
+        <v>85</v>
+      </c>
+      <c r="G406" t="s">
+        <v>13</v>
+      </c>
+      <c r="H406" s="2">
+        <v>0</v>
+      </c>
+      <c r="I406" s="1">
+        <v>46146.67291666667</v>
+      </c>
+      <c r="J406">
+        <v>0</v>
+      </c>
+      <c r="K406" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="407" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B407" t="s">
+        <v>22</v>
+      </c>
+      <c r="C407">
+        <v>3521</v>
+      </c>
+      <c r="D407" t="s">
+        <v>27</v>
+      </c>
+      <c r="F407" t="s">
+        <v>85</v>
+      </c>
+      <c r="G407" t="s">
+        <v>13</v>
+      </c>
+      <c r="H407" s="2">
+        <v>0</v>
+      </c>
+      <c r="I407" s="1">
+        <v>46146.673611111109</v>
+      </c>
+      <c r="J407">
+        <v>0</v>
+      </c>
+      <c r="K407" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="408" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B408" t="s">
+        <v>22</v>
+      </c>
+      <c r="C408">
+        <v>3479</v>
+      </c>
+      <c r="D408" t="s">
+        <v>28</v>
+      </c>
+      <c r="F408" t="s">
+        <v>85</v>
+      </c>
+      <c r="G408" t="s">
+        <v>13</v>
+      </c>
+      <c r="H408" s="2">
+        <v>0</v>
+      </c>
+      <c r="I408" s="1">
+        <v>46146.673611111109</v>
+      </c>
+      <c r="J408">
+        <v>0</v>
+      </c>
+      <c r="K408" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="409" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B409" t="s">
+        <v>22</v>
+      </c>
+      <c r="C409">
+        <v>3526</v>
+      </c>
+      <c r="D409" t="s">
+        <v>29</v>
+      </c>
+      <c r="F409" t="s">
+        <v>85</v>
+      </c>
+      <c r="G409" t="s">
+        <v>13</v>
+      </c>
+      <c r="H409" s="2">
+        <v>0</v>
+      </c>
+      <c r="I409" s="1">
+        <v>46146.674305555556</v>
+      </c>
+      <c r="J409">
+        <v>0</v>
+      </c>
+      <c r="K409" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="410" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B410" t="s">
+        <v>22</v>
+      </c>
+      <c r="C410">
+        <v>4917</v>
+      </c>
+      <c r="D410" t="s">
+        <v>30</v>
+      </c>
+      <c r="F410" t="s">
+        <v>85</v>
+      </c>
+      <c r="G410" t="s">
+        <v>13</v>
+      </c>
+      <c r="H410" s="2">
+        <v>0</v>
+      </c>
+      <c r="I410" s="1">
+        <v>46146.675000000003</v>
+      </c>
+      <c r="J410">
+        <v>0</v>
+      </c>
+      <c r="K410" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="411" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B411" t="s">
+        <v>22</v>
+      </c>
+      <c r="C411">
+        <v>3524</v>
+      </c>
+      <c r="D411" t="s">
+        <v>31</v>
+      </c>
+      <c r="F411" t="s">
+        <v>85</v>
+      </c>
+      <c r="G411" t="s">
+        <v>13</v>
+      </c>
+      <c r="H411" s="2">
+        <v>0</v>
+      </c>
+      <c r="I411" s="1">
+        <v>46146.675000000003</v>
+      </c>
+      <c r="J411">
+        <v>0</v>
+      </c>
+      <c r="K411" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="412" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B412" t="s">
+        <v>22</v>
+      </c>
+      <c r="C412">
+        <v>3804</v>
+      </c>
+      <c r="D412" t="s">
+        <v>32</v>
+      </c>
+      <c r="F412" t="s">
+        <v>85</v>
+      </c>
+      <c r="G412" t="s">
+        <v>13</v>
+      </c>
+      <c r="H412" s="2">
+        <v>0</v>
+      </c>
+      <c r="I412" s="1">
+        <v>46146.675694444442</v>
+      </c>
+      <c r="J412">
+        <v>0</v>
+      </c>
+      <c r="K412" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="413" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B413" t="s">
+        <v>22</v>
+      </c>
+      <c r="C413">
+        <v>3495</v>
+      </c>
+      <c r="D413" t="s">
+        <v>33</v>
+      </c>
+      <c r="F413" t="s">
+        <v>85</v>
+      </c>
+      <c r="G413" t="s">
+        <v>10</v>
+      </c>
+      <c r="H413" s="2">
+        <v>4.43287037037037E-3</v>
+      </c>
+      <c r="I413" s="1">
+        <v>46146.676388888889</v>
+      </c>
+      <c r="J413">
+        <v>0</v>
+      </c>
+      <c r="K413" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="414" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B414" t="s">
+        <v>22</v>
+      </c>
+      <c r="C414">
+        <v>3739</v>
+      </c>
+      <c r="D414" t="s">
+        <v>34</v>
+      </c>
+      <c r="F414" t="s">
+        <v>85</v>
+      </c>
+      <c r="G414" t="s">
+        <v>12</v>
+      </c>
+      <c r="H414" s="2">
+        <v>5.2430555555555555E-3</v>
+      </c>
+      <c r="I414" s="1">
+        <v>46146.677083333336</v>
+      </c>
+      <c r="J414">
+        <v>0</v>
+      </c>
+      <c r="K414" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="415" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H415" s="2"/>
       <c r="I415" s="1"/>
-    </row>
-    <row r="416" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H416" s="2"/>
-      <c r="I416" s="1"/>
-    </row>
-    <row r="417" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H417" s="2"/>
-      <c r="I417" s="1"/>
-    </row>
-    <row r="418" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H418" s="2"/>
-      <c r="I418" s="1"/>
-    </row>
-    <row r="419" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H419" s="2"/>
-      <c r="I419" s="1"/>
-    </row>
-    <row r="420" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H420" s="2"/>
-      <c r="I420" s="1"/>
-    </row>
-    <row r="421" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K415" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="416" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B416" t="s">
+        <v>22</v>
+      </c>
+      <c r="C416">
+        <v>3520</v>
+      </c>
+      <c r="D416" t="s">
+        <v>35</v>
+      </c>
+      <c r="F416" t="s">
+        <v>85</v>
+      </c>
+      <c r="G416" t="s">
+        <v>13</v>
+      </c>
+      <c r="H416" s="2">
+        <v>0</v>
+      </c>
+      <c r="I416" s="1">
+        <v>46146.677083333336</v>
+      </c>
+      <c r="J416">
+        <v>0</v>
+      </c>
+      <c r="K416" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="417" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B417" t="s">
+        <v>22</v>
+      </c>
+      <c r="C417">
+        <v>3486</v>
+      </c>
+      <c r="D417" t="s">
+        <v>36</v>
+      </c>
+      <c r="F417" t="s">
+        <v>85</v>
+      </c>
+      <c r="G417" t="s">
+        <v>13</v>
+      </c>
+      <c r="H417" s="2">
+        <v>0</v>
+      </c>
+      <c r="I417" s="1">
+        <v>46146.677777777775</v>
+      </c>
+      <c r="J417">
+        <v>0</v>
+      </c>
+      <c r="K417" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="418" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B418" t="s">
+        <v>22</v>
+      </c>
+      <c r="C418">
+        <v>3886</v>
+      </c>
+      <c r="D418" t="s">
+        <v>37</v>
+      </c>
+      <c r="F418" t="s">
+        <v>85</v>
+      </c>
+      <c r="G418" t="s">
+        <v>13</v>
+      </c>
+      <c r="H418" s="2">
+        <v>0</v>
+      </c>
+      <c r="I418" s="1">
+        <v>46146.678472222222</v>
+      </c>
+      <c r="J418">
+        <v>0</v>
+      </c>
+      <c r="K418" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="419" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B419" t="s">
+        <v>22</v>
+      </c>
+      <c r="C419">
+        <v>3397</v>
+      </c>
+      <c r="D419" t="s">
+        <v>38</v>
+      </c>
+      <c r="F419" t="s">
+        <v>85</v>
+      </c>
+      <c r="G419" t="s">
+        <v>13</v>
+      </c>
+      <c r="H419" s="2">
+        <v>0</v>
+      </c>
+      <c r="I419" s="1">
+        <v>46146.678472222222</v>
+      </c>
+      <c r="J419">
+        <v>0</v>
+      </c>
+      <c r="K419" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="420" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B420" t="s">
+        <v>22</v>
+      </c>
+      <c r="C420">
+        <v>3765</v>
+      </c>
+      <c r="D420" t="s">
+        <v>39</v>
+      </c>
+      <c r="F420" t="s">
+        <v>85</v>
+      </c>
+      <c r="G420" t="s">
+        <v>14</v>
+      </c>
+      <c r="H420" s="2">
+        <v>0</v>
+      </c>
+      <c r="I420" s="1">
+        <v>46146.679166666669</v>
+      </c>
+      <c r="J420">
+        <v>0</v>
+      </c>
+      <c r="K420" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="421" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H421" s="2"/>
       <c r="I421" s="1"/>
-    </row>
-    <row r="422" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H422" s="2"/>
-      <c r="I422" s="1"/>
-    </row>
-    <row r="423" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H423" s="2"/>
-      <c r="I423" s="1"/>
-    </row>
-    <row r="424" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H424" s="2"/>
-      <c r="I424" s="1"/>
-    </row>
-    <row r="425" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H425" s="2"/>
-      <c r="I425" s="1"/>
-    </row>
-    <row r="426" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H426" s="2"/>
-      <c r="I426" s="1"/>
-    </row>
-    <row r="427" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H427" s="2"/>
-      <c r="I427" s="1"/>
-    </row>
-    <row r="428" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H428" s="2"/>
-      <c r="I428" s="1"/>
-    </row>
-    <row r="429" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K421" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="422" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B422" t="s">
+        <v>22</v>
+      </c>
+      <c r="C422">
+        <v>3496</v>
+      </c>
+      <c r="D422" t="s">
+        <v>40</v>
+      </c>
+      <c r="F422" t="s">
+        <v>85</v>
+      </c>
+      <c r="G422" t="s">
+        <v>13</v>
+      </c>
+      <c r="H422" s="2">
+        <v>0</v>
+      </c>
+      <c r="I422" s="1">
+        <v>46146.679861111108</v>
+      </c>
+      <c r="J422">
+        <v>0</v>
+      </c>
+      <c r="K422" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="423" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B423" t="s">
+        <v>22</v>
+      </c>
+      <c r="C423">
+        <v>3525</v>
+      </c>
+      <c r="D423" t="s">
+        <v>42</v>
+      </c>
+      <c r="F423" t="s">
+        <v>85</v>
+      </c>
+      <c r="G423" t="s">
+        <v>10</v>
+      </c>
+      <c r="H423" s="2">
+        <v>5.5208333333333333E-3</v>
+      </c>
+      <c r="I423" s="1">
+        <v>46146.680555555555</v>
+      </c>
+      <c r="J423">
+        <v>0</v>
+      </c>
+      <c r="K423" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="424" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B424" t="s">
+        <v>22</v>
+      </c>
+      <c r="C424">
+        <v>3513</v>
+      </c>
+      <c r="D424" t="s">
+        <v>43</v>
+      </c>
+      <c r="F424" t="s">
+        <v>85</v>
+      </c>
+      <c r="G424" t="s">
+        <v>13</v>
+      </c>
+      <c r="H424" s="2">
+        <v>0</v>
+      </c>
+      <c r="I424" s="1">
+        <v>46146.680555555555</v>
+      </c>
+      <c r="J424">
+        <v>0</v>
+      </c>
+      <c r="K424" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="425" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B425" t="s">
+        <v>22</v>
+      </c>
+      <c r="C425">
+        <v>3508</v>
+      </c>
+      <c r="D425" t="s">
+        <v>44</v>
+      </c>
+      <c r="F425" t="s">
+        <v>85</v>
+      </c>
+      <c r="G425" t="s">
+        <v>13</v>
+      </c>
+      <c r="H425" s="2">
+        <v>0</v>
+      </c>
+      <c r="I425" s="1">
+        <v>46146.681250000001</v>
+      </c>
+      <c r="J425">
+        <v>0</v>
+      </c>
+      <c r="K425" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="426" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B426" t="s">
+        <v>22</v>
+      </c>
+      <c r="C426">
+        <v>3483</v>
+      </c>
+      <c r="D426" t="s">
+        <v>45</v>
+      </c>
+      <c r="F426" t="s">
+        <v>85</v>
+      </c>
+      <c r="G426" t="s">
+        <v>13</v>
+      </c>
+      <c r="H426" s="2">
+        <v>0</v>
+      </c>
+      <c r="I426" s="1">
+        <v>46146.681944444441</v>
+      </c>
+      <c r="J426">
+        <v>0</v>
+      </c>
+      <c r="K426" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="427" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B427" t="s">
+        <v>22</v>
+      </c>
+      <c r="C427">
+        <v>3499</v>
+      </c>
+      <c r="D427" t="s">
+        <v>46</v>
+      </c>
+      <c r="F427" t="s">
+        <v>85</v>
+      </c>
+      <c r="G427" t="s">
+        <v>13</v>
+      </c>
+      <c r="H427" s="2">
+        <v>0</v>
+      </c>
+      <c r="I427" s="1">
+        <v>46146.681944444441</v>
+      </c>
+      <c r="J427">
+        <v>0</v>
+      </c>
+      <c r="K427" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="428" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B428" t="s">
+        <v>22</v>
+      </c>
+      <c r="C428">
+        <v>3699</v>
+      </c>
+      <c r="D428" t="s">
+        <v>47</v>
+      </c>
+      <c r="F428" t="s">
+        <v>85</v>
+      </c>
+      <c r="G428" t="s">
+        <v>12</v>
+      </c>
+      <c r="H428" s="2">
+        <v>0</v>
+      </c>
+      <c r="I428" s="1">
+        <v>46146.682638888888</v>
+      </c>
+      <c r="J428">
+        <v>0</v>
+      </c>
+      <c r="K428" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H429" s="2"/>
       <c r="I429" s="1"/>
-    </row>
-    <row r="430" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H430" s="2"/>
-      <c r="I430" s="1"/>
-    </row>
-    <row r="431" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H431" s="2"/>
-      <c r="I431" s="1"/>
-    </row>
-    <row r="432" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H432" s="2"/>
-      <c r="I432" s="1"/>
-    </row>
-    <row r="433" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H433" s="2"/>
-      <c r="I433" s="1"/>
-    </row>
-    <row r="434" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H434" s="2"/>
-      <c r="I434" s="1"/>
-    </row>
-    <row r="435" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H435" s="2"/>
-      <c r="I435" s="1"/>
-    </row>
-    <row r="436" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H436" s="2"/>
-      <c r="I436" s="1"/>
-    </row>
-    <row r="437" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H437" s="2"/>
-      <c r="I437" s="1"/>
-    </row>
-    <row r="438" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H438" s="2"/>
-      <c r="I438" s="1"/>
-    </row>
-    <row r="439" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H439" s="2"/>
-      <c r="I439" s="1"/>
-    </row>
-    <row r="440" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K429" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B430" t="s">
+        <v>22</v>
+      </c>
+      <c r="C430">
+        <v>3491</v>
+      </c>
+      <c r="D430" t="s">
+        <v>48</v>
+      </c>
+      <c r="F430" t="s">
+        <v>85</v>
+      </c>
+      <c r="G430" t="s">
+        <v>13</v>
+      </c>
+      <c r="H430" s="2">
+        <v>0</v>
+      </c>
+      <c r="I430" s="1">
+        <v>46146.683333333334</v>
+      </c>
+      <c r="J430">
+        <v>0</v>
+      </c>
+      <c r="K430" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="431" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B431" t="s">
+        <v>22</v>
+      </c>
+      <c r="C431">
+        <v>3487</v>
+      </c>
+      <c r="D431" t="s">
+        <v>49</v>
+      </c>
+      <c r="F431" t="s">
+        <v>85</v>
+      </c>
+      <c r="G431" t="s">
+        <v>13</v>
+      </c>
+      <c r="H431" s="2">
+        <v>0</v>
+      </c>
+      <c r="I431" s="1">
+        <v>46146.683333333334</v>
+      </c>
+      <c r="J431">
+        <v>0</v>
+      </c>
+      <c r="K431" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="432" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B432" t="s">
+        <v>22</v>
+      </c>
+      <c r="C432">
+        <v>3704</v>
+      </c>
+      <c r="D432" t="s">
+        <v>50</v>
+      </c>
+      <c r="F432" t="s">
+        <v>85</v>
+      </c>
+      <c r="G432" t="s">
+        <v>13</v>
+      </c>
+      <c r="H432" s="2">
+        <v>0</v>
+      </c>
+      <c r="I432" s="1">
+        <v>46146.684027777781</v>
+      </c>
+      <c r="J432">
+        <v>0</v>
+      </c>
+      <c r="K432" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="433" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B433" t="s">
+        <v>22</v>
+      </c>
+      <c r="C433">
+        <v>3481</v>
+      </c>
+      <c r="D433" t="s">
+        <v>51</v>
+      </c>
+      <c r="F433" t="s">
+        <v>85</v>
+      </c>
+      <c r="G433" t="s">
+        <v>13</v>
+      </c>
+      <c r="H433" s="2">
+        <v>0</v>
+      </c>
+      <c r="I433" s="1">
+        <v>46146.68472222222</v>
+      </c>
+      <c r="J433">
+        <v>0</v>
+      </c>
+      <c r="K433" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="434" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B434" t="s">
+        <v>22</v>
+      </c>
+      <c r="C434">
+        <v>3480</v>
+      </c>
+      <c r="D434" t="s">
+        <v>52</v>
+      </c>
+      <c r="F434" t="s">
+        <v>85</v>
+      </c>
+      <c r="G434" t="s">
+        <v>13</v>
+      </c>
+      <c r="H434" s="2">
+        <v>0</v>
+      </c>
+      <c r="I434" s="1">
+        <v>46146.68472222222</v>
+      </c>
+      <c r="J434">
+        <v>0</v>
+      </c>
+      <c r="K434" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="435" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B435" t="s">
+        <v>22</v>
+      </c>
+      <c r="C435">
+        <v>3511</v>
+      </c>
+      <c r="D435" t="s">
+        <v>53</v>
+      </c>
+      <c r="F435" t="s">
+        <v>85</v>
+      </c>
+      <c r="G435" t="s">
+        <v>10</v>
+      </c>
+      <c r="H435" s="2">
+        <v>6.3194444444444444E-3</v>
+      </c>
+      <c r="I435" s="1">
+        <v>46146.685416666667</v>
+      </c>
+      <c r="J435">
+        <v>0</v>
+      </c>
+      <c r="K435" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B436" t="s">
+        <v>22</v>
+      </c>
+      <c r="C436">
+        <v>3484</v>
+      </c>
+      <c r="D436" t="s">
+        <v>55</v>
+      </c>
+      <c r="F436" t="s">
+        <v>85</v>
+      </c>
+      <c r="G436" t="s">
+        <v>10</v>
+      </c>
+      <c r="H436" s="2">
+        <v>5.3935185185185188E-3</v>
+      </c>
+      <c r="I436" s="1">
+        <v>46146.686111111114</v>
+      </c>
+      <c r="J436">
+        <v>0</v>
+      </c>
+      <c r="K436" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="437" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B437" t="s">
+        <v>22</v>
+      </c>
+      <c r="C437">
+        <v>3514</v>
+      </c>
+      <c r="D437" t="s">
+        <v>56</v>
+      </c>
+      <c r="F437" t="s">
+        <v>85</v>
+      </c>
+      <c r="G437" t="s">
+        <v>10</v>
+      </c>
+      <c r="H437" s="2">
+        <v>3.8171296296296293E-2</v>
+      </c>
+      <c r="I437" s="1">
+        <v>46146.686111111114</v>
+      </c>
+      <c r="J437">
+        <v>0</v>
+      </c>
+      <c r="K437" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="438" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B438" t="s">
+        <v>22</v>
+      </c>
+      <c r="C438">
+        <v>3725</v>
+      </c>
+      <c r="D438" t="s">
+        <v>58</v>
+      </c>
+      <c r="F438" t="s">
+        <v>85</v>
+      </c>
+      <c r="G438" t="s">
+        <v>13</v>
+      </c>
+      <c r="H438" s="2">
+        <v>0</v>
+      </c>
+      <c r="I438" s="1">
+        <v>46146.686805555553</v>
+      </c>
+      <c r="J438">
+        <v>0</v>
+      </c>
+      <c r="K438" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="439" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B439" t="s">
+        <v>22</v>
+      </c>
+      <c r="C439">
+        <v>3488</v>
+      </c>
+      <c r="D439" t="s">
+        <v>59</v>
+      </c>
+      <c r="F439" t="s">
+        <v>85</v>
+      </c>
+      <c r="G439" t="s">
+        <v>12</v>
+      </c>
+      <c r="H439" s="2">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="I439" s="1">
+        <v>46146.6875</v>
+      </c>
+      <c r="J439">
+        <v>0</v>
+      </c>
+      <c r="K439" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="440" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H440" s="2"/>
       <c r="I440" s="1"/>
-    </row>
-    <row r="441" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H441" s="2"/>
-      <c r="I441" s="1"/>
-    </row>
-    <row r="442" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H442" s="2"/>
-      <c r="I442" s="1"/>
-    </row>
-    <row r="443" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H443" s="2"/>
-      <c r="I443" s="1"/>
-    </row>
-    <row r="444" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H444" s="2"/>
-      <c r="I444" s="1"/>
-    </row>
-    <row r="445" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H445" s="2"/>
-      <c r="I445" s="1"/>
-    </row>
-    <row r="446" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H446" s="2"/>
-      <c r="I446" s="1"/>
-    </row>
-    <row r="447" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H447" s="2"/>
-      <c r="I447" s="1"/>
-    </row>
-    <row r="448" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H448" s="2"/>
-      <c r="I448" s="1"/>
-    </row>
-    <row r="449" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H449" s="2"/>
-      <c r="I449" s="1"/>
-    </row>
-    <row r="450" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H450" s="2"/>
-      <c r="I450" s="1"/>
-    </row>
-    <row r="451" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H451" s="2"/>
-      <c r="I451" s="1"/>
-    </row>
-    <row r="452" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H452" s="2"/>
-      <c r="I452" s="1"/>
-    </row>
-    <row r="453" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H453" s="2"/>
-      <c r="I453" s="1"/>
-    </row>
-    <row r="454" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H454" s="2"/>
-      <c r="I454" s="1"/>
-    </row>
-    <row r="455" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K440" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="441" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B441" t="s">
+        <v>22</v>
+      </c>
+      <c r="C441">
+        <v>3478</v>
+      </c>
+      <c r="D441" t="s">
+        <v>60</v>
+      </c>
+      <c r="F441" t="s">
+        <v>85</v>
+      </c>
+      <c r="G441" t="s">
+        <v>13</v>
+      </c>
+      <c r="H441" s="2">
+        <v>0</v>
+      </c>
+      <c r="I441" s="1">
+        <v>46146.6875</v>
+      </c>
+      <c r="J441">
+        <v>0</v>
+      </c>
+      <c r="K441" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="442" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B442" t="s">
+        <v>22</v>
+      </c>
+      <c r="C442">
+        <v>3494</v>
+      </c>
+      <c r="D442" t="s">
+        <v>61</v>
+      </c>
+      <c r="F442" t="s">
+        <v>85</v>
+      </c>
+      <c r="G442" t="s">
+        <v>10</v>
+      </c>
+      <c r="H442" s="2">
+        <v>5.2199074074074075E-3</v>
+      </c>
+      <c r="I442" s="1">
+        <v>46146.688194444447</v>
+      </c>
+      <c r="J442">
+        <v>0</v>
+      </c>
+      <c r="K442" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="443" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B443" t="s">
+        <v>22</v>
+      </c>
+      <c r="C443">
+        <v>3523</v>
+      </c>
+      <c r="D443" t="s">
+        <v>62</v>
+      </c>
+      <c r="F443" t="s">
+        <v>85</v>
+      </c>
+      <c r="G443" t="s">
+        <v>13</v>
+      </c>
+      <c r="H443" s="2">
+        <v>0</v>
+      </c>
+      <c r="I443" s="1">
+        <v>46146.688888888886</v>
+      </c>
+      <c r="J443">
+        <v>0</v>
+      </c>
+      <c r="K443" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="444" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B444" t="s">
+        <v>22</v>
+      </c>
+      <c r="C444">
+        <v>3504</v>
+      </c>
+      <c r="D444" t="s">
+        <v>64</v>
+      </c>
+      <c r="F444" t="s">
+        <v>85</v>
+      </c>
+      <c r="G444" t="s">
+        <v>13</v>
+      </c>
+      <c r="H444" s="2">
+        <v>0</v>
+      </c>
+      <c r="I444" s="1">
+        <v>46146.688888888886</v>
+      </c>
+      <c r="J444">
+        <v>0</v>
+      </c>
+      <c r="K444" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="445" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B445" t="s">
+        <v>22</v>
+      </c>
+      <c r="C445">
+        <v>3498</v>
+      </c>
+      <c r="D445" t="s">
+        <v>65</v>
+      </c>
+      <c r="F445" t="s">
+        <v>85</v>
+      </c>
+      <c r="G445" t="s">
+        <v>10</v>
+      </c>
+      <c r="H445" s="2">
+        <v>6.2037037037037035E-3</v>
+      </c>
+      <c r="I445" s="1">
+        <v>46146.689583333333</v>
+      </c>
+      <c r="J445">
+        <v>0</v>
+      </c>
+      <c r="K445" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="446" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B446" t="s">
+        <v>22</v>
+      </c>
+      <c r="C446">
+        <v>3344</v>
+      </c>
+      <c r="D446" t="s">
+        <v>66</v>
+      </c>
+      <c r="F446" t="s">
+        <v>85</v>
+      </c>
+      <c r="G446" t="s">
+        <v>13</v>
+      </c>
+      <c r="H446" s="2">
+        <v>0</v>
+      </c>
+      <c r="I446" s="1">
+        <v>46146.69027777778</v>
+      </c>
+      <c r="J446">
+        <v>0</v>
+      </c>
+      <c r="K446" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="447" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B447" t="s">
+        <v>22</v>
+      </c>
+      <c r="C447">
+        <v>3515</v>
+      </c>
+      <c r="D447" t="s">
+        <v>67</v>
+      </c>
+      <c r="F447" t="s">
+        <v>85</v>
+      </c>
+      <c r="G447" t="s">
+        <v>13</v>
+      </c>
+      <c r="H447" s="2">
+        <v>0</v>
+      </c>
+      <c r="I447" s="1">
+        <v>46146.690972222219</v>
+      </c>
+      <c r="J447">
+        <v>0</v>
+      </c>
+      <c r="K447" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="448" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B448" t="s">
+        <v>22</v>
+      </c>
+      <c r="C448">
+        <v>3522</v>
+      </c>
+      <c r="D448" t="s">
+        <v>68</v>
+      </c>
+      <c r="F448" t="s">
+        <v>85</v>
+      </c>
+      <c r="G448" t="s">
+        <v>13</v>
+      </c>
+      <c r="H448" s="2">
+        <v>0</v>
+      </c>
+      <c r="I448" s="1">
+        <v>46146.690972222219</v>
+      </c>
+      <c r="J448">
+        <v>0</v>
+      </c>
+      <c r="K448" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="449" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B449" t="s">
+        <v>22</v>
+      </c>
+      <c r="C449">
+        <v>3751</v>
+      </c>
+      <c r="D449" t="s">
+        <v>69</v>
+      </c>
+      <c r="F449" t="s">
+        <v>85</v>
+      </c>
+      <c r="G449" t="s">
+        <v>13</v>
+      </c>
+      <c r="H449" s="2">
+        <v>0</v>
+      </c>
+      <c r="I449" s="1">
+        <v>46146.691666666666</v>
+      </c>
+      <c r="J449">
+        <v>0</v>
+      </c>
+      <c r="K449" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="450" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B450" t="s">
+        <v>22</v>
+      </c>
+      <c r="C450">
+        <v>3662</v>
+      </c>
+      <c r="D450" t="s">
+        <v>70</v>
+      </c>
+      <c r="F450" t="s">
+        <v>85</v>
+      </c>
+      <c r="G450" t="s">
+        <v>13</v>
+      </c>
+      <c r="H450" s="2">
+        <v>0</v>
+      </c>
+      <c r="I450" s="1">
+        <v>46146.692361111112</v>
+      </c>
+      <c r="J450">
+        <v>0</v>
+      </c>
+      <c r="K450" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="451" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B451" t="s">
+        <v>22</v>
+      </c>
+      <c r="C451">
+        <v>3503</v>
+      </c>
+      <c r="D451" t="s">
+        <v>72</v>
+      </c>
+      <c r="F451" t="s">
+        <v>85</v>
+      </c>
+      <c r="G451" t="s">
+        <v>13</v>
+      </c>
+      <c r="H451" s="2">
+        <v>0</v>
+      </c>
+      <c r="I451" s="1">
+        <v>46146.668171296296</v>
+      </c>
+      <c r="J451">
+        <v>0</v>
+      </c>
+      <c r="K451" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="452" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B452" t="s">
+        <v>22</v>
+      </c>
+      <c r="C452">
+        <v>3652</v>
+      </c>
+      <c r="D452" t="s">
+        <v>73</v>
+      </c>
+      <c r="F452" t="s">
+        <v>85</v>
+      </c>
+      <c r="G452" t="s">
+        <v>13</v>
+      </c>
+      <c r="H452" s="2">
+        <v>0</v>
+      </c>
+      <c r="I452" s="1">
+        <v>46146.668865740743</v>
+      </c>
+      <c r="J452">
+        <v>0</v>
+      </c>
+      <c r="K452" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="453" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B453" t="s">
+        <v>22</v>
+      </c>
+      <c r="C453">
+        <v>3509</v>
+      </c>
+      <c r="D453" t="s">
+        <v>74</v>
+      </c>
+      <c r="F453" t="s">
+        <v>85</v>
+      </c>
+      <c r="G453" t="s">
+        <v>13</v>
+      </c>
+      <c r="H453" s="2">
+        <v>0</v>
+      </c>
+      <c r="I453" s="1">
+        <v>46146.669560185182</v>
+      </c>
+      <c r="J453">
+        <v>0</v>
+      </c>
+      <c r="K453" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="454" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B454" t="s">
+        <v>22</v>
+      </c>
+      <c r="C454">
+        <v>5465</v>
+      </c>
+      <c r="D454" t="s">
+        <v>87</v>
+      </c>
+      <c r="F454" t="s">
+        <v>85</v>
+      </c>
+      <c r="G454" t="s">
+        <v>12</v>
+      </c>
+      <c r="H454" s="2">
+        <v>7.1875000000000003E-3</v>
+      </c>
+      <c r="I454" s="1">
+        <v>46146.669560185182</v>
+      </c>
+      <c r="J454">
+        <v>0</v>
+      </c>
+      <c r="K454" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="455" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H455" s="2"/>
       <c r="I455" s="1"/>
-    </row>
-    <row r="456" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H456" s="2"/>
-      <c r="I456" s="1"/>
-    </row>
-    <row r="457" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K455" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="456" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B456" t="s">
+        <v>22</v>
+      </c>
+      <c r="C456">
+        <v>3512</v>
+      </c>
+      <c r="D456" t="s">
+        <v>75</v>
+      </c>
+      <c r="F456" t="s">
+        <v>85</v>
+      </c>
+      <c r="G456" t="s">
+        <v>12</v>
+      </c>
+      <c r="H456" s="2">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="I456" s="1">
+        <v>46146.670254629629</v>
+      </c>
+      <c r="J456">
+        <v>0</v>
+      </c>
+      <c r="K456" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="457" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H457" s="2"/>
       <c r="I457" s="1"/>
-    </row>
-    <row r="458" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H458" s="2"/>
-      <c r="I458" s="1"/>
-    </row>
-    <row r="459" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H459" s="2"/>
-      <c r="I459" s="1"/>
-    </row>
-    <row r="460" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H460" s="2"/>
-      <c r="I460" s="1"/>
-    </row>
-    <row r="461" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H461" s="2"/>
-      <c r="I461" s="1"/>
-    </row>
-    <row r="462" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H462" s="2"/>
-      <c r="I462" s="1"/>
-    </row>
-    <row r="463" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H463" s="2"/>
-      <c r="I463" s="1"/>
-    </row>
-    <row r="464" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H464" s="2"/>
-      <c r="I464" s="1"/>
-    </row>
-    <row r="465" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H465" s="2"/>
-      <c r="I465" s="1"/>
-    </row>
-    <row r="466" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K457" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="458" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B458" t="s">
+        <v>22</v>
+      </c>
+      <c r="C458">
+        <v>3489</v>
+      </c>
+      <c r="D458" t="s">
+        <v>76</v>
+      </c>
+      <c r="F458" t="s">
+        <v>85</v>
+      </c>
+      <c r="G458" t="s">
+        <v>13</v>
+      </c>
+      <c r="H458" s="2">
+        <v>0</v>
+      </c>
+      <c r="I458" s="1">
+        <v>46146.670949074076</v>
+      </c>
+      <c r="J458">
+        <v>0</v>
+      </c>
+      <c r="K458" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="459" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B459" t="s">
+        <v>22</v>
+      </c>
+      <c r="C459">
+        <v>3266</v>
+      </c>
+      <c r="D459" t="s">
+        <v>77</v>
+      </c>
+      <c r="F459" t="s">
+        <v>85</v>
+      </c>
+      <c r="G459" t="s">
+        <v>13</v>
+      </c>
+      <c r="H459" s="2">
+        <v>0</v>
+      </c>
+      <c r="I459" s="1">
+        <v>46146.671643518515</v>
+      </c>
+      <c r="J459">
+        <v>0</v>
+      </c>
+      <c r="K459" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="460" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B460" t="s">
+        <v>22</v>
+      </c>
+      <c r="C460">
+        <v>3492</v>
+      </c>
+      <c r="D460" t="s">
+        <v>78</v>
+      </c>
+      <c r="F460" t="s">
+        <v>85</v>
+      </c>
+      <c r="G460" t="s">
+        <v>13</v>
+      </c>
+      <c r="H460" s="2">
+        <v>0</v>
+      </c>
+      <c r="I460" s="1">
+        <v>46146.671643518515</v>
+      </c>
+      <c r="J460">
+        <v>0</v>
+      </c>
+      <c r="K460" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="461" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B461" t="s">
+        <v>22</v>
+      </c>
+      <c r="C461">
+        <v>3493</v>
+      </c>
+      <c r="D461" t="s">
+        <v>79</v>
+      </c>
+      <c r="F461" t="s">
+        <v>85</v>
+      </c>
+      <c r="G461" t="s">
+        <v>13</v>
+      </c>
+      <c r="H461" s="2">
+        <v>0</v>
+      </c>
+      <c r="I461" s="1">
+        <v>46146.672337962962</v>
+      </c>
+      <c r="J461">
+        <v>0</v>
+      </c>
+      <c r="K461" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="462" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B462" t="s">
+        <v>22</v>
+      </c>
+      <c r="C462">
+        <v>3505</v>
+      </c>
+      <c r="D462" t="s">
+        <v>80</v>
+      </c>
+      <c r="F462" t="s">
+        <v>85</v>
+      </c>
+      <c r="G462" t="s">
+        <v>10</v>
+      </c>
+      <c r="H462" s="2">
+        <v>6.030092592592593E-3</v>
+      </c>
+      <c r="I462" s="1">
+        <v>46146.672337962962</v>
+      </c>
+      <c r="J462">
+        <v>0</v>
+      </c>
+      <c r="K462" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="463" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B463" t="s">
+        <v>22</v>
+      </c>
+      <c r="C463">
+        <v>3861</v>
+      </c>
+      <c r="D463" t="s">
+        <v>81</v>
+      </c>
+      <c r="F463" t="s">
+        <v>85</v>
+      </c>
+      <c r="G463" t="s">
+        <v>13</v>
+      </c>
+      <c r="H463" s="2">
+        <v>0</v>
+      </c>
+      <c r="I463" s="1">
+        <v>46146.673032407409</v>
+      </c>
+      <c r="J463">
+        <v>0</v>
+      </c>
+      <c r="K463" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="464" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B464" t="s">
+        <v>22</v>
+      </c>
+      <c r="C464">
+        <v>5205</v>
+      </c>
+      <c r="D464" t="s">
+        <v>83</v>
+      </c>
+      <c r="F464" t="s">
+        <v>85</v>
+      </c>
+      <c r="G464" t="s">
+        <v>13</v>
+      </c>
+      <c r="H464" s="2">
+        <v>0</v>
+      </c>
+      <c r="I464" s="1">
+        <v>46146.673726851855</v>
+      </c>
+      <c r="J464">
+        <v>0</v>
+      </c>
+      <c r="K464" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="465" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B465" t="s">
+        <v>22</v>
+      </c>
+      <c r="C465">
+        <v>3538</v>
+      </c>
+      <c r="D465" t="s">
+        <v>82</v>
+      </c>
+      <c r="F465" t="s">
+        <v>85</v>
+      </c>
+      <c r="G465" t="s">
+        <v>13</v>
+      </c>
+      <c r="H465" s="2">
+        <v>0</v>
+      </c>
+      <c r="I465" s="1">
+        <v>46146.674421296295</v>
+      </c>
+      <c r="J465">
+        <v>0</v>
+      </c>
+      <c r="K465" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="466" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H466" s="2"/>
       <c r="I466" s="1"/>
     </row>
-    <row r="467" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H467" s="2"/>
       <c r="I467" s="1"/>
     </row>
-    <row r="468" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H468" s="2"/>
       <c r="I468" s="1"/>
     </row>
-    <row r="469" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H469" s="2"/>
       <c r="I469" s="1"/>
     </row>
-    <row r="470" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H470" s="2"/>
       <c r="I470" s="1"/>
     </row>
-    <row r="471" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H471" s="2"/>
       <c r="I471" s="1"/>
     </row>
-    <row r="472" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H472" s="2"/>
       <c r="I472" s="1"/>
     </row>
-    <row r="473" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H473" s="2"/>
       <c r="I473" s="1"/>
     </row>
-    <row r="474" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H474" s="2"/>
       <c r="I474" s="1"/>
     </row>
-    <row r="475" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H475" s="2"/>
       <c r="I475" s="1"/>
     </row>
-    <row r="476" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H476" s="2"/>
       <c r="I476" s="1"/>
     </row>
-    <row r="477" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H477" s="2"/>
       <c r="I477" s="1"/>
     </row>
-    <row r="478" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H478" s="2"/>
       <c r="I478" s="1"/>
     </row>
-    <row r="479" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H479" s="2"/>
       <c r="I479" s="1"/>
     </row>
-    <row r="480" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H480" s="2"/>
       <c r="I480" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Fiore and Sons - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47721AC2-44E0-4F76-8F1E-51F99CA91770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CEF935B-31FE-4DDF-9418-0E562A502FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="88">
   <si>
     <t>Company Name</t>
   </si>
@@ -9849,7 +9849,7 @@
         <v>46118.76840277778</v>
       </c>
       <c r="J347">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K347" t="s">
         <v>11</v>
@@ -9878,7 +9878,7 @@
         <v>46118.76840277778</v>
       </c>
       <c r="J348">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K348" t="s">
         <v>11</v>
@@ -9907,7 +9907,7 @@
         <v>46118.769097222219</v>
       </c>
       <c r="J349">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K349" t="s">
         <v>11</v>
@@ -9936,7 +9936,7 @@
         <v>46118.769791666666</v>
       </c>
       <c r="J350">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K350" t="s">
         <v>11</v>
@@ -9994,7 +9994,7 @@
         <v>46118.770486111112</v>
       </c>
       <c r="J352">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K352" t="s">
         <v>11</v>
@@ -10168,7 +10168,7 @@
         <v>46118.773263888892</v>
       </c>
       <c r="J358">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K358" t="s">
         <v>11</v>
@@ -10226,7 +10226,7 @@
         <v>46118.752546296295</v>
       </c>
       <c r="J360">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K360" t="s">
         <v>11</v>
@@ -10255,7 +10255,7 @@
         <v>46118.752546296295</v>
       </c>
       <c r="J361">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K361" t="s">
         <v>11</v>
@@ -10400,7 +10400,7 @@
         <v>46118.754629629628</v>
       </c>
       <c r="J366">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K366" t="s">
         <v>11</v>
@@ -10429,7 +10429,7 @@
         <v>46118.755324074074</v>
       </c>
       <c r="J367">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K367" t="s">
         <v>11</v>
@@ -10603,7 +10603,7 @@
         <v>46118.758101851854</v>
       </c>
       <c r="J373">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K373" t="s">
         <v>11</v>
@@ -10849,7 +10849,7 @@
         <v>46118.760879629626</v>
       </c>
       <c r="J383">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K383" t="s">
         <v>11</v>
@@ -10907,7 +10907,7 @@
         <v>46118.76226851852</v>
       </c>
       <c r="J385">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K385" t="s">
         <v>11</v>
@@ -10936,7 +10936,7 @@
         <v>46118.76226851852</v>
       </c>
       <c r="J386">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K386" t="s">
         <v>11</v>
@@ -10994,7 +10994,7 @@
         <v>46118.762962962966</v>
       </c>
       <c r="J388">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K388" t="s">
         <v>11</v>
@@ -11052,7 +11052,7 @@
         <v>46118.764351851853</v>
       </c>
       <c r="J390">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K390" t="s">
         <v>11</v>
@@ -11197,7 +11197,7 @@
         <v>46118.766435185185</v>
       </c>
       <c r="J395">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K395" t="s">
         <v>11</v>
@@ -11398,10 +11398,10 @@
         <v>85</v>
       </c>
       <c r="G403" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H403" s="2">
-        <v>0</v>
+        <v>4.31712962962963E-3</v>
       </c>
       <c r="I403" s="1">
         <v>46146.672222222223</v>
@@ -11430,7 +11430,7 @@
         <v>12</v>
       </c>
       <c r="H404" s="2">
-        <v>0</v>
+        <v>2.6620370370370372E-4</v>
       </c>
       <c r="I404" s="1">
         <v>46146.672222222223</v>
@@ -11521,10 +11521,10 @@
         <v>85</v>
       </c>
       <c r="G408" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H408" s="2">
-        <v>0</v>
+        <v>1.1909722222222223E-2</v>
       </c>
       <c r="I408" s="1">
         <v>46146.673611111109</v>
@@ -11740,7 +11740,7 @@
         <v>46146.677083333336</v>
       </c>
       <c r="J416">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K416" t="s">
         <v>11</v>
@@ -11760,16 +11760,16 @@
         <v>85</v>
       </c>
       <c r="G417" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H417" s="2">
-        <v>0</v>
+        <v>5.347222222222222E-3</v>
       </c>
       <c r="I417" s="1">
         <v>46146.677777777775</v>
       </c>
       <c r="J417">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K417" t="s">
         <v>11</v>
@@ -11789,10 +11789,10 @@
         <v>85</v>
       </c>
       <c r="G418" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H418" s="2">
-        <v>0</v>
+        <v>4.6527777777777774E-3</v>
       </c>
       <c r="I418" s="1">
         <v>46146.678472222222</v>
@@ -11827,7 +11827,7 @@
         <v>46146.678472222222</v>
       </c>
       <c r="J419">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K419" t="s">
         <v>11</v>
@@ -11892,7 +11892,7 @@
         <v>46146.679861111108</v>
       </c>
       <c r="J422">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K422" t="s">
         <v>11</v>
@@ -11950,7 +11950,7 @@
         <v>46146.680555555555</v>
       </c>
       <c r="J424">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K424" t="s">
         <v>11</v>
@@ -11979,7 +11979,7 @@
         <v>46146.681250000001</v>
       </c>
       <c r="J425">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K425" t="s">
         <v>11</v>
@@ -12008,7 +12008,7 @@
         <v>46146.681944444441</v>
       </c>
       <c r="J426">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K426" t="s">
         <v>11</v>
@@ -12028,7 +12028,7 @@
         <v>85</v>
       </c>
       <c r="G427" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H427" s="2">
         <v>0</v>
@@ -12037,75 +12037,53 @@
         <v>46146.681944444441</v>
       </c>
       <c r="J427">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K427" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="428" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B428" t="s">
-        <v>22</v>
-      </c>
-      <c r="C428">
+      <c r="H428" s="2"/>
+      <c r="I428" s="1"/>
+      <c r="K428" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B429" t="s">
+        <v>22</v>
+      </c>
+      <c r="C429">
         <v>3699</v>
       </c>
-      <c r="D428" t="s">
+      <c r="D429" t="s">
         <v>47</v>
       </c>
-      <c r="F428" t="s">
+      <c r="F429" t="s">
         <v>85</v>
       </c>
-      <c r="G428" t="s">
+      <c r="G429" t="s">
         <v>12</v>
       </c>
-      <c r="H428" s="2">
-        <v>0</v>
-      </c>
-      <c r="I428" s="1">
+      <c r="H429" s="2">
+        <v>0</v>
+      </c>
+      <c r="I429" s="1">
         <v>46146.682638888888</v>
       </c>
-      <c r="J428">
-        <v>0</v>
-      </c>
-      <c r="K428" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H429" s="2"/>
-      <c r="I429" s="1"/>
+      <c r="J429">
+        <v>0</v>
+      </c>
       <c r="K429" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H430" s="2"/>
+      <c r="I430" s="1"/>
+      <c r="K430" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B430" t="s">
-        <v>22</v>
-      </c>
-      <c r="C430">
-        <v>3491</v>
-      </c>
-      <c r="D430" t="s">
-        <v>48</v>
-      </c>
-      <c r="F430" t="s">
-        <v>85</v>
-      </c>
-      <c r="G430" t="s">
-        <v>13</v>
-      </c>
-      <c r="H430" s="2">
-        <v>0</v>
-      </c>
-      <c r="I430" s="1">
-        <v>46146.683333333334</v>
-      </c>
-      <c r="J430">
-        <v>0</v>
-      </c>
-      <c r="K430" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="431" spans="2:11" x14ac:dyDescent="0.25">
@@ -12113,10 +12091,10 @@
         <v>22</v>
       </c>
       <c r="C431">
-        <v>3487</v>
+        <v>3491</v>
       </c>
       <c r="D431" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F431" t="s">
         <v>85</v>
@@ -12142,10 +12120,10 @@
         <v>22</v>
       </c>
       <c r="C432">
-        <v>3704</v>
+        <v>3487</v>
       </c>
       <c r="D432" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F432" t="s">
         <v>85</v>
@@ -12157,7 +12135,7 @@
         <v>0</v>
       </c>
       <c r="I432" s="1">
-        <v>46146.684027777781</v>
+        <v>46146.683333333334</v>
       </c>
       <c r="J432">
         <v>0</v>
@@ -12171,10 +12149,10 @@
         <v>22</v>
       </c>
       <c r="C433">
-        <v>3481</v>
+        <v>3704</v>
       </c>
       <c r="D433" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F433" t="s">
         <v>85</v>
@@ -12186,7 +12164,7 @@
         <v>0</v>
       </c>
       <c r="I433" s="1">
-        <v>46146.68472222222</v>
+        <v>46146.684027777781</v>
       </c>
       <c r="J433">
         <v>0</v>
@@ -12200,10 +12178,10 @@
         <v>22</v>
       </c>
       <c r="C434">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="D434" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F434" t="s">
         <v>85</v>
@@ -12229,10 +12207,10 @@
         <v>22</v>
       </c>
       <c r="C435">
-        <v>3511</v>
+        <v>3480</v>
       </c>
       <c r="D435" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F435" t="s">
         <v>85</v>
@@ -12241,10 +12219,10 @@
         <v>10</v>
       </c>
       <c r="H435" s="2">
-        <v>6.3194444444444444E-3</v>
+        <v>6.7939814814814816E-3</v>
       </c>
       <c r="I435" s="1">
-        <v>46146.685416666667</v>
+        <v>46146.68472222222</v>
       </c>
       <c r="J435">
         <v>0</v>
@@ -12258,10 +12236,10 @@
         <v>22</v>
       </c>
       <c r="C436">
-        <v>3484</v>
+        <v>3511</v>
       </c>
       <c r="D436" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F436" t="s">
         <v>85</v>
@@ -12270,10 +12248,10 @@
         <v>10</v>
       </c>
       <c r="H436" s="2">
-        <v>5.3935185185185188E-3</v>
+        <v>6.3194444444444444E-3</v>
       </c>
       <c r="I436" s="1">
-        <v>46146.686111111114</v>
+        <v>46146.685416666667</v>
       </c>
       <c r="J436">
         <v>0</v>
@@ -12287,10 +12265,10 @@
         <v>22</v>
       </c>
       <c r="C437">
-        <v>3514</v>
+        <v>3484</v>
       </c>
       <c r="D437" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F437" t="s">
         <v>85</v>
@@ -12299,7 +12277,7 @@
         <v>10</v>
       </c>
       <c r="H437" s="2">
-        <v>3.8171296296296293E-2</v>
+        <v>5.3935185185185188E-3</v>
       </c>
       <c r="I437" s="1">
         <v>46146.686111111114</v>
@@ -12316,22 +12294,22 @@
         <v>22</v>
       </c>
       <c r="C438">
-        <v>3725</v>
+        <v>3514</v>
       </c>
       <c r="D438" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F438" t="s">
         <v>85</v>
       </c>
       <c r="G438" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H438" s="2">
-        <v>0</v>
+        <v>4.4027777777777777E-2</v>
       </c>
       <c r="I438" s="1">
-        <v>46146.686805555553</v>
+        <v>46146.686111111114</v>
       </c>
       <c r="J438">
         <v>0</v>
@@ -12345,64 +12323,64 @@
         <v>22</v>
       </c>
       <c r="C439">
-        <v>3488</v>
+        <v>3725</v>
       </c>
       <c r="D439" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F439" t="s">
         <v>85</v>
       </c>
       <c r="G439" t="s">
+        <v>13</v>
+      </c>
+      <c r="H439" s="2">
+        <v>0</v>
+      </c>
+      <c r="I439" s="1">
+        <v>46146.686805555553</v>
+      </c>
+      <c r="J439">
+        <v>0</v>
+      </c>
+      <c r="K439" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="440" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B440" t="s">
+        <v>22</v>
+      </c>
+      <c r="C440">
+        <v>3488</v>
+      </c>
+      <c r="D440" t="s">
+        <v>59</v>
+      </c>
+      <c r="F440" t="s">
+        <v>85</v>
+      </c>
+      <c r="G440" t="s">
         <v>12</v>
       </c>
-      <c r="H439" s="2">
+      <c r="H440" s="2">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="I439" s="1">
+      <c r="I440" s="1">
         <v>46146.6875</v>
       </c>
-      <c r="J439">
-        <v>0</v>
-      </c>
-      <c r="K439" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="440" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H440" s="2"/>
-      <c r="I440" s="1"/>
+      <c r="J440">
+        <v>0</v>
+      </c>
       <c r="K440" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="441" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H441" s="2"/>
+      <c r="I441" s="1"/>
+      <c r="K441" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="441" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B441" t="s">
-        <v>22</v>
-      </c>
-      <c r="C441">
-        <v>3478</v>
-      </c>
-      <c r="D441" t="s">
-        <v>60</v>
-      </c>
-      <c r="F441" t="s">
-        <v>85</v>
-      </c>
-      <c r="G441" t="s">
-        <v>13</v>
-      </c>
-      <c r="H441" s="2">
-        <v>0</v>
-      </c>
-      <c r="I441" s="1">
-        <v>46146.6875</v>
-      </c>
-      <c r="J441">
-        <v>0</v>
-      </c>
-      <c r="K441" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="442" spans="2:11" x14ac:dyDescent="0.25">
@@ -12410,22 +12388,22 @@
         <v>22</v>
       </c>
       <c r="C442">
-        <v>3494</v>
+        <v>3478</v>
       </c>
       <c r="D442" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F442" t="s">
         <v>85</v>
       </c>
       <c r="G442" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H442" s="2">
-        <v>5.2199074074074075E-3</v>
+        <v>0</v>
       </c>
       <c r="I442" s="1">
-        <v>46146.688194444447</v>
+        <v>46146.6875</v>
       </c>
       <c r="J442">
         <v>0</v>
@@ -12439,22 +12417,22 @@
         <v>22</v>
       </c>
       <c r="C443">
-        <v>3523</v>
+        <v>3494</v>
       </c>
       <c r="D443" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F443" t="s">
         <v>85</v>
       </c>
       <c r="G443" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H443" s="2">
-        <v>0</v>
+        <v>5.2199074074074075E-3</v>
       </c>
       <c r="I443" s="1">
-        <v>46146.688888888886</v>
+        <v>46146.688194444447</v>
       </c>
       <c r="J443">
         <v>0</v>
@@ -12468,10 +12446,10 @@
         <v>22</v>
       </c>
       <c r="C444">
-        <v>3504</v>
+        <v>3523</v>
       </c>
       <c r="D444" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F444" t="s">
         <v>85</v>
@@ -12497,22 +12475,22 @@
         <v>22</v>
       </c>
       <c r="C445">
-        <v>3498</v>
+        <v>3504</v>
       </c>
       <c r="D445" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F445" t="s">
         <v>85</v>
       </c>
       <c r="G445" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H445" s="2">
-        <v>6.2037037037037035E-3</v>
+        <v>0</v>
       </c>
       <c r="I445" s="1">
-        <v>46146.689583333333</v>
+        <v>46146.688888888886</v>
       </c>
       <c r="J445">
         <v>0</v>
@@ -12526,22 +12504,22 @@
         <v>22</v>
       </c>
       <c r="C446">
-        <v>3344</v>
+        <v>3498</v>
       </c>
       <c r="D446" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F446" t="s">
         <v>85</v>
       </c>
       <c r="G446" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H446" s="2">
-        <v>0</v>
+        <v>6.2037037037037035E-3</v>
       </c>
       <c r="I446" s="1">
-        <v>46146.69027777778</v>
+        <v>46146.689583333333</v>
       </c>
       <c r="J446">
         <v>0</v>
@@ -12555,10 +12533,10 @@
         <v>22</v>
       </c>
       <c r="C447">
-        <v>3515</v>
+        <v>3344</v>
       </c>
       <c r="D447" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F447" t="s">
         <v>85</v>
@@ -12570,7 +12548,7 @@
         <v>0</v>
       </c>
       <c r="I447" s="1">
-        <v>46146.690972222219</v>
+        <v>46146.69027777778</v>
       </c>
       <c r="J447">
         <v>0</v>
@@ -12584,10 +12562,10 @@
         <v>22</v>
       </c>
       <c r="C448">
-        <v>3522</v>
+        <v>3515</v>
       </c>
       <c r="D448" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F448" t="s">
         <v>85</v>
@@ -12613,22 +12591,22 @@
         <v>22</v>
       </c>
       <c r="C449">
-        <v>3751</v>
+        <v>3522</v>
       </c>
       <c r="D449" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F449" t="s">
         <v>85</v>
       </c>
       <c r="G449" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H449" s="2">
-        <v>0</v>
+        <v>4.6412037037037038E-3</v>
       </c>
       <c r="I449" s="1">
-        <v>46146.691666666666</v>
+        <v>46146.690972222219</v>
       </c>
       <c r="J449">
         <v>0</v>
@@ -12642,10 +12620,10 @@
         <v>22</v>
       </c>
       <c r="C450">
-        <v>3662</v>
+        <v>3751</v>
       </c>
       <c r="D450" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F450" t="s">
         <v>85</v>
@@ -12657,7 +12635,7 @@
         <v>0</v>
       </c>
       <c r="I450" s="1">
-        <v>46146.692361111112</v>
+        <v>46146.691666666666</v>
       </c>
       <c r="J450">
         <v>0</v>
@@ -12671,10 +12649,10 @@
         <v>22</v>
       </c>
       <c r="C451">
-        <v>3503</v>
+        <v>3662</v>
       </c>
       <c r="D451" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F451" t="s">
         <v>85</v>
@@ -12686,7 +12664,7 @@
         <v>0</v>
       </c>
       <c r="I451" s="1">
-        <v>46146.668171296296</v>
+        <v>46146.692361111112</v>
       </c>
       <c r="J451">
         <v>0</v>
@@ -12700,10 +12678,10 @@
         <v>22</v>
       </c>
       <c r="C452">
-        <v>3652</v>
+        <v>3503</v>
       </c>
       <c r="D452" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F452" t="s">
         <v>85</v>
@@ -12715,7 +12693,7 @@
         <v>0</v>
       </c>
       <c r="I452" s="1">
-        <v>46146.668865740743</v>
+        <v>46146.668171296296</v>
       </c>
       <c r="J452">
         <v>0</v>
@@ -12729,10 +12707,10 @@
         <v>22</v>
       </c>
       <c r="C453">
-        <v>3509</v>
+        <v>3652</v>
       </c>
       <c r="D453" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F453" t="s">
         <v>85</v>
@@ -12744,7 +12722,7 @@
         <v>0</v>
       </c>
       <c r="I453" s="1">
-        <v>46146.669560185182</v>
+        <v>46146.668865740743</v>
       </c>
       <c r="J453">
         <v>0</v>
@@ -12758,19 +12736,19 @@
         <v>22</v>
       </c>
       <c r="C454">
-        <v>5465</v>
+        <v>3509</v>
       </c>
       <c r="D454" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F454" t="s">
         <v>85</v>
       </c>
       <c r="G454" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H454" s="2">
-        <v>7.1875000000000003E-3</v>
+        <v>0</v>
       </c>
       <c r="I454" s="1">
         <v>46146.669560185182</v>
@@ -12783,10 +12761,32 @@
       </c>
     </row>
     <row r="455" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H455" s="2"/>
-      <c r="I455" s="1"/>
+      <c r="B455" t="s">
+        <v>22</v>
+      </c>
+      <c r="C455">
+        <v>5465</v>
+      </c>
+      <c r="D455" t="s">
+        <v>87</v>
+      </c>
+      <c r="F455" t="s">
+        <v>85</v>
+      </c>
+      <c r="G455" t="s">
+        <v>10</v>
+      </c>
+      <c r="H455" s="2">
+        <v>0.14789351851851851</v>
+      </c>
+      <c r="I455" s="1">
+        <v>46146.669560185182</v>
+      </c>
+      <c r="J455">
+        <v>0</v>
+      </c>
       <c r="K455" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="456" spans="2:11" x14ac:dyDescent="0.25">
@@ -12803,10 +12803,10 @@
         <v>85</v>
       </c>
       <c r="G456" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H456" s="2">
-        <v>3.4722222222222222E-5</v>
+        <v>5.0462962962962961E-3</v>
       </c>
       <c r="I456" s="1">
         <v>46146.670254629629</v>
@@ -12819,10 +12819,32 @@
       </c>
     </row>
     <row r="457" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H457" s="2"/>
-      <c r="I457" s="1"/>
+      <c r="B457" t="s">
+        <v>22</v>
+      </c>
+      <c r="C457">
+        <v>3489</v>
+      </c>
+      <c r="D457" t="s">
+        <v>76</v>
+      </c>
+      <c r="F457" t="s">
+        <v>85</v>
+      </c>
+      <c r="G457" t="s">
+        <v>13</v>
+      </c>
+      <c r="H457" s="2">
+        <v>0</v>
+      </c>
+      <c r="I457" s="1">
+        <v>46146.670949074076</v>
+      </c>
+      <c r="J457">
+        <v>0</v>
+      </c>
       <c r="K457" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="458" spans="2:11" x14ac:dyDescent="0.25">
@@ -12830,22 +12852,22 @@
         <v>22</v>
       </c>
       <c r="C458">
-        <v>3489</v>
+        <v>3266</v>
       </c>
       <c r="D458" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F458" t="s">
         <v>85</v>
       </c>
       <c r="G458" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H458" s="2">
-        <v>0</v>
+        <v>4.9652777777777777E-3</v>
       </c>
       <c r="I458" s="1">
-        <v>46146.670949074076</v>
+        <v>46146.671643518515</v>
       </c>
       <c r="J458">
         <v>0</v>
@@ -12859,19 +12881,19 @@
         <v>22</v>
       </c>
       <c r="C459">
-        <v>3266</v>
+        <v>3492</v>
       </c>
       <c r="D459" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F459" t="s">
         <v>85</v>
       </c>
       <c r="G459" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H459" s="2">
-        <v>0</v>
+        <v>5.4745370370370373E-3</v>
       </c>
       <c r="I459" s="1">
         <v>46146.671643518515</v>
@@ -12888,10 +12910,10 @@
         <v>22</v>
       </c>
       <c r="C460">
-        <v>3492</v>
+        <v>3493</v>
       </c>
       <c r="D460" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F460" t="s">
         <v>85</v>
@@ -12903,7 +12925,7 @@
         <v>0</v>
       </c>
       <c r="I460" s="1">
-        <v>46146.671643518515</v>
+        <v>46146.672337962962</v>
       </c>
       <c r="J460">
         <v>0</v>
@@ -12917,19 +12939,19 @@
         <v>22</v>
       </c>
       <c r="C461">
-        <v>3493</v>
+        <v>3505</v>
       </c>
       <c r="D461" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F461" t="s">
         <v>85</v>
       </c>
       <c r="G461" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H461" s="2">
-        <v>0</v>
+        <v>6.030092592592593E-3</v>
       </c>
       <c r="I461" s="1">
         <v>46146.672337962962</v>
@@ -12946,22 +12968,22 @@
         <v>22</v>
       </c>
       <c r="C462">
-        <v>3505</v>
+        <v>3861</v>
       </c>
       <c r="D462" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F462" t="s">
         <v>85</v>
       </c>
       <c r="G462" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H462" s="2">
-        <v>6.030092592592593E-3</v>
+        <v>0</v>
       </c>
       <c r="I462" s="1">
-        <v>46146.672337962962</v>
+        <v>46146.673032407409</v>
       </c>
       <c r="J462">
         <v>0</v>
@@ -12975,10 +12997,10 @@
         <v>22</v>
       </c>
       <c r="C463">
-        <v>3861</v>
+        <v>5205</v>
       </c>
       <c r="D463" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F463" t="s">
         <v>85</v>
@@ -12990,7 +13012,7 @@
         <v>0</v>
       </c>
       <c r="I463" s="1">
-        <v>46146.673032407409</v>
+        <v>46146.673726851855</v>
       </c>
       <c r="J463">
         <v>0</v>
@@ -13004,22 +13026,22 @@
         <v>22</v>
       </c>
       <c r="C464">
-        <v>5205</v>
+        <v>3538</v>
       </c>
       <c r="D464" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F464" t="s">
         <v>85</v>
       </c>
       <c r="G464" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H464" s="2">
-        <v>0</v>
+        <v>5.2893518518518515E-3</v>
       </c>
       <c r="I464" s="1">
-        <v>46146.673726851855</v>
+        <v>46146.674421296295</v>
       </c>
       <c r="J464">
         <v>0</v>
@@ -13028,92 +13050,67 @@
         <v>11</v>
       </c>
     </row>
-    <row r="465" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B465" t="s">
-        <v>22</v>
-      </c>
-      <c r="C465">
-        <v>3538</v>
-      </c>
-      <c r="D465" t="s">
-        <v>82</v>
-      </c>
-      <c r="F465" t="s">
-        <v>85</v>
-      </c>
-      <c r="G465" t="s">
-        <v>13</v>
-      </c>
-      <c r="H465" s="2">
-        <v>0</v>
-      </c>
-      <c r="I465" s="1">
-        <v>46146.674421296295</v>
-      </c>
-      <c r="J465">
-        <v>0</v>
-      </c>
-      <c r="K465" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="466" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="465" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H465" s="2"/>
+      <c r="I465" s="1"/>
+    </row>
+    <row r="466" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H466" s="2"/>
       <c r="I466" s="1"/>
     </row>
-    <row r="467" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="467" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H467" s="2"/>
       <c r="I467" s="1"/>
     </row>
-    <row r="468" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="468" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H468" s="2"/>
       <c r="I468" s="1"/>
     </row>
-    <row r="469" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="469" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H469" s="2"/>
       <c r="I469" s="1"/>
     </row>
-    <row r="470" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="470" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H470" s="2"/>
       <c r="I470" s="1"/>
     </row>
-    <row r="471" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="471" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H471" s="2"/>
       <c r="I471" s="1"/>
     </row>
-    <row r="472" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="472" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H472" s="2"/>
       <c r="I472" s="1"/>
     </row>
-    <row r="473" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="473" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H473" s="2"/>
       <c r="I473" s="1"/>
     </row>
-    <row r="474" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="474" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H474" s="2"/>
       <c r="I474" s="1"/>
     </row>
-    <row r="475" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="475" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H475" s="2"/>
       <c r="I475" s="1"/>
     </row>
-    <row r="476" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="476" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H476" s="2"/>
       <c r="I476" s="1"/>
     </row>
-    <row r="477" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="477" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H477" s="2"/>
       <c r="I477" s="1"/>
     </row>
-    <row r="478" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="478" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H478" s="2"/>
       <c r="I478" s="1"/>
     </row>
-    <row r="479" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="479" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H479" s="2"/>
       <c r="I479" s="1"/>
     </row>
-    <row r="480" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="480" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H480" s="2"/>
       <c r="I480" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Fiore and Sons - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05238650-E74F-4F21-9466-5373E06017B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834601F5-ECDA-4472-8941-28ACC27A76BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="88">
   <si>
     <t>Company Name</t>
   </si>
@@ -299,10 +299,10 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Aldo Salinas</t>
+    <t>Richard Fleckenstein</t>
   </si>
   <si>
-    <t>Richard Fleckenstein</t>
+    <t>Aldo Salinas Montes</t>
   </si>
 </sst>
 </file>
@@ -10391,10 +10391,10 @@
         <v>84</v>
       </c>
       <c r="G366" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H366" s="2">
-        <v>0</v>
+        <v>2.4305555555555555E-4</v>
       </c>
       <c r="I366" s="1">
         <v>46118.754629629628</v>
@@ -10407,32 +10407,10 @@
       </c>
     </row>
     <row r="367" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B367" t="s">
-        <v>22</v>
-      </c>
-      <c r="C367">
-        <v>3704</v>
-      </c>
-      <c r="D367" t="s">
-        <v>50</v>
-      </c>
-      <c r="F367" t="s">
-        <v>84</v>
-      </c>
-      <c r="G367" t="s">
-        <v>13</v>
-      </c>
-      <c r="H367" s="2">
-        <v>0</v>
-      </c>
-      <c r="I367" s="1">
-        <v>46118.755324074074</v>
-      </c>
-      <c r="J367">
-        <v>5</v>
-      </c>
+      <c r="H367" s="2"/>
+      <c r="I367" s="1"/>
       <c r="K367" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="368" spans="2:11" x14ac:dyDescent="0.3">
@@ -10440,25 +10418,25 @@
         <v>22</v>
       </c>
       <c r="C368">
-        <v>3481</v>
+        <v>3704</v>
       </c>
       <c r="D368" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F368" t="s">
         <v>84</v>
       </c>
       <c r="G368" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H368" s="2">
-        <v>7.3379629629629628E-3</v>
+        <v>0</v>
       </c>
       <c r="I368" s="1">
-        <v>46118.756018518521</v>
+        <v>46118.755324074074</v>
       </c>
       <c r="J368">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K368" t="s">
         <v>11</v>
@@ -10469,10 +10447,10 @@
         <v>22</v>
       </c>
       <c r="C369">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="D369" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F369" t="s">
         <v>84</v>
@@ -10481,13 +10459,13 @@
         <v>10</v>
       </c>
       <c r="H369" s="2">
-        <v>1.1342592592592593E-2</v>
+        <v>7.3379629629629628E-3</v>
       </c>
       <c r="I369" s="1">
         <v>46118.756018518521</v>
       </c>
       <c r="J369">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K369" t="s">
         <v>11</v>
@@ -10498,10 +10476,10 @@
         <v>22</v>
       </c>
       <c r="C370">
-        <v>3511</v>
+        <v>3480</v>
       </c>
       <c r="D370" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F370" t="s">
         <v>84</v>
@@ -10510,13 +10488,13 @@
         <v>10</v>
       </c>
       <c r="H370" s="2">
-        <v>1.0393518518518519E-2</v>
+        <v>1.1342592592592593E-2</v>
       </c>
       <c r="I370" s="1">
-        <v>46118.756712962961</v>
+        <v>46118.756018518521</v>
       </c>
       <c r="J370">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K370" t="s">
         <v>11</v>
@@ -10527,10 +10505,10 @@
         <v>22</v>
       </c>
       <c r="C371">
-        <v>3484</v>
+        <v>3511</v>
       </c>
       <c r="D371" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F371" t="s">
         <v>84</v>
@@ -10539,13 +10517,13 @@
         <v>10</v>
       </c>
       <c r="H371" s="2">
-        <v>1.1296296296296296E-2</v>
+        <v>1.0393518518518519E-2</v>
       </c>
       <c r="I371" s="1">
         <v>46118.756712962961</v>
       </c>
       <c r="J371">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K371" t="s">
         <v>11</v>
@@ -10556,10 +10534,10 @@
         <v>22</v>
       </c>
       <c r="C372">
-        <v>3514</v>
+        <v>3484</v>
       </c>
       <c r="D372" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F372" t="s">
         <v>84</v>
@@ -10568,10 +10546,10 @@
         <v>10</v>
       </c>
       <c r="H372" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>1.1296296296296296E-2</v>
       </c>
       <c r="I372" s="1">
-        <v>46118.757407407407</v>
+        <v>46118.756712962961</v>
       </c>
       <c r="J372">
         <v>1</v>
@@ -10585,25 +10563,25 @@
         <v>22</v>
       </c>
       <c r="C373">
-        <v>3725</v>
+        <v>3514</v>
       </c>
       <c r="D373" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F373" t="s">
         <v>84</v>
       </c>
       <c r="G373" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H373" s="2">
-        <v>0</v>
+        <v>7.8009259259259256E-3</v>
       </c>
       <c r="I373" s="1">
-        <v>46118.758101851854</v>
+        <v>46118.757407407407</v>
       </c>
       <c r="J373">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K373" t="s">
         <v>11</v>
@@ -10614,10 +10592,10 @@
         <v>22</v>
       </c>
       <c r="C374">
-        <v>3488</v>
+        <v>3725</v>
       </c>
       <c r="D374" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F374" t="s">
         <v>84</v>
@@ -10626,13 +10604,13 @@
         <v>10</v>
       </c>
       <c r="H374" s="2">
-        <v>6.7824074074074071E-3</v>
+        <v>7.1759259259259259E-3</v>
       </c>
       <c r="I374" s="1">
         <v>46118.758101851854</v>
       </c>
       <c r="J374">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K374" t="s">
         <v>11</v>
@@ -10643,64 +10621,64 @@
         <v>22</v>
       </c>
       <c r="C375">
-        <v>3478</v>
+        <v>3488</v>
       </c>
       <c r="D375" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F375" t="s">
         <v>84</v>
       </c>
       <c r="G375" t="s">
+        <v>10</v>
+      </c>
+      <c r="H375" s="2">
+        <v>6.7824074074074071E-3</v>
+      </c>
+      <c r="I375" s="1">
+        <v>46118.758101851854</v>
+      </c>
+      <c r="J375">
+        <v>0</v>
+      </c>
+      <c r="K375" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="376" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B376" t="s">
+        <v>22</v>
+      </c>
+      <c r="C376">
+        <v>3478</v>
+      </c>
+      <c r="D376" t="s">
+        <v>60</v>
+      </c>
+      <c r="F376" t="s">
+        <v>84</v>
+      </c>
+      <c r="G376" t="s">
         <v>12</v>
       </c>
-      <c r="H375" s="2">
+      <c r="H376" s="2">
         <v>5.7870370370370373E-5</v>
       </c>
-      <c r="I375" s="1">
+      <c r="I376" s="1">
         <v>46118.758796296293</v>
       </c>
-      <c r="J375">
+      <c r="J376">
         <v>1</v>
       </c>
-      <c r="K375" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="376" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H376" s="2"/>
-      <c r="I376" s="1"/>
       <c r="K376" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="377" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H377" s="2"/>
+      <c r="I377" s="1"/>
+      <c r="K377" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="377" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B377" t="s">
-        <v>22</v>
-      </c>
-      <c r="C377">
-        <v>3494</v>
-      </c>
-      <c r="D377" t="s">
-        <v>61</v>
-      </c>
-      <c r="F377" t="s">
-        <v>84</v>
-      </c>
-      <c r="G377" t="s">
-        <v>10</v>
-      </c>
-      <c r="H377" s="2">
-        <v>7.1064814814814819E-3</v>
-      </c>
-      <c r="I377" s="1">
-        <v>46118.758796296293</v>
-      </c>
-      <c r="J377">
-        <v>1</v>
-      </c>
-      <c r="K377" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="378" spans="2:11" x14ac:dyDescent="0.3">
@@ -10708,10 +10686,10 @@
         <v>22</v>
       </c>
       <c r="C378">
-        <v>3523</v>
+        <v>3494</v>
       </c>
       <c r="D378" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F378" t="s">
         <v>84</v>
@@ -10720,13 +10698,13 @@
         <v>10</v>
       </c>
       <c r="H378" s="2">
-        <v>7.5925925925925926E-3</v>
+        <v>7.1064814814814819E-3</v>
       </c>
       <c r="I378" s="1">
-        <v>46118.75949074074</v>
+        <v>46118.758796296293</v>
       </c>
       <c r="J378">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K378" t="s">
         <v>11</v>
@@ -10737,10 +10715,10 @@
         <v>22</v>
       </c>
       <c r="C379">
-        <v>3504</v>
+        <v>3523</v>
       </c>
       <c r="D379" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F379" t="s">
         <v>84</v>
@@ -10749,10 +10727,10 @@
         <v>10</v>
       </c>
       <c r="H379" s="2">
-        <v>1.0763888888888889E-2</v>
+        <v>7.5925925925925926E-3</v>
       </c>
       <c r="I379" s="1">
-        <v>46118.760185185187</v>
+        <v>46118.75949074074</v>
       </c>
       <c r="J379">
         <v>2</v>
@@ -10766,10 +10744,10 @@
         <v>22</v>
       </c>
       <c r="C380">
-        <v>3498</v>
+        <v>3504</v>
       </c>
       <c r="D380" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F380" t="s">
         <v>84</v>
@@ -10778,13 +10756,13 @@
         <v>10</v>
       </c>
       <c r="H380" s="2">
-        <v>8.1250000000000003E-3</v>
+        <v>1.0763888888888889E-2</v>
       </c>
       <c r="I380" s="1">
         <v>46118.760185185187</v>
       </c>
       <c r="J380">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K380" t="s">
         <v>11</v>
@@ -10795,22 +10773,22 @@
         <v>22</v>
       </c>
       <c r="C381">
-        <v>3344</v>
+        <v>3498</v>
       </c>
       <c r="D381" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F381" t="s">
         <v>84</v>
       </c>
       <c r="G381" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H381" s="2">
-        <v>4.6296296296296294E-5</v>
+        <v>8.1250000000000003E-3</v>
       </c>
       <c r="I381" s="1">
-        <v>46118.760879629626</v>
+        <v>46118.760185185187</v>
       </c>
       <c r="J381">
         <v>1</v>
@@ -10820,39 +10798,39 @@
       </c>
     </row>
     <row r="382" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H382" s="2"/>
-      <c r="I382" s="1"/>
+      <c r="B382" t="s">
+        <v>22</v>
+      </c>
+      <c r="C382">
+        <v>3344</v>
+      </c>
+      <c r="D382" t="s">
+        <v>66</v>
+      </c>
+      <c r="F382" t="s">
+        <v>84</v>
+      </c>
+      <c r="G382" t="s">
+        <v>12</v>
+      </c>
+      <c r="H382" s="2">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="I382" s="1">
+        <v>46118.760879629626</v>
+      </c>
+      <c r="J382">
+        <v>1</v>
+      </c>
       <c r="K382" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="383" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H383" s="2"/>
+      <c r="I383" s="1"/>
+      <c r="K383" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="383" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B383" t="s">
-        <v>22</v>
-      </c>
-      <c r="C383">
-        <v>3515</v>
-      </c>
-      <c r="D383" t="s">
-        <v>67</v>
-      </c>
-      <c r="F383" t="s">
-        <v>84</v>
-      </c>
-      <c r="G383" t="s">
-        <v>13</v>
-      </c>
-      <c r="H383" s="2">
-        <v>0</v>
-      </c>
-      <c r="I383" s="1">
-        <v>46118.760879629626</v>
-      </c>
-      <c r="J383">
-        <v>5</v>
-      </c>
-      <c r="K383" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="384" spans="2:11" x14ac:dyDescent="0.3">
@@ -10860,25 +10838,25 @@
         <v>22</v>
       </c>
       <c r="C384">
-        <v>3522</v>
+        <v>3515</v>
       </c>
       <c r="D384" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F384" t="s">
         <v>84</v>
       </c>
       <c r="G384" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H384" s="2">
-        <v>7.5925925925925926E-3</v>
+        <v>0</v>
       </c>
       <c r="I384" s="1">
-        <v>46118.761574074073</v>
+        <v>46118.760879629626</v>
       </c>
       <c r="J384">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K384" t="s">
         <v>11</v>
@@ -10889,25 +10867,25 @@
         <v>22</v>
       </c>
       <c r="C385">
-        <v>3751</v>
+        <v>3522</v>
       </c>
       <c r="D385" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F385" t="s">
         <v>84</v>
       </c>
       <c r="G385" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H385" s="2">
-        <v>0</v>
+        <v>7.5925925925925926E-3</v>
       </c>
       <c r="I385" s="1">
-        <v>46118.76226851852</v>
+        <v>46118.761574074073</v>
       </c>
       <c r="J385">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K385" t="s">
         <v>11</v>
@@ -10918,10 +10896,10 @@
         <v>22</v>
       </c>
       <c r="C386">
-        <v>3662</v>
+        <v>3751</v>
       </c>
       <c r="D386" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F386" t="s">
         <v>84</v>
@@ -10947,25 +10925,25 @@
         <v>22</v>
       </c>
       <c r="C387">
-        <v>3517</v>
+        <v>3662</v>
       </c>
       <c r="D387" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F387" t="s">
         <v>84</v>
       </c>
       <c r="G387" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H387" s="2">
-        <v>7.2800925925925923E-3</v>
+        <v>0</v>
       </c>
       <c r="I387" s="1">
-        <v>46118.762962962966</v>
+        <v>46118.76226851852</v>
       </c>
       <c r="J387">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K387" t="s">
         <v>11</v>
@@ -10976,25 +10954,25 @@
         <v>22</v>
       </c>
       <c r="C388">
-        <v>3503</v>
+        <v>3517</v>
       </c>
       <c r="D388" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F388" t="s">
         <v>84</v>
       </c>
       <c r="G388" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H388" s="2">
-        <v>0</v>
+        <v>7.2800925925925923E-3</v>
       </c>
       <c r="I388" s="1">
         <v>46118.762962962966</v>
       </c>
       <c r="J388">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K388" t="s">
         <v>11</v>
@@ -11005,25 +10983,25 @@
         <v>22</v>
       </c>
       <c r="C389">
-        <v>3652</v>
+        <v>3503</v>
       </c>
       <c r="D389" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F389" t="s">
         <v>84</v>
       </c>
       <c r="G389" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H389" s="2">
-        <v>1.0462962962962962E-2</v>
+        <v>0</v>
       </c>
       <c r="I389" s="1">
-        <v>46118.763657407406</v>
+        <v>46118.762962962966</v>
       </c>
       <c r="J389">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K389" t="s">
         <v>11</v>
@@ -11034,25 +11012,25 @@
         <v>22</v>
       </c>
       <c r="C390">
-        <v>3509</v>
+        <v>3652</v>
       </c>
       <c r="D390" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F390" t="s">
         <v>84</v>
       </c>
       <c r="G390" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H390" s="2">
-        <v>0</v>
+        <v>1.0462962962962962E-2</v>
       </c>
       <c r="I390" s="1">
-        <v>46118.764351851853</v>
+        <v>46118.763657407406</v>
       </c>
       <c r="J390">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K390" t="s">
         <v>11</v>
@@ -11063,25 +11041,25 @@
         <v>22</v>
       </c>
       <c r="C391">
-        <v>3512</v>
+        <v>3509</v>
       </c>
       <c r="D391" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F391" t="s">
         <v>84</v>
       </c>
       <c r="G391" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H391" s="2">
-        <v>7.3726851851851852E-3</v>
+        <v>0</v>
       </c>
       <c r="I391" s="1">
-        <v>46118.765046296299</v>
+        <v>46118.764351851853</v>
       </c>
       <c r="J391">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K391" t="s">
         <v>11</v>
@@ -11092,10 +11070,10 @@
         <v>22</v>
       </c>
       <c r="C392">
-        <v>3489</v>
+        <v>3512</v>
       </c>
       <c r="D392" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F392" t="s">
         <v>84</v>
@@ -11104,13 +11082,13 @@
         <v>10</v>
       </c>
       <c r="H392" s="2">
-        <v>7.5462962962962966E-3</v>
+        <v>7.3726851851851852E-3</v>
       </c>
       <c r="I392" s="1">
         <v>46118.765046296299</v>
       </c>
       <c r="J392">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K392" t="s">
         <v>11</v>
@@ -11121,10 +11099,10 @@
         <v>22</v>
       </c>
       <c r="C393">
-        <v>3266</v>
+        <v>3489</v>
       </c>
       <c r="D393" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F393" t="s">
         <v>84</v>
@@ -11133,13 +11111,13 @@
         <v>10</v>
       </c>
       <c r="H393" s="2">
-        <v>7.3842592592592597E-3</v>
+        <v>7.5462962962962966E-3</v>
       </c>
       <c r="I393" s="1">
-        <v>46118.765740740739</v>
+        <v>46118.765046296299</v>
       </c>
       <c r="J393">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K393" t="s">
         <v>11</v>
@@ -11150,10 +11128,10 @@
         <v>22</v>
       </c>
       <c r="C394">
-        <v>3492</v>
+        <v>3266</v>
       </c>
       <c r="D394" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F394" t="s">
         <v>84</v>
@@ -11162,13 +11140,13 @@
         <v>10</v>
       </c>
       <c r="H394" s="2">
-        <v>9.8958333333333329E-3</v>
+        <v>7.3842592592592597E-3</v>
       </c>
       <c r="I394" s="1">
-        <v>46118.766435185185</v>
+        <v>46118.765740740739</v>
       </c>
       <c r="J394">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K394" t="s">
         <v>11</v>
@@ -11179,25 +11157,25 @@
         <v>22</v>
       </c>
       <c r="C395">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="D395" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F395" t="s">
         <v>84</v>
       </c>
       <c r="G395" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H395" s="2">
-        <v>0</v>
+        <v>9.8958333333333329E-3</v>
       </c>
       <c r="I395" s="1">
         <v>46118.766435185185</v>
       </c>
       <c r="J395">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K395" t="s">
         <v>11</v>
@@ -11208,64 +11186,64 @@
         <v>22</v>
       </c>
       <c r="C396">
-        <v>3505</v>
+        <v>3493</v>
       </c>
       <c r="D396" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F396" t="s">
         <v>84</v>
       </c>
       <c r="G396" t="s">
+        <v>13</v>
+      </c>
+      <c r="H396" s="2">
+        <v>0</v>
+      </c>
+      <c r="I396" s="1">
+        <v>46118.766435185185</v>
+      </c>
+      <c r="J396">
+        <v>5</v>
+      </c>
+      <c r="K396" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="397" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B397" t="s">
+        <v>22</v>
+      </c>
+      <c r="C397">
+        <v>3505</v>
+      </c>
+      <c r="D397" t="s">
+        <v>80</v>
+      </c>
+      <c r="F397" t="s">
+        <v>84</v>
+      </c>
+      <c r="G397" t="s">
         <v>12</v>
       </c>
-      <c r="H396" s="2">
+      <c r="H397" s="2">
         <v>6.145833333333333E-3</v>
       </c>
-      <c r="I396" s="1">
+      <c r="I397" s="1">
         <v>46118.767129629632</v>
       </c>
-      <c r="J396">
+      <c r="J397">
         <v>0</v>
       </c>
-      <c r="K396" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="397" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H397" s="2"/>
-      <c r="I397" s="1"/>
       <c r="K397" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="398" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H398" s="2"/>
+      <c r="I398" s="1"/>
+      <c r="K398" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="398" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B398" t="s">
-        <v>22</v>
-      </c>
-      <c r="C398">
-        <v>3861</v>
-      </c>
-      <c r="D398" t="s">
-        <v>81</v>
-      </c>
-      <c r="F398" t="s">
-        <v>84</v>
-      </c>
-      <c r="G398" t="s">
-        <v>10</v>
-      </c>
-      <c r="H398" s="2">
-        <v>7.3611111111111108E-3</v>
-      </c>
-      <c r="I398" s="1">
-        <v>46118.767824074072</v>
-      </c>
-      <c r="J398">
-        <v>1</v>
-      </c>
-      <c r="K398" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="399" spans="2:11" x14ac:dyDescent="0.3">
@@ -11273,10 +11251,10 @@
         <v>22</v>
       </c>
       <c r="C399">
-        <v>5205</v>
+        <v>3861</v>
       </c>
       <c r="D399" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F399" t="s">
         <v>84</v>
@@ -11285,13 +11263,13 @@
         <v>10</v>
       </c>
       <c r="H399" s="2">
-        <v>7.6273148148148151E-3</v>
+        <v>7.3611111111111108E-3</v>
       </c>
       <c r="I399" s="1">
         <v>46118.767824074072</v>
       </c>
       <c r="J399">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K399" t="s">
         <v>11</v>
@@ -11302,10 +11280,10 @@
         <v>22</v>
       </c>
       <c r="C400">
-        <v>3538</v>
+        <v>5205</v>
       </c>
       <c r="D400" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F400" t="s">
         <v>84</v>
@@ -11314,13 +11292,13 @@
         <v>10</v>
       </c>
       <c r="H400" s="2">
-        <v>9.8032407407407408E-3</v>
+        <v>7.6273148148148151E-3</v>
       </c>
       <c r="I400" s="1">
-        <v>46118.768518518518</v>
+        <v>46118.767824074072</v>
       </c>
       <c r="J400">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K400" t="s">
         <v>11</v>
@@ -11331,25 +11309,25 @@
         <v>22</v>
       </c>
       <c r="C401">
-        <v>3200</v>
+        <v>3538</v>
       </c>
       <c r="D401" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="F401" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G401" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H401" s="2">
+        <v>9.8032407407407408E-3</v>
+      </c>
+      <c r="I401" s="1">
+        <v>46118.768518518518</v>
+      </c>
+      <c r="J401">
         <v>0</v>
-      </c>
-      <c r="I401" s="1">
-        <v>46146.67083333333</v>
-      </c>
-      <c r="J401">
-        <v>1</v>
       </c>
       <c r="K401" t="s">
         <v>11</v>
@@ -11360,25 +11338,25 @@
         <v>22</v>
       </c>
       <c r="C402">
-        <v>3501</v>
+        <v>3200</v>
       </c>
       <c r="D402" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F402" t="s">
         <v>85</v>
       </c>
       <c r="G402" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H402" s="2">
-        <v>4.31712962962963E-3</v>
+        <v>0</v>
       </c>
       <c r="I402" s="1">
-        <v>46146.671527777777</v>
+        <v>46146.67083333333</v>
       </c>
       <c r="J402">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K402" t="s">
         <v>11</v>
@@ -11389,10 +11367,10 @@
         <v>22</v>
       </c>
       <c r="C403">
-        <v>4915</v>
+        <v>3501</v>
       </c>
       <c r="D403" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F403" t="s">
         <v>85</v>
@@ -11404,7 +11382,7 @@
         <v>4.31712962962963E-3</v>
       </c>
       <c r="I403" s="1">
-        <v>46146.672222222223</v>
+        <v>46146.671527777777</v>
       </c>
       <c r="J403">
         <v>0</v>
@@ -11418,19 +11396,19 @@
         <v>22</v>
       </c>
       <c r="C404">
-        <v>5524</v>
+        <v>4915</v>
       </c>
       <c r="D404" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="F404" t="s">
         <v>85</v>
       </c>
       <c r="G404" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H404" s="2">
-        <v>2.6620370370370372E-4</v>
+        <v>4.31712962962963E-3</v>
       </c>
       <c r="I404" s="1">
         <v>46146.672222222223</v>
@@ -11443,39 +11421,39 @@
       </c>
     </row>
     <row r="405" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H405" s="2"/>
-      <c r="I405" s="1"/>
+      <c r="B405" t="s">
+        <v>22</v>
+      </c>
+      <c r="C405">
+        <v>5524</v>
+      </c>
+      <c r="D405" t="s">
+        <v>87</v>
+      </c>
+      <c r="F405" t="s">
+        <v>85</v>
+      </c>
+      <c r="G405" t="s">
+        <v>12</v>
+      </c>
+      <c r="H405" s="2">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="I405" s="1">
+        <v>46146.672222222223</v>
+      </c>
+      <c r="J405">
+        <v>0</v>
+      </c>
       <c r="K405" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="406" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H406" s="2"/>
+      <c r="I406" s="1"/>
+      <c r="K406" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="406" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B406" t="s">
-        <v>22</v>
-      </c>
-      <c r="C406">
-        <v>3360</v>
-      </c>
-      <c r="D406" t="s">
-        <v>26</v>
-      </c>
-      <c r="F406" t="s">
-        <v>85</v>
-      </c>
-      <c r="G406" t="s">
-        <v>10</v>
-      </c>
-      <c r="H406" s="2">
-        <v>8.8541666666666664E-3</v>
-      </c>
-      <c r="I406" s="1">
-        <v>46146.67291666667</v>
-      </c>
-      <c r="J406">
-        <v>1</v>
-      </c>
-      <c r="K406" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="407" spans="2:11" x14ac:dyDescent="0.3">
@@ -11483,22 +11461,22 @@
         <v>22</v>
       </c>
       <c r="C407">
-        <v>3521</v>
+        <v>3360</v>
       </c>
       <c r="D407" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F407" t="s">
         <v>85</v>
       </c>
       <c r="G407" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H407" s="2">
-        <v>0</v>
+        <v>8.8541666666666664E-3</v>
       </c>
       <c r="I407" s="1">
-        <v>46146.673611111109</v>
+        <v>46146.67291666667</v>
       </c>
       <c r="J407">
         <v>1</v>
@@ -11512,25 +11490,25 @@
         <v>22</v>
       </c>
       <c r="C408">
-        <v>3479</v>
+        <v>3521</v>
       </c>
       <c r="D408" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F408" t="s">
         <v>85</v>
       </c>
       <c r="G408" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H408" s="2">
-        <v>1.1909722222222223E-2</v>
+        <v>0</v>
       </c>
       <c r="I408" s="1">
         <v>46146.673611111109</v>
       </c>
       <c r="J408">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K408" t="s">
         <v>11</v>
@@ -11541,25 +11519,25 @@
         <v>22</v>
       </c>
       <c r="C409">
-        <v>3526</v>
+        <v>3479</v>
       </c>
       <c r="D409" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F409" t="s">
         <v>85</v>
       </c>
       <c r="G409" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H409" s="2">
+        <v>1.1909722222222223E-2</v>
+      </c>
+      <c r="I409" s="1">
+        <v>46146.673611111109</v>
+      </c>
+      <c r="J409">
         <v>0</v>
-      </c>
-      <c r="I409" s="1">
-        <v>46146.674305555556</v>
-      </c>
-      <c r="J409">
-        <v>1</v>
       </c>
       <c r="K409" t="s">
         <v>11</v>
@@ -11570,10 +11548,10 @@
         <v>22</v>
       </c>
       <c r="C410">
-        <v>4917</v>
+        <v>3526</v>
       </c>
       <c r="D410" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F410" t="s">
         <v>85</v>
@@ -11585,10 +11563,10 @@
         <v>0</v>
       </c>
       <c r="I410" s="1">
-        <v>46146.675000000003</v>
+        <v>46146.674305555556</v>
       </c>
       <c r="J410">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K410" t="s">
         <v>11</v>
@@ -11599,10 +11577,10 @@
         <v>22</v>
       </c>
       <c r="C411">
-        <v>3524</v>
+        <v>4917</v>
       </c>
       <c r="D411" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F411" t="s">
         <v>85</v>
@@ -11617,7 +11595,7 @@
         <v>46146.675000000003</v>
       </c>
       <c r="J411">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K411" t="s">
         <v>11</v>
@@ -11628,10 +11606,10 @@
         <v>22</v>
       </c>
       <c r="C412">
-        <v>3804</v>
+        <v>3524</v>
       </c>
       <c r="D412" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F412" t="s">
         <v>85</v>
@@ -11643,10 +11621,10 @@
         <v>0</v>
       </c>
       <c r="I412" s="1">
-        <v>46146.675694444442</v>
+        <v>46146.675000000003</v>
       </c>
       <c r="J412">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K412" t="s">
         <v>11</v>
@@ -11657,25 +11635,25 @@
         <v>22</v>
       </c>
       <c r="C413">
-        <v>3495</v>
+        <v>3804</v>
       </c>
       <c r="D413" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F413" t="s">
         <v>85</v>
       </c>
       <c r="G413" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H413" s="2">
-        <v>4.43287037037037E-3</v>
+        <v>0</v>
       </c>
       <c r="I413" s="1">
-        <v>46146.676388888889</v>
+        <v>46146.675694444442</v>
       </c>
       <c r="J413">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K413" t="s">
         <v>11</v>
@@ -11686,22 +11664,22 @@
         <v>22</v>
       </c>
       <c r="C414">
-        <v>3739</v>
+        <v>3495</v>
       </c>
       <c r="D414" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F414" t="s">
         <v>85</v>
       </c>
       <c r="G414" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H414" s="2">
-        <v>5.2430555555555555E-3</v>
+        <v>4.43287037037037E-3</v>
       </c>
       <c r="I414" s="1">
-        <v>46146.677083333336</v>
+        <v>46146.676388888889</v>
       </c>
       <c r="J414">
         <v>0</v>
@@ -11711,39 +11689,39 @@
       </c>
     </row>
     <row r="415" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H415" s="2"/>
-      <c r="I415" s="1"/>
+      <c r="B415" t="s">
+        <v>22</v>
+      </c>
+      <c r="C415">
+        <v>3739</v>
+      </c>
+      <c r="D415" t="s">
+        <v>34</v>
+      </c>
+      <c r="F415" t="s">
+        <v>85</v>
+      </c>
+      <c r="G415" t="s">
+        <v>12</v>
+      </c>
+      <c r="H415" s="2">
+        <v>5.2430555555555555E-3</v>
+      </c>
+      <c r="I415" s="1">
+        <v>46146.677083333336</v>
+      </c>
+      <c r="J415">
+        <v>0</v>
+      </c>
       <c r="K415" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="416" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H416" s="2"/>
+      <c r="I416" s="1"/>
+      <c r="K416" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="416" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B416" t="s">
-        <v>22</v>
-      </c>
-      <c r="C416">
-        <v>3520</v>
-      </c>
-      <c r="D416" t="s">
-        <v>35</v>
-      </c>
-      <c r="F416" t="s">
-        <v>85</v>
-      </c>
-      <c r="G416" t="s">
-        <v>13</v>
-      </c>
-      <c r="H416" s="2">
-        <v>0</v>
-      </c>
-      <c r="I416" s="1">
-        <v>46146.677083333336</v>
-      </c>
-      <c r="J416">
-        <v>2</v>
-      </c>
-      <c r="K416" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="417" spans="2:11" x14ac:dyDescent="0.3">
@@ -11751,10 +11729,10 @@
         <v>22</v>
       </c>
       <c r="C417">
-        <v>3486</v>
+        <v>3520</v>
       </c>
       <c r="D417" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F417" t="s">
         <v>85</v>
@@ -11763,13 +11741,13 @@
         <v>10</v>
       </c>
       <c r="H417" s="2">
-        <v>5.347222222222222E-3</v>
+        <v>5.6481481481481478E-3</v>
       </c>
       <c r="I417" s="1">
-        <v>46146.677777777775</v>
+        <v>46146.677083333336</v>
       </c>
       <c r="J417">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K417" t="s">
         <v>11</v>
@@ -11780,10 +11758,10 @@
         <v>22</v>
       </c>
       <c r="C418">
-        <v>3886</v>
+        <v>3486</v>
       </c>
       <c r="D418" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F418" t="s">
         <v>85</v>
@@ -11792,13 +11770,13 @@
         <v>10</v>
       </c>
       <c r="H418" s="2">
-        <v>4.6527777777777774E-3</v>
+        <v>5.347222222222222E-3</v>
       </c>
       <c r="I418" s="1">
-        <v>46146.678472222222</v>
+        <v>46146.677777777775</v>
       </c>
       <c r="J418">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K418" t="s">
         <v>11</v>
@@ -11809,25 +11787,25 @@
         <v>22</v>
       </c>
       <c r="C419">
-        <v>3397</v>
+        <v>3886</v>
       </c>
       <c r="D419" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F419" t="s">
         <v>85</v>
       </c>
       <c r="G419" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H419" s="2">
-        <v>0</v>
+        <v>4.6527777777777774E-3</v>
       </c>
       <c r="I419" s="1">
         <v>46146.678472222222</v>
       </c>
       <c r="J419">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K419" t="s">
         <v>11</v>
@@ -11838,25 +11816,25 @@
         <v>22</v>
       </c>
       <c r="C420">
-        <v>3765</v>
+        <v>3397</v>
       </c>
       <c r="D420" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F420" t="s">
         <v>85</v>
       </c>
       <c r="G420" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H420" s="2">
-        <v>0</v>
+        <v>4.1666666666666669E-4</v>
       </c>
       <c r="I420" s="1">
-        <v>46146.679166666669</v>
+        <v>46146.678472222222</v>
       </c>
       <c r="J420">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K420" t="s">
         <v>11</v>
@@ -11874,57 +11852,35 @@
         <v>22</v>
       </c>
       <c r="C422">
-        <v>3496</v>
+        <v>3765</v>
       </c>
       <c r="D422" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F422" t="s">
         <v>85</v>
       </c>
       <c r="G422" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H422" s="2">
         <v>0</v>
       </c>
       <c r="I422" s="1">
-        <v>46146.679861111108</v>
+        <v>46146.679166666669</v>
       </c>
       <c r="J422">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K422" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="423" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B423" t="s">
-        <v>22</v>
-      </c>
-      <c r="C423">
-        <v>3525</v>
-      </c>
-      <c r="D423" t="s">
-        <v>42</v>
-      </c>
-      <c r="F423" t="s">
-        <v>85</v>
-      </c>
-      <c r="G423" t="s">
-        <v>10</v>
-      </c>
-      <c r="H423" s="2">
-        <v>5.5208333333333333E-3</v>
-      </c>
-      <c r="I423" s="1">
-        <v>46146.680555555555</v>
-      </c>
-      <c r="J423">
-        <v>0</v>
-      </c>
+      <c r="H423" s="2"/>
+      <c r="I423" s="1"/>
       <c r="K423" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="424" spans="2:11" x14ac:dyDescent="0.3">
@@ -11932,10 +11888,10 @@
         <v>22</v>
       </c>
       <c r="C424">
-        <v>3513</v>
+        <v>3496</v>
       </c>
       <c r="D424" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F424" t="s">
         <v>85</v>
@@ -11947,10 +11903,10 @@
         <v>0</v>
       </c>
       <c r="I424" s="1">
-        <v>46146.680555555555</v>
+        <v>46146.679861111108</v>
       </c>
       <c r="J424">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K424" t="s">
         <v>11</v>
@@ -11961,25 +11917,25 @@
         <v>22</v>
       </c>
       <c r="C425">
-        <v>3508</v>
+        <v>3525</v>
       </c>
       <c r="D425" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F425" t="s">
         <v>85</v>
       </c>
       <c r="G425" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H425" s="2">
+        <v>5.5208333333333333E-3</v>
+      </c>
+      <c r="I425" s="1">
+        <v>46146.680555555555</v>
+      </c>
+      <c r="J425">
         <v>0</v>
-      </c>
-      <c r="I425" s="1">
-        <v>46146.681250000001</v>
-      </c>
-      <c r="J425">
-        <v>2</v>
       </c>
       <c r="K425" t="s">
         <v>11</v>
@@ -11990,10 +11946,10 @@
         <v>22</v>
       </c>
       <c r="C426">
-        <v>3483</v>
+        <v>3513</v>
       </c>
       <c r="D426" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F426" t="s">
         <v>85</v>
@@ -12005,10 +11961,10 @@
         <v>0</v>
       </c>
       <c r="I426" s="1">
-        <v>46146.681944444441</v>
+        <v>46146.680555555555</v>
       </c>
       <c r="J426">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K426" t="s">
         <v>11</v>
@@ -12019,35 +11975,57 @@
         <v>22</v>
       </c>
       <c r="C427">
-        <v>3499</v>
+        <v>3508</v>
       </c>
       <c r="D427" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F427" t="s">
         <v>85</v>
       </c>
       <c r="G427" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H427" s="2">
         <v>0</v>
       </c>
       <c r="I427" s="1">
+        <v>46146.681250000001</v>
+      </c>
+      <c r="J427">
+        <v>3</v>
+      </c>
+      <c r="K427" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="428" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B428" t="s">
+        <v>22</v>
+      </c>
+      <c r="C428">
+        <v>3483</v>
+      </c>
+      <c r="D428" t="s">
+        <v>45</v>
+      </c>
+      <c r="F428" t="s">
+        <v>85</v>
+      </c>
+      <c r="G428" t="s">
+        <v>13</v>
+      </c>
+      <c r="H428" s="2">
+        <v>0</v>
+      </c>
+      <c r="I428" s="1">
         <v>46146.681944444441</v>
       </c>
-      <c r="J427">
-        <v>1</v>
-      </c>
-      <c r="K427" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="428" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H428" s="2"/>
-      <c r="I428" s="1"/>
+      <c r="J428">
+        <v>3</v>
+      </c>
       <c r="K428" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="429" spans="2:11" x14ac:dyDescent="0.3">
@@ -12055,25 +12033,25 @@
         <v>22</v>
       </c>
       <c r="C429">
-        <v>3699</v>
+        <v>3499</v>
       </c>
       <c r="D429" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F429" t="s">
         <v>85</v>
       </c>
       <c r="G429" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H429" s="2">
         <v>0</v>
       </c>
       <c r="I429" s="1">
-        <v>46146.682638888888</v>
+        <v>46146.681944444441</v>
       </c>
       <c r="J429">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K429" t="s">
         <v>11</v>
@@ -12091,57 +12069,35 @@
         <v>22</v>
       </c>
       <c r="C431">
-        <v>3491</v>
+        <v>3699</v>
       </c>
       <c r="D431" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F431" t="s">
         <v>85</v>
       </c>
       <c r="G431" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H431" s="2">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="I431" s="1">
+        <v>46146.682638888888</v>
+      </c>
+      <c r="J431">
         <v>0</v>
       </c>
-      <c r="I431" s="1">
-        <v>46146.683333333334</v>
-      </c>
-      <c r="J431">
-        <v>1</v>
-      </c>
       <c r="K431" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="432" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B432" t="s">
-        <v>22</v>
-      </c>
-      <c r="C432">
-        <v>3487</v>
-      </c>
-      <c r="D432" t="s">
-        <v>49</v>
-      </c>
-      <c r="F432" t="s">
-        <v>85</v>
-      </c>
-      <c r="G432" t="s">
-        <v>13</v>
-      </c>
-      <c r="H432" s="2">
-        <v>0</v>
-      </c>
-      <c r="I432" s="1">
-        <v>46146.683333333334</v>
-      </c>
-      <c r="J432">
-        <v>1</v>
-      </c>
+      <c r="H432" s="2"/>
+      <c r="I432" s="1"/>
       <c r="K432" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="433" spans="2:11" x14ac:dyDescent="0.3">
@@ -12149,10 +12105,10 @@
         <v>22</v>
       </c>
       <c r="C433">
-        <v>3704</v>
+        <v>3491</v>
       </c>
       <c r="D433" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F433" t="s">
         <v>85</v>
@@ -12164,10 +12120,10 @@
         <v>0</v>
       </c>
       <c r="I433" s="1">
-        <v>46146.684027777781</v>
+        <v>46146.683333333334</v>
       </c>
       <c r="J433">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K433" t="s">
         <v>11</v>
@@ -12178,25 +12134,25 @@
         <v>22</v>
       </c>
       <c r="C434">
-        <v>3481</v>
+        <v>3487</v>
       </c>
       <c r="D434" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F434" t="s">
         <v>85</v>
       </c>
       <c r="G434" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H434" s="2">
-        <v>0</v>
+        <v>4.8958333333333336E-3</v>
       </c>
       <c r="I434" s="1">
-        <v>46146.68472222222</v>
+        <v>46146.683333333334</v>
       </c>
       <c r="J434">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K434" t="s">
         <v>11</v>
@@ -12207,25 +12163,25 @@
         <v>22</v>
       </c>
       <c r="C435">
-        <v>3480</v>
+        <v>3704</v>
       </c>
       <c r="D435" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F435" t="s">
         <v>85</v>
       </c>
       <c r="G435" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H435" s="2">
-        <v>6.7939814814814816E-3</v>
+        <v>0</v>
       </c>
       <c r="I435" s="1">
-        <v>46146.68472222222</v>
+        <v>46146.684027777781</v>
       </c>
       <c r="J435">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K435" t="s">
         <v>11</v>
@@ -12236,10 +12192,10 @@
         <v>22</v>
       </c>
       <c r="C436">
-        <v>3511</v>
+        <v>3481</v>
       </c>
       <c r="D436" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F436" t="s">
         <v>85</v>
@@ -12248,13 +12204,13 @@
         <v>10</v>
       </c>
       <c r="H436" s="2">
-        <v>6.3194444444444444E-3</v>
+        <v>0.10783564814814815</v>
       </c>
       <c r="I436" s="1">
-        <v>46146.685416666667</v>
+        <v>46146.68472222222</v>
       </c>
       <c r="J436">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K436" t="s">
         <v>11</v>
@@ -12265,10 +12221,10 @@
         <v>22</v>
       </c>
       <c r="C437">
-        <v>3484</v>
+        <v>3480</v>
       </c>
       <c r="D437" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F437" t="s">
         <v>85</v>
@@ -12277,10 +12233,10 @@
         <v>10</v>
       </c>
       <c r="H437" s="2">
-        <v>5.3935185185185188E-3</v>
+        <v>6.7939814814814816E-3</v>
       </c>
       <c r="I437" s="1">
-        <v>46146.686111111114</v>
+        <v>46146.68472222222</v>
       </c>
       <c r="J437">
         <v>0</v>
@@ -12294,10 +12250,10 @@
         <v>22</v>
       </c>
       <c r="C438">
-        <v>3514</v>
+        <v>3511</v>
       </c>
       <c r="D438" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F438" t="s">
         <v>85</v>
@@ -12306,10 +12262,10 @@
         <v>10</v>
       </c>
       <c r="H438" s="2">
-        <v>4.4027777777777777E-2</v>
+        <v>6.3194444444444444E-3</v>
       </c>
       <c r="I438" s="1">
-        <v>46146.686111111114</v>
+        <v>46146.685416666667</v>
       </c>
       <c r="J438">
         <v>0</v>
@@ -12323,25 +12279,25 @@
         <v>22</v>
       </c>
       <c r="C439">
-        <v>3725</v>
+        <v>3484</v>
       </c>
       <c r="D439" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F439" t="s">
         <v>85</v>
       </c>
       <c r="G439" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H439" s="2">
+        <v>5.3935185185185188E-3</v>
+      </c>
+      <c r="I439" s="1">
+        <v>46146.686111111114</v>
+      </c>
+      <c r="J439">
         <v>0</v>
-      </c>
-      <c r="I439" s="1">
-        <v>46146.686805555553</v>
-      </c>
-      <c r="J439">
-        <v>1</v>
       </c>
       <c r="K439" t="s">
         <v>11</v>
@@ -12352,22 +12308,22 @@
         <v>22</v>
       </c>
       <c r="C440">
-        <v>3488</v>
+        <v>3514</v>
       </c>
       <c r="D440" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F440" t="s">
         <v>85</v>
       </c>
       <c r="G440" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H440" s="2">
-        <v>9.2592592592592588E-5</v>
+        <v>4.4027777777777777E-2</v>
       </c>
       <c r="I440" s="1">
-        <v>46146.6875</v>
+        <v>46146.686111111114</v>
       </c>
       <c r="J440">
         <v>0</v>
@@ -12377,10 +12333,32 @@
       </c>
     </row>
     <row r="441" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H441" s="2"/>
-      <c r="I441" s="1"/>
+      <c r="B441" t="s">
+        <v>22</v>
+      </c>
+      <c r="C441">
+        <v>3725</v>
+      </c>
+      <c r="D441" t="s">
+        <v>58</v>
+      </c>
+      <c r="F441" t="s">
+        <v>85</v>
+      </c>
+      <c r="G441" t="s">
+        <v>10</v>
+      </c>
+      <c r="H441" s="2">
+        <v>6.898148148148148E-3</v>
+      </c>
+      <c r="I441" s="1">
+        <v>46146.686805555553</v>
+      </c>
+      <c r="J441">
+        <v>2</v>
+      </c>
       <c r="K441" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="442" spans="2:11" x14ac:dyDescent="0.3">
@@ -12388,57 +12366,35 @@
         <v>22</v>
       </c>
       <c r="C442">
-        <v>3478</v>
+        <v>3488</v>
       </c>
       <c r="D442" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F442" t="s">
         <v>85</v>
       </c>
       <c r="G442" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H442" s="2">
-        <v>0</v>
+        <v>9.2592592592592588E-5</v>
       </c>
       <c r="I442" s="1">
         <v>46146.6875</v>
       </c>
       <c r="J442">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K442" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="443" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B443" t="s">
-        <v>22</v>
-      </c>
-      <c r="C443">
-        <v>3494</v>
-      </c>
-      <c r="D443" t="s">
-        <v>61</v>
-      </c>
-      <c r="F443" t="s">
-        <v>85</v>
-      </c>
-      <c r="G443" t="s">
-        <v>10</v>
-      </c>
-      <c r="H443" s="2">
-        <v>5.2199074074074075E-3</v>
-      </c>
-      <c r="I443" s="1">
-        <v>46146.688194444447</v>
-      </c>
-      <c r="J443">
-        <v>0</v>
-      </c>
+      <c r="H443" s="2"/>
+      <c r="I443" s="1"/>
       <c r="K443" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="444" spans="2:11" x14ac:dyDescent="0.3">
@@ -12446,35 +12402,57 @@
         <v>22</v>
       </c>
       <c r="C444">
-        <v>3523</v>
+        <v>3478</v>
       </c>
       <c r="D444" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F444" t="s">
         <v>85</v>
       </c>
       <c r="G444" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H444" s="2">
-        <v>1.5393518518518519E-3</v>
+        <v>4.8379629629629632E-3</v>
       </c>
       <c r="I444" s="1">
-        <v>46146.688888888886</v>
+        <v>46146.6875</v>
       </c>
       <c r="J444">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K444" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="445" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H445" s="2"/>
-      <c r="I445" s="1"/>
+      <c r="B445" t="s">
+        <v>22</v>
+      </c>
+      <c r="C445">
+        <v>3494</v>
+      </c>
+      <c r="D445" t="s">
+        <v>61</v>
+      </c>
+      <c r="F445" t="s">
+        <v>85</v>
+      </c>
+      <c r="G445" t="s">
+        <v>10</v>
+      </c>
+      <c r="H445" s="2">
+        <v>5.2199074074074075E-3</v>
+      </c>
+      <c r="I445" s="1">
+        <v>46146.688194444447</v>
+      </c>
+      <c r="J445">
+        <v>0</v>
+      </c>
       <c r="K445" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="446" spans="2:11" x14ac:dyDescent="0.3">
@@ -12482,19 +12460,19 @@
         <v>22</v>
       </c>
       <c r="C446">
-        <v>3504</v>
+        <v>3523</v>
       </c>
       <c r="D446" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F446" t="s">
         <v>85</v>
       </c>
       <c r="G446" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H446" s="2">
-        <v>0</v>
+        <v>6.6550925925925927E-3</v>
       </c>
       <c r="I446" s="1">
         <v>46146.688888888886</v>
@@ -12511,25 +12489,25 @@
         <v>22</v>
       </c>
       <c r="C447">
-        <v>3498</v>
+        <v>3504</v>
       </c>
       <c r="D447" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F447" t="s">
         <v>85</v>
       </c>
       <c r="G447" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H447" s="2">
-        <v>6.2037037037037035E-3</v>
+        <v>0</v>
       </c>
       <c r="I447" s="1">
-        <v>46146.689583333333</v>
+        <v>46146.688888888886</v>
       </c>
       <c r="J447">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K447" t="s">
         <v>11</v>
@@ -12540,25 +12518,25 @@
         <v>22</v>
       </c>
       <c r="C448">
-        <v>3344</v>
+        <v>3498</v>
       </c>
       <c r="D448" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F448" t="s">
         <v>85</v>
       </c>
       <c r="G448" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H448" s="2">
+        <v>6.2037037037037035E-3</v>
+      </c>
+      <c r="I448" s="1">
+        <v>46146.689583333333</v>
+      </c>
+      <c r="J448">
         <v>0</v>
-      </c>
-      <c r="I448" s="1">
-        <v>46146.69027777778</v>
-      </c>
-      <c r="J448">
-        <v>1</v>
       </c>
       <c r="K448" t="s">
         <v>11</v>
@@ -12569,10 +12547,10 @@
         <v>22</v>
       </c>
       <c r="C449">
-        <v>3515</v>
+        <v>3344</v>
       </c>
       <c r="D449" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F449" t="s">
         <v>85</v>
@@ -12584,10 +12562,10 @@
         <v>0</v>
       </c>
       <c r="I449" s="1">
-        <v>46146.690972222219</v>
+        <v>46146.69027777778</v>
       </c>
       <c r="J449">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K449" t="s">
         <v>11</v>
@@ -12598,25 +12576,25 @@
         <v>22</v>
       </c>
       <c r="C450">
-        <v>3522</v>
+        <v>3515</v>
       </c>
       <c r="D450" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F450" t="s">
         <v>85</v>
       </c>
       <c r="G450" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H450" s="2">
-        <v>4.6412037037037038E-3</v>
+        <v>0</v>
       </c>
       <c r="I450" s="1">
         <v>46146.690972222219</v>
       </c>
       <c r="J450">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K450" t="s">
         <v>11</v>
@@ -12627,25 +12605,25 @@
         <v>22</v>
       </c>
       <c r="C451">
-        <v>3751</v>
+        <v>3522</v>
       </c>
       <c r="D451" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F451" t="s">
         <v>85</v>
       </c>
       <c r="G451" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H451" s="2">
+        <v>4.6412037037037038E-3</v>
+      </c>
+      <c r="I451" s="1">
+        <v>46146.690972222219</v>
+      </c>
+      <c r="J451">
         <v>0</v>
-      </c>
-      <c r="I451" s="1">
-        <v>46146.691666666666</v>
-      </c>
-      <c r="J451">
-        <v>1</v>
       </c>
       <c r="K451" t="s">
         <v>11</v>
@@ -12656,10 +12634,10 @@
         <v>22</v>
       </c>
       <c r="C452">
-        <v>3662</v>
+        <v>3751</v>
       </c>
       <c r="D452" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F452" t="s">
         <v>85</v>
@@ -12671,10 +12649,10 @@
         <v>0</v>
       </c>
       <c r="I452" s="1">
-        <v>46146.692361111112</v>
+        <v>46146.691666666666</v>
       </c>
       <c r="J452">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K452" t="s">
         <v>11</v>
@@ -12685,10 +12663,10 @@
         <v>22</v>
       </c>
       <c r="C453">
-        <v>3503</v>
+        <v>3662</v>
       </c>
       <c r="D453" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F453" t="s">
         <v>85</v>
@@ -12700,10 +12678,10 @@
         <v>0</v>
       </c>
       <c r="I453" s="1">
-        <v>46146.668171296296</v>
+        <v>46146.692361111112</v>
       </c>
       <c r="J453">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K453" t="s">
         <v>11</v>
@@ -12714,25 +12692,25 @@
         <v>22</v>
       </c>
       <c r="C454">
-        <v>3652</v>
+        <v>3503</v>
       </c>
       <c r="D454" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F454" t="s">
         <v>85</v>
       </c>
       <c r="G454" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H454" s="2">
-        <v>1.6562500000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="I454" s="1">
-        <v>46146.668865740743</v>
+        <v>46146.668171296296</v>
       </c>
       <c r="J454">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K454" t="s">
         <v>11</v>
@@ -12743,22 +12721,22 @@
         <v>22</v>
       </c>
       <c r="C455">
-        <v>3509</v>
+        <v>3652</v>
       </c>
       <c r="D455" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F455" t="s">
         <v>85</v>
       </c>
       <c r="G455" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H455" s="2">
-        <v>0</v>
+        <v>1.6562500000000001E-2</v>
       </c>
       <c r="I455" s="1">
-        <v>46146.669560185182</v>
+        <v>46146.668865740743</v>
       </c>
       <c r="J455">
         <v>1</v>
@@ -12772,25 +12750,25 @@
         <v>22</v>
       </c>
       <c r="C456">
-        <v>5465</v>
+        <v>3509</v>
       </c>
       <c r="D456" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F456" t="s">
         <v>85</v>
       </c>
       <c r="G456" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H456" s="2">
-        <v>0.14789351851851851</v>
+        <v>0</v>
       </c>
       <c r="I456" s="1">
         <v>46146.669560185182</v>
       </c>
       <c r="J456">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K456" t="s">
         <v>11</v>
@@ -12801,10 +12779,10 @@
         <v>22</v>
       </c>
       <c r="C457">
-        <v>3512</v>
+        <v>5465</v>
       </c>
       <c r="D457" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F457" t="s">
         <v>85</v>
@@ -12813,10 +12791,10 @@
         <v>10</v>
       </c>
       <c r="H457" s="2">
-        <v>5.0462962962962961E-3</v>
+        <v>0.14789351851851851</v>
       </c>
       <c r="I457" s="1">
-        <v>46146.670254629629</v>
+        <v>46146.669560185182</v>
       </c>
       <c r="J457">
         <v>0</v>
@@ -12830,10 +12808,10 @@
         <v>22</v>
       </c>
       <c r="C458">
-        <v>3489</v>
+        <v>3512</v>
       </c>
       <c r="D458" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F458" t="s">
         <v>85</v>
@@ -12842,13 +12820,13 @@
         <v>10</v>
       </c>
       <c r="H458" s="2">
-        <v>5.5787037037037038E-3</v>
+        <v>5.0462962962962961E-3</v>
       </c>
       <c r="I458" s="1">
-        <v>46146.670949074076</v>
+        <v>46146.670254629629</v>
       </c>
       <c r="J458">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K458" t="s">
         <v>11</v>
@@ -12859,10 +12837,10 @@
         <v>22</v>
       </c>
       <c r="C459">
-        <v>3266</v>
+        <v>3489</v>
       </c>
       <c r="D459" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F459" t="s">
         <v>85</v>
@@ -12871,13 +12849,13 @@
         <v>10</v>
       </c>
       <c r="H459" s="2">
-        <v>4.9652777777777777E-3</v>
+        <v>1.0543981481481482E-2</v>
       </c>
       <c r="I459" s="1">
-        <v>46146.671643518515</v>
+        <v>46146.670949074076</v>
       </c>
       <c r="J459">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K459" t="s">
         <v>11</v>
@@ -12888,10 +12866,10 @@
         <v>22</v>
       </c>
       <c r="C460">
-        <v>3492</v>
+        <v>3266</v>
       </c>
       <c r="D460" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F460" t="s">
         <v>85</v>
@@ -12900,7 +12878,7 @@
         <v>10</v>
       </c>
       <c r="H460" s="2">
-        <v>5.4745370370370373E-3</v>
+        <v>4.9652777777777777E-3</v>
       </c>
       <c r="I460" s="1">
         <v>46146.671643518515</v>
@@ -12917,25 +12895,25 @@
         <v>22</v>
       </c>
       <c r="C461">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="D461" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F461" t="s">
         <v>85</v>
       </c>
       <c r="G461" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H461" s="2">
+        <v>5.4745370370370373E-3</v>
+      </c>
+      <c r="I461" s="1">
+        <v>46146.671643518515</v>
+      </c>
+      <c r="J461">
         <v>0</v>
-      </c>
-      <c r="I461" s="1">
-        <v>46146.672337962962</v>
-      </c>
-      <c r="J461">
-        <v>1</v>
       </c>
       <c r="K461" t="s">
         <v>11</v>
@@ -12946,25 +12924,25 @@
         <v>22</v>
       </c>
       <c r="C462">
-        <v>3505</v>
+        <v>3493</v>
       </c>
       <c r="D462" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F462" t="s">
         <v>85</v>
       </c>
       <c r="G462" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H462" s="2">
-        <v>6.030092592592593E-3</v>
+        <v>0</v>
       </c>
       <c r="I462" s="1">
         <v>46146.672337962962</v>
       </c>
       <c r="J462">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K462" t="s">
         <v>11</v>
@@ -12975,10 +12953,10 @@
         <v>22</v>
       </c>
       <c r="C463">
-        <v>3861</v>
+        <v>3505</v>
       </c>
       <c r="D463" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F463" t="s">
         <v>85</v>
@@ -12987,13 +12965,13 @@
         <v>10</v>
       </c>
       <c r="H463" s="2">
-        <v>7.9166666666666673E-3</v>
+        <v>6.030092592592593E-3</v>
       </c>
       <c r="I463" s="1">
-        <v>46146.673032407409</v>
+        <v>46146.672337962962</v>
       </c>
       <c r="J463">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K463" t="s">
         <v>11</v>
@@ -13004,22 +12982,22 @@
         <v>22</v>
       </c>
       <c r="C464">
-        <v>5205</v>
+        <v>3861</v>
       </c>
       <c r="D464" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F464" t="s">
         <v>85</v>
       </c>
       <c r="G464" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H464" s="2">
-        <v>0</v>
+        <v>7.9166666666666673E-3</v>
       </c>
       <c r="I464" s="1">
-        <v>46146.673726851855</v>
+        <v>46146.673032407409</v>
       </c>
       <c r="J464">
         <v>1</v>
@@ -13033,33 +13011,58 @@
         <v>22</v>
       </c>
       <c r="C465">
-        <v>3538</v>
+        <v>5205</v>
       </c>
       <c r="D465" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F465" t="s">
         <v>85</v>
       </c>
       <c r="G465" t="s">
+        <v>13</v>
+      </c>
+      <c r="H465" s="2">
+        <v>0</v>
+      </c>
+      <c r="I465" s="1">
+        <v>46146.673726851855</v>
+      </c>
+      <c r="J465">
+        <v>2</v>
+      </c>
+      <c r="K465" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="466" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B466" t="s">
+        <v>22</v>
+      </c>
+      <c r="C466">
+        <v>3538</v>
+      </c>
+      <c r="D466" t="s">
+        <v>82</v>
+      </c>
+      <c r="F466" t="s">
+        <v>85</v>
+      </c>
+      <c r="G466" t="s">
         <v>10</v>
       </c>
-      <c r="H465" s="2">
+      <c r="H466" s="2">
         <v>5.2893518518518515E-3</v>
       </c>
-      <c r="I465" s="1">
+      <c r="I466" s="1">
         <v>46146.674421296295</v>
       </c>
-      <c r="J465">
+      <c r="J466">
         <v>0</v>
       </c>
-      <c r="K465" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="466" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H466" s="2"/>
-      <c r="I466" s="1"/>
+      <c r="K466" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="467" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H467" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Fiore and Sons - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BD5FDD-0A8D-4FBC-9BAD-58C92B03EFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FE8CB3-58ED-4775-BAAB-ABF8EC6A73E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -697,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K5929"/>
+  <dimension ref="B1:K5929"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -712,39 +712,39 @@
     <col min="11" max="11" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>22</v>
       </c>
@@ -773,14 +773,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H3" s="2"/>
       <c r="I3" s="1"/>
       <c r="K3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>22</v>
       </c>
@@ -809,14 +809,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H5" s="2"/>
       <c r="I5" s="1"/>
       <c r="K5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>22</v>
       </c>
@@ -845,7 +845,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>22</v>
       </c>
@@ -874,14 +874,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H8" s="2"/>
       <c r="I8" s="1"/>
       <c r="K8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>22</v>
       </c>
@@ -910,7 +910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>22</v>
       </c>
@@ -939,7 +939,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>22</v>
       </c>
@@ -968,7 +968,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>22</v>
       </c>
@@ -997,7 +997,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>22</v>
       </c>
@@ -1026,14 +1026,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H14" s="2"/>
       <c r="I14" s="1"/>
       <c r="K14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>22</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>22</v>
       </c>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Fiore and Sons - Samsara\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Fiore-and-Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF8CB04F-5103-4E2F-AE6B-6BD971DA20A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA8DD73-C044-4038-8A52-33686D46CE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="95">
   <si>
     <t>Company Name</t>
   </si>
@@ -13839,16 +13839,16 @@
         <v>23</v>
       </c>
       <c r="G489" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H489" s="2">
-        <v>0</v>
+        <v>6.2962962962962957E-2</v>
       </c>
       <c r="I489" s="1">
         <v>46175.813310185185</v>
       </c>
       <c r="J489">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K489" t="s">
         <v>11</v>
@@ -13943,7 +13943,7 @@
         <v>46175.815393518518</v>
       </c>
       <c r="J493">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K493" t="s">
         <v>11</v>
@@ -13972,7 +13972,7 @@
         <v>46175.815393518518</v>
       </c>
       <c r="J494">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K494" t="s">
         <v>11</v>
@@ -14001,7 +14001,7 @@
         <v>46175.816087962965</v>
       </c>
       <c r="J495">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K495" t="s">
         <v>11</v>
@@ -14030,7 +14030,7 @@
         <v>46175.816782407404</v>
       </c>
       <c r="J496">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K496" t="s">
         <v>11</v>
@@ -14059,7 +14059,7 @@
         <v>46175.817476851851</v>
       </c>
       <c r="J497">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K497" t="s">
         <v>11</v>
@@ -14079,48 +14079,27 @@
         <v>23</v>
       </c>
       <c r="G498" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H498" s="2">
-        <v>0</v>
+        <v>1.4236111111111112E-3</v>
       </c>
       <c r="I498" s="1">
         <v>46175.817476851851</v>
       </c>
       <c r="J498">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K498" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="499" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B499" t="s">
-        <v>26</v>
-      </c>
-      <c r="C499">
-        <v>3520</v>
-      </c>
-      <c r="D499" t="s">
-        <v>39</v>
-      </c>
-      <c r="F499" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G499" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H499">
-        <v>0</v>
-      </c>
-      <c r="I499" s="1">
-        <v>46175.818171296298</v>
-      </c>
-      <c r="J499">
-        <v>1</v>
-      </c>
+      <c r="F499" s="2"/>
+      <c r="G499" s="1"/>
+      <c r="I499" s="1"/>
       <c r="K499" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="500" spans="2:11" x14ac:dyDescent="0.25">
@@ -14128,25 +14107,25 @@
         <v>26</v>
       </c>
       <c r="C500">
-        <v>3486</v>
+        <v>3520</v>
       </c>
       <c r="D500" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F500" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G500" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H500" s="2">
-        <v>6.7939814814814816E-3</v>
+        <v>0</v>
       </c>
       <c r="I500" s="1">
-        <v>46175.818865740737</v>
+        <v>46175.818171296298</v>
       </c>
       <c r="J500">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K500" t="s">
         <v>11</v>
@@ -14157,10 +14136,10 @@
         <v>26</v>
       </c>
       <c r="C501">
-        <v>3886</v>
+        <v>3486</v>
       </c>
       <c r="D501" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F501" s="2" t="s">
         <v>23</v>
@@ -14169,13 +14148,13 @@
         <v>10</v>
       </c>
       <c r="H501" s="2">
-        <v>1.5219907407407408E-2</v>
+        <v>6.7939814814814816E-3</v>
       </c>
       <c r="I501" s="1">
-        <v>46175.819560185184</v>
+        <v>46175.818865740737</v>
       </c>
       <c r="J501">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K501" t="s">
         <v>11</v>
@@ -14186,10 +14165,10 @@
         <v>26</v>
       </c>
       <c r="C502">
-        <v>3397</v>
+        <v>3886</v>
       </c>
       <c r="D502" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F502" s="2" t="s">
         <v>23</v>
@@ -14198,7 +14177,7 @@
         <v>10</v>
       </c>
       <c r="H502" s="2">
-        <v>8.3101851851851843E-3</v>
+        <v>1.5219907407407408E-2</v>
       </c>
       <c r="I502" s="1">
         <v>46175.819560185184</v>
@@ -14215,10 +14194,10 @@
         <v>26</v>
       </c>
       <c r="C503">
-        <v>3765</v>
+        <v>3397</v>
       </c>
       <c r="D503" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F503" s="2" t="s">
         <v>23</v>
@@ -14227,10 +14206,10 @@
         <v>10</v>
       </c>
       <c r="H503" s="2">
-        <v>7.2222222222222219E-3</v>
+        <v>8.3101851851851843E-3</v>
       </c>
       <c r="I503" s="1">
-        <v>46175.793981481482</v>
+        <v>46175.819560185184</v>
       </c>
       <c r="J503">
         <v>1</v>
@@ -14244,22 +14223,22 @@
         <v>26</v>
       </c>
       <c r="C504">
-        <v>3496</v>
+        <v>3765</v>
       </c>
       <c r="D504" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F504" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G504" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H504" s="2">
-        <v>0</v>
+        <v>7.2222222222222219E-3</v>
       </c>
       <c r="I504" s="1">
-        <v>46175.794675925928</v>
+        <v>46175.793981481482</v>
       </c>
       <c r="J504">
         <v>1</v>
@@ -14273,10 +14252,10 @@
         <v>26</v>
       </c>
       <c r="C505">
-        <v>3508</v>
+        <v>3496</v>
       </c>
       <c r="D505" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F505" s="2" t="s">
         <v>23</v>
@@ -14288,10 +14267,10 @@
         <v>0</v>
       </c>
       <c r="I505" s="1">
-        <v>46175.795370370368</v>
+        <v>46175.794675925928</v>
       </c>
       <c r="J505">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K505" t="s">
         <v>11</v>
@@ -14302,25 +14281,25 @@
         <v>26</v>
       </c>
       <c r="C506">
-        <v>3483</v>
+        <v>3508</v>
       </c>
       <c r="D506" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F506" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G506" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H506" s="2">
-        <v>1.21875E-2</v>
+        <v>0</v>
       </c>
       <c r="I506" s="1">
-        <v>46175.796064814815</v>
+        <v>46175.795370370368</v>
       </c>
       <c r="J506">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K506" t="s">
         <v>11</v>
@@ -14331,22 +14310,22 @@
         <v>26</v>
       </c>
       <c r="C507">
-        <v>3499</v>
+        <v>3483</v>
       </c>
       <c r="D507" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F507" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G507" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H507" s="2">
-        <v>0</v>
+        <v>1.21875E-2</v>
       </c>
       <c r="I507" s="1">
-        <v>46175.796759259261</v>
+        <v>46175.796064814815</v>
       </c>
       <c r="J507">
         <v>1</v>
@@ -14360,25 +14339,25 @@
         <v>26</v>
       </c>
       <c r="C508">
-        <v>3491</v>
+        <v>3499</v>
       </c>
       <c r="D508" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F508" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G508" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H508" s="2">
-        <v>7.9629629629629634E-3</v>
+        <v>0</v>
       </c>
       <c r="I508" s="1">
-        <v>46175.797453703701</v>
+        <v>46175.796759259261</v>
       </c>
       <c r="J508">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K508" t="s">
         <v>11</v>
@@ -14389,25 +14368,25 @@
         <v>26</v>
       </c>
       <c r="C509">
-        <v>3487</v>
+        <v>3491</v>
       </c>
       <c r="D509" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F509" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G509" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H509">
+        <v>10</v>
+      </c>
+      <c r="H509" s="2">
+        <v>7.9629629629629634E-3</v>
+      </c>
+      <c r="I509" s="1">
+        <v>46175.797453703701</v>
+      </c>
+      <c r="J509">
         <v>0</v>
-      </c>
-      <c r="I509" s="1">
-        <v>46175.798148148147</v>
-      </c>
-      <c r="J509">
-        <v>1</v>
       </c>
       <c r="K509" t="s">
         <v>11</v>
@@ -14418,10 +14397,10 @@
         <v>26</v>
       </c>
       <c r="C510">
-        <v>3704</v>
+        <v>3487</v>
       </c>
       <c r="D510" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F510" s="2" t="s">
         <v>23</v>
@@ -14433,10 +14412,10 @@
         <v>0</v>
       </c>
       <c r="I510" s="1">
-        <v>46175.798842592594</v>
+        <v>46175.798148148147</v>
       </c>
       <c r="J510">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K510" t="s">
         <v>11</v>
@@ -14447,10 +14426,10 @@
         <v>26</v>
       </c>
       <c r="C511">
-        <v>3480</v>
+        <v>3704</v>
       </c>
       <c r="D511" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F511" s="2" t="s">
         <v>23</v>
@@ -14465,7 +14444,7 @@
         <v>46175.798842592594</v>
       </c>
       <c r="J511">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K511" t="s">
         <v>11</v>
@@ -14476,25 +14455,25 @@
         <v>26</v>
       </c>
       <c r="C512">
-        <v>3484</v>
+        <v>3480</v>
       </c>
       <c r="D512" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F512" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G512" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H512" s="2">
-        <v>8.9467592592592585E-3</v>
+        <v>0</v>
       </c>
       <c r="I512" s="1">
-        <v>46175.799537037034</v>
+        <v>46175.798842592594</v>
       </c>
       <c r="J512">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K512" t="s">
         <v>11</v>
@@ -14505,22 +14484,22 @@
         <v>26</v>
       </c>
       <c r="C513">
-        <v>3514</v>
+        <v>3484</v>
       </c>
       <c r="D513" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F513" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G513" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H513" s="2">
-        <v>0</v>
+        <v>8.9467592592592585E-3</v>
       </c>
       <c r="I513" s="1">
-        <v>46175.80023148148</v>
+        <v>46175.799537037034</v>
       </c>
       <c r="J513">
         <v>0</v>
@@ -14530,41 +14509,41 @@
       </c>
     </row>
     <row r="514" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F514" s="2"/>
-      <c r="G514" s="1"/>
-      <c r="H514" s="2"/>
-      <c r="I514" s="1"/>
+      <c r="B514" t="s">
+        <v>26</v>
+      </c>
+      <c r="C514">
+        <v>3514</v>
+      </c>
+      <c r="D514" t="s">
+        <v>60</v>
+      </c>
+      <c r="F514" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G514" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H514" s="2">
+        <v>0</v>
+      </c>
+      <c r="I514" s="1">
+        <v>46175.80023148148</v>
+      </c>
+      <c r="J514">
+        <v>0</v>
+      </c>
       <c r="K514" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="515" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F515" s="2"/>
+      <c r="G515" s="1"/>
+      <c r="H515" s="2"/>
+      <c r="I515" s="1"/>
+      <c r="K515" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="515" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B515" t="s">
-        <v>26</v>
-      </c>
-      <c r="C515">
-        <v>3725</v>
-      </c>
-      <c r="D515" t="s">
-        <v>62</v>
-      </c>
-      <c r="F515" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G515" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H515" s="2">
-        <v>7.1643518518518514E-3</v>
-      </c>
-      <c r="I515" s="1">
-        <v>46175.800925925927</v>
-      </c>
-      <c r="J515">
-        <v>0</v>
-      </c>
-      <c r="K515" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="516" spans="2:11" x14ac:dyDescent="0.25">
@@ -14572,10 +14551,10 @@
         <v>26</v>
       </c>
       <c r="C516">
-        <v>3488</v>
+        <v>3725</v>
       </c>
       <c r="D516" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F516" s="2" t="s">
         <v>23</v>
@@ -14584,13 +14563,13 @@
         <v>10</v>
       </c>
       <c r="H516" s="2">
-        <v>1.0300925925925925E-2</v>
+        <v>4.0150462962962964E-2</v>
       </c>
       <c r="I516" s="1">
-        <v>46175.801620370374</v>
+        <v>46175.800925925927</v>
       </c>
       <c r="J516">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K516" t="s">
         <v>11</v>
@@ -14601,19 +14580,19 @@
         <v>26</v>
       </c>
       <c r="C517">
-        <v>3478</v>
+        <v>3488</v>
       </c>
       <c r="D517" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F517" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H517" s="2">
-        <v>0</v>
+        <v>1.0300925925925925E-2</v>
       </c>
       <c r="I517" s="1">
         <v>46175.801620370374</v>
@@ -14630,25 +14609,25 @@
         <v>26</v>
       </c>
       <c r="C518">
-        <v>3523</v>
+        <v>3478</v>
       </c>
       <c r="D518" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F518" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H518" s="2">
-        <v>0</v>
+        <v>8.2060185185185187E-3</v>
       </c>
       <c r="I518" s="1">
-        <v>46175.802314814813</v>
+        <v>46175.801620370374</v>
       </c>
       <c r="J518">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K518" t="s">
         <v>11</v>
@@ -14659,10 +14638,10 @@
         <v>26</v>
       </c>
       <c r="C519">
-        <v>3504</v>
+        <v>3523</v>
       </c>
       <c r="D519" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F519" s="2" t="s">
         <v>23</v>
@@ -14674,10 +14653,10 @@
         <v>0</v>
       </c>
       <c r="I519" s="1">
-        <v>46175.80300925926</v>
+        <v>46175.802314814813</v>
       </c>
       <c r="J519">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K519" t="s">
         <v>11</v>
@@ -14688,10 +14667,10 @@
         <v>26</v>
       </c>
       <c r="C520">
-        <v>3344</v>
+        <v>3504</v>
       </c>
       <c r="D520" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F520" s="2" t="s">
         <v>23</v>
@@ -14703,10 +14682,10 @@
         <v>0</v>
       </c>
       <c r="I520" s="1">
-        <v>46175.803703703707</v>
+        <v>46175.80300925926</v>
       </c>
       <c r="J520">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K520" t="s">
         <v>11</v>
@@ -14717,25 +14696,25 @@
         <v>26</v>
       </c>
       <c r="C521">
-        <v>3515</v>
+        <v>3344</v>
       </c>
       <c r="D521" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F521" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G521" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H521" s="2">
-        <v>0</v>
+        <v>7.4537037037037037E-3</v>
       </c>
       <c r="I521" s="1">
         <v>46175.803703703707</v>
       </c>
       <c r="J521">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K521" t="s">
         <v>11</v>
@@ -14746,65 +14725,66 @@
         <v>26</v>
       </c>
       <c r="C522">
-        <v>3522</v>
+        <v>3515</v>
       </c>
       <c r="D522" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F522" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H522" s="2">
-        <v>3.0092592592592595E-4</v>
+        <v>0</v>
       </c>
       <c r="I522" s="1">
-        <v>46175.804398148146</v>
+        <v>46175.803703703707</v>
       </c>
       <c r="J522">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K522" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="523" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F523" s="2"/>
-      <c r="G523" s="1"/>
-      <c r="I523" s="1"/>
+      <c r="B523" t="s">
+        <v>26</v>
+      </c>
+      <c r="C523">
+        <v>3522</v>
+      </c>
+      <c r="D523" t="s">
+        <v>72</v>
+      </c>
+      <c r="F523" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G523" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H523" s="2">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="I523" s="1">
+        <v>46175.804398148146</v>
+      </c>
+      <c r="J523">
+        <v>0</v>
+      </c>
       <c r="K523" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="524" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F524" s="2"/>
+      <c r="G524" s="1"/>
+      <c r="H524" s="2"/>
+      <c r="I524" s="1"/>
+      <c r="K524" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="524" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B524" t="s">
-        <v>26</v>
-      </c>
-      <c r="C524">
-        <v>3751</v>
-      </c>
-      <c r="D524" t="s">
-        <v>73</v>
-      </c>
-      <c r="F524" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G524" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H524" s="2">
-        <v>0</v>
-      </c>
-      <c r="I524" s="1">
-        <v>46175.805092592593</v>
-      </c>
-      <c r="J524">
-        <v>1</v>
-      </c>
-      <c r="K524" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="525" spans="2:11" x14ac:dyDescent="0.25">
@@ -14812,65 +14792,66 @@
         <v>26</v>
       </c>
       <c r="C525">
-        <v>3652</v>
+        <v>3751</v>
       </c>
       <c r="D525" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F525" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G525" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H525" s="2">
         <v>0</v>
       </c>
       <c r="I525" s="1">
-        <v>46175.805787037039</v>
+        <v>46175.805092592593</v>
       </c>
       <c r="J525">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K525" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="526" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F526" s="2"/>
-      <c r="G526" s="1"/>
-      <c r="I526" s="1"/>
+      <c r="B526" t="s">
+        <v>26</v>
+      </c>
+      <c r="C526">
+        <v>3652</v>
+      </c>
+      <c r="D526" t="s">
+        <v>77</v>
+      </c>
+      <c r="F526" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G526" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H526">
+        <v>0</v>
+      </c>
+      <c r="I526" s="1">
+        <v>46175.805787037039</v>
+      </c>
+      <c r="J526">
+        <v>0</v>
+      </c>
       <c r="K526" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="527" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F527" s="2"/>
+      <c r="G527" s="1"/>
+      <c r="H527" s="2"/>
+      <c r="I527" s="1"/>
+      <c r="K527" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="527" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B527" t="s">
-        <v>26</v>
-      </c>
-      <c r="C527">
-        <v>3509</v>
-      </c>
-      <c r="D527" t="s">
-        <v>78</v>
-      </c>
-      <c r="F527" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G527" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H527" s="2">
-        <v>0</v>
-      </c>
-      <c r="I527" s="1">
-        <v>46175.805787037039</v>
-      </c>
-      <c r="J527">
-        <v>1</v>
-      </c>
-      <c r="K527" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="528" spans="2:11" x14ac:dyDescent="0.25">
@@ -14878,25 +14859,25 @@
         <v>26</v>
       </c>
       <c r="C528">
-        <v>5617</v>
+        <v>3509</v>
       </c>
       <c r="D528" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F528" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G528" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H528" s="2">
-        <v>0</v>
+        <v>6.5277777777777782E-3</v>
       </c>
       <c r="I528" s="1">
-        <v>46175.806481481479</v>
+        <v>46175.805787037039</v>
       </c>
       <c r="J528">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K528" t="s">
         <v>11</v>
@@ -14907,66 +14888,66 @@
         <v>26</v>
       </c>
       <c r="C529">
-        <v>3492</v>
+        <v>5617</v>
       </c>
       <c r="D529" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F529" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G529" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H529">
         <v>0</v>
       </c>
       <c r="I529" s="1">
-        <v>46175.807175925926</v>
+        <v>46175.806481481479</v>
       </c>
       <c r="J529">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K529" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="530" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F530" s="2"/>
-      <c r="G530" s="1"/>
-      <c r="H530" s="2"/>
-      <c r="I530" s="1"/>
+      <c r="B530" t="s">
+        <v>26</v>
+      </c>
+      <c r="C530">
+        <v>3492</v>
+      </c>
+      <c r="D530" t="s">
+        <v>82</v>
+      </c>
+      <c r="F530" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G530" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H530" s="2">
+        <v>0</v>
+      </c>
+      <c r="I530" s="1">
+        <v>46175.807175925926</v>
+      </c>
+      <c r="J530">
+        <v>0</v>
+      </c>
       <c r="K530" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="531" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F531" s="2"/>
+      <c r="G531" s="1"/>
+      <c r="H531" s="2"/>
+      <c r="I531" s="1"/>
+      <c r="K531" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="531" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B531" t="s">
-        <v>26</v>
-      </c>
-      <c r="C531">
-        <v>3493</v>
-      </c>
-      <c r="D531" t="s">
-        <v>83</v>
-      </c>
-      <c r="F531" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G531" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H531" s="2">
-        <v>0</v>
-      </c>
-      <c r="I531" s="1">
-        <v>46175.807870370372</v>
-      </c>
-      <c r="J531">
-        <v>1</v>
-      </c>
-      <c r="K531" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="532" spans="2:11" x14ac:dyDescent="0.25">
@@ -14974,10 +14955,10 @@
         <v>26</v>
       </c>
       <c r="C532">
-        <v>5205</v>
+        <v>3493</v>
       </c>
       <c r="D532" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F532" s="2" t="s">
         <v>23</v>
@@ -14989,10 +14970,10 @@
         <v>0</v>
       </c>
       <c r="I532" s="1">
-        <v>46175.808564814812</v>
+        <v>46175.807870370372</v>
       </c>
       <c r="J532">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K532" t="s">
         <v>11</v>
@@ -15003,35 +14984,58 @@
         <v>26</v>
       </c>
       <c r="C533">
-        <v>3538</v>
+        <v>5205</v>
       </c>
       <c r="D533" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F533" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G533" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H533" s="2">
-        <v>8.0902777777777778E-3</v>
+        <v>0</v>
       </c>
       <c r="I533" s="1">
         <v>46175.808564814812</v>
       </c>
       <c r="J533">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K533" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="534" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F534" s="2"/>
-      <c r="G534" s="1"/>
-      <c r="H534" s="2"/>
-      <c r="I534" s="1"/>
+      <c r="B534" t="s">
+        <v>26</v>
+      </c>
+      <c r="C534">
+        <v>3538</v>
+      </c>
+      <c r="D534" t="s">
+        <v>86</v>
+      </c>
+      <c r="F534" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G534" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H534" s="2">
+        <v>8.0902777777777778E-3</v>
+      </c>
+      <c r="I534" s="1">
+        <v>46175.808564814812</v>
+      </c>
+      <c r="J534">
+        <v>1</v>
+      </c>
+      <c r="K534" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="535" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F535" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Fiore-and-Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{675582DE-7E91-4D1F-BF0A-FAE3567C2BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21D18C14-3AB1-40AC-BDC5-73E7F7C70B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2790" uniqueCount="104">
   <si>
     <t>Company Name</t>
   </si>
@@ -113,10 +113,10 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>In Cab Distractions</t>
+    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
-    <t>Camera Event Management Orientation for Drivers</t>
+    <t>In Cab Distractions</t>
   </si>
   <si>
     <t>Fiore &amp; Sons</t>
@@ -324,6 +324,33 @@
   </si>
   <si>
     <t>Alexis Calderon Reyes</t>
+  </si>
+  <si>
+    <t>Brennan Westendorf</t>
+  </si>
+  <si>
+    <t>Craig Rodriguez</t>
+  </si>
+  <si>
+    <t>Efrain Sotelo</t>
+  </si>
+  <si>
+    <t>Johnny Ortiz-Prudente</t>
+  </si>
+  <si>
+    <t>Larry Gertson</t>
+  </si>
+  <si>
+    <t>Mark Davis</t>
+  </si>
+  <si>
+    <t>Miguel Michael Quintana</t>
+  </si>
+  <si>
+    <t>VICTOR SENA</t>
+  </si>
+  <si>
+    <t>Wade Cruser</t>
   </si>
 </sst>
 </file>
@@ -697,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -755,7 +782,7 @@
         <v>27</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>12</v>
@@ -6225,7 +6252,7 @@
         <v>27</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>10</v>
@@ -6254,7 +6281,7 @@
         <v>28</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>10</v>
@@ -6283,7 +6310,7 @@
         <v>29</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>10</v>
@@ -6312,7 +6339,7 @@
         <v>30</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>10</v>
@@ -6341,7 +6368,7 @@
         <v>31</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>10</v>
@@ -6370,7 +6397,7 @@
         <v>32</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -6399,7 +6426,7 @@
         <v>33</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>12</v>
@@ -6437,7 +6464,7 @@
         <v>34</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>14</v>
@@ -6475,7 +6502,7 @@
         <v>35</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>13</v>
@@ -6504,7 +6531,7 @@
         <v>36</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>13</v>
@@ -6533,7 +6560,7 @@
         <v>37</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>10</v>
@@ -6562,7 +6589,7 @@
         <v>38</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>10</v>
@@ -6591,7 +6618,7 @@
         <v>39</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>10</v>
@@ -6620,7 +6647,7 @@
         <v>40</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>10</v>
@@ -6649,7 +6676,7 @@
         <v>41</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>10</v>
@@ -6678,7 +6705,7 @@
         <v>42</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>10</v>
@@ -6707,7 +6734,7 @@
         <v>43</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>14</v>
@@ -6745,7 +6772,7 @@
         <v>44</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>14</v>
@@ -6783,7 +6810,7 @@
         <v>45</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>10</v>
@@ -6812,7 +6839,7 @@
         <v>46</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>10</v>
@@ -6841,7 +6868,7 @@
         <v>47</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>13</v>
@@ -6870,7 +6897,7 @@
         <v>48</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>13</v>
@@ -6899,7 +6926,7 @@
         <v>49</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>10</v>
@@ -6928,7 +6955,7 @@
         <v>50</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -6957,7 +6984,7 @@
         <v>51</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>12</v>
@@ -6995,7 +7022,7 @@
         <v>52</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>10</v>
@@ -7024,7 +7051,7 @@
         <v>53</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>10</v>
@@ -7053,7 +7080,7 @@
         <v>54</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>13</v>
@@ -7082,7 +7109,7 @@
         <v>55</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>12</v>
@@ -7120,7 +7147,7 @@
         <v>56</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>10</v>
@@ -7149,7 +7176,7 @@
         <v>57</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>10</v>
@@ -7178,7 +7205,7 @@
         <v>58</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>12</v>
@@ -7216,7 +7243,7 @@
         <v>59</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>10</v>
@@ -7245,7 +7272,7 @@
         <v>60</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7274,7 +7301,7 @@
         <v>61</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>13</v>
@@ -7303,7 +7330,7 @@
         <v>62</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>10</v>
@@ -7332,7 +7359,7 @@
         <v>63</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>10</v>
@@ -7361,7 +7388,7 @@
         <v>64</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>10</v>
@@ -7390,7 +7417,7 @@
         <v>65</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>10</v>
@@ -7419,7 +7446,7 @@
         <v>66</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>10</v>
@@ -7448,7 +7475,7 @@
         <v>68</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>13</v>
@@ -7477,7 +7504,7 @@
         <v>69</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>10</v>
@@ -7506,7 +7533,7 @@
         <v>70</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>10</v>
@@ -7535,7 +7562,7 @@
         <v>71</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>10</v>
@@ -7564,7 +7591,7 @@
         <v>72</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>10</v>
@@ -7593,7 +7620,7 @@
         <v>73</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>10</v>
@@ -7622,7 +7649,7 @@
         <v>74</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>13</v>
@@ -7651,7 +7678,7 @@
         <v>75</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>10</v>
@@ -7680,7 +7707,7 @@
         <v>76</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>13</v>
@@ -7709,7 +7736,7 @@
         <v>77</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>10</v>
@@ -7738,7 +7765,7 @@
         <v>78</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>10</v>
@@ -7767,7 +7794,7 @@
         <v>79</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>10</v>
@@ -7796,7 +7823,7 @@
         <v>80</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>10</v>
@@ -7825,7 +7852,7 @@
         <v>81</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>10</v>
@@ -7854,7 +7881,7 @@
         <v>82</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>10</v>
@@ -7883,7 +7910,7 @@
         <v>83</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>13</v>
@@ -7912,7 +7939,7 @@
         <v>84</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>10</v>
@@ -7941,7 +7968,7 @@
         <v>85</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>10</v>
@@ -7970,7 +7997,7 @@
         <v>87</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>10</v>
@@ -7999,7 +8026,7 @@
         <v>86</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>10</v>
@@ -15033,545 +15060,2133 @@
       </c>
     </row>
     <row r="534" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H534" s="2"/>
-      <c r="I534" s="1"/>
-      <c r="J534" s="2"/>
-      <c r="K534" s="1"/>
+      <c r="D534" t="s">
+        <v>26</v>
+      </c>
+      <c r="E534">
+        <v>3200</v>
+      </c>
+      <c r="F534" t="s">
+        <v>27</v>
+      </c>
+      <c r="H534" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I534" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J534" s="2">
+        <v>0</v>
+      </c>
+      <c r="K534" s="1">
+        <v>46210.765162037038</v>
+      </c>
+      <c r="L534">
+        <v>0</v>
+      </c>
+      <c r="M534" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="535" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H535" s="2"/>
-      <c r="I535" s="1"/>
-      <c r="J535" s="2"/>
-      <c r="K535" s="1"/>
+      <c r="D535" t="s">
+        <v>26</v>
+      </c>
+      <c r="E535">
+        <v>3501</v>
+      </c>
+      <c r="F535" t="s">
+        <v>28</v>
+      </c>
+      <c r="H535" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I535" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J535" s="2">
+        <v>0</v>
+      </c>
+      <c r="K535" s="1">
+        <v>46210.765856481485</v>
+      </c>
+      <c r="L535">
+        <v>0</v>
+      </c>
+      <c r="M535" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="536" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H536" s="2"/>
       <c r="I536" s="1"/>
       <c r="J536" s="2"/>
       <c r="K536" s="1"/>
+      <c r="M536" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="537" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H537" s="2"/>
-      <c r="I537" s="1"/>
-      <c r="J537" s="2"/>
-      <c r="K537" s="1"/>
+      <c r="D537" t="s">
+        <v>26</v>
+      </c>
+      <c r="E537">
+        <v>4915</v>
+      </c>
+      <c r="F537" t="s">
+        <v>29</v>
+      </c>
+      <c r="H537" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I537" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J537" s="2">
+        <v>0</v>
+      </c>
+      <c r="K537" s="1">
+        <v>46210.765856481485</v>
+      </c>
+      <c r="L537">
+        <v>0</v>
+      </c>
+      <c r="M537" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="538" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H538" s="2"/>
-      <c r="I538" s="1"/>
-      <c r="J538" s="2"/>
-      <c r="K538" s="1"/>
+      <c r="D538" t="s">
+        <v>26</v>
+      </c>
+      <c r="E538">
+        <v>5595</v>
+      </c>
+      <c r="F538" t="s">
+        <v>94</v>
+      </c>
+      <c r="H538" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I538" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J538" s="2">
+        <v>0</v>
+      </c>
+      <c r="K538" s="1">
+        <v>46210.766550925924</v>
+      </c>
+      <c r="L538">
+        <v>0</v>
+      </c>
+      <c r="M538" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="539" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H539" s="2"/>
-      <c r="I539" s="1"/>
-      <c r="J539" s="2"/>
-      <c r="K539" s="1"/>
+      <c r="D539" t="s">
+        <v>26</v>
+      </c>
+      <c r="E539">
+        <v>3360</v>
+      </c>
+      <c r="F539" t="s">
+        <v>30</v>
+      </c>
+      <c r="H539" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I539" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J539" s="2">
+        <v>8.564814814814815E-3</v>
+      </c>
+      <c r="K539" s="1">
+        <v>46210.767245370371</v>
+      </c>
+      <c r="L539">
+        <v>0</v>
+      </c>
+      <c r="M539" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="540" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H540" s="2"/>
-      <c r="I540" s="1"/>
-      <c r="J540" s="2"/>
-      <c r="K540" s="1"/>
+      <c r="D540" t="s">
+        <v>26</v>
+      </c>
+      <c r="E540">
+        <v>3521</v>
+      </c>
+      <c r="F540" t="s">
+        <v>31</v>
+      </c>
+      <c r="H540" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I540" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J540" s="2">
+        <v>0</v>
+      </c>
+      <c r="K540" s="1">
+        <v>46210.767939814818</v>
+      </c>
+      <c r="L540">
+        <v>0</v>
+      </c>
+      <c r="M540" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="541" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H541" s="2"/>
-      <c r="I541" s="1"/>
-      <c r="J541" s="2"/>
-      <c r="K541" s="1"/>
+      <c r="D541" t="s">
+        <v>26</v>
+      </c>
+      <c r="E541">
+        <v>3479</v>
+      </c>
+      <c r="F541" t="s">
+        <v>32</v>
+      </c>
+      <c r="H541" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I541" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J541" s="2">
+        <v>1.0995370370370371E-2</v>
+      </c>
+      <c r="K541" s="1">
+        <v>46210.768634259257</v>
+      </c>
+      <c r="L541">
+        <v>0</v>
+      </c>
+      <c r="M541" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="542" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H542" s="2"/>
       <c r="I542" s="1"/>
       <c r="J542" s="2"/>
       <c r="K542" s="1"/>
+      <c r="M542" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="543" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H543" s="2"/>
-      <c r="I543" s="1"/>
-      <c r="J543" s="2"/>
-      <c r="K543" s="1"/>
+      <c r="D543" t="s">
+        <v>26</v>
+      </c>
+      <c r="E543">
+        <v>5609</v>
+      </c>
+      <c r="F543" t="s">
+        <v>90</v>
+      </c>
+      <c r="H543" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I543" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J543" s="2">
+        <v>6.1342592592592594E-3</v>
+      </c>
+      <c r="K543" s="1">
+        <v>46210.768634259257</v>
+      </c>
+      <c r="L543">
+        <v>0</v>
+      </c>
+      <c r="M543" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="544" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H544" s="2"/>
-      <c r="I544" s="1"/>
-      <c r="J544" s="2"/>
-      <c r="K544" s="1"/>
-    </row>
-    <row r="545" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D544" t="s">
+        <v>26</v>
+      </c>
+      <c r="E544">
+        <v>5613</v>
+      </c>
+      <c r="F544" t="s">
+        <v>91</v>
+      </c>
+      <c r="H544" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I544" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J544" s="2">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="K544" s="1">
+        <v>46210.769328703704</v>
+      </c>
+      <c r="L544">
+        <v>0</v>
+      </c>
+      <c r="M544" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="545" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H545" s="2"/>
       <c r="I545" s="1"/>
       <c r="J545" s="2"/>
       <c r="K545" s="1"/>
-    </row>
-    <row r="546" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H546" s="2"/>
-      <c r="I546" s="1"/>
-      <c r="J546" s="2"/>
-      <c r="K546" s="1"/>
-    </row>
-    <row r="547" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H547" s="2"/>
-      <c r="I547" s="1"/>
-      <c r="J547" s="2"/>
-      <c r="K547" s="1"/>
-    </row>
-    <row r="548" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H548" s="2"/>
-      <c r="I548" s="1"/>
-      <c r="J548" s="2"/>
-      <c r="K548" s="1"/>
-    </row>
-    <row r="549" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H549" s="2"/>
-      <c r="I549" s="1"/>
-      <c r="J549" s="2"/>
-      <c r="K549" s="1"/>
-    </row>
-    <row r="550" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H550" s="2"/>
-      <c r="I550" s="1"/>
-      <c r="J550" s="2"/>
-      <c r="K550" s="1"/>
-    </row>
-    <row r="551" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H551" s="2"/>
-      <c r="I551" s="1"/>
-      <c r="J551" s="2"/>
-      <c r="K551" s="1"/>
-    </row>
-    <row r="552" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H552" s="2"/>
-      <c r="I552" s="1"/>
-      <c r="J552" s="2"/>
-      <c r="K552" s="1"/>
-    </row>
-    <row r="553" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H553" s="2"/>
-      <c r="I553" s="1"/>
-      <c r="J553" s="2"/>
-      <c r="K553" s="1"/>
-    </row>
-    <row r="554" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H554" s="2"/>
-      <c r="I554" s="1"/>
-      <c r="J554" s="2"/>
-      <c r="K554" s="1"/>
-    </row>
-    <row r="555" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H555" s="2"/>
-      <c r="I555" s="1"/>
-      <c r="J555" s="2"/>
-      <c r="K555" s="1"/>
-    </row>
-    <row r="556" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H556" s="2"/>
-      <c r="I556" s="1"/>
-      <c r="J556" s="2"/>
-      <c r="K556" s="1"/>
-    </row>
-    <row r="557" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H557" s="2"/>
-      <c r="I557" s="1"/>
-      <c r="J557" s="2"/>
-      <c r="K557" s="1"/>
-    </row>
-    <row r="558" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M545" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="546" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D546" t="s">
+        <v>26</v>
+      </c>
+      <c r="E546">
+        <v>5888</v>
+      </c>
+      <c r="F546" t="s">
+        <v>95</v>
+      </c>
+      <c r="H546" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I546" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J546" s="2">
+        <v>6.1805555555555555E-3</v>
+      </c>
+      <c r="K546" s="1">
+        <v>46210.77002314815</v>
+      </c>
+      <c r="L546">
+        <v>0</v>
+      </c>
+      <c r="M546" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="547" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D547" t="s">
+        <v>26</v>
+      </c>
+      <c r="E547">
+        <v>4917</v>
+      </c>
+      <c r="F547" t="s">
+        <v>34</v>
+      </c>
+      <c r="H547" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I547" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J547" s="2">
+        <v>0</v>
+      </c>
+      <c r="K547" s="1">
+        <v>46210.77071759259</v>
+      </c>
+      <c r="L547">
+        <v>0</v>
+      </c>
+      <c r="M547" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="548" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D548" t="s">
+        <v>26</v>
+      </c>
+      <c r="E548">
+        <v>3524</v>
+      </c>
+      <c r="F548" t="s">
+        <v>35</v>
+      </c>
+      <c r="H548" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I548" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J548" s="2">
+        <v>0</v>
+      </c>
+      <c r="K548" s="1">
+        <v>46210.77071759259</v>
+      </c>
+      <c r="L548">
+        <v>0</v>
+      </c>
+      <c r="M548" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="549" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D549" t="s">
+        <v>26</v>
+      </c>
+      <c r="E549">
+        <v>3804</v>
+      </c>
+      <c r="F549" t="s">
+        <v>36</v>
+      </c>
+      <c r="H549" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I549" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J549" s="2">
+        <v>0</v>
+      </c>
+      <c r="K549" s="1">
+        <v>46210.771412037036</v>
+      </c>
+      <c r="L549">
+        <v>0</v>
+      </c>
+      <c r="M549" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="550" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D550" t="s">
+        <v>26</v>
+      </c>
+      <c r="E550">
+        <v>3495</v>
+      </c>
+      <c r="F550" t="s">
+        <v>37</v>
+      </c>
+      <c r="H550" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I550" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J550" s="2">
+        <v>5.9837962962962961E-3</v>
+      </c>
+      <c r="K550" s="1">
+        <v>46210.772106481483</v>
+      </c>
+      <c r="L550">
+        <v>0</v>
+      </c>
+      <c r="M550" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="551" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D551" t="s">
+        <v>26</v>
+      </c>
+      <c r="E551">
+        <v>3739</v>
+      </c>
+      <c r="F551" t="s">
+        <v>38</v>
+      </c>
+      <c r="H551" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I551" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J551" s="2">
+        <v>0</v>
+      </c>
+      <c r="K551" s="1">
+        <v>46210.772800925923</v>
+      </c>
+      <c r="L551">
+        <v>0</v>
+      </c>
+      <c r="M551" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="552" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D552" t="s">
+        <v>26</v>
+      </c>
+      <c r="E552">
+        <v>3520</v>
+      </c>
+      <c r="F552" t="s">
+        <v>39</v>
+      </c>
+      <c r="H552" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I552" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J552" s="2">
+        <v>6.5624999999999998E-3</v>
+      </c>
+      <c r="K552" s="1">
+        <v>46210.772800925923</v>
+      </c>
+      <c r="L552">
+        <v>0</v>
+      </c>
+      <c r="M552" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="553" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D553" t="s">
+        <v>26</v>
+      </c>
+      <c r="E553">
+        <v>5889</v>
+      </c>
+      <c r="F553" t="s">
+        <v>96</v>
+      </c>
+      <c r="H553" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I553" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J553" s="2">
+        <v>0</v>
+      </c>
+      <c r="K553" s="1">
+        <v>46210.773495370369</v>
+      </c>
+      <c r="L553">
+        <v>0</v>
+      </c>
+      <c r="M553" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="554" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D554" t="s">
+        <v>26</v>
+      </c>
+      <c r="E554">
+        <v>3486</v>
+      </c>
+      <c r="F554" t="s">
+        <v>40</v>
+      </c>
+      <c r="H554" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I554" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J554" s="2">
+        <v>0</v>
+      </c>
+      <c r="K554" s="1">
+        <v>46210.774189814816</v>
+      </c>
+      <c r="L554">
+        <v>0</v>
+      </c>
+      <c r="M554" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="555" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D555" t="s">
+        <v>26</v>
+      </c>
+      <c r="E555">
+        <v>3886</v>
+      </c>
+      <c r="F555" t="s">
+        <v>41</v>
+      </c>
+      <c r="H555" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I555" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J555" s="2">
+        <v>0</v>
+      </c>
+      <c r="K555" s="1">
+        <v>46210.774884259263</v>
+      </c>
+      <c r="L555">
+        <v>0</v>
+      </c>
+      <c r="M555" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="556" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D556" t="s">
+        <v>26</v>
+      </c>
+      <c r="E556">
+        <v>3397</v>
+      </c>
+      <c r="F556" t="s">
+        <v>42</v>
+      </c>
+      <c r="H556" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I556" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J556" s="2">
+        <v>0</v>
+      </c>
+      <c r="K556" s="1">
+        <v>46210.774884259263</v>
+      </c>
+      <c r="L556">
+        <v>0</v>
+      </c>
+      <c r="M556" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="557" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D557" t="s">
+        <v>26</v>
+      </c>
+      <c r="E557">
+        <v>3765</v>
+      </c>
+      <c r="F557" t="s">
+        <v>43</v>
+      </c>
+      <c r="H557" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I557" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J557" s="2">
+        <v>0</v>
+      </c>
+      <c r="K557" s="1">
+        <v>46210.775578703702</v>
+      </c>
+      <c r="L557">
+        <v>0</v>
+      </c>
+      <c r="M557" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="558" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H558" s="2"/>
       <c r="I558" s="1"/>
       <c r="J558" s="2"/>
       <c r="K558" s="1"/>
-    </row>
-    <row r="559" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H559" s="2"/>
-      <c r="I559" s="1"/>
-      <c r="J559" s="2"/>
-      <c r="K559" s="1"/>
-    </row>
-    <row r="560" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H560" s="2"/>
-      <c r="I560" s="1"/>
-      <c r="J560" s="2"/>
-      <c r="K560" s="1"/>
-    </row>
-    <row r="561" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H561" s="2"/>
-      <c r="I561" s="1"/>
-      <c r="J561" s="2"/>
-      <c r="K561" s="1"/>
-    </row>
-    <row r="562" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H562" s="2"/>
-      <c r="I562" s="1"/>
-      <c r="J562" s="2"/>
-      <c r="K562" s="1"/>
-    </row>
-    <row r="563" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H563" s="2"/>
-      <c r="I563" s="1"/>
-      <c r="J563" s="2"/>
-      <c r="K563" s="1"/>
-    </row>
-    <row r="564" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H564" s="2"/>
-      <c r="I564" s="1"/>
-      <c r="J564" s="2"/>
-      <c r="K564" s="1"/>
-    </row>
-    <row r="565" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H565" s="2"/>
-      <c r="I565" s="1"/>
-      <c r="J565" s="2"/>
-      <c r="K565" s="1"/>
-    </row>
-    <row r="566" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H566" s="2"/>
-      <c r="I566" s="1"/>
-      <c r="J566" s="2"/>
-      <c r="K566" s="1"/>
-    </row>
-    <row r="567" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H567" s="2"/>
-      <c r="I567" s="1"/>
-      <c r="J567" s="2"/>
-      <c r="K567" s="1"/>
-    </row>
-    <row r="568" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H568" s="2"/>
-      <c r="I568" s="1"/>
-      <c r="J568" s="2"/>
-      <c r="K568" s="1"/>
-    </row>
-    <row r="569" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H569" s="2"/>
-      <c r="I569" s="1"/>
-      <c r="J569" s="2"/>
-      <c r="K569" s="1"/>
-    </row>
-    <row r="570" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H570" s="2"/>
-      <c r="I570" s="1"/>
-      <c r="J570" s="2"/>
-      <c r="K570" s="1"/>
-    </row>
-    <row r="571" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H571" s="2"/>
-      <c r="I571" s="1"/>
-      <c r="J571" s="2"/>
-      <c r="K571" s="1"/>
-    </row>
-    <row r="572" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H572" s="2"/>
-      <c r="I572" s="1"/>
-      <c r="J572" s="2"/>
-      <c r="K572" s="1"/>
-    </row>
-    <row r="573" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H573" s="2"/>
-      <c r="I573" s="1"/>
-      <c r="J573" s="2"/>
-      <c r="K573" s="1"/>
-    </row>
-    <row r="574" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H574" s="2"/>
-      <c r="I574" s="1"/>
-      <c r="J574" s="2"/>
-      <c r="K574" s="1"/>
-    </row>
-    <row r="575" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H575" s="2"/>
-      <c r="I575" s="1"/>
-      <c r="J575" s="2"/>
-      <c r="K575" s="1"/>
-    </row>
-    <row r="576" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H576" s="2"/>
-      <c r="I576" s="1"/>
-      <c r="J576" s="2"/>
-      <c r="K576" s="1"/>
-    </row>
-    <row r="577" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H577" s="2"/>
-      <c r="I577" s="1"/>
-      <c r="J577" s="2"/>
-      <c r="K577" s="1"/>
-    </row>
-    <row r="578" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H578" s="2"/>
-      <c r="I578" s="1"/>
-      <c r="J578" s="2"/>
-      <c r="K578" s="1"/>
-    </row>
-    <row r="579" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H579" s="2"/>
-      <c r="I579" s="1"/>
-      <c r="J579" s="2"/>
-      <c r="K579" s="1"/>
-    </row>
-    <row r="580" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H580" s="2"/>
-      <c r="I580" s="1"/>
-      <c r="J580" s="2"/>
-      <c r="K580" s="1"/>
-    </row>
-    <row r="581" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H581" s="2"/>
-      <c r="I581" s="1"/>
-      <c r="J581" s="2"/>
-      <c r="K581" s="1"/>
-    </row>
-    <row r="582" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M558" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="559" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D559" t="s">
+        <v>26</v>
+      </c>
+      <c r="E559">
+        <v>3496</v>
+      </c>
+      <c r="F559" t="s">
+        <v>44</v>
+      </c>
+      <c r="H559" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I559" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J559" s="2">
+        <v>0</v>
+      </c>
+      <c r="K559" s="1">
+        <v>46210.776273148149</v>
+      </c>
+      <c r="L559">
+        <v>0</v>
+      </c>
+      <c r="M559" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="560" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D560" t="s">
+        <v>26</v>
+      </c>
+      <c r="E560">
+        <v>3525</v>
+      </c>
+      <c r="F560" t="s">
+        <v>46</v>
+      </c>
+      <c r="H560" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I560" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J560" s="2">
+        <v>6.5277777777777782E-3</v>
+      </c>
+      <c r="K560" s="1">
+        <v>46210.776967592596</v>
+      </c>
+      <c r="L560">
+        <v>0</v>
+      </c>
+      <c r="M560" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="561" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D561" t="s">
+        <v>26</v>
+      </c>
+      <c r="E561">
+        <v>3508</v>
+      </c>
+      <c r="F561" t="s">
+        <v>48</v>
+      </c>
+      <c r="H561" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I561" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J561" s="2">
+        <v>0</v>
+      </c>
+      <c r="K561" s="1">
+        <v>46210.776967592596</v>
+      </c>
+      <c r="L561">
+        <v>0</v>
+      </c>
+      <c r="M561" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="562" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D562" t="s">
+        <v>26</v>
+      </c>
+      <c r="E562">
+        <v>5885</v>
+      </c>
+      <c r="F562" t="s">
+        <v>97</v>
+      </c>
+      <c r="H562" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I562" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J562" s="2">
+        <v>0</v>
+      </c>
+      <c r="K562" s="1">
+        <v>46210.777662037035</v>
+      </c>
+      <c r="L562">
+        <v>0</v>
+      </c>
+      <c r="M562" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="563" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D563" t="s">
+        <v>26</v>
+      </c>
+      <c r="E563">
+        <v>3483</v>
+      </c>
+      <c r="F563" t="s">
+        <v>49</v>
+      </c>
+      <c r="H563" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I563" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J563" s="2">
+        <v>0</v>
+      </c>
+      <c r="K563" s="1">
+        <v>46210.778356481482</v>
+      </c>
+      <c r="L563">
+        <v>0</v>
+      </c>
+      <c r="M563" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="564" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D564" t="s">
+        <v>26</v>
+      </c>
+      <c r="E564">
+        <v>3499</v>
+      </c>
+      <c r="F564" t="s">
+        <v>50</v>
+      </c>
+      <c r="H564" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I564" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J564" s="2">
+        <v>7.1643518518518514E-3</v>
+      </c>
+      <c r="K564" s="1">
+        <v>46210.779050925928</v>
+      </c>
+      <c r="L564">
+        <v>0</v>
+      </c>
+      <c r="M564" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="565" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D565" t="s">
+        <v>26</v>
+      </c>
+      <c r="E565">
+        <v>3699</v>
+      </c>
+      <c r="F565" t="s">
+        <v>51</v>
+      </c>
+      <c r="H565" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I565" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J565" s="2">
+        <v>0</v>
+      </c>
+      <c r="K565" s="1">
+        <v>46210.793055555558</v>
+      </c>
+      <c r="L565">
+        <v>0</v>
+      </c>
+      <c r="M565" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="566" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D566" t="s">
+        <v>26</v>
+      </c>
+      <c r="E566">
+        <v>3491</v>
+      </c>
+      <c r="F566" t="s">
+        <v>52</v>
+      </c>
+      <c r="H566" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I566" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J566" s="2">
+        <v>0</v>
+      </c>
+      <c r="K566" s="1">
+        <v>46210.793749999997</v>
+      </c>
+      <c r="L566">
+        <v>0</v>
+      </c>
+      <c r="M566" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="567" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D567" t="s">
+        <v>26</v>
+      </c>
+      <c r="E567">
+        <v>3487</v>
+      </c>
+      <c r="F567" t="s">
+        <v>53</v>
+      </c>
+      <c r="H567" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I567" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J567" s="2">
+        <v>0</v>
+      </c>
+      <c r="K567" s="1">
+        <v>46210.794444444444</v>
+      </c>
+      <c r="L567">
+        <v>0</v>
+      </c>
+      <c r="M567" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="568" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D568" t="s">
+        <v>26</v>
+      </c>
+      <c r="E568">
+        <v>3704</v>
+      </c>
+      <c r="F568" t="s">
+        <v>54</v>
+      </c>
+      <c r="H568" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I568" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J568" s="2">
+        <v>0</v>
+      </c>
+      <c r="K568" s="1">
+        <v>46210.795138888891</v>
+      </c>
+      <c r="L568">
+        <v>0</v>
+      </c>
+      <c r="M568" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="569" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D569" t="s">
+        <v>26</v>
+      </c>
+      <c r="E569">
+        <v>3481</v>
+      </c>
+      <c r="F569" t="s">
+        <v>55</v>
+      </c>
+      <c r="H569" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I569" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J569" s="2">
+        <v>1.3518518518518518E-2</v>
+      </c>
+      <c r="K569" s="1">
+        <v>46210.79583333333</v>
+      </c>
+      <c r="L569">
+        <v>0</v>
+      </c>
+      <c r="M569" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="570" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D570" t="s">
+        <v>26</v>
+      </c>
+      <c r="E570">
+        <v>3480</v>
+      </c>
+      <c r="F570" t="s">
+        <v>56</v>
+      </c>
+      <c r="H570" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I570" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J570" s="2">
+        <v>0</v>
+      </c>
+      <c r="K570" s="1">
+        <v>46210.796527777777</v>
+      </c>
+      <c r="L570">
+        <v>0</v>
+      </c>
+      <c r="M570" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="571" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D571" t="s">
+        <v>26</v>
+      </c>
+      <c r="E571">
+        <v>3511</v>
+      </c>
+      <c r="F571" t="s">
+        <v>57</v>
+      </c>
+      <c r="H571" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I571" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J571" s="2">
+        <v>6.0069444444444441E-3</v>
+      </c>
+      <c r="K571" s="1">
+        <v>46210.797222222223</v>
+      </c>
+      <c r="L571">
+        <v>0</v>
+      </c>
+      <c r="M571" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="572" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D572" t="s">
+        <v>26</v>
+      </c>
+      <c r="E572">
+        <v>3484</v>
+      </c>
+      <c r="F572" t="s">
+        <v>59</v>
+      </c>
+      <c r="H572" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I572" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J572" s="2">
+        <v>6.6550925925925927E-3</v>
+      </c>
+      <c r="K572" s="1">
+        <v>46210.79791666667</v>
+      </c>
+      <c r="L572">
+        <v>0</v>
+      </c>
+      <c r="M572" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="573" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D573" t="s">
+        <v>26</v>
+      </c>
+      <c r="E573">
+        <v>3514</v>
+      </c>
+      <c r="F573" t="s">
+        <v>60</v>
+      </c>
+      <c r="H573" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I573" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J573" s="2">
+        <v>6.4236111111111108E-3</v>
+      </c>
+      <c r="K573" s="1">
+        <v>46210.79791666667</v>
+      </c>
+      <c r="L573">
+        <v>0</v>
+      </c>
+      <c r="M573" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="574" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D574" t="s">
+        <v>26</v>
+      </c>
+      <c r="E574">
+        <v>3725</v>
+      </c>
+      <c r="F574" t="s">
+        <v>62</v>
+      </c>
+      <c r="H574" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I574" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J574" s="2">
+        <v>0</v>
+      </c>
+      <c r="K574" s="1">
+        <v>46210.798611111109</v>
+      </c>
+      <c r="L574">
+        <v>0</v>
+      </c>
+      <c r="M574" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="575" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D575" t="s">
+        <v>26</v>
+      </c>
+      <c r="E575">
+        <v>3488</v>
+      </c>
+      <c r="F575" t="s">
+        <v>63</v>
+      </c>
+      <c r="H575" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I575" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J575" s="2">
+        <v>0</v>
+      </c>
+      <c r="K575" s="1">
+        <v>46210.799305555556</v>
+      </c>
+      <c r="L575">
+        <v>0</v>
+      </c>
+      <c r="M575" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="576" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D576" t="s">
+        <v>26</v>
+      </c>
+      <c r="E576">
+        <v>5884</v>
+      </c>
+      <c r="F576" t="s">
+        <v>98</v>
+      </c>
+      <c r="H576" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I576" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J576" s="2">
+        <v>0</v>
+      </c>
+      <c r="K576" s="1">
+        <v>46210.8</v>
+      </c>
+      <c r="L576">
+        <v>0</v>
+      </c>
+      <c r="M576" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="577" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D577" t="s">
+        <v>26</v>
+      </c>
+      <c r="E577">
+        <v>3478</v>
+      </c>
+      <c r="F577" t="s">
+        <v>64</v>
+      </c>
+      <c r="H577" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I577" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J577" s="2">
+        <v>0</v>
+      </c>
+      <c r="K577" s="1">
+        <v>46210.800694444442</v>
+      </c>
+      <c r="L577">
+        <v>0</v>
+      </c>
+      <c r="M577" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="578" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D578" t="s">
+        <v>26</v>
+      </c>
+      <c r="E578">
+        <v>3494</v>
+      </c>
+      <c r="F578" t="s">
+        <v>65</v>
+      </c>
+      <c r="H578" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I578" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J578" s="2">
+        <v>2.0474537037037038E-2</v>
+      </c>
+      <c r="K578" s="1">
+        <v>46210.801388888889</v>
+      </c>
+      <c r="L578">
+        <v>0</v>
+      </c>
+      <c r="M578" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="579" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D579" t="s">
+        <v>26</v>
+      </c>
+      <c r="E579">
+        <v>3523</v>
+      </c>
+      <c r="F579" t="s">
+        <v>66</v>
+      </c>
+      <c r="H579" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I579" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J579" s="2">
+        <v>8.5532407407407415E-3</v>
+      </c>
+      <c r="K579" s="1">
+        <v>46210.802083333336</v>
+      </c>
+      <c r="L579">
+        <v>0</v>
+      </c>
+      <c r="M579" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="580" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D580" t="s">
+        <v>26</v>
+      </c>
+      <c r="E580">
+        <v>5886</v>
+      </c>
+      <c r="F580" t="s">
+        <v>99</v>
+      </c>
+      <c r="H580" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I580" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J580" s="2">
+        <v>6.1111111111111114E-3</v>
+      </c>
+      <c r="K580" s="1">
+        <v>46210.802777777775</v>
+      </c>
+      <c r="L580">
+        <v>0</v>
+      </c>
+      <c r="M580" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="581" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D581" t="s">
+        <v>26</v>
+      </c>
+      <c r="E581">
+        <v>3504</v>
+      </c>
+      <c r="F581" t="s">
+        <v>68</v>
+      </c>
+      <c r="H581" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I581" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J581" s="2">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="K581" s="1">
+        <v>46210.802777777775</v>
+      </c>
+      <c r="L581">
+        <v>0</v>
+      </c>
+      <c r="M581" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="582" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H582" s="2"/>
       <c r="I582" s="1"/>
       <c r="J582" s="2"/>
       <c r="K582" s="1"/>
-    </row>
-    <row r="583" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H583" s="2"/>
-      <c r="I583" s="1"/>
-      <c r="J583" s="2"/>
-      <c r="K583" s="1"/>
-    </row>
-    <row r="584" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H584" s="2"/>
-      <c r="I584" s="1"/>
-      <c r="J584" s="2"/>
-      <c r="K584" s="1"/>
-    </row>
-    <row r="585" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H585" s="2"/>
-      <c r="I585" s="1"/>
-      <c r="J585" s="2"/>
-      <c r="K585" s="1"/>
-    </row>
-    <row r="586" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H586" s="2"/>
-      <c r="I586" s="1"/>
-      <c r="J586" s="2"/>
-      <c r="K586" s="1"/>
-    </row>
-    <row r="587" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H587" s="2"/>
-      <c r="I587" s="1"/>
-      <c r="J587" s="2"/>
-      <c r="K587" s="1"/>
-    </row>
-    <row r="588" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H588" s="2"/>
-      <c r="I588" s="1"/>
-      <c r="J588" s="2"/>
-      <c r="K588" s="1"/>
-    </row>
-    <row r="589" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H589" s="2"/>
-      <c r="I589" s="1"/>
-      <c r="J589" s="2"/>
-      <c r="K589" s="1"/>
-    </row>
-    <row r="590" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H590" s="2"/>
-      <c r="I590" s="1"/>
-      <c r="J590" s="2"/>
-      <c r="K590" s="1"/>
-    </row>
-    <row r="591" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H591" s="2"/>
-      <c r="I591" s="1"/>
-      <c r="J591" s="2"/>
-      <c r="K591" s="1"/>
-    </row>
-    <row r="592" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H592" s="2"/>
-      <c r="I592" s="1"/>
-      <c r="J592" s="2"/>
-      <c r="K592" s="1"/>
-    </row>
-    <row r="593" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H593" s="2"/>
-      <c r="I593" s="1"/>
-      <c r="J593" s="2"/>
-      <c r="K593" s="1"/>
-    </row>
-    <row r="594" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M582" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="583" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D583" t="s">
+        <v>26</v>
+      </c>
+      <c r="E583">
+        <v>3498</v>
+      </c>
+      <c r="F583" t="s">
+        <v>69</v>
+      </c>
+      <c r="H583" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I583" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J583" s="2">
+        <v>7.3842592592592597E-3</v>
+      </c>
+      <c r="K583" s="1">
+        <v>46210.803472222222</v>
+      </c>
+      <c r="L583">
+        <v>0</v>
+      </c>
+      <c r="M583" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="584" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D584" t="s">
+        <v>26</v>
+      </c>
+      <c r="E584">
+        <v>3344</v>
+      </c>
+      <c r="F584" t="s">
+        <v>70</v>
+      </c>
+      <c r="H584" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I584" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J584" s="2">
+        <v>0</v>
+      </c>
+      <c r="K584" s="1">
+        <v>46210.804166666669</v>
+      </c>
+      <c r="L584">
+        <v>0</v>
+      </c>
+      <c r="M584" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="585" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D585" t="s">
+        <v>26</v>
+      </c>
+      <c r="E585">
+        <v>3515</v>
+      </c>
+      <c r="F585" t="s">
+        <v>71</v>
+      </c>
+      <c r="H585" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I585" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J585" s="2">
+        <v>0</v>
+      </c>
+      <c r="K585" s="1">
+        <v>46210.804861111108</v>
+      </c>
+      <c r="L585">
+        <v>0</v>
+      </c>
+      <c r="M585" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="586" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D586" t="s">
+        <v>26</v>
+      </c>
+      <c r="E586">
+        <v>3522</v>
+      </c>
+      <c r="F586" t="s">
+        <v>72</v>
+      </c>
+      <c r="H586" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I586" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J586" s="2">
+        <v>0</v>
+      </c>
+      <c r="K586" s="1">
+        <v>46210.805555555555</v>
+      </c>
+      <c r="L586">
+        <v>0</v>
+      </c>
+      <c r="M586" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="587" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D587" t="s">
+        <v>26</v>
+      </c>
+      <c r="E587">
+        <v>3751</v>
+      </c>
+      <c r="F587" t="s">
+        <v>73</v>
+      </c>
+      <c r="H587" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I587" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J587" s="2">
+        <v>0</v>
+      </c>
+      <c r="K587" s="1">
+        <v>46210.805555555555</v>
+      </c>
+      <c r="L587">
+        <v>0</v>
+      </c>
+      <c r="M587" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="588" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D588" t="s">
+        <v>26</v>
+      </c>
+      <c r="E588">
+        <v>5890</v>
+      </c>
+      <c r="F588" t="s">
+        <v>100</v>
+      </c>
+      <c r="H588" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I588" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J588" s="2">
+        <v>0</v>
+      </c>
+      <c r="K588" s="1">
+        <v>46210.806250000001</v>
+      </c>
+      <c r="L588">
+        <v>0</v>
+      </c>
+      <c r="M588" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="589" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D589" t="s">
+        <v>26</v>
+      </c>
+      <c r="E589">
+        <v>5891</v>
+      </c>
+      <c r="F589" t="s">
+        <v>101</v>
+      </c>
+      <c r="H589" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I589" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J589" s="2">
+        <v>0</v>
+      </c>
+      <c r="K589" s="1">
+        <v>46210.806944444441</v>
+      </c>
+      <c r="L589">
+        <v>0</v>
+      </c>
+      <c r="M589" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="590" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D590" t="s">
+        <v>26</v>
+      </c>
+      <c r="E590">
+        <v>3503</v>
+      </c>
+      <c r="F590" t="s">
+        <v>76</v>
+      </c>
+      <c r="H590" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I590" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J590" s="2">
+        <v>0</v>
+      </c>
+      <c r="K590" s="1">
+        <v>46210.807638888888</v>
+      </c>
+      <c r="L590">
+        <v>0</v>
+      </c>
+      <c r="M590" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="591" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D591" t="s">
+        <v>26</v>
+      </c>
+      <c r="E591">
+        <v>3652</v>
+      </c>
+      <c r="F591" t="s">
+        <v>77</v>
+      </c>
+      <c r="H591" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I591" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J591" s="2">
+        <v>0</v>
+      </c>
+      <c r="K591" s="1">
+        <v>46210.808333333334</v>
+      </c>
+      <c r="L591">
+        <v>0</v>
+      </c>
+      <c r="M591" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="592" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D592" t="s">
+        <v>26</v>
+      </c>
+      <c r="E592">
+        <v>3509</v>
+      </c>
+      <c r="F592" t="s">
+        <v>78</v>
+      </c>
+      <c r="H592" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I592" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J592" s="2">
+        <v>0</v>
+      </c>
+      <c r="K592" s="1">
+        <v>46210.809027777781</v>
+      </c>
+      <c r="L592">
+        <v>0</v>
+      </c>
+      <c r="M592" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="593" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D593" t="s">
+        <v>26</v>
+      </c>
+      <c r="E593">
+        <v>5617</v>
+      </c>
+      <c r="F593" t="s">
+        <v>92</v>
+      </c>
+      <c r="H593" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I593" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J593" s="2">
+        <v>0</v>
+      </c>
+      <c r="K593" s="1">
+        <v>46210.809027777781</v>
+      </c>
+      <c r="L593">
+        <v>0</v>
+      </c>
+      <c r="M593" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="594" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H594" s="2"/>
       <c r="I594" s="1"/>
       <c r="J594" s="2"/>
       <c r="K594" s="1"/>
-    </row>
-    <row r="595" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H595" s="2"/>
-      <c r="I595" s="1"/>
-      <c r="J595" s="2"/>
-      <c r="K595" s="1"/>
-    </row>
-    <row r="596" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H596" s="2"/>
-      <c r="I596" s="1"/>
-      <c r="J596" s="2"/>
-      <c r="K596" s="1"/>
-    </row>
-    <row r="597" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M594" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="595" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D595" t="s">
+        <v>26</v>
+      </c>
+      <c r="E595">
+        <v>5465</v>
+      </c>
+      <c r="F595" t="s">
+        <v>89</v>
+      </c>
+      <c r="H595" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I595" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J595" s="2">
+        <v>7.905092592592592E-3</v>
+      </c>
+      <c r="K595" s="1">
+        <v>46210.80972222222</v>
+      </c>
+      <c r="L595">
+        <v>0</v>
+      </c>
+      <c r="M595" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="596" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D596" t="s">
+        <v>26</v>
+      </c>
+      <c r="E596">
+        <v>3512</v>
+      </c>
+      <c r="F596" t="s">
+        <v>79</v>
+      </c>
+      <c r="H596" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I596" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J596" s="2">
+        <v>1.1331018518518518E-2</v>
+      </c>
+      <c r="K596" s="1">
+        <v>46210.810416666667</v>
+      </c>
+      <c r="L596">
+        <v>0</v>
+      </c>
+      <c r="M596" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="597" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H597" s="2"/>
       <c r="I597" s="1"/>
       <c r="J597" s="2"/>
       <c r="K597" s="1"/>
-    </row>
-    <row r="598" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H598" s="2"/>
-      <c r="I598" s="1"/>
-      <c r="J598" s="2"/>
-      <c r="K598" s="1"/>
-    </row>
-    <row r="599" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H599" s="2"/>
-      <c r="I599" s="1"/>
-      <c r="J599" s="2"/>
-      <c r="K599" s="1"/>
-    </row>
-    <row r="600" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H600" s="2"/>
-      <c r="I600" s="1"/>
-      <c r="J600" s="2"/>
-      <c r="K600" s="1"/>
-    </row>
-    <row r="601" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H601" s="2"/>
-      <c r="I601" s="1"/>
-      <c r="J601" s="2"/>
-      <c r="K601" s="1"/>
-    </row>
-    <row r="602" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H602" s="2"/>
-      <c r="I602" s="1"/>
-      <c r="J602" s="2"/>
-      <c r="K602" s="1"/>
-    </row>
-    <row r="603" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H603" s="2"/>
-      <c r="I603" s="1"/>
-      <c r="J603" s="2"/>
-      <c r="K603" s="1"/>
-    </row>
-    <row r="604" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H604" s="2"/>
-      <c r="I604" s="1"/>
-      <c r="J604" s="2"/>
-      <c r="K604" s="1"/>
-    </row>
-    <row r="605" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H605" s="2"/>
-      <c r="I605" s="1"/>
-      <c r="J605" s="2"/>
-      <c r="K605" s="1"/>
-    </row>
-    <row r="606" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H606" s="2"/>
-      <c r="I606" s="1"/>
-      <c r="J606" s="2"/>
-      <c r="K606" s="1"/>
-    </row>
-    <row r="607" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H607" s="2"/>
-      <c r="I607" s="1"/>
-      <c r="J607" s="2"/>
-      <c r="K607" s="1"/>
-    </row>
-    <row r="608" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H608" s="2"/>
-      <c r="I608" s="1"/>
-      <c r="J608" s="2"/>
-      <c r="K608" s="1"/>
-    </row>
-    <row r="609" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M597" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="598" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D598" t="s">
+        <v>26</v>
+      </c>
+      <c r="E598">
+        <v>3489</v>
+      </c>
+      <c r="F598" t="s">
+        <v>80</v>
+      </c>
+      <c r="H598" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I598" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J598" s="2">
+        <v>0</v>
+      </c>
+      <c r="K598" s="1">
+        <v>46210.811111111114</v>
+      </c>
+      <c r="L598">
+        <v>0</v>
+      </c>
+      <c r="M598" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="599" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D599" t="s">
+        <v>26</v>
+      </c>
+      <c r="E599">
+        <v>3266</v>
+      </c>
+      <c r="F599" t="s">
+        <v>81</v>
+      </c>
+      <c r="H599" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I599" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J599" s="2">
+        <v>6.122685185185185E-3</v>
+      </c>
+      <c r="K599" s="1">
+        <v>46210.811805555553</v>
+      </c>
+      <c r="L599">
+        <v>0</v>
+      </c>
+      <c r="M599" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="600" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D600" t="s">
+        <v>26</v>
+      </c>
+      <c r="E600">
+        <v>3492</v>
+      </c>
+      <c r="F600" t="s">
+        <v>82</v>
+      </c>
+      <c r="H600" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I600" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J600" s="2">
+        <v>0</v>
+      </c>
+      <c r="K600" s="1">
+        <v>46210.8125</v>
+      </c>
+      <c r="L600">
+        <v>0</v>
+      </c>
+      <c r="M600" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="601" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D601" t="s">
+        <v>26</v>
+      </c>
+      <c r="E601">
+        <v>3493</v>
+      </c>
+      <c r="F601" t="s">
+        <v>83</v>
+      </c>
+      <c r="H601" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I601" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J601" s="2">
+        <v>0</v>
+      </c>
+      <c r="K601" s="1">
+        <v>46210.8125</v>
+      </c>
+      <c r="L601">
+        <v>0</v>
+      </c>
+      <c r="M601" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="602" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D602" t="s">
+        <v>26</v>
+      </c>
+      <c r="E602">
+        <v>3505</v>
+      </c>
+      <c r="F602" t="s">
+        <v>84</v>
+      </c>
+      <c r="H602" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I602" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J602" s="2">
+        <v>6.7708333333333336E-3</v>
+      </c>
+      <c r="K602" s="1">
+        <v>46210.813194444447</v>
+      </c>
+      <c r="L602">
+        <v>0</v>
+      </c>
+      <c r="M602" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="603" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D603" t="s">
+        <v>26</v>
+      </c>
+      <c r="E603">
+        <v>3861</v>
+      </c>
+      <c r="F603" t="s">
+        <v>85</v>
+      </c>
+      <c r="H603" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I603" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J603" s="2">
+        <v>2.4699074074074075E-2</v>
+      </c>
+      <c r="K603" s="1">
+        <v>46210.813888888886</v>
+      </c>
+      <c r="L603">
+        <v>0</v>
+      </c>
+      <c r="M603" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="604" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D604" t="s">
+        <v>26</v>
+      </c>
+      <c r="E604">
+        <v>5205</v>
+      </c>
+      <c r="F604" t="s">
+        <v>87</v>
+      </c>
+      <c r="H604" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I604" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J604" s="2">
+        <v>0</v>
+      </c>
+      <c r="K604" s="1">
+        <v>46210.814583333333</v>
+      </c>
+      <c r="L604">
+        <v>0</v>
+      </c>
+      <c r="M604" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="605" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D605" t="s">
+        <v>26</v>
+      </c>
+      <c r="E605">
+        <v>5782</v>
+      </c>
+      <c r="F605" t="s">
+        <v>102</v>
+      </c>
+      <c r="H605" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I605" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J605" s="2">
+        <v>0</v>
+      </c>
+      <c r="K605" s="1">
+        <v>46210.81527777778</v>
+      </c>
+      <c r="L605">
+        <v>0</v>
+      </c>
+      <c r="M605" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="606" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D606" t="s">
+        <v>26</v>
+      </c>
+      <c r="E606">
+        <v>5887</v>
+      </c>
+      <c r="F606" t="s">
+        <v>103</v>
+      </c>
+      <c r="H606" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I606" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J606" s="2">
+        <v>0</v>
+      </c>
+      <c r="K606" s="1">
+        <v>46210.81527777778</v>
+      </c>
+      <c r="L606">
+        <v>0</v>
+      </c>
+      <c r="M606" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="607" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D607" t="s">
+        <v>26</v>
+      </c>
+      <c r="E607">
+        <v>3538</v>
+      </c>
+      <c r="F607" t="s">
+        <v>86</v>
+      </c>
+      <c r="H607" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I607" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J607" s="2">
+        <v>8.067129629629629E-3</v>
+      </c>
+      <c r="K607" s="1">
+        <v>46210.815972222219</v>
+      </c>
+      <c r="L607">
+        <v>0</v>
+      </c>
+      <c r="M607" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="608" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D608" t="s">
+        <v>26</v>
+      </c>
+      <c r="E608">
+        <v>5603</v>
+      </c>
+      <c r="F608" t="s">
+        <v>93</v>
+      </c>
+      <c r="H608" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I608" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J608" s="2">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="K608" s="1">
+        <v>46210.816666666666</v>
+      </c>
+      <c r="L608">
+        <v>0</v>
+      </c>
+      <c r="M608" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="609" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H609" s="2"/>
       <c r="I609" s="1"/>
       <c r="J609" s="2"/>
       <c r="K609" s="1"/>
-    </row>
-    <row r="610" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M609" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="610" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H610" s="2"/>
       <c r="I610" s="1"/>
       <c r="J610" s="2"/>
       <c r="K610" s="1"/>
     </row>
-    <row r="611" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="611" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H611" s="2"/>
       <c r="I611" s="1"/>
       <c r="J611" s="2"/>
       <c r="K611" s="1"/>
     </row>
-    <row r="612" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="612" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H612" s="2"/>
       <c r="I612" s="1"/>
       <c r="J612" s="2"/>
       <c r="K612" s="1"/>
     </row>
-    <row r="613" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="613" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H613" s="2"/>
       <c r="I613" s="1"/>
       <c r="J613" s="2"/>
       <c r="K613" s="1"/>
     </row>
-    <row r="614" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="614" spans="8:13" x14ac:dyDescent="0.3">
       <c r="I614" s="1"/>
       <c r="J614" s="2"/>
       <c r="K614" s="1"/>
     </row>
-    <row r="615" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="615" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H615" s="2"/>
       <c r="I615" s="1"/>
       <c r="J615" s="2"/>
       <c r="K615" s="1"/>
     </row>
-    <row r="616" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="616" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H616" s="2"/>
       <c r="I616" s="1"/>
       <c r="J616" s="2"/>
       <c r="K616" s="1"/>
     </row>
-    <row r="617" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="617" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H617" s="2"/>
       <c r="I617" s="1"/>
       <c r="J617" s="2"/>
       <c r="K617" s="1"/>
     </row>
-    <row r="618" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="618" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H618" s="2"/>
       <c r="I618" s="1"/>
       <c r="J618" s="2"/>
       <c r="K618" s="1"/>
     </row>
-    <row r="619" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="619" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H619" s="2"/>
       <c r="I619" s="1"/>
       <c r="J619" s="2"/>
       <c r="K619" s="1"/>
     </row>
-    <row r="620" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="620" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H620" s="2"/>
       <c r="I620" s="1"/>
       <c r="J620" s="2"/>
       <c r="K620" s="1"/>
     </row>
-    <row r="621" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="621" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H621" s="2"/>
       <c r="I621" s="1"/>
       <c r="J621" s="2"/>
       <c r="K621" s="1"/>
     </row>
-    <row r="622" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="622" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H622" s="2"/>
       <c r="I622" s="1"/>
       <c r="J622" s="2"/>
       <c r="K622" s="1"/>
     </row>
-    <row r="623" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="623" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H623" s="2"/>
       <c r="I623" s="1"/>
       <c r="J623" s="2"/>
       <c r="K623" s="1"/>
     </row>
-    <row r="624" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="624" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H624" s="2"/>
       <c r="I624" s="1"/>
       <c r="J624" s="2"/>
@@ -50167,7 +51782,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Fiore-and-Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21D18C14-3AB1-40AC-BDC5-73E7F7C70B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84B1B22F-70AC-4321-A030-4ECEB82E2D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -86,7 +86,10 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
     <t>Winter Weather</t>
@@ -98,22 +101,19 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
+    <t>Speed Management</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
   </si>
   <si>
     <t>Speed Mangement-C</t>
-  </si>
-  <si>
-    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
     <t>In Cab Distractions</t>
@@ -724,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -806,7 +806,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="1"/>
       <c r="M3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
@@ -820,7 +820,7 @@
         <v>27</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>12</v>
@@ -844,7 +844,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="1"/>
       <c r="M5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
@@ -858,7 +858,7 @@
         <v>28</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -887,7 +887,7 @@
         <v>29</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>12</v>
@@ -911,7 +911,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="1"/>
       <c r="M8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
@@ -925,7 +925,7 @@
         <v>30</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -954,7 +954,7 @@
         <v>31</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -983,7 +983,7 @@
         <v>32</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -1012,7 +1012,7 @@
         <v>33</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>13</v>
@@ -1041,7 +1041,7 @@
         <v>34</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>12</v>
@@ -1065,7 +1065,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="1"/>
       <c r="M14" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
@@ -1079,7 +1079,7 @@
         <v>35</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1108,7 +1108,7 @@
         <v>36</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>13</v>
@@ -1137,7 +1137,7 @@
         <v>37</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1166,7 +1166,7 @@
         <v>38</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>13</v>
@@ -1195,7 +1195,7 @@
         <v>39</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -1224,7 +1224,7 @@
         <v>40</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -1253,7 +1253,7 @@
         <v>41</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -1282,7 +1282,7 @@
         <v>42</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
@@ -1311,7 +1311,7 @@
         <v>43</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>12</v>
@@ -1335,7 +1335,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="1"/>
       <c r="M24" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
@@ -1349,7 +1349,7 @@
         <v>44</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
@@ -1378,7 +1378,7 @@
         <v>45</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>12</v>
@@ -1402,7 +1402,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="1"/>
       <c r="M27" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
@@ -1416,7 +1416,7 @@
         <v>46</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1445,7 +1445,7 @@
         <v>47</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>13</v>
@@ -1474,7 +1474,7 @@
         <v>48</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>13</v>
@@ -1503,7 +1503,7 @@
         <v>49</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1532,7 +1532,7 @@
         <v>50</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>12</v>
@@ -1556,7 +1556,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="1"/>
       <c r="M33" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
@@ -1570,7 +1570,7 @@
         <v>51</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1599,7 +1599,7 @@
         <v>52</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -1628,7 +1628,7 @@
         <v>53</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>12</v>
@@ -1652,7 +1652,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="1"/>
       <c r="M37" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
@@ -1666,7 +1666,7 @@
         <v>54</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>13</v>
@@ -1695,7 +1695,7 @@
         <v>55</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1724,7 +1724,7 @@
         <v>56</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1753,7 +1753,7 @@
         <v>57</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1782,7 +1782,7 @@
         <v>58</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
@@ -1811,7 +1811,7 @@
         <v>59</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
@@ -1840,7 +1840,7 @@
         <v>60</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>13</v>
@@ -1869,7 +1869,7 @@
         <v>61</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>13</v>
@@ -1898,7 +1898,7 @@
         <v>62</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>10</v>
@@ -1927,7 +1927,7 @@
         <v>63</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>12</v>
@@ -1951,7 +1951,7 @@
       <c r="J48" s="2"/>
       <c r="K48" s="1"/>
       <c r="M48" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
@@ -1965,7 +1965,7 @@
         <v>64</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>12</v>
@@ -1989,7 +1989,7 @@
       <c r="J50" s="2"/>
       <c r="K50" s="1"/>
       <c r="M50" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
@@ -2003,7 +2003,7 @@
         <v>65</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
@@ -2032,7 +2032,7 @@
         <v>66</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>13</v>
@@ -2061,7 +2061,7 @@
         <v>67</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>13</v>
@@ -2090,7 +2090,7 @@
         <v>68</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>13</v>
@@ -2119,7 +2119,7 @@
         <v>69</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2148,7 +2148,7 @@
         <v>70</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>12</v>
@@ -2172,7 +2172,7 @@
       <c r="J57" s="2"/>
       <c r="K57" s="1"/>
       <c r="M57" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.3">
@@ -2186,7 +2186,7 @@
         <v>71</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>12</v>
@@ -2210,7 +2210,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="1"/>
       <c r="M59" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
@@ -2224,7 +2224,7 @@
         <v>72</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -2253,7 +2253,7 @@
         <v>73</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>10</v>
@@ -2282,7 +2282,7 @@
         <v>74</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>14</v>
@@ -2306,7 +2306,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="1"/>
       <c r="M63" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
@@ -2320,7 +2320,7 @@
         <v>75</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -2349,7 +2349,7 @@
         <v>76</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2378,7 +2378,7 @@
         <v>77</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>12</v>
@@ -2402,7 +2402,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="1"/>
       <c r="M67" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
@@ -2416,7 +2416,7 @@
         <v>78</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>10</v>
@@ -2445,7 +2445,7 @@
         <v>79</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2474,7 +2474,7 @@
         <v>80</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2503,7 +2503,7 @@
         <v>81</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2532,7 +2532,7 @@
         <v>82</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>13</v>
@@ -2561,7 +2561,7 @@
         <v>83</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>13</v>
@@ -2590,7 +2590,7 @@
         <v>84</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2619,7 +2619,7 @@
         <v>85</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>13</v>
@@ -2648,7 +2648,7 @@
         <v>86</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>10</v>
@@ -2677,7 +2677,7 @@
         <v>27</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>13</v>
@@ -2706,7 +2706,7 @@
         <v>28</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>12</v>
@@ -2730,7 +2730,7 @@
       <c r="J79" s="2"/>
       <c r="K79" s="1"/>
       <c r="M79" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
@@ -2744,7 +2744,7 @@
         <v>29</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>13</v>
@@ -2773,7 +2773,7 @@
         <v>30</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -2802,7 +2802,7 @@
         <v>31</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2831,7 +2831,7 @@
         <v>32</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -2860,7 +2860,7 @@
         <v>33</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>13</v>
@@ -2889,7 +2889,7 @@
         <v>34</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>13</v>
@@ -2918,7 +2918,7 @@
         <v>35</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>10</v>
@@ -2947,7 +2947,7 @@
         <v>36</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>13</v>
@@ -2976,7 +2976,7 @@
         <v>37</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>10</v>
@@ -3005,7 +3005,7 @@
         <v>38</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -3034,7 +3034,7 @@
         <v>39</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>10</v>
@@ -3063,7 +3063,7 @@
         <v>40</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>10</v>
@@ -3092,7 +3092,7 @@
         <v>41</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>10</v>
@@ -3121,7 +3121,7 @@
         <v>42</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3150,7 +3150,7 @@
         <v>43</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>14</v>
@@ -3174,7 +3174,7 @@
       <c r="J95" s="2"/>
       <c r="K95" s="1"/>
       <c r="M95" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
@@ -3188,7 +3188,7 @@
         <v>44</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>13</v>
@@ -3217,7 +3217,7 @@
         <v>45</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>13</v>
@@ -3246,7 +3246,7 @@
         <v>46</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3275,7 +3275,7 @@
         <v>47</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>13</v>
@@ -3304,7 +3304,7 @@
         <v>48</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>13</v>
@@ -3333,7 +3333,7 @@
         <v>49</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>12</v>
@@ -3357,7 +3357,7 @@
       <c r="J102" s="2"/>
       <c r="K102" s="1"/>
       <c r="M102" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
@@ -3371,7 +3371,7 @@
         <v>50</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3400,7 +3400,7 @@
         <v>51</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>12</v>
@@ -3424,7 +3424,7 @@
       <c r="J105" s="2"/>
       <c r="K105" s="1"/>
       <c r="M105" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106" spans="4:13" x14ac:dyDescent="0.3">
@@ -3438,7 +3438,7 @@
         <v>52</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>13</v>
@@ -3467,7 +3467,7 @@
         <v>53</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>13</v>
@@ -3496,7 +3496,7 @@
         <v>54</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>13</v>
@@ -3525,7 +3525,7 @@
         <v>55</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>12</v>
@@ -3549,7 +3549,7 @@
       <c r="J110" s="2"/>
       <c r="K110" s="1"/>
       <c r="M110" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
@@ -3563,7 +3563,7 @@
         <v>56</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>10</v>
@@ -3592,7 +3592,7 @@
         <v>57</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>10</v>
@@ -3621,7 +3621,7 @@
         <v>58</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>12</v>
@@ -3645,7 +3645,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
       <c r="M114" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
@@ -3659,7 +3659,7 @@
         <v>59</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>10</v>
@@ -3688,7 +3688,7 @@
         <v>60</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>13</v>
@@ -3717,7 +3717,7 @@
         <v>61</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>13</v>
@@ -3746,7 +3746,7 @@
         <v>62</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>13</v>
@@ -3775,7 +3775,7 @@
         <v>63</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>12</v>
@@ -3799,7 +3799,7 @@
       <c r="J120" s="2"/>
       <c r="K120" s="1"/>
       <c r="M120" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
@@ -3813,7 +3813,7 @@
         <v>64</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>13</v>
@@ -3842,7 +3842,7 @@
         <v>65</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -3871,7 +3871,7 @@
         <v>66</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>13</v>
@@ -3900,7 +3900,7 @@
         <v>68</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>13</v>
@@ -3929,7 +3929,7 @@
         <v>69</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>10</v>
@@ -3958,7 +3958,7 @@
         <v>70</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -3987,7 +3987,7 @@
         <v>71</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>13</v>
@@ -4016,7 +4016,7 @@
         <v>72</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>10</v>
@@ -4045,7 +4045,7 @@
         <v>73</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>13</v>
@@ -4074,7 +4074,7 @@
         <v>74</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4103,7 +4103,7 @@
         <v>75</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>13</v>
@@ -4132,7 +4132,7 @@
         <v>76</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>14</v>
@@ -4156,7 +4156,7 @@
       <c r="J133" s="2"/>
       <c r="K133" s="1"/>
       <c r="M133" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
@@ -4170,7 +4170,7 @@
         <v>77</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4199,7 +4199,7 @@
         <v>78</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4228,7 +4228,7 @@
         <v>79</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>12</v>
@@ -4252,7 +4252,7 @@
       <c r="J137" s="2"/>
       <c r="K137" s="1"/>
       <c r="M137" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.3">
@@ -4266,7 +4266,7 @@
         <v>80</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>13</v>
@@ -4295,7 +4295,7 @@
         <v>81</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>10</v>
@@ -4324,7 +4324,7 @@
         <v>82</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>13</v>
@@ -4353,7 +4353,7 @@
         <v>83</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>13</v>
@@ -4382,7 +4382,7 @@
         <v>84</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>10</v>
@@ -4411,7 +4411,7 @@
         <v>85</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>10</v>
@@ -4440,7 +4440,7 @@
         <v>86</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>10</v>
@@ -4754,7 +4754,7 @@
       <c r="J155" s="2"/>
       <c r="K155" s="1"/>
       <c r="M155" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="156" spans="4:13" x14ac:dyDescent="0.3">
@@ -4966,7 +4966,7 @@
       <c r="J163" s="2"/>
       <c r="K163" s="1"/>
       <c r="M163" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
@@ -5178,7 +5178,7 @@
       <c r="J171" s="2"/>
       <c r="K171" s="1"/>
       <c r="M171" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172" spans="4:13" x14ac:dyDescent="0.3">
@@ -5216,7 +5216,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
       <c r="M173" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174" spans="4:13" x14ac:dyDescent="0.3">
@@ -5341,7 +5341,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
       <c r="M178" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="179" spans="4:13" x14ac:dyDescent="0.3">
@@ -5437,7 +5437,7 @@
       <c r="J182" s="2"/>
       <c r="K182" s="1"/>
       <c r="M182" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="183" spans="4:13" x14ac:dyDescent="0.3">
@@ -5765,7 +5765,7 @@
       <c r="J194" s="2"/>
       <c r="K194" s="1"/>
       <c r="M194" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="195" spans="4:13" x14ac:dyDescent="0.3">
@@ -6064,7 +6064,7 @@
       <c r="J205" s="2"/>
       <c r="K205" s="1"/>
       <c r="M205" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="206" spans="4:13" x14ac:dyDescent="0.3">
@@ -6252,7 +6252,7 @@
         <v>27</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>10</v>
@@ -6281,7 +6281,7 @@
         <v>28</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>10</v>
@@ -6310,7 +6310,7 @@
         <v>29</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>10</v>
@@ -6339,7 +6339,7 @@
         <v>30</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>10</v>
@@ -6368,7 +6368,7 @@
         <v>31</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>10</v>
@@ -6397,7 +6397,7 @@
         <v>32</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -6426,7 +6426,7 @@
         <v>33</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>12</v>
@@ -6450,7 +6450,7 @@
       <c r="J219" s="2"/>
       <c r="K219" s="1"/>
       <c r="M219" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="220" spans="4:13" x14ac:dyDescent="0.3">
@@ -6464,7 +6464,7 @@
         <v>34</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>14</v>
@@ -6488,7 +6488,7 @@
       <c r="J221" s="2"/>
       <c r="K221" s="1"/>
       <c r="M221" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="222" spans="4:13" x14ac:dyDescent="0.3">
@@ -6502,7 +6502,7 @@
         <v>35</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>13</v>
@@ -6531,7 +6531,7 @@
         <v>36</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>13</v>
@@ -6560,7 +6560,7 @@
         <v>37</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>10</v>
@@ -6589,7 +6589,7 @@
         <v>38</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>10</v>
@@ -6618,7 +6618,7 @@
         <v>39</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>10</v>
@@ -6647,7 +6647,7 @@
         <v>40</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>10</v>
@@ -6676,7 +6676,7 @@
         <v>41</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>10</v>
@@ -6705,7 +6705,7 @@
         <v>42</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>10</v>
@@ -6734,7 +6734,7 @@
         <v>43</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>14</v>
@@ -6758,7 +6758,7 @@
       <c r="J231" s="2"/>
       <c r="K231" s="1"/>
       <c r="M231" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="232" spans="4:13" x14ac:dyDescent="0.3">
@@ -6772,7 +6772,7 @@
         <v>44</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>14</v>
@@ -6796,7 +6796,7 @@
       <c r="J233" s="2"/>
       <c r="K233" s="1"/>
       <c r="M233" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="234" spans="4:13" x14ac:dyDescent="0.3">
@@ -6810,7 +6810,7 @@
         <v>45</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>10</v>
@@ -6839,7 +6839,7 @@
         <v>46</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>10</v>
@@ -6868,7 +6868,7 @@
         <v>47</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>13</v>
@@ -6897,7 +6897,7 @@
         <v>48</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>13</v>
@@ -6926,7 +6926,7 @@
         <v>49</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>10</v>
@@ -6955,7 +6955,7 @@
         <v>50</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -6984,7 +6984,7 @@
         <v>51</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>12</v>
@@ -7008,7 +7008,7 @@
       <c r="J241" s="2"/>
       <c r="K241" s="1"/>
       <c r="M241" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="242" spans="4:13" x14ac:dyDescent="0.3">
@@ -7022,7 +7022,7 @@
         <v>52</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>10</v>
@@ -7051,7 +7051,7 @@
         <v>53</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>10</v>
@@ -7080,7 +7080,7 @@
         <v>54</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>13</v>
@@ -7109,7 +7109,7 @@
         <v>55</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>12</v>
@@ -7133,7 +7133,7 @@
       <c r="J246" s="2"/>
       <c r="K246" s="1"/>
       <c r="M246" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="247" spans="4:13" x14ac:dyDescent="0.3">
@@ -7147,7 +7147,7 @@
         <v>56</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>10</v>
@@ -7176,7 +7176,7 @@
         <v>57</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>10</v>
@@ -7205,7 +7205,7 @@
         <v>58</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>12</v>
@@ -7229,7 +7229,7 @@
       <c r="J250" s="2"/>
       <c r="K250" s="1"/>
       <c r="M250" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="251" spans="4:13" x14ac:dyDescent="0.3">
@@ -7243,7 +7243,7 @@
         <v>59</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>10</v>
@@ -7272,7 +7272,7 @@
         <v>60</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7301,7 +7301,7 @@
         <v>61</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>13</v>
@@ -7330,7 +7330,7 @@
         <v>62</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>10</v>
@@ -7359,7 +7359,7 @@
         <v>63</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>10</v>
@@ -7388,7 +7388,7 @@
         <v>64</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>10</v>
@@ -7417,7 +7417,7 @@
         <v>65</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>10</v>
@@ -7446,7 +7446,7 @@
         <v>66</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>10</v>
@@ -7475,7 +7475,7 @@
         <v>68</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>13</v>
@@ -7504,7 +7504,7 @@
         <v>69</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>10</v>
@@ -7533,7 +7533,7 @@
         <v>70</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>10</v>
@@ -7562,7 +7562,7 @@
         <v>71</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>10</v>
@@ -7591,7 +7591,7 @@
         <v>72</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>10</v>
@@ -7620,7 +7620,7 @@
         <v>73</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>10</v>
@@ -7649,7 +7649,7 @@
         <v>74</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>13</v>
@@ -7678,7 +7678,7 @@
         <v>75</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>10</v>
@@ -7707,7 +7707,7 @@
         <v>76</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>13</v>
@@ -7736,7 +7736,7 @@
         <v>77</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>10</v>
@@ -7765,7 +7765,7 @@
         <v>78</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>10</v>
@@ -7794,7 +7794,7 @@
         <v>79</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>10</v>
@@ -7823,7 +7823,7 @@
         <v>80</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>10</v>
@@ -7852,7 +7852,7 @@
         <v>81</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>10</v>
@@ -7881,7 +7881,7 @@
         <v>82</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>10</v>
@@ -7910,7 +7910,7 @@
         <v>83</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>13</v>
@@ -7939,7 +7939,7 @@
         <v>84</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>10</v>
@@ -7968,7 +7968,7 @@
         <v>85</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>10</v>
@@ -7997,7 +7997,7 @@
         <v>87</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>10</v>
@@ -8026,7 +8026,7 @@
         <v>86</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>10</v>
@@ -8055,7 +8055,7 @@
         <v>27</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>12</v>
@@ -8079,7 +8079,7 @@
       <c r="J280" s="2"/>
       <c r="K280" s="1"/>
       <c r="M280" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="281" spans="4:13" x14ac:dyDescent="0.3">
@@ -8093,7 +8093,7 @@
         <v>28</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>10</v>
@@ -8122,7 +8122,7 @@
         <v>29</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>10</v>
@@ -8151,7 +8151,7 @@
         <v>30</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>10</v>
@@ -8180,7 +8180,7 @@
         <v>31</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>10</v>
@@ -8209,7 +8209,7 @@
         <v>32</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>10</v>
@@ -8238,7 +8238,7 @@
         <v>33</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>13</v>
@@ -8267,7 +8267,7 @@
         <v>34</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>13</v>
@@ -8296,7 +8296,7 @@
         <v>35</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>13</v>
@@ -8325,7 +8325,7 @@
         <v>36</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>13</v>
@@ -8354,7 +8354,7 @@
         <v>37</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>10</v>
@@ -8383,7 +8383,7 @@
         <v>38</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>13</v>
@@ -8412,7 +8412,7 @@
         <v>39</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>10</v>
@@ -8441,7 +8441,7 @@
         <v>40</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>10</v>
@@ -8470,7 +8470,7 @@
         <v>41</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>10</v>
@@ -8499,7 +8499,7 @@
         <v>42</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>10</v>
@@ -8528,7 +8528,7 @@
         <v>43</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>10</v>
@@ -8557,7 +8557,7 @@
         <v>44</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>13</v>
@@ -8586,7 +8586,7 @@
         <v>45</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>13</v>
@@ -8615,7 +8615,7 @@
         <v>46</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>10</v>
@@ -8644,7 +8644,7 @@
         <v>47</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>13</v>
@@ -8673,7 +8673,7 @@
         <v>48</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>13</v>
@@ -8702,7 +8702,7 @@
         <v>49</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>10</v>
@@ -8731,7 +8731,7 @@
         <v>50</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>13</v>
@@ -8760,7 +8760,7 @@
         <v>51</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>10</v>
@@ -8789,7 +8789,7 @@
         <v>52</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>10</v>
@@ -8818,7 +8818,7 @@
         <v>53</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>10</v>
@@ -8847,7 +8847,7 @@
         <v>54</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>13</v>
@@ -8876,7 +8876,7 @@
         <v>55</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>10</v>
@@ -8905,7 +8905,7 @@
         <v>56</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>10</v>
@@ -8934,7 +8934,7 @@
         <v>57</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>10</v>
@@ -8963,7 +8963,7 @@
         <v>59</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>10</v>
@@ -8992,7 +8992,7 @@
         <v>60</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>10</v>
@@ -9021,7 +9021,7 @@
         <v>61</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>13</v>
@@ -9050,7 +9050,7 @@
         <v>62</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>12</v>
@@ -9074,7 +9074,7 @@
       <c r="J315" s="2"/>
       <c r="K315" s="1"/>
       <c r="M315" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="316" spans="4:13" x14ac:dyDescent="0.3">
@@ -9088,7 +9088,7 @@
         <v>63</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>10</v>
@@ -9117,7 +9117,7 @@
         <v>64</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>10</v>
@@ -9146,7 +9146,7 @@
         <v>65</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>10</v>
@@ -9175,7 +9175,7 @@
         <v>66</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>10</v>
@@ -9204,7 +9204,7 @@
         <v>68</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>13</v>
@@ -9233,7 +9233,7 @@
         <v>69</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>10</v>
@@ -9262,7 +9262,7 @@
         <v>70</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>10</v>
@@ -9291,7 +9291,7 @@
         <v>71</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>10</v>
@@ -9320,7 +9320,7 @@
         <v>72</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>10</v>
@@ -9349,7 +9349,7 @@
         <v>73</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>10</v>
@@ -9378,7 +9378,7 @@
         <v>74</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>13</v>
@@ -9407,7 +9407,7 @@
         <v>75</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I327" s="1" t="s">
         <v>10</v>
@@ -9436,7 +9436,7 @@
         <v>76</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>13</v>
@@ -9465,7 +9465,7 @@
         <v>77</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>10</v>
@@ -9494,7 +9494,7 @@
         <v>78</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>10</v>
@@ -9523,7 +9523,7 @@
         <v>79</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>10</v>
@@ -9552,7 +9552,7 @@
         <v>80</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>10</v>
@@ -9581,7 +9581,7 @@
         <v>81</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>10</v>
@@ -9610,7 +9610,7 @@
         <v>82</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>10</v>
@@ -9639,7 +9639,7 @@
         <v>83</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>13</v>
@@ -9668,7 +9668,7 @@
         <v>84</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>10</v>
@@ -9697,7 +9697,7 @@
         <v>85</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>10</v>
@@ -9726,7 +9726,7 @@
         <v>87</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>13</v>
@@ -9755,7 +9755,7 @@
         <v>86</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>10</v>
@@ -9784,7 +9784,7 @@
         <v>27</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>12</v>
@@ -9808,7 +9808,7 @@
       <c r="J341" s="2"/>
       <c r="K341" s="1"/>
       <c r="M341" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="342" spans="4:13" x14ac:dyDescent="0.3">
@@ -9822,7 +9822,7 @@
         <v>28</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>10</v>
@@ -9851,7 +9851,7 @@
         <v>29</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -9880,7 +9880,7 @@
         <v>30</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>10</v>
@@ -9909,7 +9909,7 @@
         <v>31</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>10</v>
@@ -9938,7 +9938,7 @@
         <v>32</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>10</v>
@@ -9967,7 +9967,7 @@
         <v>33</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>13</v>
@@ -9996,7 +9996,7 @@
         <v>34</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>13</v>
@@ -10025,7 +10025,7 @@
         <v>35</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>13</v>
@@ -10054,7 +10054,7 @@
         <v>36</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>13</v>
@@ -10083,7 +10083,7 @@
         <v>37</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>10</v>
@@ -10112,7 +10112,7 @@
         <v>38</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>13</v>
@@ -10141,7 +10141,7 @@
         <v>39</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>10</v>
@@ -10170,7 +10170,7 @@
         <v>40</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>10</v>
@@ -10199,7 +10199,7 @@
         <v>41</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>10</v>
@@ -10228,7 +10228,7 @@
         <v>42</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>10</v>
@@ -10257,7 +10257,7 @@
         <v>43</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>10</v>
@@ -10286,7 +10286,7 @@
         <v>44</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I358" s="1" t="s">
         <v>13</v>
@@ -10315,7 +10315,7 @@
         <v>46</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>10</v>
@@ -10344,7 +10344,7 @@
         <v>47</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>13</v>
@@ -10373,7 +10373,7 @@
         <v>48</v>
       </c>
       <c r="H361" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I361" s="1" t="s">
         <v>13</v>
@@ -10402,7 +10402,7 @@
         <v>49</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I362" s="1" t="s">
         <v>10</v>
@@ -10431,7 +10431,7 @@
         <v>50</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I363" s="1" t="s">
         <v>10</v>
@@ -10460,7 +10460,7 @@
         <v>51</v>
       </c>
       <c r="H364" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I364" s="1" t="s">
         <v>10</v>
@@ -10489,7 +10489,7 @@
         <v>52</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I365" s="1" t="s">
         <v>10</v>
@@ -10518,7 +10518,7 @@
         <v>53</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I366" s="1" t="s">
         <v>12</v>
@@ -10542,7 +10542,7 @@
       <c r="J367" s="2"/>
       <c r="K367" s="1"/>
       <c r="M367" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="368" spans="4:13" x14ac:dyDescent="0.3">
@@ -10556,7 +10556,7 @@
         <v>54</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>13</v>
@@ -10585,7 +10585,7 @@
         <v>55</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I369" s="1" t="s">
         <v>10</v>
@@ -10614,7 +10614,7 @@
         <v>56</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>10</v>
@@ -10643,7 +10643,7 @@
         <v>57</v>
       </c>
       <c r="H371" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I371" s="1" t="s">
         <v>10</v>
@@ -10672,7 +10672,7 @@
         <v>59</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I372" s="1" t="s">
         <v>10</v>
@@ -10701,7 +10701,7 @@
         <v>60</v>
       </c>
       <c r="H373" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I373" s="1" t="s">
         <v>10</v>
@@ -10730,7 +10730,7 @@
         <v>62</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>10</v>
@@ -10759,7 +10759,7 @@
         <v>63</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>10</v>
@@ -10788,7 +10788,7 @@
         <v>64</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>12</v>
@@ -10812,7 +10812,7 @@
       <c r="J377" s="2"/>
       <c r="K377" s="1"/>
       <c r="M377" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="378" spans="4:13" x14ac:dyDescent="0.3">
@@ -10826,7 +10826,7 @@
         <v>65</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>10</v>
@@ -10855,7 +10855,7 @@
         <v>66</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>10</v>
@@ -10884,7 +10884,7 @@
         <v>68</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>10</v>
@@ -10913,7 +10913,7 @@
         <v>69</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>10</v>
@@ -10942,7 +10942,7 @@
         <v>70</v>
       </c>
       <c r="H382" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I382" s="1" t="s">
         <v>12</v>
@@ -10966,7 +10966,7 @@
       <c r="J383" s="2"/>
       <c r="K383" s="1"/>
       <c r="M383" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="384" spans="4:13" x14ac:dyDescent="0.3">
@@ -10980,7 +10980,7 @@
         <v>71</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>13</v>
@@ -11009,7 +11009,7 @@
         <v>72</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>10</v>
@@ -11038,7 +11038,7 @@
         <v>73</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I386" s="1" t="s">
         <v>13</v>
@@ -11067,7 +11067,7 @@
         <v>74</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>13</v>
@@ -11096,7 +11096,7 @@
         <v>75</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I388" s="1" t="s">
         <v>10</v>
@@ -11125,7 +11125,7 @@
         <v>76</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I389" s="1" t="s">
         <v>13</v>
@@ -11154,7 +11154,7 @@
         <v>77</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I390" s="1" t="s">
         <v>10</v>
@@ -11183,7 +11183,7 @@
         <v>78</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I391" s="1" t="s">
         <v>13</v>
@@ -11212,7 +11212,7 @@
         <v>79</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I392" s="1" t="s">
         <v>10</v>
@@ -11241,7 +11241,7 @@
         <v>80</v>
       </c>
       <c r="H393" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I393" s="1" t="s">
         <v>10</v>
@@ -11270,7 +11270,7 @@
         <v>81</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I394" s="1" t="s">
         <v>10</v>
@@ -11299,7 +11299,7 @@
         <v>82</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I395" s="1" t="s">
         <v>10</v>
@@ -11328,7 +11328,7 @@
         <v>83</v>
       </c>
       <c r="H396" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I396" s="1" t="s">
         <v>13</v>
@@ -11357,7 +11357,7 @@
         <v>84</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I397" s="1" t="s">
         <v>12</v>
@@ -11381,7 +11381,7 @@
       <c r="J398" s="2"/>
       <c r="K398" s="1"/>
       <c r="M398" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="399" spans="4:13" x14ac:dyDescent="0.3">
@@ -11395,7 +11395,7 @@
         <v>85</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I399" s="1" t="s">
         <v>10</v>
@@ -11424,7 +11424,7 @@
         <v>87</v>
       </c>
       <c r="H400" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I400" s="1" t="s">
         <v>10</v>
@@ -11453,7 +11453,7 @@
         <v>86</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I401" s="1" t="s">
         <v>10</v>
@@ -11482,7 +11482,7 @@
         <v>27</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I402" s="1" t="s">
         <v>13</v>
@@ -11511,7 +11511,7 @@
         <v>28</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I403" s="1" t="s">
         <v>10</v>
@@ -11540,7 +11540,7 @@
         <v>29</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I404" s="1" t="s">
         <v>10</v>
@@ -11569,7 +11569,7 @@
         <v>88</v>
       </c>
       <c r="H405" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I405" s="1" t="s">
         <v>12</v>
@@ -11593,7 +11593,7 @@
       <c r="J406" s="2"/>
       <c r="K406" s="1"/>
       <c r="M406" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="407" spans="4:13" x14ac:dyDescent="0.3">
@@ -11607,7 +11607,7 @@
         <v>30</v>
       </c>
       <c r="H407" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I407" s="1" t="s">
         <v>10</v>
@@ -11636,7 +11636,7 @@
         <v>31</v>
       </c>
       <c r="H408" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I408" s="1" t="s">
         <v>10</v>
@@ -11665,7 +11665,7 @@
         <v>32</v>
       </c>
       <c r="H409" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I409" s="1" t="s">
         <v>10</v>
@@ -11694,7 +11694,7 @@
         <v>33</v>
       </c>
       <c r="H410" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I410" s="1" t="s">
         <v>13</v>
@@ -11723,7 +11723,7 @@
         <v>34</v>
       </c>
       <c r="H411" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I411" s="1" t="s">
         <v>13</v>
@@ -11752,7 +11752,7 @@
         <v>35</v>
       </c>
       <c r="H412" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I412" s="1" t="s">
         <v>10</v>
@@ -11781,7 +11781,7 @@
         <v>36</v>
       </c>
       <c r="H413" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I413" s="1" t="s">
         <v>13</v>
@@ -11810,7 +11810,7 @@
         <v>37</v>
       </c>
       <c r="H414" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I414" s="1" t="s">
         <v>10</v>
@@ -11839,7 +11839,7 @@
         <v>38</v>
       </c>
       <c r="H415" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I415" s="1" t="s">
         <v>12</v>
@@ -11863,7 +11863,7 @@
       <c r="J416" s="2"/>
       <c r="K416" s="1"/>
       <c r="M416" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="417" spans="4:13" x14ac:dyDescent="0.3">
@@ -11877,7 +11877,7 @@
         <v>39</v>
       </c>
       <c r="H417" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I417" s="1" t="s">
         <v>10</v>
@@ -11906,7 +11906,7 @@
         <v>40</v>
       </c>
       <c r="H418" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I418" s="1" t="s">
         <v>10</v>
@@ -11935,7 +11935,7 @@
         <v>41</v>
       </c>
       <c r="H419" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I419" s="1" t="s">
         <v>10</v>
@@ -11964,7 +11964,7 @@
         <v>42</v>
       </c>
       <c r="H420" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I420" s="1" t="s">
         <v>12</v>
@@ -11988,7 +11988,7 @@
       <c r="J421" s="2"/>
       <c r="K421" s="1"/>
       <c r="M421" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="422" spans="4:13" x14ac:dyDescent="0.3">
@@ -12002,7 +12002,7 @@
         <v>43</v>
       </c>
       <c r="H422" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I422" s="1" t="s">
         <v>14</v>
@@ -12026,7 +12026,7 @@
       <c r="J423" s="2"/>
       <c r="K423" s="1"/>
       <c r="M423" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="424" spans="4:13" x14ac:dyDescent="0.3">
@@ -12040,7 +12040,7 @@
         <v>44</v>
       </c>
       <c r="H424" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I424" s="1" t="s">
         <v>13</v>
@@ -12069,7 +12069,7 @@
         <v>46</v>
       </c>
       <c r="H425" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I425" s="1" t="s">
         <v>10</v>
@@ -12098,7 +12098,7 @@
         <v>47</v>
       </c>
       <c r="H426" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I426" s="1" t="s">
         <v>13</v>
@@ -12127,7 +12127,7 @@
         <v>48</v>
       </c>
       <c r="H427" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I427" s="1" t="s">
         <v>13</v>
@@ -12156,7 +12156,7 @@
         <v>49</v>
       </c>
       <c r="H428" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I428" s="1" t="s">
         <v>13</v>
@@ -12185,7 +12185,7 @@
         <v>50</v>
       </c>
       <c r="H429" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I429" s="1" t="s">
         <v>14</v>
@@ -12209,7 +12209,7 @@
       <c r="J430" s="2"/>
       <c r="K430" s="1"/>
       <c r="M430" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="431" spans="4:13" x14ac:dyDescent="0.3">
@@ -12223,7 +12223,7 @@
         <v>51</v>
       </c>
       <c r="H431" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I431" s="1" t="s">
         <v>10</v>
@@ -12252,7 +12252,7 @@
         <v>52</v>
       </c>
       <c r="H432" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I432" s="1" t="s">
         <v>10</v>
@@ -12281,7 +12281,7 @@
         <v>53</v>
       </c>
       <c r="H433" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I433" s="1" t="s">
         <v>10</v>
@@ -12310,7 +12310,7 @@
         <v>54</v>
       </c>
       <c r="H434" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I434" s="1" t="s">
         <v>13</v>
@@ -12339,7 +12339,7 @@
         <v>55</v>
       </c>
       <c r="H435" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I435" s="1" t="s">
         <v>10</v>
@@ -12368,7 +12368,7 @@
         <v>56</v>
       </c>
       <c r="H436" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I436" s="1" t="s">
         <v>10</v>
@@ -12397,7 +12397,7 @@
         <v>57</v>
       </c>
       <c r="H437" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I437" s="1" t="s">
         <v>10</v>
@@ -12426,7 +12426,7 @@
         <v>59</v>
       </c>
       <c r="H438" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I438" s="1" t="s">
         <v>10</v>
@@ -12455,7 +12455,7 @@
         <v>60</v>
       </c>
       <c r="H439" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I439" s="1" t="s">
         <v>10</v>
@@ -12484,7 +12484,7 @@
         <v>62</v>
       </c>
       <c r="H440" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I440" s="1" t="s">
         <v>10</v>
@@ -12513,7 +12513,7 @@
         <v>63</v>
       </c>
       <c r="H441" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I441" s="1" t="s">
         <v>12</v>
@@ -12537,7 +12537,7 @@
       <c r="J442" s="2"/>
       <c r="K442" s="1"/>
       <c r="M442" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="443" spans="4:13" x14ac:dyDescent="0.3">
@@ -12551,7 +12551,7 @@
         <v>64</v>
       </c>
       <c r="H443" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I443" s="1" t="s">
         <v>10</v>
@@ -12580,7 +12580,7 @@
         <v>65</v>
       </c>
       <c r="H444" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I444" s="1" t="s">
         <v>10</v>
@@ -12609,7 +12609,7 @@
         <v>66</v>
       </c>
       <c r="H445" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I445" s="1" t="s">
         <v>10</v>
@@ -12638,7 +12638,7 @@
         <v>68</v>
       </c>
       <c r="H446" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I446" s="1" t="s">
         <v>13</v>
@@ -12667,7 +12667,7 @@
         <v>69</v>
       </c>
       <c r="H447" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I447" s="1" t="s">
         <v>10</v>
@@ -12696,7 +12696,7 @@
         <v>70</v>
       </c>
       <c r="H448" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I448" s="1" t="s">
         <v>12</v>
@@ -12720,7 +12720,7 @@
       <c r="J449" s="2"/>
       <c r="K449" s="1"/>
       <c r="M449" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="450" spans="4:13" x14ac:dyDescent="0.3">
@@ -12734,7 +12734,7 @@
         <v>71</v>
       </c>
       <c r="H450" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I450" s="1" t="s">
         <v>13</v>
@@ -12763,7 +12763,7 @@
         <v>72</v>
       </c>
       <c r="H451" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I451" s="1" t="s">
         <v>10</v>
@@ -12792,7 +12792,7 @@
         <v>73</v>
       </c>
       <c r="H452" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I452" s="1" t="s">
         <v>13</v>
@@ -12821,7 +12821,7 @@
         <v>74</v>
       </c>
       <c r="H453" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I453" s="1" t="s">
         <v>13</v>
@@ -12850,7 +12850,7 @@
         <v>76</v>
       </c>
       <c r="H454" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I454" s="1" t="s">
         <v>13</v>
@@ -12879,7 +12879,7 @@
         <v>77</v>
       </c>
       <c r="H455" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I455" s="1" t="s">
         <v>10</v>
@@ -12908,7 +12908,7 @@
         <v>78</v>
       </c>
       <c r="H456" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I456" s="1" t="s">
         <v>13</v>
@@ -12937,7 +12937,7 @@
         <v>89</v>
       </c>
       <c r="H457" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I457" s="1" t="s">
         <v>10</v>
@@ -12966,7 +12966,7 @@
         <v>79</v>
       </c>
       <c r="H458" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I458" s="1" t="s">
         <v>10</v>
@@ -12995,7 +12995,7 @@
         <v>80</v>
       </c>
       <c r="H459" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I459" s="1" t="s">
         <v>10</v>
@@ -13024,7 +13024,7 @@
         <v>81</v>
       </c>
       <c r="H460" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I460" s="1" t="s">
         <v>10</v>
@@ -13053,7 +13053,7 @@
         <v>82</v>
       </c>
       <c r="H461" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I461" s="1" t="s">
         <v>10</v>
@@ -13082,7 +13082,7 @@
         <v>83</v>
       </c>
       <c r="H462" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I462" s="1" t="s">
         <v>13</v>
@@ -13111,7 +13111,7 @@
         <v>84</v>
       </c>
       <c r="H463" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I463" s="1" t="s">
         <v>10</v>
@@ -13140,7 +13140,7 @@
         <v>85</v>
       </c>
       <c r="H464" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I464" s="1" t="s">
         <v>10</v>
@@ -13169,7 +13169,7 @@
         <v>87</v>
       </c>
       <c r="H465" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I465" s="1" t="s">
         <v>13</v>
@@ -13198,7 +13198,7 @@
         <v>86</v>
       </c>
       <c r="H466" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I466" s="1" t="s">
         <v>10</v>
@@ -13227,7 +13227,7 @@
         <v>88</v>
       </c>
       <c r="H467" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I467" s="1" t="s">
         <v>10</v>
@@ -13256,7 +13256,7 @@
         <v>30</v>
       </c>
       <c r="H468" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I468" s="1" t="s">
         <v>10</v>
@@ -13285,7 +13285,7 @@
         <v>31</v>
       </c>
       <c r="H469" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I469" s="1" t="s">
         <v>10</v>
@@ -13314,7 +13314,7 @@
         <v>32</v>
       </c>
       <c r="H470" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I470" s="1" t="s">
         <v>10</v>
@@ -13343,7 +13343,7 @@
         <v>90</v>
       </c>
       <c r="H471" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I471" s="1" t="s">
         <v>10</v>
@@ -13372,7 +13372,7 @@
         <v>91</v>
       </c>
       <c r="H472" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I472" s="1" t="s">
         <v>10</v>
@@ -13401,7 +13401,7 @@
         <v>37</v>
       </c>
       <c r="H473" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I473" s="1" t="s">
         <v>10</v>
@@ -13430,7 +13430,7 @@
         <v>46</v>
       </c>
       <c r="H474" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I474" s="1" t="s">
         <v>10</v>
@@ -13459,7 +13459,7 @@
         <v>51</v>
       </c>
       <c r="H475" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I475" s="1" t="s">
         <v>10</v>
@@ -13488,7 +13488,7 @@
         <v>55</v>
       </c>
       <c r="H476" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I476" s="1" t="s">
         <v>10</v>
@@ -13517,7 +13517,7 @@
         <v>57</v>
       </c>
       <c r="H477" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I477" s="1" t="s">
         <v>10</v>
@@ -13546,7 +13546,7 @@
         <v>65</v>
       </c>
       <c r="H478" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I478" s="1" t="s">
         <v>10</v>
@@ -13575,7 +13575,7 @@
         <v>69</v>
       </c>
       <c r="H479" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I479" s="1" t="s">
         <v>10</v>
@@ -13604,7 +13604,7 @@
         <v>77</v>
       </c>
       <c r="H480" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I480" s="1" t="s">
         <v>10</v>
@@ -13633,7 +13633,7 @@
         <v>92</v>
       </c>
       <c r="H481" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I481" s="1" t="s">
         <v>10</v>
@@ -13662,7 +13662,7 @@
         <v>89</v>
       </c>
       <c r="H482" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I482" s="1" t="s">
         <v>10</v>
@@ -13691,7 +13691,7 @@
         <v>79</v>
       </c>
       <c r="H483" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I483" s="1" t="s">
         <v>10</v>
@@ -13720,7 +13720,7 @@
         <v>80</v>
       </c>
       <c r="H484" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I484" s="1" t="s">
         <v>10</v>
@@ -13749,7 +13749,7 @@
         <v>81</v>
       </c>
       <c r="H485" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I485" s="1" t="s">
         <v>10</v>
@@ -13778,7 +13778,7 @@
         <v>84</v>
       </c>
       <c r="H486" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I486" s="1" t="s">
         <v>10</v>
@@ -13807,7 +13807,7 @@
         <v>85</v>
       </c>
       <c r="H487" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I487" s="1" t="s">
         <v>10</v>
@@ -13836,7 +13836,7 @@
         <v>93</v>
       </c>
       <c r="H488" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I488" s="1" t="s">
         <v>10</v>
@@ -13865,7 +13865,7 @@
         <v>27</v>
       </c>
       <c r="H489" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I489" s="1" t="s">
         <v>10</v>
@@ -13894,7 +13894,7 @@
         <v>28</v>
       </c>
       <c r="H490" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I490" s="1" t="s">
         <v>10</v>
@@ -13923,7 +13923,7 @@
         <v>29</v>
       </c>
       <c r="H491" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I491" s="1" t="s">
         <v>12</v>
@@ -13947,7 +13947,7 @@
       <c r="J492" s="2"/>
       <c r="K492" s="1"/>
       <c r="M492" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="493" spans="4:13" x14ac:dyDescent="0.3">
@@ -13961,7 +13961,7 @@
         <v>94</v>
       </c>
       <c r="H493" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I493" s="1" t="s">
         <v>13</v>
@@ -13990,7 +13990,7 @@
         <v>33</v>
       </c>
       <c r="H494" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I494" s="1" t="s">
         <v>13</v>
@@ -14019,7 +14019,7 @@
         <v>34</v>
       </c>
       <c r="H495" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I495" s="1" t="s">
         <v>13</v>
@@ -14048,7 +14048,7 @@
         <v>35</v>
       </c>
       <c r="H496" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I496" s="1" t="s">
         <v>13</v>
@@ -14077,7 +14077,7 @@
         <v>36</v>
       </c>
       <c r="H497" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I497" s="1" t="s">
         <v>13</v>
@@ -14106,7 +14106,7 @@
         <v>38</v>
       </c>
       <c r="H498" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I498" s="1" t="s">
         <v>12</v>
@@ -14130,7 +14130,7 @@
       <c r="J499" s="2"/>
       <c r="K499" s="1"/>
       <c r="M499" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="500" spans="4:13" x14ac:dyDescent="0.3">
@@ -14144,7 +14144,7 @@
         <v>39</v>
       </c>
       <c r="H500" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I500" s="1" t="s">
         <v>13</v>
@@ -14173,7 +14173,7 @@
         <v>40</v>
       </c>
       <c r="H501" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I501" s="1" t="s">
         <v>10</v>
@@ -14202,7 +14202,7 @@
         <v>41</v>
       </c>
       <c r="H502" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I502" s="1" t="s">
         <v>10</v>
@@ -14231,7 +14231,7 @@
         <v>42</v>
       </c>
       <c r="H503" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I503" s="1" t="s">
         <v>10</v>
@@ -14260,7 +14260,7 @@
         <v>43</v>
       </c>
       <c r="H504" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I504" s="1" t="s">
         <v>10</v>
@@ -14289,7 +14289,7 @@
         <v>44</v>
       </c>
       <c r="H505" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I505" s="1" t="s">
         <v>13</v>
@@ -14318,7 +14318,7 @@
         <v>48</v>
       </c>
       <c r="H506" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I506" s="1" t="s">
         <v>13</v>
@@ -14347,7 +14347,7 @@
         <v>49</v>
       </c>
       <c r="H507" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I507" s="1" t="s">
         <v>10</v>
@@ -14376,7 +14376,7 @@
         <v>50</v>
       </c>
       <c r="H508" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I508" s="1" t="s">
         <v>13</v>
@@ -14405,7 +14405,7 @@
         <v>52</v>
       </c>
       <c r="H509" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I509" s="1" t="s">
         <v>10</v>
@@ -14434,7 +14434,7 @@
         <v>53</v>
       </c>
       <c r="H510" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I510" s="1" t="s">
         <v>13</v>
@@ -14463,7 +14463,7 @@
         <v>54</v>
       </c>
       <c r="H511" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I511" s="1" t="s">
         <v>13</v>
@@ -14492,7 +14492,7 @@
         <v>56</v>
       </c>
       <c r="H512" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I512" s="1" t="s">
         <v>13</v>
@@ -14521,7 +14521,7 @@
         <v>59</v>
       </c>
       <c r="H513" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I513" s="1" t="s">
         <v>10</v>
@@ -14550,7 +14550,7 @@
         <v>60</v>
       </c>
       <c r="H514" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I514" s="1" t="s">
         <v>10</v>
@@ -14579,7 +14579,7 @@
         <v>62</v>
       </c>
       <c r="H515" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I515" s="1" t="s">
         <v>10</v>
@@ -14608,7 +14608,7 @@
         <v>63</v>
       </c>
       <c r="H516" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I516" s="1" t="s">
         <v>10</v>
@@ -14637,7 +14637,7 @@
         <v>64</v>
       </c>
       <c r="H517" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I517" s="1" t="s">
         <v>10</v>
@@ -14666,7 +14666,7 @@
         <v>66</v>
       </c>
       <c r="H518" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I518" s="1" t="s">
         <v>10</v>
@@ -14695,7 +14695,7 @@
         <v>68</v>
       </c>
       <c r="H519" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I519" s="1" t="s">
         <v>13</v>
@@ -14724,7 +14724,7 @@
         <v>70</v>
       </c>
       <c r="H520" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I520" s="1" t="s">
         <v>10</v>
@@ -14753,7 +14753,7 @@
         <v>71</v>
       </c>
       <c r="H521" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I521" s="1" t="s">
         <v>13</v>
@@ -14782,7 +14782,7 @@
         <v>72</v>
       </c>
       <c r="H522" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I522" s="1" t="s">
         <v>12</v>
@@ -14806,7 +14806,7 @@
       <c r="J523" s="2"/>
       <c r="K523" s="1"/>
       <c r="M523" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="524" spans="4:13" x14ac:dyDescent="0.3">
@@ -14820,7 +14820,7 @@
         <v>73</v>
       </c>
       <c r="H524" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I524" s="1" t="s">
         <v>13</v>
@@ -14849,7 +14849,7 @@
         <v>77</v>
       </c>
       <c r="H525" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I525" s="1" t="s">
         <v>12</v>
@@ -14873,7 +14873,7 @@
       <c r="J526" s="2"/>
       <c r="K526" s="1"/>
       <c r="M526" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="527" spans="4:13" x14ac:dyDescent="0.3">
@@ -14887,7 +14887,7 @@
         <v>78</v>
       </c>
       <c r="H527" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I527" s="1" t="s">
         <v>10</v>
@@ -14916,7 +14916,7 @@
         <v>92</v>
       </c>
       <c r="H528" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I528" s="1" t="s">
         <v>13</v>
@@ -14945,7 +14945,7 @@
         <v>82</v>
       </c>
       <c r="H529" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I529" s="1" t="s">
         <v>12</v>
@@ -14969,7 +14969,7 @@
       <c r="J530" s="2"/>
       <c r="K530" s="1"/>
       <c r="M530" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="531" spans="4:13" x14ac:dyDescent="0.3">
@@ -14983,7 +14983,7 @@
         <v>83</v>
       </c>
       <c r="H531" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I531" s="1" t="s">
         <v>13</v>
@@ -15012,7 +15012,7 @@
         <v>87</v>
       </c>
       <c r="H532" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I532" s="1" t="s">
         <v>13</v>
@@ -15041,7 +15041,7 @@
         <v>86</v>
       </c>
       <c r="H533" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I533" s="1" t="s">
         <v>10</v>
@@ -15123,7 +15123,7 @@
       <c r="J536" s="2"/>
       <c r="K536" s="1"/>
       <c r="M536" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="537" spans="4:13" x14ac:dyDescent="0.3">
@@ -15277,7 +15277,7 @@
       <c r="J542" s="2"/>
       <c r="K542" s="1"/>
       <c r="M542" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="543" spans="4:13" x14ac:dyDescent="0.3">
@@ -15344,7 +15344,7 @@
       <c r="J545" s="2"/>
       <c r="K545" s="1"/>
       <c r="M545" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="546" spans="4:13" x14ac:dyDescent="0.3">
@@ -15701,7 +15701,7 @@
       <c r="J558" s="2"/>
       <c r="K558" s="1"/>
       <c r="M558" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="559" spans="4:13" x14ac:dyDescent="0.3">
@@ -15921,10 +15921,10 @@
         <v>21</v>
       </c>
       <c r="I566" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J566" s="2">
-        <v>0</v>
+        <v>6.9907407407407409E-3</v>
       </c>
       <c r="K566" s="1">
         <v>46210.793749999997</v>
@@ -16211,10 +16211,10 @@
         <v>21</v>
       </c>
       <c r="I576" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J576" s="2">
-        <v>0</v>
+        <v>2.3148148148148147E-5</v>
       </c>
       <c r="K576" s="1">
         <v>46210.8</v>
@@ -16227,32 +16227,12 @@
       </c>
     </row>
     <row r="577" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D577" t="s">
-        <v>26</v>
-      </c>
-      <c r="E577">
-        <v>3478</v>
-      </c>
-      <c r="F577" t="s">
-        <v>64</v>
-      </c>
-      <c r="H577" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I577" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J577" s="2">
-        <v>0</v>
-      </c>
-      <c r="K577" s="1">
-        <v>46210.800694444442</v>
-      </c>
-      <c r="L577">
-        <v>0</v>
-      </c>
+      <c r="H577" s="2"/>
+      <c r="I577" s="1"/>
+      <c r="J577" s="2"/>
+      <c r="K577" s="1"/>
       <c r="M577" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="578" spans="4:13" x14ac:dyDescent="0.3">
@@ -16260,22 +16240,22 @@
         <v>26</v>
       </c>
       <c r="E578">
-        <v>3494</v>
+        <v>3478</v>
       </c>
       <c r="F578" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H578" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I578" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J578" s="2">
-        <v>2.0474537037037038E-2</v>
+        <v>0</v>
       </c>
       <c r="K578" s="1">
-        <v>46210.801388888889</v>
+        <v>46210.800694444442</v>
       </c>
       <c r="L578">
         <v>0</v>
@@ -16289,10 +16269,10 @@
         <v>26</v>
       </c>
       <c r="E579">
-        <v>3523</v>
+        <v>3494</v>
       </c>
       <c r="F579" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H579" s="2" t="s">
         <v>21</v>
@@ -16301,10 +16281,10 @@
         <v>10</v>
       </c>
       <c r="J579" s="2">
-        <v>8.5532407407407415E-3</v>
+        <v>2.0474537037037038E-2</v>
       </c>
       <c r="K579" s="1">
-        <v>46210.802083333336</v>
+        <v>46210.801388888889</v>
       </c>
       <c r="L579">
         <v>0</v>
@@ -16318,10 +16298,10 @@
         <v>26</v>
       </c>
       <c r="E580">
-        <v>5886</v>
+        <v>3523</v>
       </c>
       <c r="F580" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="H580" s="2" t="s">
         <v>21</v>
@@ -16330,10 +16310,10 @@
         <v>10</v>
       </c>
       <c r="J580" s="2">
-        <v>6.1111111111111114E-3</v>
+        <v>8.5532407407407415E-3</v>
       </c>
       <c r="K580" s="1">
-        <v>46210.802777777775</v>
+        <v>46210.802083333336</v>
       </c>
       <c r="L580">
         <v>0</v>
@@ -16347,19 +16327,19 @@
         <v>26</v>
       </c>
       <c r="E581">
-        <v>3504</v>
+        <v>5886</v>
       </c>
       <c r="F581" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="H581" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I581" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J581" s="2">
-        <v>4.6296296296296294E-5</v>
+        <v>6.1111111111111114E-3</v>
       </c>
       <c r="K581" s="1">
         <v>46210.802777777775</v>
@@ -16372,41 +16352,41 @@
       </c>
     </row>
     <row r="582" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H582" s="2"/>
-      <c r="I582" s="1"/>
-      <c r="J582" s="2"/>
-      <c r="K582" s="1"/>
+      <c r="D582" t="s">
+        <v>26</v>
+      </c>
+      <c r="E582">
+        <v>3504</v>
+      </c>
+      <c r="F582" t="s">
+        <v>68</v>
+      </c>
+      <c r="H582" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I582" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J582" s="2">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="K582" s="1">
+        <v>46210.802777777775</v>
+      </c>
+      <c r="L582">
+        <v>0</v>
+      </c>
       <c r="M582" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="583" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D583" t="s">
-        <v>26</v>
-      </c>
-      <c r="E583">
-        <v>3498</v>
-      </c>
-      <c r="F583" t="s">
-        <v>69</v>
-      </c>
-      <c r="H583" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I583" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J583" s="2">
-        <v>7.3842592592592597E-3</v>
-      </c>
-      <c r="K583" s="1">
-        <v>46210.803472222222</v>
-      </c>
-      <c r="L583">
-        <v>0</v>
-      </c>
+      <c r="H583" s="2"/>
+      <c r="I583" s="1"/>
+      <c r="J583" s="2"/>
+      <c r="K583" s="1"/>
       <c r="M583" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="584" spans="4:13" x14ac:dyDescent="0.3">
@@ -16414,22 +16394,22 @@
         <v>26</v>
       </c>
       <c r="E584">
-        <v>3344</v>
+        <v>3498</v>
       </c>
       <c r="F584" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H584" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I584" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J584" s="2">
-        <v>0</v>
+        <v>7.3842592592592597E-3</v>
       </c>
       <c r="K584" s="1">
-        <v>46210.804166666669</v>
+        <v>46210.803472222222</v>
       </c>
       <c r="L584">
         <v>0</v>
@@ -16443,10 +16423,10 @@
         <v>26</v>
       </c>
       <c r="E585">
-        <v>3515</v>
+        <v>3344</v>
       </c>
       <c r="F585" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H585" s="2" t="s">
         <v>21</v>
@@ -16458,7 +16438,7 @@
         <v>0</v>
       </c>
       <c r="K585" s="1">
-        <v>46210.804861111108</v>
+        <v>46210.804166666669</v>
       </c>
       <c r="L585">
         <v>0</v>
@@ -16472,10 +16452,10 @@
         <v>26</v>
       </c>
       <c r="E586">
-        <v>3522</v>
+        <v>3515</v>
       </c>
       <c r="F586" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H586" s="2" t="s">
         <v>21</v>
@@ -16487,7 +16467,7 @@
         <v>0</v>
       </c>
       <c r="K586" s="1">
-        <v>46210.805555555555</v>
+        <v>46210.804861111108</v>
       </c>
       <c r="L586">
         <v>0</v>
@@ -16501,10 +16481,10 @@
         <v>26</v>
       </c>
       <c r="E587">
-        <v>3751</v>
+        <v>3522</v>
       </c>
       <c r="F587" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H587" s="2" t="s">
         <v>21</v>
@@ -16530,10 +16510,10 @@
         <v>26</v>
       </c>
       <c r="E588">
-        <v>5890</v>
+        <v>3751</v>
       </c>
       <c r="F588" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="H588" s="2" t="s">
         <v>21</v>
@@ -16545,7 +16525,7 @@
         <v>0</v>
       </c>
       <c r="K588" s="1">
-        <v>46210.806250000001</v>
+        <v>46210.805555555555</v>
       </c>
       <c r="L588">
         <v>0</v>
@@ -16559,10 +16539,10 @@
         <v>26</v>
       </c>
       <c r="E589">
-        <v>5891</v>
+        <v>5890</v>
       </c>
       <c r="F589" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H589" s="2" t="s">
         <v>21</v>
@@ -16574,7 +16554,7 @@
         <v>0</v>
       </c>
       <c r="K589" s="1">
-        <v>46210.806944444441</v>
+        <v>46210.806250000001</v>
       </c>
       <c r="L589">
         <v>0</v>
@@ -16588,10 +16568,10 @@
         <v>26</v>
       </c>
       <c r="E590">
-        <v>3503</v>
+        <v>5891</v>
       </c>
       <c r="F590" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="H590" s="2" t="s">
         <v>21</v>
@@ -16603,7 +16583,7 @@
         <v>0</v>
       </c>
       <c r="K590" s="1">
-        <v>46210.807638888888</v>
+        <v>46210.806944444441</v>
       </c>
       <c r="L590">
         <v>0</v>
@@ -16617,10 +16597,10 @@
         <v>26</v>
       </c>
       <c r="E591">
-        <v>3652</v>
+        <v>3503</v>
       </c>
       <c r="F591" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H591" s="2" t="s">
         <v>21</v>
@@ -16632,7 +16612,7 @@
         <v>0</v>
       </c>
       <c r="K591" s="1">
-        <v>46210.808333333334</v>
+        <v>46210.807638888888</v>
       </c>
       <c r="L591">
         <v>0</v>
@@ -16646,10 +16626,10 @@
         <v>26</v>
       </c>
       <c r="E592">
-        <v>3509</v>
+        <v>3652</v>
       </c>
       <c r="F592" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H592" s="2" t="s">
         <v>21</v>
@@ -16661,7 +16641,7 @@
         <v>0</v>
       </c>
       <c r="K592" s="1">
-        <v>46210.809027777781</v>
+        <v>46210.808333333334</v>
       </c>
       <c r="L592">
         <v>0</v>
@@ -16675,16 +16655,16 @@
         <v>26</v>
       </c>
       <c r="E593">
-        <v>5617</v>
+        <v>3509</v>
       </c>
       <c r="F593" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="H593" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I593" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J593" s="2">
         <v>0</v>
@@ -16700,41 +16680,41 @@
       </c>
     </row>
     <row r="594" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H594" s="2"/>
-      <c r="I594" s="1"/>
-      <c r="J594" s="2"/>
-      <c r="K594" s="1"/>
+      <c r="D594" t="s">
+        <v>26</v>
+      </c>
+      <c r="E594">
+        <v>5617</v>
+      </c>
+      <c r="F594" t="s">
+        <v>92</v>
+      </c>
+      <c r="H594" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I594" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J594" s="2">
+        <v>0</v>
+      </c>
+      <c r="K594" s="1">
+        <v>46210.809027777781</v>
+      </c>
+      <c r="L594">
+        <v>0</v>
+      </c>
       <c r="M594" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="595" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D595" t="s">
-        <v>26</v>
-      </c>
-      <c r="E595">
-        <v>5465</v>
-      </c>
-      <c r="F595" t="s">
-        <v>89</v>
-      </c>
-      <c r="H595" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I595" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J595" s="2">
-        <v>7.905092592592592E-3</v>
-      </c>
-      <c r="K595" s="1">
-        <v>46210.80972222222</v>
-      </c>
-      <c r="L595">
-        <v>0</v>
-      </c>
+      <c r="H595" s="2"/>
+      <c r="I595" s="1"/>
+      <c r="J595" s="2"/>
+      <c r="K595" s="1"/>
       <c r="M595" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="596" spans="4:13" x14ac:dyDescent="0.3">
@@ -16742,22 +16722,22 @@
         <v>26</v>
       </c>
       <c r="E596">
-        <v>3512</v>
+        <v>5465</v>
       </c>
       <c r="F596" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H596" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I596" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J596" s="2">
-        <v>1.1331018518518518E-2</v>
+        <v>7.905092592592592E-3</v>
       </c>
       <c r="K596" s="1">
-        <v>46210.810416666667</v>
+        <v>46210.80972222222</v>
       </c>
       <c r="L596">
         <v>0</v>
@@ -16767,12 +16747,32 @@
       </c>
     </row>
     <row r="597" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H597" s="2"/>
-      <c r="I597" s="1"/>
-      <c r="J597" s="2"/>
-      <c r="K597" s="1"/>
+      <c r="D597" t="s">
+        <v>26</v>
+      </c>
+      <c r="E597">
+        <v>3512</v>
+      </c>
+      <c r="F597" t="s">
+        <v>79</v>
+      </c>
+      <c r="H597" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I597" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J597" s="2">
+        <v>1.9953703703703703E-2</v>
+      </c>
+      <c r="K597" s="1">
+        <v>46210.810416666667</v>
+      </c>
+      <c r="L597">
+        <v>0</v>
+      </c>
       <c r="M597" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="598" spans="4:13" x14ac:dyDescent="0.3">
@@ -17100,7 +17100,7 @@
       <c r="J609" s="2"/>
       <c r="K609" s="1"/>
       <c r="M609" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="610" spans="8:13" x14ac:dyDescent="0.3">
@@ -17627,6 +17627,7 @@
     <row r="697" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H697" s="2"/>
       <c r="I697" s="1"/>
+      <c r="J697" s="2"/>
       <c r="K697" s="1"/>
     </row>
     <row r="698" spans="8:11" x14ac:dyDescent="0.3">
@@ -17936,6 +17937,7 @@
     <row r="749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H749" s="2"/>
       <c r="I749" s="1"/>
+      <c r="J749" s="2"/>
       <c r="K749" s="1"/>
     </row>
     <row r="750" spans="8:11" x14ac:dyDescent="0.3">
@@ -18025,6 +18027,7 @@
     <row r="764" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H764" s="2"/>
       <c r="I764" s="1"/>
+      <c r="J764" s="2"/>
       <c r="K764" s="1"/>
     </row>
     <row r="765" spans="8:11" x14ac:dyDescent="0.3">
@@ -18131,6 +18134,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -18148,6 +18152,7 @@
     <row r="785" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H785" s="2"/>
       <c r="I785" s="1"/>
+      <c r="J785" s="2"/>
       <c r="K785" s="1"/>
     </row>
     <row r="786" spans="8:11" x14ac:dyDescent="0.3">
@@ -18159,6 +18164,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -18200,6 +18206,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -18223,6 +18230,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -18246,6 +18254,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -18263,6 +18272,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -18274,11 +18284,13 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -18398,6 +18410,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -18481,6 +18494,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -18504,6 +18518,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -18515,6 +18530,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -18526,6 +18542,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -18573,6 +18590,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -18626,6 +18644,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -18798,6 +18817,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -18809,6 +18829,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -18886,6 +18907,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -18903,6 +18925,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -18950,6 +18973,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -19062,6 +19086,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -19121,6 +19146,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -19132,6 +19158,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -19203,6 +19230,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -19255,6 +19283,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -19331,11 +19360,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -19395,6 +19426,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -19406,6 +19438,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -19417,11 +19450,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -19475,6 +19510,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -19491,6 +19527,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -19514,6 +19551,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -19531,6 +19569,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -19577,11 +19616,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -19623,11 +19664,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -19645,6 +19688,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -19656,6 +19700,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -19667,6 +19712,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -19684,6 +19730,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -19761,6 +19808,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -19790,6 +19838,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -19801,16 +19850,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -19822,16 +19874,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -19843,11 +19898,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -19871,6 +19928,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -19912,6 +19970,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -19941,21 +20000,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -19967,6 +20030,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -19984,6 +20048,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -20023,11 +20088,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -20075,6 +20142,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -20104,6 +20172,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -20180,6 +20249,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -20226,6 +20296,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -20261,11 +20332,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -20282,6 +20355,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -20292,6 +20366,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -20327,6 +20402,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -20338,6 +20414,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -20349,6 +20426,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -20360,6 +20438,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -20371,6 +20450,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -20412,6 +20492,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -20429,6 +20510,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -20446,6 +20528,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -20487,6 +20570,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -20510,6 +20594,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -20556,6 +20641,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -20591,6 +20677,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -20614,6 +20701,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -20654,6 +20742,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -20671,11 +20760,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -20734,6 +20825,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -20750,6 +20842,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -20761,6 +20854,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -20772,11 +20866,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -20812,6 +20908,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -20864,6 +20961,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -20874,6 +20972,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -20889,6 +20988,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -20912,16 +21012,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -20992,6 +21095,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -21003,6 +21107,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -21103,6 +21208,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -21159,6 +21266,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -21182,6 +21290,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -21306,6 +21415,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -21464,6 +21574,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -21481,6 +21592,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -21521,6 +21633,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -21853,6 +21966,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -21941,6 +22055,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -22034,6 +22149,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -22093,11 +22209,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -22149,6 +22267,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -22190,6 +22309,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -22234,6 +22354,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -22280,11 +22401,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -22482,6 +22605,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -22511,6 +22635,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -22526,6 +22652,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -22585,6 +22712,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -22656,6 +22784,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -22697,6 +22826,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -22815,6 +22945,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -22879,6 +23010,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -23003,6 +23135,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -23229,6 +23362,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -23346,6 +23480,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -23429,6 +23564,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -23488,6 +23624,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -23511,6 +23648,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -23558,6 +23696,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -23617,6 +23756,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -23640,6 +23780,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -23657,6 +23798,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -23740,6 +23882,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -23931,6 +24074,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -51787,6 +51931,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -51794,6 +51939,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -51801,6 +51947,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -51816,6 +51963,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -51825,6 +51973,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -51832,9 +51981,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -51842,12 +51997,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -51855,12 +52013,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -51872,9 +52033,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -51889,6 +52052,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -51915,6 +52079,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -51925,7 +52090,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -51933,6 +52103,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -51944,6 +52115,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -51951,6 +52123,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -51965,13 +52138,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -51982,15 +52161,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -52006,6 +52188,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -52024,6 +52207,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -52035,6 +52219,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -52052,18 +52237,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -52092,6 +52282,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -52099,9 +52290,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -52124,12 +52317,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -52144,9 +52340,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -52162,12 +52360,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -52188,6 +52388,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -52199,9 +52400,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -52213,6 +52416,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -52252,9 +52456,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -52262,9 +52468,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -52275,6 +52483,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -52282,18 +52491,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -52301,6 +52518,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -52311,6 +52529,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -52337,15 +52556,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -52367,6 +52590,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -52374,9 +52598,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -52384,6 +52610,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -52395,6 +52622,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -52409,6 +52637,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -52418,6 +52650,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -52429,6 +52662,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -52439,10 +52673,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -52450,6 +52689,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -52464,6 +52704,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -52486,6 +52727,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -52505,25 +52747,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -52531,6 +52785,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -52538,15 +52793,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -52560,6 +52822,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -52578,9 +52841,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -52588,9 +52853,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -52598,6 +52865,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -52614,10 +52882,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Fiore-and-Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87F57C5B-80CD-4787-BD6A-90058665AA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{505D2B98-27E4-485E-86EC-884F0D25038A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3145" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3142" uniqueCount="108">
   <si>
     <t>Company Name</t>
   </si>
@@ -736,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -812,7 +812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
       <c r="I3" s="1"/>
       <c r="J3" s="2"/>
@@ -923,7 +923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>27</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>27</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>27</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>27</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>27</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>27</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>27</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>27</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>27</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>27</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>27</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>27</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>27</v>
       </c>
@@ -5597,7 +5597,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>27</v>
       </c>
@@ -6077,7 +6077,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>27</v>
       </c>
@@ -6921,7 +6921,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>27</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>27</v>
       </c>
@@ -9629,7 +9629,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>27</v>
       </c>
@@ -9687,7 +9687,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>27</v>
       </c>
@@ -10130,7 +10130,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>27</v>
       </c>
@@ -10188,7 +10188,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>27</v>
       </c>
@@ -10631,7 +10631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>27</v>
       </c>
@@ -10900,7 +10900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>27</v>
       </c>
@@ -17056,16 +17056,16 @@
         <v>24</v>
       </c>
       <c r="G609" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H609" s="2">
-        <v>0</v>
+        <v>6.030092592592593E-3</v>
       </c>
       <c r="I609" s="1">
         <v>46237.754629629628</v>
       </c>
       <c r="J609" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K609" s="1" t="s">
         <v>11</v>
@@ -17123,7 +17123,7 @@
         <v>46237.756018518521</v>
       </c>
       <c r="J611" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K611" s="1" t="s">
         <v>11</v>
@@ -17152,7 +17152,7 @@
         <v>46237.756712962961</v>
       </c>
       <c r="J612" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K612" s="1" t="s">
         <v>11</v>
@@ -17210,7 +17210,7 @@
         <v>46237.757407407407</v>
       </c>
       <c r="J614" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K614" s="1" t="s">
         <v>11</v>
@@ -17259,16 +17259,16 @@
         <v>24</v>
       </c>
       <c r="G616" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H616" s="2">
-        <v>0</v>
+        <v>7.8819444444444449E-3</v>
       </c>
       <c r="I616" s="1">
         <v>46237.758101851854</v>
       </c>
       <c r="J616" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K616" s="1" t="s">
         <v>11</v>
@@ -17297,7 +17297,7 @@
         <v>46237.758796296293</v>
       </c>
       <c r="J617" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K617" s="1" t="s">
         <v>11</v>
@@ -17363,7 +17363,7 @@
         <v>46237.75949074074</v>
       </c>
       <c r="J620" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K620" s="1" t="s">
         <v>11</v>
@@ -17392,7 +17392,7 @@
         <v>46237.760185185187</v>
       </c>
       <c r="J621" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K621" s="1" t="s">
         <v>11</v>
@@ -17421,7 +17421,7 @@
         <v>46237.760879629626</v>
       </c>
       <c r="J622" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K622" s="1" t="s">
         <v>11</v>
@@ -17508,7 +17508,7 @@
         <v>46237.76226851852</v>
       </c>
       <c r="J625" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K625" s="1" t="s">
         <v>11</v>
@@ -17537,7 +17537,7 @@
         <v>46237.762962962966</v>
       </c>
       <c r="J626" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K626" s="1" t="s">
         <v>11</v>
@@ -17557,16 +17557,16 @@
         <v>24</v>
       </c>
       <c r="G627" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H627" s="2">
-        <v>0</v>
+        <v>7.4537037037037037E-3</v>
       </c>
       <c r="I627" s="1">
         <v>46237.762962962966</v>
       </c>
       <c r="J627" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K627" s="1" t="s">
         <v>11</v>
@@ -17586,10 +17586,10 @@
         <v>24</v>
       </c>
       <c r="G628" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H628" s="2">
-        <v>0</v>
+        <v>5.9722222222222225E-3</v>
       </c>
       <c r="I628" s="1">
         <v>46237.763657407406</v>
@@ -17615,16 +17615,16 @@
         <v>24</v>
       </c>
       <c r="G629" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H629" s="2">
-        <v>0</v>
+        <v>5.9837962962962961E-3</v>
       </c>
       <c r="I629" s="1">
         <v>46237.764351851853</v>
       </c>
       <c r="J629" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K629" s="1" t="s">
         <v>11</v>
@@ -17644,16 +17644,16 @@
         <v>24</v>
       </c>
       <c r="G630" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H630" s="2">
-        <v>0</v>
+        <v>8.8541666666666664E-3</v>
       </c>
       <c r="I630" s="1">
         <v>46237.765046296299</v>
       </c>
       <c r="J630" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K630" s="1" t="s">
         <v>11</v>
@@ -17682,7 +17682,7 @@
         <v>46237.765046296299</v>
       </c>
       <c r="J631" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K631" s="1" t="s">
         <v>11</v>
@@ -17719,7 +17719,7 @@
         <v>46237.765740740739</v>
       </c>
       <c r="J633" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K633" s="1" t="s">
         <v>11</v>
@@ -17777,7 +17777,7 @@
         <v>46237.766435185185</v>
       </c>
       <c r="J635" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K635" s="1" t="s">
         <v>11</v>
@@ -17797,16 +17797,16 @@
         <v>24</v>
       </c>
       <c r="G636" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H636" s="2">
-        <v>0</v>
+        <v>6.851851851851852E-3</v>
       </c>
       <c r="I636" s="1">
         <v>46237.767129629632</v>
       </c>
       <c r="J636" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K636" s="1" t="s">
         <v>11</v>
@@ -17826,16 +17826,16 @@
         <v>24</v>
       </c>
       <c r="G637" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H637" s="2">
-        <v>0</v>
+        <v>6.0185185185185185E-3</v>
       </c>
       <c r="I637" s="1">
         <v>46237.767824074072</v>
       </c>
       <c r="J637" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K637" s="1" t="s">
         <v>11</v>
@@ -17864,7 +17864,7 @@
         <v>46237.768518518518</v>
       </c>
       <c r="J638" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K638" s="1" t="s">
         <v>11</v>
@@ -17913,16 +17913,16 @@
         <v>24</v>
       </c>
       <c r="G640" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H640" s="2">
-        <v>0</v>
+        <v>7.4884259259259262E-3</v>
       </c>
       <c r="I640" s="1">
         <v>46237.769212962965</v>
       </c>
       <c r="J640" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K640" s="1" t="s">
         <v>11</v>
@@ -17951,7 +17951,7 @@
         <v>46237.769907407404</v>
       </c>
       <c r="J641" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K641" s="1" t="s">
         <v>11</v>
@@ -17980,7 +17980,7 @@
         <v>46237.770601851851</v>
       </c>
       <c r="J642" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K642" s="1" t="s">
         <v>11</v>
@@ -18154,7 +18154,7 @@
         <v>46237.773379629631</v>
       </c>
       <c r="J648" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K648" s="1" t="s">
         <v>11</v>
@@ -18174,10 +18174,10 @@
         <v>24</v>
       </c>
       <c r="G649" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H649" s="2">
-        <v>0</v>
+        <v>5.7523148148148151E-3</v>
       </c>
       <c r="I649" s="1">
         <v>46237.773379629631</v>
@@ -18212,7 +18212,7 @@
         <v>46237.774074074077</v>
       </c>
       <c r="J650" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K650" s="1" t="s">
         <v>11</v>
@@ -18232,48 +18232,27 @@
         <v>24</v>
       </c>
       <c r="G651" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H651" s="2">
-        <v>0</v>
+        <v>8.1018518518518516E-5</v>
       </c>
       <c r="I651" s="1">
         <v>46237.774768518517</v>
       </c>
       <c r="J651" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K651" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="652" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B652" t="s">
-        <v>27</v>
-      </c>
-      <c r="C652">
-        <v>3478</v>
-      </c>
-      <c r="D652" t="s">
-        <v>65</v>
-      </c>
-      <c r="F652" t="s">
-        <v>24</v>
-      </c>
-      <c r="G652" t="s">
-        <v>13</v>
-      </c>
-      <c r="H652" s="2">
-        <v>0</v>
-      </c>
-      <c r="I652" s="1">
-        <v>46237.775462962964</v>
-      </c>
-      <c r="J652" s="2">
-        <v>0</v>
-      </c>
+      <c r="H652" s="2"/>
+      <c r="I652" s="1"/>
+      <c r="J652" s="2"/>
       <c r="K652" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="653" spans="2:11" x14ac:dyDescent="0.25">
@@ -18281,25 +18260,25 @@
         <v>27</v>
       </c>
       <c r="C653">
-        <v>3494</v>
+        <v>3478</v>
       </c>
       <c r="D653" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F653" t="s">
         <v>24</v>
       </c>
       <c r="G653" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H653" s="2">
-        <v>6.076388888888889E-3</v>
+        <v>0</v>
       </c>
       <c r="I653" s="1">
         <v>46237.775462962964</v>
       </c>
       <c r="J653" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K653" s="1" t="s">
         <v>11</v>
@@ -18310,22 +18289,22 @@
         <v>27</v>
       </c>
       <c r="C654">
-        <v>3523</v>
+        <v>3494</v>
       </c>
       <c r="D654" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F654" t="s">
         <v>24</v>
       </c>
       <c r="G654" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H654" s="2">
-        <v>0</v>
+        <v>6.076388888888889E-3</v>
       </c>
       <c r="I654" s="1">
-        <v>46237.77615740741</v>
+        <v>46237.775462962964</v>
       </c>
       <c r="J654" s="2">
         <v>0</v>
@@ -18339,10 +18318,10 @@
         <v>27</v>
       </c>
       <c r="C655">
-        <v>5886</v>
+        <v>3523</v>
       </c>
       <c r="D655" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="F655" t="s">
         <v>24</v>
@@ -18351,13 +18330,13 @@
         <v>10</v>
       </c>
       <c r="H655" s="2">
-        <v>8.4490740740740741E-3</v>
+        <v>6.5856481481481478E-3</v>
       </c>
       <c r="I655" s="1">
-        <v>46237.751967592594</v>
+        <v>46237.77615740741</v>
       </c>
       <c r="J655" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K655" s="1" t="s">
         <v>11</v>
@@ -18368,19 +18347,19 @@
         <v>27</v>
       </c>
       <c r="C656">
-        <v>3504</v>
+        <v>5886</v>
       </c>
       <c r="D656" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="F656" t="s">
         <v>24</v>
       </c>
       <c r="G656" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H656" s="2">
-        <v>0</v>
+        <v>8.4490740740740741E-3</v>
       </c>
       <c r="I656" s="1">
         <v>46237.751967592594</v>
@@ -18397,25 +18376,25 @@
         <v>27</v>
       </c>
       <c r="C657">
-        <v>3498</v>
+        <v>3504</v>
       </c>
       <c r="D657" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F657" t="s">
         <v>24</v>
       </c>
       <c r="G657" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H657" s="2">
-        <v>6.9560185185185185E-3</v>
+        <v>0</v>
       </c>
       <c r="I657" s="1">
-        <v>46237.752662037034</v>
+        <v>46237.751967592594</v>
       </c>
       <c r="J657" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K657" s="1" t="s">
         <v>11</v>
@@ -18426,22 +18405,22 @@
         <v>27</v>
       </c>
       <c r="C658">
-        <v>3344</v>
+        <v>3498</v>
       </c>
       <c r="D658" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F658" t="s">
         <v>24</v>
       </c>
       <c r="G658" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H658" s="2">
-        <v>0</v>
+        <v>6.9560185185185185E-3</v>
       </c>
       <c r="I658" s="1">
-        <v>46237.75335648148</v>
+        <v>46237.752662037034</v>
       </c>
       <c r="J658" s="2">
         <v>0</v>
@@ -18455,25 +18434,25 @@
         <v>27</v>
       </c>
       <c r="C659">
-        <v>3515</v>
+        <v>3344</v>
       </c>
       <c r="D659" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F659" t="s">
         <v>24</v>
       </c>
       <c r="G659" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H659" s="2">
-        <v>0</v>
+        <v>8.9351851851851849E-3</v>
       </c>
       <c r="I659" s="1">
         <v>46237.75335648148</v>
       </c>
       <c r="J659" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K659" s="1" t="s">
         <v>11</v>
@@ -18484,25 +18463,25 @@
         <v>27</v>
       </c>
       <c r="C660">
-        <v>3522</v>
+        <v>3515</v>
       </c>
       <c r="D660" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F660" t="s">
         <v>24</v>
       </c>
       <c r="G660" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H660" s="2">
-        <v>0</v>
+        <v>7.6041666666666671E-3</v>
       </c>
       <c r="I660" s="1">
-        <v>46237.754050925927</v>
+        <v>46237.75335648148</v>
       </c>
       <c r="J660" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K660" s="1" t="s">
         <v>11</v>
@@ -18513,10 +18492,10 @@
         <v>27</v>
       </c>
       <c r="C661">
-        <v>3751</v>
+        <v>3522</v>
       </c>
       <c r="D661" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F661" t="s">
         <v>24</v>
@@ -18528,10 +18507,10 @@
         <v>0</v>
       </c>
       <c r="I661" s="1">
-        <v>46237.754745370374</v>
+        <v>46237.754050925927</v>
       </c>
       <c r="J661" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K661" s="1" t="s">
         <v>11</v>
@@ -18542,10 +18521,10 @@
         <v>27</v>
       </c>
       <c r="C662">
-        <v>5890</v>
+        <v>3751</v>
       </c>
       <c r="D662" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="F662" t="s">
         <v>24</v>
@@ -18557,10 +18536,10 @@
         <v>0</v>
       </c>
       <c r="I662" s="1">
-        <v>46237.755439814813</v>
+        <v>46237.754745370374</v>
       </c>
       <c r="J662" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K662" s="1" t="s">
         <v>11</v>
@@ -18571,25 +18550,25 @@
         <v>27</v>
       </c>
       <c r="C663">
-        <v>5891</v>
+        <v>5890</v>
       </c>
       <c r="D663" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F663" t="s">
         <v>24</v>
       </c>
       <c r="G663" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H663" s="2">
-        <v>0</v>
+        <v>6.099537037037037E-3</v>
       </c>
       <c r="I663" s="1">
         <v>46237.755439814813</v>
       </c>
       <c r="J663" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K663" s="1" t="s">
         <v>11</v>
@@ -18600,10 +18579,10 @@
         <v>27</v>
       </c>
       <c r="C664">
-        <v>3503</v>
+        <v>5891</v>
       </c>
       <c r="D664" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="F664" t="s">
         <v>24</v>
@@ -18615,10 +18594,10 @@
         <v>0</v>
       </c>
       <c r="I664" s="1">
-        <v>46237.75613425926</v>
+        <v>46237.755439814813</v>
       </c>
       <c r="J664" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K664" s="1" t="s">
         <v>11</v>
@@ -18629,36 +18608,57 @@
         <v>27</v>
       </c>
       <c r="C665">
-        <v>3652</v>
+        <v>3503</v>
       </c>
       <c r="D665" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F665" t="s">
         <v>24</v>
       </c>
       <c r="G665" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H665" s="2">
         <v>0</v>
       </c>
       <c r="I665" s="1">
+        <v>46237.75613425926</v>
+      </c>
+      <c r="J665" s="2">
+        <v>3</v>
+      </c>
+      <c r="K665" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="666" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B666" t="s">
+        <v>27</v>
+      </c>
+      <c r="C666">
+        <v>3652</v>
+      </c>
+      <c r="D666" t="s">
+        <v>78</v>
+      </c>
+      <c r="F666" t="s">
+        <v>24</v>
+      </c>
+      <c r="G666" t="s">
+        <v>10</v>
+      </c>
+      <c r="H666" s="2">
+        <v>1.068287037037037E-2</v>
+      </c>
+      <c r="I666" s="1">
         <v>46237.756828703707</v>
       </c>
-      <c r="J665" s="2">
-        <v>0</v>
-      </c>
-      <c r="K665" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="666" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H666" s="2"/>
-      <c r="I666" s="1"/>
-      <c r="J666" s="2"/>
+      <c r="J666" s="2">
+        <v>1</v>
+      </c>
       <c r="K666" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="667" spans="2:11" x14ac:dyDescent="0.25">
@@ -18684,7 +18684,7 @@
         <v>46237.756828703707</v>
       </c>
       <c r="J667" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K667" s="1" t="s">
         <v>11</v>
@@ -18704,27 +18704,48 @@
         <v>24</v>
       </c>
       <c r="G668" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H668" s="2">
-        <v>1.9456018518518518E-2</v>
+        <v>1.9791666666666666E-2</v>
       </c>
       <c r="I668" s="1">
         <v>46237.757523148146</v>
       </c>
       <c r="J668" s="2">
+        <v>2</v>
+      </c>
+      <c r="K668" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="669" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B669" t="s">
+        <v>27</v>
+      </c>
+      <c r="C669">
+        <v>3512</v>
+      </c>
+      <c r="D669" t="s">
+        <v>80</v>
+      </c>
+      <c r="F669" t="s">
+        <v>24</v>
+      </c>
+      <c r="G669" t="s">
+        <v>10</v>
+      </c>
+      <c r="H669" s="2">
+        <v>6.5393518518518517E-3</v>
+      </c>
+      <c r="I669" s="1">
+        <v>46237.758217592593</v>
+      </c>
+      <c r="J669" s="2">
         <v>0</v>
       </c>
-      <c r="K668" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="669" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H669" s="2"/>
-      <c r="I669" s="1"/>
-      <c r="J669" s="2"/>
       <c r="K669" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="670" spans="2:11" x14ac:dyDescent="0.25">
@@ -18732,10 +18753,10 @@
         <v>27</v>
       </c>
       <c r="C670">
-        <v>3512</v>
+        <v>3489</v>
       </c>
       <c r="D670" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F670" t="s">
         <v>24</v>
@@ -18747,7 +18768,7 @@
         <v>6.5393518518518517E-3</v>
       </c>
       <c r="I670" s="1">
-        <v>46237.758217592593</v>
+        <v>46237.758912037039</v>
       </c>
       <c r="J670" s="2">
         <v>0</v>
@@ -18761,10 +18782,10 @@
         <v>27</v>
       </c>
       <c r="C671">
-        <v>3489</v>
+        <v>3266</v>
       </c>
       <c r="D671" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F671" t="s">
         <v>24</v>
@@ -18773,13 +18794,13 @@
         <v>10</v>
       </c>
       <c r="H671" s="2">
-        <v>6.5393518518518517E-3</v>
+        <v>6.1921296296296299E-3</v>
       </c>
       <c r="I671" s="1">
         <v>46237.758912037039</v>
       </c>
       <c r="J671" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K671" s="1" t="s">
         <v>11</v>
@@ -18790,22 +18811,22 @@
         <v>27</v>
       </c>
       <c r="C672">
-        <v>3266</v>
+        <v>3492</v>
       </c>
       <c r="D672" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F672" t="s">
         <v>24</v>
       </c>
       <c r="G672" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H672" s="2">
-        <v>1.1574074074074073E-5</v>
+        <v>8.518518518518519E-3</v>
       </c>
       <c r="I672" s="1">
-        <v>46237.758912037039</v>
+        <v>46237.759606481479</v>
       </c>
       <c r="J672" s="2">
         <v>0</v>
@@ -18815,11 +18836,32 @@
       </c>
     </row>
     <row r="673" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H673" s="2"/>
-      <c r="I673" s="1"/>
-      <c r="J673" s="2"/>
+      <c r="B673" t="s">
+        <v>27</v>
+      </c>
+      <c r="C673">
+        <v>3493</v>
+      </c>
+      <c r="D673" t="s">
+        <v>84</v>
+      </c>
+      <c r="F673" t="s">
+        <v>24</v>
+      </c>
+      <c r="G673" t="s">
+        <v>13</v>
+      </c>
+      <c r="H673" s="2">
+        <v>0</v>
+      </c>
+      <c r="I673" s="1">
+        <v>46237.760300925926</v>
+      </c>
+      <c r="J673" s="2">
+        <v>3</v>
+      </c>
       <c r="K673" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="674" spans="2:11" x14ac:dyDescent="0.25">
@@ -18827,10 +18869,10 @@
         <v>27</v>
       </c>
       <c r="C674">
-        <v>3492</v>
+        <v>3505</v>
       </c>
       <c r="D674" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F674" t="s">
         <v>24</v>
@@ -18839,13 +18881,13 @@
         <v>10</v>
       </c>
       <c r="H674" s="2">
-        <v>8.518518518518519E-3</v>
+        <v>5.7986111111111112E-3</v>
       </c>
       <c r="I674" s="1">
-        <v>46237.759606481479</v>
+        <v>46237.760300925926</v>
       </c>
       <c r="J674" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K674" s="1" t="s">
         <v>11</v>
@@ -18856,25 +18898,25 @@
         <v>27</v>
       </c>
       <c r="C675">
-        <v>3493</v>
+        <v>6003</v>
       </c>
       <c r="D675" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="F675" t="s">
         <v>24</v>
       </c>
       <c r="G675" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H675" s="2">
-        <v>0</v>
+        <v>7.1990740740740739E-3</v>
       </c>
       <c r="I675" s="1">
-        <v>46237.760300925926</v>
+        <v>46237.760995370372</v>
       </c>
       <c r="J675" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K675" s="1" t="s">
         <v>11</v>
@@ -18885,22 +18927,22 @@
         <v>27</v>
       </c>
       <c r="C676">
-        <v>3505</v>
+        <v>3861</v>
       </c>
       <c r="D676" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F676" t="s">
         <v>24</v>
       </c>
       <c r="G676" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H676" s="2">
-        <v>0</v>
+        <v>6.3194444444444444E-3</v>
       </c>
       <c r="I676" s="1">
-        <v>46237.760300925926</v>
+        <v>46237.761689814812</v>
       </c>
       <c r="J676" s="2">
         <v>0</v>
@@ -18910,11 +18952,32 @@
       </c>
     </row>
     <row r="677" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H677" s="2"/>
-      <c r="I677" s="1"/>
-      <c r="J677" s="2"/>
+      <c r="B677" t="s">
+        <v>27</v>
+      </c>
+      <c r="C677">
+        <v>5205</v>
+      </c>
+      <c r="D677" t="s">
+        <v>88</v>
+      </c>
+      <c r="F677" t="s">
+        <v>24</v>
+      </c>
+      <c r="G677" t="s">
+        <v>13</v>
+      </c>
+      <c r="H677" s="2">
+        <v>0</v>
+      </c>
+      <c r="I677" s="1">
+        <v>46237.761689814812</v>
+      </c>
+      <c r="J677" s="2">
+        <v>3</v>
+      </c>
       <c r="K677" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="678" spans="2:11" x14ac:dyDescent="0.25">
@@ -18922,22 +18985,22 @@
         <v>27</v>
       </c>
       <c r="C678">
-        <v>6003</v>
+        <v>5782</v>
       </c>
       <c r="D678" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F678" t="s">
         <v>24</v>
       </c>
       <c r="G678" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H678" s="2">
-        <v>0</v>
+        <v>9.5138888888888894E-3</v>
       </c>
       <c r="I678" s="1">
-        <v>46237.760995370372</v>
+        <v>46237.762384259258</v>
       </c>
       <c r="J678" s="2">
         <v>0</v>
@@ -18951,10 +19014,10 @@
         <v>27</v>
       </c>
       <c r="C679">
-        <v>3861</v>
+        <v>5887</v>
       </c>
       <c r="D679" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="F679" t="s">
         <v>24</v>
@@ -18963,10 +19026,10 @@
         <v>10</v>
       </c>
       <c r="H679" s="2">
-        <v>6.3194444444444444E-3</v>
+        <v>1.7222222222222222E-2</v>
       </c>
       <c r="I679" s="1">
-        <v>46237.761689814812</v>
+        <v>46237.763078703705</v>
       </c>
       <c r="J679" s="2">
         <v>0</v>
@@ -18980,22 +19043,22 @@
         <v>27</v>
       </c>
       <c r="C680">
-        <v>5205</v>
+        <v>3538</v>
       </c>
       <c r="D680" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F680" t="s">
         <v>24</v>
       </c>
       <c r="G680" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H680" s="2">
-        <v>0</v>
+        <v>8.9120370370370378E-3</v>
       </c>
       <c r="I680" s="1">
-        <v>46237.761689814812</v>
+        <v>46237.763078703705</v>
       </c>
       <c r="J680" s="2">
         <v>0</v>
@@ -19009,10 +19072,10 @@
         <v>27</v>
       </c>
       <c r="C681">
-        <v>5782</v>
+        <v>5603</v>
       </c>
       <c r="D681" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F681" t="s">
         <v>24</v>
@@ -19021,10 +19084,10 @@
         <v>10</v>
       </c>
       <c r="H681" s="2">
-        <v>9.5138888888888894E-3</v>
+        <v>6.5162037037037037E-3</v>
       </c>
       <c r="I681" s="1">
-        <v>46237.762384259258</v>
+        <v>46237.763773148145</v>
       </c>
       <c r="J681" s="2">
         <v>0</v>
@@ -19034,91 +19097,22 @@
       </c>
     </row>
     <row r="682" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B682" t="s">
-        <v>27</v>
-      </c>
-      <c r="C682">
-        <v>5887</v>
-      </c>
-      <c r="D682" t="s">
-        <v>104</v>
-      </c>
-      <c r="F682" t="s">
-        <v>24</v>
-      </c>
-      <c r="G682" t="s">
-        <v>10</v>
-      </c>
-      <c r="H682" s="2">
-        <v>1.7222222222222222E-2</v>
-      </c>
-      <c r="I682" s="1">
-        <v>46237.763078703705</v>
-      </c>
-      <c r="J682" s="2">
-        <v>0</v>
-      </c>
-      <c r="K682" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="H682" s="2"/>
+      <c r="I682" s="1"/>
+      <c r="J682" s="2"/>
+      <c r="K682" s="1"/>
     </row>
     <row r="683" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B683" t="s">
-        <v>27</v>
-      </c>
-      <c r="C683">
-        <v>3538</v>
-      </c>
-      <c r="D683" t="s">
-        <v>87</v>
-      </c>
-      <c r="F683" t="s">
-        <v>24</v>
-      </c>
-      <c r="G683" t="s">
-        <v>10</v>
-      </c>
-      <c r="H683" s="2">
-        <v>8.9120370370370378E-3</v>
-      </c>
-      <c r="I683" s="1">
-        <v>46237.763078703705</v>
-      </c>
-      <c r="J683" s="2">
-        <v>0</v>
-      </c>
-      <c r="K683" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="H683" s="2"/>
+      <c r="I683" s="1"/>
+      <c r="J683" s="2"/>
+      <c r="K683" s="1"/>
     </row>
     <row r="684" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B684" t="s">
-        <v>27</v>
-      </c>
-      <c r="C684">
-        <v>5603</v>
-      </c>
-      <c r="D684" t="s">
-        <v>94</v>
-      </c>
-      <c r="F684" t="s">
-        <v>24</v>
-      </c>
-      <c r="G684" t="s">
-        <v>10</v>
-      </c>
-      <c r="H684" s="2">
-        <v>6.5162037037037037E-3</v>
-      </c>
-      <c r="I684" s="1">
-        <v>46237.763773148145</v>
-      </c>
-      <c r="J684" s="2">
-        <v>0</v>
-      </c>
-      <c r="K684" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="H684" s="2"/>
+      <c r="I684" s="1"/>
+      <c r="J684" s="2"/>
+      <c r="K684" s="1"/>
     </row>
     <row r="685" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H685" s="2"/>
@@ -56255,6 +56249,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -56547,6 +56542,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -56857,6 +56854,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -56981,6 +56979,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -56992,6 +56991,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -57140,6 +57140,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -57150,10 +57151,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -57187,15 +57190,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -57236,18 +57242,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -57263,6 +57273,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -57272,10 +57283,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -57311,10 +57324,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -57340,6 +57355,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -57354,6 +57370,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -57388,6 +57405,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -57397,6 +57415,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -57406,6 +57425,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -57420,15 +57440,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -57458,6 +57479,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -57478,11 +57500,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -57491,6 +57515,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -57520,6 +57545,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -57529,10 +57555,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -57547,14 +57575,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -57574,10 +57605,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -57597,9 +57630,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -57634,18 +57670,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -57660,12 +57700,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -57680,10 +57720,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -57703,6 +57745,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -57722,6 +57765,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -57731,6 +57775,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -57776,6 +57821,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -57785,6 +57831,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -57799,6 +57846,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -57808,10 +57856,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -57826,6 +57876,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -57835,6 +57886,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -57854,6 +57906,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -57873,10 +57926,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -57886,6 +57941,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -57896,10 +57952,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -57914,18 +57972,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -57945,10 +58007,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -57968,6 +58032,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -57998,7 +58063,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -58013,10 +58077,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -58031,6 +58097,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -58045,11 +58112,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -58059,6 +58126,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -58074,6 +58142,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -58088,6 +58157,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -58108,6 +58178,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -58133,11 +58204,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -58156,15 +58229,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -58174,6 +58248,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -58193,6 +58268,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -58207,6 +58283,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -58226,10 +58303,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -58239,6 +58318,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -58249,6 +58329,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -58285,7 +58366,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -58294,6 +58374,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -58307,10 +58388,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Fiore-and-Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{505D2B98-27E4-485E-86EC-884F0D25038A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FB414A3-3CFB-48DC-8D12-2255A83A3AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -736,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -812,7 +812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
       <c r="I3" s="1"/>
       <c r="J3" s="2"/>
@@ -923,7 +923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>27</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>27</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>27</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>27</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>27</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>27</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>27</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>27</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>27</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>27</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>27</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>27</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>27</v>
       </c>
@@ -5597,7 +5597,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>27</v>
       </c>
@@ -6077,7 +6077,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>27</v>
       </c>
@@ -6921,7 +6921,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>27</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>27</v>
       </c>
@@ -9629,7 +9629,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>27</v>
       </c>
@@ -9687,7 +9687,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>27</v>
       </c>
@@ -10130,7 +10130,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>27</v>
       </c>
@@ -10188,7 +10188,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>27</v>
       </c>
@@ -10631,7 +10631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>27</v>
       </c>
@@ -10900,7 +10900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>27</v>
       </c>
@@ -17114,10 +17114,10 @@
         <v>24</v>
       </c>
       <c r="G611" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H611" s="2">
-        <v>0</v>
+        <v>9.6527777777777775E-3</v>
       </c>
       <c r="I611" s="1">
         <v>46237.756018518521</v>
@@ -56249,7 +56249,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -56542,8 +56541,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -56854,7 +56851,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -56979,7 +56975,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -56991,7 +56986,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -57140,35 +57134,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -57179,44 +57167,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -57227,37 +57206,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -57268,52 +57240,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -57324,17 +57286,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -57345,32 +57304,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -57380,106 +57333,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -57489,7 +57422,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -57500,127 +57432,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -57630,62 +57536,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -57705,67 +57598,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -57775,38 +57655,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -57821,117 +57694,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -57940,99 +57790,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -58042,23 +57873,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -58067,52 +57894,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -58126,38 +57943,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -58167,7 +57977,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -58178,23 +57987,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -58204,37 +58009,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -58243,72 +58041,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -58318,76 +58102,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Fiore-and-Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FB414A3-3CFB-48DC-8D12-2255A83A3AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79FEF107-FF58-45F4-850F-E561EFE261CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -736,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7400"/>
+  <dimension ref="A1:K7401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -56249,6 +56249,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -56541,6 +56542,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -56851,6 +56854,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -56975,6 +56979,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -56986,6 +56991,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -57134,29 +57140,35 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -57167,35 +57179,44 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -57206,30 +57227,37 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -57240,42 +57268,52 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -57286,14 +57324,17 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -57304,26 +57345,32 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -57333,86 +57380,107 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -57422,6 +57490,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -57432,101 +57501,127 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -57536,49 +57631,62 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -57593,59 +57701,73 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -57655,31 +57777,38 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -57689,99 +57818,123 @@
       <c r="K7287" s="1"/>
     </row>
     <row r="7288" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7288" s="2"/>
       <c r="I7288" s="1"/>
       <c r="J7288" s="2"/>
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -57790,80 +57943,99 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -57873,67 +58045,83 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -57943,31 +58131,38 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -57977,6 +58172,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -57987,19 +58183,23 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -58009,90 +58209,112 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -58102,51 +58324,71 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7394" s="2"/>
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7398" s="2"/>
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
